--- a/ACG_UNIFENAS_Medicina.xlsx
+++ b/ACG_UNIFENAS_Medicina.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo" sheetId="1" r:id="R468e890910824663"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regras UNIFENAS" sheetId="2" r:id="Ra7d04fb282a24b17"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Certificados" sheetId="3" r:id="R219b2c340da94971"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Excluídos" sheetId="4" r:id="R825f1c0c07834f4e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pendências" sheetId="5" r:id="R02d4692ebe774030"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo" sheetId="1" r:id="Rbcb49d509f77490b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regras UNIFENAS" sheetId="2" r:id="R27aab66ab4c64650"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Certificados" sheetId="3" r:id="Rcf6dbe21f640464a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Excluídos" sheetId="4" r:id="R17671312f80c41f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pendências" sheetId="5" r:id="R4a2acac1b43f46e1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -466,7 +466,7 @@
       </x:c>
       <x:c r="B6" s="16" t="n">
         <x:f>SUM('Certificados'!$J$2:$J$389)</x:f>
-        <x:v>1087.5</x:v>
+        <x:v>2084.5</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -475,7 +475,7 @@
       </x:c>
       <x:c r="B7" s="16" t="n">
         <x:f>SUM('Certificados'!$K$2:$K$389)</x:f>
-        <x:v>1087.5</x:v>
+        <x:v>2084.5</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -484,7 +484,7 @@
       </x:c>
       <x:c r="B8" s="16" t="n">
         <x:f>B3-B7</x:f>
-        <x:v>-637.5</x:v>
+        <x:v>-1634.5</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -519,11 +519,11 @@
       </x:c>
       <x:c r="C12" s="30" t="n">
         <x:f>SUMIF('Certificados'!$G$2:$G$389,A12,'Certificados'!$J$2:$J$389)</x:f>
-        <x:v>413.25</x:v>
+        <x:v>1410.25</x:v>
       </x:c>
       <x:c r="D12" s="30" t="n">
         <x:f>SUMIF('Certificados'!$G$2:$G$389,A12,'Certificados'!$K$2:$K$389)</x:f>
-        <x:v>413.25</x:v>
+        <x:v>1410.25</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -2012,10 +2012,10 @@
         <x:v>BSI-Coursera ISO 42001 Readiness Specialization Certificate K99N55L2EZNG.pdf</x:v>
       </x:c>
       <x:c r="C26" s="32" t="str">
-        <x:v>BSI</x:v>
+        <x:v>British Standards Institution (BSI)</x:v>
       </x:c>
       <x:c r="D26" s="32" t="str">
-        <x:v>BSI-Coursera ISO 42001 Readiness Specialization Certificate K99N55L2EZNG</x:v>
+        <x:v>AI Governance &amp; ISO 42001 Readiness for GRC, Audit, &amp; Legal</x:v>
       </x:c>
       <x:c r="E26" s="32" t="str">
         <x:v>5 C o u r s e s I S O / I E C 2 2 9 8 9 : 2 0 2 3 A n I n t r o d u c t i o n t o t h e F u n d a m e n t a l s o f A I A I S y s t e m I m p a c t A s s e s s m e n t G u i d a n c e A I M a n a g e m e n t E s s e n t i a l s : I n t e g r a t i n g I S O 4 2 0 0 1 &amp; I S O 2 3 8 9 4 U n d e r s t a n d i n g t h e F o u n d a t i o n s o f t h e E U A I A c t A p p r o a c h e s t o E s t a b l i s h T r u s t i n A I S y s t e m s H e c t o r N e m o t o , B S I G l o b a l T r a i n i n g D </x:v>
@@ -2030,11 +2030,17 @@
       <x:c r="I26" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J26" s="33"/>
-      <x:c r="K26" s="33"/>
-      <x:c r="L26" s="33"/>
+      <x:c r="J26" s="33" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="K26" s="33" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="L26" s="33" t="n">
+        <x:v>40</x:v>
+      </x:c>
       <x:c r="M26" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/specialization/K99N55L2EZNG; estimativa derivada do tempo exibido: 1 meses com 10 por semana para concluir</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -2045,10 +2051,10 @@
         <x:v>BSI-Coursera_AIMS Essentials Certificate_7M8MXVWELB5L.pdf</x:v>
       </x:c>
       <x:c r="C27" s="32" t="str">
-        <x:v>BSI</x:v>
+        <x:v>British Standards Institution (BSI)</x:v>
       </x:c>
       <x:c r="D27" s="32" t="str">
-        <x:v>BSI-Coursera_AIMS Essentials Certificate_7M8MXVWELB5L</x:v>
+        <x:v>AI Management Essentials: Integrating ISO 42001 &amp; ISO 23894</x:v>
       </x:c>
       <x:c r="E27" s="32" t="str">
         <x:v>A u g 1 5 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o A I M a n a g e m e n t E s s e n t i a l s : I n t e g r a t i n g I S O 4 2 0 0 1 &amp; I S O 2 3 8 9 4 a n o n l i n e c o u r s e a u t h o r i z e d b y B r i t i s h S t a n d a r d s I n s t i t u t i o n a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d H e c t o r N e m o t o B S I G l o b a l T r a i n i n g D i r e c t o r V e r i f y a t : h t t p s : / / c o u r s e r a . o r g </x:v>
@@ -2063,11 +2069,17 @@
       <x:c r="I27" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J27" s="33"/>
-      <x:c r="K27" s="33"/>
-      <x:c r="L27" s="33"/>
+      <x:c r="J27" s="33" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="K27" s="33" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="L27" s="33" t="n">
+        <x:v>5</x:v>
+      </x:c>
       <x:c r="M27" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/7M8MXVWELB5L</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -2078,10 +2090,10 @@
         <x:v>BSI-Coursera_AISIA_Certificate JMK7JAW5O7R9.pdf</x:v>
       </x:c>
       <x:c r="C28" s="32" t="str">
-        <x:v>BSI</x:v>
+        <x:v>British Standards Institution (BSI)</x:v>
       </x:c>
       <x:c r="D28" s="32" t="str">
-        <x:v>BSI-Coursera_AISIA_Certificate JMK7JAW5O7R9</x:v>
+        <x:v>AI System Impact Assessment Guidance</x:v>
       </x:c>
       <x:c r="E28" s="32" t="str">
         <x:v>A u g 1 4 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o A I S y s t e m I m p a c t A s s e s s m e n t G u i d a n c e a n o n l i n e c o u r s e a u t h o r i z e d b y B r i t i s h S t a n d a r d s I n s t i t u t i o n a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d H e c t o r N e m o t o B S I G l o b a l T r a i n i n g D i r e c t o r V e r i f y a t : h t t p s : / / c o u r s e r a . o r g / v e r i f y / J M K 7 J A W 5 O 7 R </x:v>
@@ -2096,11 +2108,17 @@
       <x:c r="I28" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J28" s="33"/>
-      <x:c r="K28" s="33"/>
-      <x:c r="L28" s="33"/>
+      <x:c r="J28" s="33" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K28" s="33" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L28" s="33" t="n">
+        <x:v>2</x:v>
+      </x:c>
       <x:c r="M28" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/JMK7JAW5O7R9</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -2111,10 +2129,10 @@
         <x:v>BSI-Coursera_EU AI Act_CertificateE0NA98PI4EVM.pdf</x:v>
       </x:c>
       <x:c r="C29" s="32" t="str">
-        <x:v>BSI</x:v>
+        <x:v>British Standards Institution (BSI)</x:v>
       </x:c>
       <x:c r="D29" s="32" t="str">
-        <x:v>BSI-Coursera_EU AI Act_CertificateE0NA98PI4EVM</x:v>
+        <x:v>Understanding the Foundations of the EU AI Act</x:v>
       </x:c>
       <x:c r="E29" s="32" t="str">
         <x:v>A u g 1 4 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o U n d e r s t a n d i n g t h e F o u n d a t i o n s o f t h e E U A I A c t a n o n l i n e c o u r s e a u t h o r i z e d b y B r i t i s h S t a n d a r d s I n s t i t u t i o n a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d H e c t o r N e m o t o B S I G l o b a l T r a i n i n g D i r e c t o r V e r i f y a t : h t t p s : / / c o u r s e r a . o r g / v e r i f y / E 0 N A </x:v>
@@ -2129,11 +2147,17 @@
       <x:c r="I29" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J29" s="33"/>
-      <x:c r="K29" s="33"/>
-      <x:c r="L29" s="33"/>
+      <x:c r="J29" s="33" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K29" s="33" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L29" s="33" t="n">
+        <x:v>2</x:v>
+      </x:c>
       <x:c r="M29" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/E0NA98PI4EVM</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -2144,10 +2168,10 @@
         <x:v>BSI-Coursera_Intro ISO 22989 Certificate_3HLETUDTZKS9.pdf</x:v>
       </x:c>
       <x:c r="C30" s="32" t="str">
-        <x:v>BSI</x:v>
+        <x:v>British Standards Institution (BSI)</x:v>
       </x:c>
       <x:c r="D30" s="32" t="str">
-        <x:v>BSI-Coursera_Intro ISO 22989 Certificate_3HLETUDTZKS9</x:v>
+        <x:v>ISO/IEC 22989:2023 An Introduction to the Fundamentals of AI</x:v>
       </x:c>
       <x:c r="E30" s="32" t="str">
         <x:v>A u g 1 3 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o I S O / I E C 2 2 9 8 9 : 2 0 2 3 A n I n t r o d u c t i o n t o t h e F u n d a m e n t a l s o f A I a n o n l i n e c o u r s e a u t h o r i z e d b y B r i t i s h S t a n d a r d s I n s t i t u t i o n a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d H e c t o r N e m o t o B S I G l o b a l T r a i n i n g D i r e c t o r V e r i f y a t : h t t p s : / / c o u r s e r a . o r </x:v>
@@ -2163,15 +2187,17 @@
         <x:v>Extraído do documento</x:v>
       </x:c>
       <x:c r="J30" s="33" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K30" s="33" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L30" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="M30" s="32" t="str"/>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="M30" s="32" t="str">
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/3HLETUDTZKS9</x:v>
+      </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="32" t="n">
@@ -3278,10 +3304,10 @@
         <x:v>Certificado JHU+Coursera SVWCQ560O1OU - Revenue Cycle, Billing and Coding.jpg</x:v>
       </x:c>
       <x:c r="C64" s="32" t="str">
-        <x:v>Certificado JHU+Coursera SVWCQ560O1OU</x:v>
+        <x:v>Johns Hopkins University</x:v>
       </x:c>
       <x:c r="D64" s="32" t="str">
-        <x:v>Certificado JHU+Coursera SVWCQ560O1OU - Revenue Cycle, Billing and Coding</x:v>
+        <x:v>Revenue Cycle, Billing, and Coding</x:v>
       </x:c>
       <x:c r="E64" s="32" t="str"/>
       <x:c r="F64" s="32" t="str"/>
@@ -3294,11 +3320,17 @@
       <x:c r="I64" s="32" t="str">
         <x:v>Sem texto extraível — revisão manual</x:v>
       </x:c>
-      <x:c r="J64" s="33"/>
-      <x:c r="K64" s="33"/>
-      <x:c r="L64" s="33"/>
+      <x:c r="J64" s="33" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K64" s="33" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L64" s="33" t="n">
+        <x:v>6</x:v>
+      </x:c>
       <x:c r="M64" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/SVWCQ560O1OU</x:v>
       </x:c>
     </x:row>
     <x:row r="65">
@@ -3309,10 +3341,10 @@
         <x:v>Certificado JHU+Coursera SVWCQ560O1OU - Revenue Cycle, Billing and Coding.pdf</x:v>
       </x:c>
       <x:c r="C65" s="32" t="str">
-        <x:v>Certificado JHU+Coursera SVWCQ560O1OU</x:v>
+        <x:v>Johns Hopkins University</x:v>
       </x:c>
       <x:c r="D65" s="32" t="str">
-        <x:v>Certificado JHU+Coursera SVWCQ560O1OU - Revenue Cycle, Billing and Coding</x:v>
+        <x:v>Revenue Cycle, Billing, and Coding</x:v>
       </x:c>
       <x:c r="E65" s="32" t="str">
         <x:v>J u n 2 8 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o R e v e n u e C y c l e , B i l l i n g , a n d C o d i n g u m c u r s o o n - l i n e a u t o r i z a d o p e l a J o h n s H o p k i n s U n i v e r s i t y e m i n i s t r a d o a t r a v é s d a C o u r s e r a c o n c l u i u c o m s u c e s s o o P r o g r a m a d e c u r s o s i n t e g r a d o s M a u r a M c G u i r e , M D , C P C , F A C P E x e c u t i v e D i r e c t o r O J H P S t r a t e g i c L e a r n i n g C e n t </x:v>
@@ -3327,11 +3359,17 @@
       <x:c r="I65" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J65" s="33"/>
-      <x:c r="K65" s="33"/>
-      <x:c r="L65" s="33"/>
+      <x:c r="J65" s="33" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K65" s="33" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L65" s="33" t="n">
+        <x:v>6</x:v>
+      </x:c>
       <x:c r="M65" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/SVWCQ560O1OU</x:v>
       </x:c>
     </x:row>
     <x:row r="66">
@@ -3342,10 +3380,10 @@
         <x:v>Certificado Profissional JHU+Coursera P7PRAOBUU4L9 - JH Medical Office Manager (On-line).pdf</x:v>
       </x:c>
       <x:c r="C66" s="32" t="str">
-        <x:v>Certificado Profissional JHU+Coursera P7PRAOBUU4L9</x:v>
+        <x:v>Johns Hopkins University</x:v>
       </x:c>
       <x:c r="D66" s="32" t="str">
-        <x:v>Certificado Profissional JHU+Coursera P7PRAOBUU4L9 - JH Medical Office Manager (On-line)</x:v>
+        <x:v>Johns Hopkins Medical Office Manager</x:v>
       </x:c>
       <x:c r="E66" s="32" t="str">
         <x:v>Certificates Specialization Certificate Johns Hopkins Medical Office Manager Completed by Pedro Lamounier Sampaio June 28, 2026 Approximately 6 months at 3 hours a week to complete Pedro Lamounier Sampaio's account is veriﬁed. Coursera certiﬁestheir successful completion of Johns Hopkins University JohnsHopkins Medical Oﬃce Manager Specialization. Course Certiﬁcates Completed Introduction to Ambulatory Healthcare Management Human Resources Management Essentials Quality and Safety in Ambulatory H</x:v>
@@ -3361,16 +3399,16 @@
         <x:v>Extraído do documento</x:v>
       </x:c>
       <x:c r="J66" s="33" t="n">
-        <x:v>3</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="K66" s="33" t="n">
-        <x:v>3</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="L66" s="33" t="n">
-        <x:v>3</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="M66" s="32" t="str">
-        <x:v>https://www.coursera.org/account/accomplishments/professional-cert/P7PRAOBUU4L9</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/professional-cert/P7PRAOBUU4L9; estimativa derivada do tempo exibido: 6 meses com 3 por semana para concluir</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
@@ -3381,10 +3419,10 @@
         <x:v>Certificado Profissional JHU+Coursera P7PRAOBUU4L9 - JH Medical Office Manager.pdf</x:v>
       </x:c>
       <x:c r="C67" s="32" t="str">
-        <x:v>Certificado Profissional JHU+Coursera P7PRAOBUU4L9</x:v>
+        <x:v>Johns Hopkins University</x:v>
       </x:c>
       <x:c r="D67" s="32" t="str">
-        <x:v>Certificado Profissional JHU+Coursera P7PRAOBUU4L9 - JH Medical Office Manager</x:v>
+        <x:v>Johns Hopkins Medical Office Manager</x:v>
       </x:c>
       <x:c r="E67" s="32" t="str">
         <x:v>6 c u r s o s I n t r o d u c t i o n t o A m b u l a t o r y H e a l t h c a r e M a n a g e m e n t H u m a n R e s o u r c e s M a n a g e m e n t E s s e n t i a l s Q u a l i t y a n d S a f e t y i n A m b u l a t o r y H e a l t h c a r e M a n a g e m e n t H e a l t h c a r e D e l i v e r y f o r M e d i c a l P r a c t i c e M a n a g e r s D a t a a n d E l e c t r o n i c H e a l t h R e c o r d s R e v e n u e C y c l e , B i l l i n g , a n d C o d i n g M i c h e l l e J . C a m </x:v>
@@ -3399,11 +3437,17 @@
       <x:c r="I67" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J67" s="33"/>
-      <x:c r="K67" s="33"/>
-      <x:c r="L67" s="33"/>
+      <x:c r="J67" s="33" t="n">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="K67" s="33" t="n">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="L67" s="33" t="n">
+        <x:v>72</x:v>
+      </x:c>
       <x:c r="M67" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/professional-cert/P7PRAOBUU4L9; estimativa derivada do tempo exibido: 6 meses com 3 por semana para concluir</x:v>
       </x:c>
     </x:row>
     <x:row r="68">
@@ -4225,10 +4269,10 @@
         <x:v>Coursera 4UIYZU51HN5L_JHU_Outbreaks and Epidemics.pdf</x:v>
       </x:c>
       <x:c r="C93" s="32" t="str">
-        <x:v>Coursera 4UIYZU51HN5L</x:v>
+        <x:v>Johns Hopkins University</x:v>
       </x:c>
       <x:c r="D93" s="32" t="str">
-        <x:v>Coursera 4UIYZU51HN5L_JHU_Outbreaks and Epidemics</x:v>
+        <x:v>Outbreaks and Epidemics</x:v>
       </x:c>
       <x:c r="E93" s="32" t="str">
         <x:v>J u l 1 9 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o O u t b r e a k s a n d E p i d e m i c s a n o n l i n e c o u r s e a u t h o r i z e d b y J o h n s H o p k i n s U n i v e r s i t y a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d J u s t i n L e s s l e r A s s o c i a t e P r o f e s s o r D e p a r t m e n t o f E p i d e m i o l o g y J o h n s H o p k i n s B l o o m b e r g S c h o o l o f P u b l i c H e a l t h V e r i f </x:v>
@@ -4244,15 +4288,17 @@
         <x:v>Extraído do documento</x:v>
       </x:c>
       <x:c r="J93" s="33" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K93" s="33" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L93" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M93" s="32" t="str"/>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="M93" s="32" t="str">
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/4UIYZU51HN5L</x:v>
+      </x:c>
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="32" t="n">
@@ -4261,11 +4307,9 @@
       <x:c r="B94" s="32" t="str">
         <x:v>Coursera 8BH1XC5QBHPD_Specialization_Epidemiology and PHP.pdf</x:v>
       </x:c>
-      <x:c r="C94" s="32" t="str">
-        <x:v>Coursera 8BH1XC5QBHPD</x:v>
-      </x:c>
+      <x:c r="C94" s="32" t="str"/>
       <x:c r="D94" s="32" t="str">
-        <x:v>Coursera 8BH1XC5QBHPD_Specialization_Epidemiology and PHP</x:v>
+        <x:v>Epidemiology in Public Health Practice</x:v>
       </x:c>
       <x:c r="E94" s="32" t="str">
         <x:v>5 C o u r s e s E s s e n t i a l E p i d e m i o l o g i c T o o l s f o r P u b l i c H e a l t h P r a c t i c e D a t a a n d H e a l t h I n d i c a t o r s i n P u b l i c H e a l t h P r a c t i c e S u r v e i l l a n c e S y s t e m s : T h e B u i l d i n g B l o c k s S u r v e i l l a n c e S y s t e m s : A n a l y s i s , D i s s e m i n a t i o n , a n d S p e c i a l S y s t e m s O u t b r e a k s a n d E p i d e m i c s K e r i A l t h o ﬀ , P h D J u l 1 9 , 2 0 2 6 P e d r o </x:v>
@@ -4280,11 +4324,17 @@
       <x:c r="I94" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J94" s="33"/>
-      <x:c r="K94" s="33"/>
-      <x:c r="L94" s="33"/>
+      <x:c r="J94" s="33" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="K94" s="33" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="L94" s="33" t="n">
+        <x:v>40</x:v>
+      </x:c>
       <x:c r="M94" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/specialization/8BH1XC5QBHPD; estimativa derivada do tempo exibido: 1 meses com 10 por semana para concluir</x:v>
       </x:c>
     </x:row>
     <x:row r="95">
@@ -4294,11 +4344,9 @@
       <x:c r="B95" s="32" t="str">
         <x:v>Coursera CUX1XMF3YS8E_Leading HC Q-S_GWU.pdf</x:v>
       </x:c>
-      <x:c r="C95" s="32" t="str">
-        <x:v>Coursera CUX1XMF3YS8E</x:v>
-      </x:c>
+      <x:c r="C95" s="32" t="str"/>
       <x:c r="D95" s="32" t="str">
-        <x:v>Coursera CUX1XMF3YS8E_Leading HC Q-S_GWU</x:v>
+        <x:v>Leading Healthcare Quality and Safety</x:v>
       </x:c>
       <x:c r="E95" s="32" t="str">
         <x:v>J u l 2 1 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o L e a d i n g H e a l t h c a r e Q u a l i t y a n d S a f e t y a n o n l i n e c o u r s e a u t h o r i z e d b y T h e G e o r g e W a s h i n g t o n U n i v e r s i t y a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d G r e g o r y P a w l s o n C l i n i c a l P r o f e s s o r o f M e d i c i n e a n d E x e c u t i v e C o a c h G W S c h o o l o f N u r s i n g J e a n J o h </x:v>
@@ -4313,11 +4361,17 @@
       <x:c r="I95" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J95" s="33"/>
-      <x:c r="K95" s="33"/>
-      <x:c r="L95" s="33"/>
+      <x:c r="J95" s="33" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="K95" s="33" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="L95" s="33" t="n">
+        <x:v>13</x:v>
+      </x:c>
       <x:c r="M95" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/CUX1XMF3YS8E</x:v>
       </x:c>
     </x:row>
     <x:row r="96">
@@ -4328,10 +4382,10 @@
         <x:v>Coursera-Duke Certificate_TeleHealth KVF3XW2SP4BV.pdf</x:v>
       </x:c>
       <x:c r="C96" s="32" t="str">
-        <x:v>Coursera</x:v>
+        <x:v>Duke University</x:v>
       </x:c>
       <x:c r="D96" s="32" t="str">
-        <x:v>Coursera-Duke Certificate_TeleHealth KVF3XW2SP4BV</x:v>
+        <x:v>Telehealth Clinical Essentials</x:v>
       </x:c>
       <x:c r="E96" s="32" t="str">
         <x:v>J u l 2 5 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o T e l e h e a l t h C l i n i c a l E s s e n t i a l s a n o n l i n e c o u r s e a u t h o r i z e d b y D u k e U n i v e r s i t y a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d D a n i e l O s t r o v s k y A s s o c i a t e P r o f e s s o r P e d i a t r i c s K a t h l e e n W a i t e P r o f e s s o r o f M e d i c i n e D i v i s i o n o f G e n e r a l I n t e r n a l M e </x:v>
@@ -4346,11 +4400,17 @@
       <x:c r="I96" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J96" s="33"/>
-      <x:c r="K96" s="33"/>
-      <x:c r="L96" s="33"/>
+      <x:c r="J96" s="33" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K96" s="33" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L96" s="33" t="n">
+        <x:v>2</x:v>
+      </x:c>
       <x:c r="M96" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/KVF3XW2SP4BV</x:v>
       </x:c>
     </x:row>
     <x:row r="97">
@@ -4361,10 +4421,10 @@
         <x:v>Coursera-ICL_Quality Improvement Specialization_Certificate 2RUAK3DPGYVQ.pdf</x:v>
       </x:c>
       <x:c r="C97" s="32" t="str">
-        <x:v>Coursera</x:v>
+        <x:v>Imperial College London</x:v>
       </x:c>
       <x:c r="D97" s="32" t="str">
-        <x:v>Coursera-ICL_Quality Improvement Specialization_Certificate 2RUAK3DPGYVQ</x:v>
+        <x:v>Quality Improvement in Healthcare</x:v>
       </x:c>
       <x:c r="E97" s="32" t="str">
         <x:v>3 C o u r s e s I n t r o d u c t i o n t o Q u a l i t y I m p r o v e m e n t i n H e a l t h c a r e U s i n g D a t a f o r H e a l t h c a r e I m p r o v e m e n t Q u a l i t y I m p r o v e m e n t f o r P o p u l a t i o n H e a l t h D r T h o m a s W o o d c o c k S e n i o r R e s e a r c h F e l l o w S c h o o l o f P u b l i c H e a l t h J u l 2 4 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o h a s s u c c e s s f u l l y c o m p l e t e d t h e o n l i n e S p e c i a l i </x:v>
@@ -4379,11 +4439,17 @@
       <x:c r="I97" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J97" s="33"/>
-      <x:c r="K97" s="33"/>
-      <x:c r="L97" s="33"/>
+      <x:c r="J97" s="33" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="K97" s="33" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="L97" s="33" t="n">
+        <x:v>40</x:v>
+      </x:c>
       <x:c r="M97" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/specialization/2RUAK3DPGYVQ; estimativa derivada do tempo exibido: 1 meses com 10 por semana para concluir</x:v>
       </x:c>
     </x:row>
     <x:row r="98">
@@ -4394,10 +4460,10 @@
         <x:v>Coursera.ICL_ONCEZO8V6040_Intro to Quality Improvement in HC.pdf</x:v>
       </x:c>
       <x:c r="C98" s="32" t="str">
-        <x:v>Coursera.ICL</x:v>
+        <x:v>Imperial College London</x:v>
       </x:c>
       <x:c r="D98" s="32" t="str">
-        <x:v>Coursera.ICL_ONCEZO8V6040_Intro to Quality Improvement in HC</x:v>
+        <x:v>Introduction to Quality Improvement in Healthcare</x:v>
       </x:c>
       <x:c r="E98" s="32" t="str">
         <x:v>J u l 2 2 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o I n t r o d u c t i o n t o Q u a l i t y I m p r o v e m e n t i n H e a l t h c a r e a n o n l i n e c o u r s e a u t h o r i z e d b y I m p e r i a l C o l l e g e L o n d o n a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d D r T h o m a s W o o d c o c k S e n i o r R e s e a r c h F e l l o w S c h o o l o f P u b l i c H e a l t h V e r i f y a t : h t t p s : / / c o u r s e </x:v>
@@ -4412,11 +4478,17 @@
       <x:c r="I98" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J98" s="33"/>
-      <x:c r="K98" s="33"/>
-      <x:c r="L98" s="33"/>
+      <x:c r="J98" s="33" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K98" s="33" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="L98" s="33" t="n">
+        <x:v>21</x:v>
+      </x:c>
       <x:c r="M98" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/ONCEZO8V6040</x:v>
       </x:c>
     </x:row>
     <x:row r="99">
@@ -4427,10 +4499,10 @@
         <x:v>Coursera_ICL_Certificate_Health Data Usage_V3XFWO53BYYT.pdf</x:v>
       </x:c>
       <x:c r="C99" s="32" t="str">
-        <x:v>Coursera</x:v>
+        <x:v>Imperial College London</x:v>
       </x:c>
       <x:c r="D99" s="32" t="str">
-        <x:v>Coursera_ICL_Certificate_Health Data Usage_V3XFWO53BYYT</x:v>
+        <x:v>Using Data for Healthcare Improvement</x:v>
       </x:c>
       <x:c r="E99" s="32" t="str">
         <x:v>J u l 2 4 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o U s i n g D a t a f o r H e a l t h c a r e I m p r o v e m e n t a n o n l i n e c o u r s e a u t h o r i z e d b y I m p e r i a l C o l l e g e L o n d o n a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d D r T h o m a s W o o d c o c k S e n i o r R e s e a r c h F e l l o w S c h o o l o f P u b l i c H e a l t h V e r i f y a t : h t t p s : / / c o u r s e r a . o r g / v e r i </x:v>
@@ -4445,11 +4517,17 @@
       <x:c r="I99" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J99" s="33"/>
-      <x:c r="K99" s="33"/>
-      <x:c r="L99" s="33"/>
+      <x:c r="J99" s="33" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="K99" s="33" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="L99" s="33" t="n">
+        <x:v>15</x:v>
+      </x:c>
       <x:c r="M99" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/V3XFWO53BYYT</x:v>
       </x:c>
     </x:row>
     <x:row r="100">
@@ -4705,10 +4783,10 @@
         <x:v>Duke-Coursera_Telehealth_Cardiopulmonary Specialization DSEV3OLMXEMK.pdf</x:v>
       </x:c>
       <x:c r="C107" s="32" t="str">
-        <x:v>Duke</x:v>
+        <x:v>Duke University</x:v>
       </x:c>
       <x:c r="D107" s="32" t="str">
-        <x:v>Duke-Coursera_Telehealth_Cardiopulmonary Specialization DSEV3OLMXEMK</x:v>
+        <x:v>Telehealth: Essentials, Teamwork, and Cardiopulmonary Exam</x:v>
       </x:c>
       <x:c r="E107" s="32" t="str">
         <x:v>3 C o u r s e s T e l e h e a l t h C l i n i c a l E s s e n t i a l s T e l e h e a l t h : I n t e r p r o f e s s i o n a l T e a m - B a s e d C a r e T e l e h e a l t h : C a r d i o p u l m o n a r y A s s e s s m e n t D a n i e l O s t r o v s k y A s s o c i a t e P r o f e s s o r P e d i a t r i c s K a t h l e e n W a i t e P r o f e s s o r o f M e d i c i n e D i v i s i o n o f G e n e r a l I n t e r n a l M e d i c i n e A u g 3 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a </x:v>
@@ -4723,11 +4801,17 @@
       <x:c r="I107" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J107" s="33"/>
-      <x:c r="K107" s="33"/>
-      <x:c r="L107" s="33"/>
+      <x:c r="J107" s="33" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="K107" s="33" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="L107" s="33" t="n">
+        <x:v>12</x:v>
+      </x:c>
       <x:c r="M107" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/specialization/DSEV3OLMXEMK; estimativa derivada do tempo exibido: 1 meses com 3 por semana para concluir</x:v>
       </x:c>
     </x:row>
     <x:row r="108">
@@ -4738,10 +4822,10 @@
         <x:v>Duke-Coursera_Telehealth_Dermatology_Certificate_R2FTYV77JH0A.pdf</x:v>
       </x:c>
       <x:c r="C108" s="32" t="str">
-        <x:v>Duke</x:v>
+        <x:v>Duke University</x:v>
       </x:c>
       <x:c r="D108" s="32" t="str">
-        <x:v>Duke-Coursera_Telehealth_Dermatology_Certificate_R2FTYV77JH0A</x:v>
+        <x:v>Telehealth: Dermatology Assessment</x:v>
       </x:c>
       <x:c r="E108" s="32" t="str">
         <x:v>A u g 3 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o T e l e h e a l t h : D e r m a t o l o g y A s s e s s m e n t a n o n l i n e c o u r s e a u t h o r i z e d b y D u k e U n i v e r s i t y a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d D a n i e l O s t r o v s k y A s s o c i a t e P r o f e s s o r P e d i a t r i c s K a t h l e e n W a i t e P r o f e s s o r o f M e d i c i n e D i v i s i o n o f G e n e r a l I n t e r n a </x:v>
@@ -4756,11 +4840,17 @@
       <x:c r="I108" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J108" s="33"/>
-      <x:c r="K108" s="33"/>
-      <x:c r="L108" s="33"/>
+      <x:c r="J108" s="33" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K108" s="33" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L108" s="33" t="n">
+        <x:v>2</x:v>
+      </x:c>
       <x:c r="M108" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/R2FTYV77JH0A</x:v>
       </x:c>
     </x:row>
     <x:row r="109">
@@ -4771,10 +4861,10 @@
         <x:v>Duke-Coursera_Telehealth_Dermatology_Specialization Certificate_CG5I6U6HR05R..pdf</x:v>
       </x:c>
       <x:c r="C109" s="32" t="str">
-        <x:v>Duke</x:v>
+        <x:v>Duke University</x:v>
       </x:c>
       <x:c r="D109" s="32" t="str">
-        <x:v>Duke-Coursera_Telehealth_Dermatology_Specialization Certificate_CG5I6U6HR05R.</x:v>
+        <x:v>Telehealth: Essentials, Teamwork, and Dermatology</x:v>
       </x:c>
       <x:c r="E109" s="32" t="str">
         <x:v>3 C o u r s e s T e l e h e a l t h C l i n i c a l E s s e n t i a l s T e l e h e a l t h : I n t e r p r o f e s s i o n a l T e a m - B a s e d C a r e T e l e h e a l t h : D e r m a t o l o g y A s s e s s m e n t D a n i e l O s t r o v s k y A s s o c i a t e P r o f e s s o r P e d i a t r i c s K a t h l e e n W a i t e P r o f e s s o r o f M e d i c i n e D i v i s i o n o f G e n e r a l I n t e r n a l M e d i c i n e A u g 3 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o h a </x:v>
@@ -4790,15 +4880,17 @@
         <x:v>Extraído do documento</x:v>
       </x:c>
       <x:c r="J109" s="33" t="n">
-        <x:v>6</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="K109" s="33" t="n">
-        <x:v>6</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L109" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="M109" s="32" t="str"/>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M109" s="32" t="str">
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/specialization/CG5I6U6HR05R; estimativa derivada do tempo exibido: 1 meses com 3 por semana para concluir</x:v>
+      </x:c>
     </x:row>
     <x:row r="110">
       <x:c r="A110" s="32" t="n">
@@ -4808,10 +4900,10 @@
         <x:v>Duke-Coursera_Telehealth_Musculoskeletal_Exam_Certificate_2J767H2OB448.pdf</x:v>
       </x:c>
       <x:c r="C110" s="32" t="str">
-        <x:v>Duke</x:v>
+        <x:v>Duke University</x:v>
       </x:c>
       <x:c r="D110" s="32" t="str">
-        <x:v>Duke-Coursera_Telehealth_Musculoskeletal_Exam_Certificate_2J767H2OB448</x:v>
+        <x:v>Telehealth: Musculoskeletal Assessment</x:v>
       </x:c>
       <x:c r="E110" s="32" t="str">
         <x:v>A u g 1 7 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o T e l e h e a l t h : M u s c u l o s k e l e t a l A s s e s s m e n t a n o n l i n e c o u r s e a u t h o r i z e d b y D u k e U n i v e r s i t y a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d D a n i e l O s t r o v s k y A s s o c i a t e P r o f e s s o r P e d i a t r i c s K a t h l e e n W a i t e P r o f e s s o r o f M e d i c i n e D i v i s i o n o f G e n e r a l I n </x:v>
@@ -4827,15 +4919,17 @@
         <x:v>Extraído do documento</x:v>
       </x:c>
       <x:c r="J110" s="33" t="n">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K110" s="33" t="n">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L110" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="M110" s="32" t="str"/>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M110" s="32" t="str">
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/2J767H2OB448</x:v>
+      </x:c>
     </x:row>
     <x:row r="111">
       <x:c r="A111" s="32" t="n">
@@ -4845,10 +4939,10 @@
         <x:v>Duke-Coursera_Telehealth_Musculoskeletal_Specialization Certificate_ZVA616EKPRVQ.pdf</x:v>
       </x:c>
       <x:c r="C111" s="32" t="str">
-        <x:v>Duke</x:v>
+        <x:v>Duke University</x:v>
       </x:c>
       <x:c r="D111" s="32" t="str">
-        <x:v>Duke-Coursera_Telehealth_Musculoskeletal_Specialization Certificate_ZVA616EKPRVQ</x:v>
+        <x:v>Telehealth: Essentials, Teamwork, and Musculoskeletal Exam</x:v>
       </x:c>
       <x:c r="E111" s="32" t="str">
         <x:v>3 C o u r s e s T e l e h e a l t h C l i n i c a l E s s e n t i a l s T e l e h e a l t h : I n t e r p r o f e s s i o n a l T e a m - B a s e d C a r e T e l e h e a l t h : M u s c u l o s k e l e t a l A s s e s s m e n t D a n i e l O s t r o v s k y A s s o c i a t e P r o f e s s o r P e d i a t r i c s K a t h l e e n W a i t e P r o f e s s o r o f M e d i c i n e D i v i s i o n o f G e n e r a l I n t e r n a l M e d i c i n e A u g 1 7 , 2 0 2 6 P e d r o L a m o u n i e r S a m p </x:v>
@@ -4863,11 +4957,17 @@
       <x:c r="I111" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J111" s="33"/>
-      <x:c r="K111" s="33"/>
-      <x:c r="L111" s="33"/>
+      <x:c r="J111" s="33" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="K111" s="33" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="L111" s="33" t="n">
+        <x:v>12</x:v>
+      </x:c>
       <x:c r="M111" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/specialization/ZVA616EKPRVQ; estimativa derivada do tempo exibido: 1 meses com 3 por semana para concluir</x:v>
       </x:c>
     </x:row>
     <x:row r="112">
@@ -4878,10 +4978,10 @@
         <x:v>Duke-Coursera_Telehealth_Neurological Exam Course_Certificate_UCSTLLOAX0QZ.pdf</x:v>
       </x:c>
       <x:c r="C112" s="32" t="str">
-        <x:v>Duke</x:v>
+        <x:v>Duke University</x:v>
       </x:c>
       <x:c r="D112" s="32" t="str">
-        <x:v>Duke-Coursera_Telehealth_Neurological Exam Course_Certificate_UCSTLLOAX0QZ</x:v>
+        <x:v>Telehealth: Neurological Exam Course</x:v>
       </x:c>
       <x:c r="E112" s="32" t="str">
         <x:v>A u g 1 7 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o T e l e h e a l t h : N e u r o l o g i c A s s e s s m e n t a n o n l i n e c o u r s e a u t h o r i z e d b y D u k e U n i v e r s i t y a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d D a n i e l O s t r o v s k y A s s o c i a t e P r o f e s s o r P e d i a t r i c s K a t h l e e n W a i t e P r o f e s s o r o f M e d i c i n e D i v i s i o n o f G e n e r a l I n t e r n a </x:v>
@@ -4900,7 +5000,7 @@
       <x:c r="K112" s="33"/>
       <x:c r="L112" s="33"/>
       <x:c r="M112" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/UCSTLLOAX0QZ</x:v>
       </x:c>
     </x:row>
     <x:row r="113">
@@ -4911,10 +5011,10 @@
         <x:v>Duke-Coursera_Telehealth_Neurology_Certificate_UCSTLLOAX0QZ.pdf</x:v>
       </x:c>
       <x:c r="C113" s="32" t="str">
-        <x:v>Duke</x:v>
+        <x:v>Duke University</x:v>
       </x:c>
       <x:c r="D113" s="32" t="str">
-        <x:v>Duke-Coursera_Telehealth_Neurology_Certificate_UCSTLLOAX0QZ</x:v>
+        <x:v>Telehealth: Neurology</x:v>
       </x:c>
       <x:c r="E113" s="32" t="str">
         <x:v>3 C o u r s e s T e l e h e a l t h C l i n i c a l E s s e n t i a l s T e l e h e a l t h : I n t e r p r o f e s s i o n a l T e a m - B a s e d C a r e T e l e h e a l t h : N e u r o l o g i c A s s e s s m e n t D a n i e l O s t r o v s k y A s s o c i a t e P r o f e s s o r P e d i a t r i c s K a t h l e e n W a i t e P r o f e s s o r o f M e d i c i n e D i v i s i o n o f G e n e r a l I n t e r n a l M e d i c i n e A u g 1 7 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o h a </x:v>
@@ -4933,7 +5033,7 @@
       <x:c r="K113" s="33"/>
       <x:c r="L113" s="33"/>
       <x:c r="M113" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/UCSTLLOAX0QZ</x:v>
       </x:c>
     </x:row>
     <x:row r="114">
@@ -6037,10 +6137,10 @@
         <x:v>HBS-Coursera_Effective Leadership_UQNUF9TGZVM9.pdf</x:v>
       </x:c>
       <x:c r="C147" s="32" t="str">
-        <x:v>HBS</x:v>
+        <x:v>Harvard Business School</x:v>
       </x:c>
       <x:c r="D147" s="32" t="str">
-        <x:v>HBS-Coursera_Effective Leadership_UQNUF9TGZVM9</x:v>
+        <x:v>Becoming an Effective Leader</x:v>
       </x:c>
       <x:c r="E147" s="32" t="str">
         <x:v>A u g 7 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o B e c o m i n g a n E f f e c t i v e L e a d e r a n o n l i n e c o u r s e a u t h o r i z e d b y H a r v a r d B u s i n e s s S c h o o l O n l i n e a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d H a r v a r d B u s i n e s s S c h o o l O n l i n e V e r i f y a t : h t t p s : / / c o u r s e r a . o r g / v e r i f y / U Q N U F 9 T G Z V M 9 C o u r s e r a h a s c o n f i r </x:v>
@@ -6055,11 +6155,17 @@
       <x:c r="I147" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J147" s="33"/>
-      <x:c r="K147" s="33"/>
-      <x:c r="L147" s="33"/>
+      <x:c r="J147" s="33" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K147" s="33" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L147" s="33" t="n">
+        <x:v>2</x:v>
+      </x:c>
       <x:c r="M147" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/UQNUF9TGZVM9</x:v>
       </x:c>
     </x:row>
     <x:row r="148">
@@ -6070,10 +6176,10 @@
         <x:v>HBS-Coursera_Intro to Leadership Specialization Certificate_53FFGZD92GQU.pdf</x:v>
       </x:c>
       <x:c r="C148" s="32" t="str">
-        <x:v>HBS</x:v>
+        <x:v>Harvard Business School</x:v>
       </x:c>
       <x:c r="D148" s="32" t="str">
-        <x:v>HBS-Coursera_Intro to Leadership Specialization Certificate_53FFGZD92GQU</x:v>
+        <x:v>Introduction to Leadership Principles</x:v>
       </x:c>
       <x:c r="E148" s="32" t="str">
         <x:v>2 C o u r s e s B e c o m i n g a n E ﬀ e c t i v e L e a d e r L e a d i n g H i g h - P e r f o r m i n g T e a m s H a r v a r d B u s i n e s s S c h o o l O n l i n e A u g 7 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o h a s s u c c e s s f u l l y c o m p l e t e d t h e o n l i n e S p e c i a l i z a t i o n I n t r o d u c t i o n t o L e a d e r s h i p P r i n c i p l e s T h i s s p e c i a l i z a t i o n , d e v e l o p e d b y H B S O n l i n e a n d o ﬀ e r e d t h r o u </x:v>
@@ -6088,11 +6194,17 @@
       <x:c r="I148" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J148" s="33"/>
-      <x:c r="K148" s="33"/>
-      <x:c r="L148" s="33"/>
+      <x:c r="J148" s="33" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="K148" s="33" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="L148" s="33" t="n">
+        <x:v>40</x:v>
+      </x:c>
       <x:c r="M148" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/specialization/53FFGZD92GQU; estimativa derivada do tempo exibido: 1 meses com 10 por semana para concluir</x:v>
       </x:c>
     </x:row>
     <x:row r="149">
@@ -6483,10 +6595,10 @@
         <x:v>ICL-Coursera_Digital Health_Specialization Certificate CO5VFFKM5MQ6.pdf</x:v>
       </x:c>
       <x:c r="C161" s="32" t="str">
-        <x:v>ICL</x:v>
+        <x:v>Imperial College London</x:v>
       </x:c>
       <x:c r="D161" s="32" t="str">
-        <x:v>ICL-Coursera_Digital Health_Specialization Certificate CO5VFFKM5MQ6</x:v>
+        <x:v>Digital Health</x:v>
       </x:c>
       <x:c r="E161" s="32" t="str">
         <x:v>3 C o u r s e s I n t r o d u c t i o n t o D i g i t a l h e a l t h D e s i g n a n d I m p l e m e n t a t i o n o f D i g i t a l H e a l t h I n t e r v e n t i o n s E v a l u a t i o n o f D i g i t a l H e a l t h I n t e r v e n t i o n s A n a L u i s a N e v e s S e n i o r C l i n i c a l L e c t u r e r &amp; D i r e c t o r o f G l o b a l D i g i t a l H e a l t h U n i t S c h o o l o f P u b l i c H e a l t h A u g 7 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o h a s s u c c </x:v>
@@ -6501,11 +6613,17 @@
       <x:c r="I161" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J161" s="33"/>
-      <x:c r="K161" s="33"/>
-      <x:c r="L161" s="33"/>
+      <x:c r="J161" s="33" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="K161" s="33" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="L161" s="33" t="n">
+        <x:v>80</x:v>
+      </x:c>
       <x:c r="M161" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/specialization/CO5VFFKM5MQ6; estimativa derivada do tempo exibido: 2 meses com 10 por semana para concluir</x:v>
       </x:c>
     </x:row>
     <x:row r="162">
@@ -6549,10 +6667,10 @@
         <x:v>IllinoisMed-Coursera_Health Ecosystem 3O4Q2WIWVNSX.pdf</x:v>
       </x:c>
       <x:c r="C163" s="32" t="str">
-        <x:v>IllinoisMed</x:v>
+        <x:v>University of Illinois Chicago</x:v>
       </x:c>
       <x:c r="D163" s="32" t="str">
-        <x:v>IllinoisMed-Coursera_Health Ecosystem 3O4Q2WIWVNSX</x:v>
+        <x:v>Understanding the Healthcare Ecosystem</x:v>
       </x:c>
       <x:c r="E163" s="32" t="str">
         <x:v>J u l 2 6 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o U n d e r s t a n d i n g t h e H e a l t h c a r e E c o s y s t e m a n o n l i n e c o u r s e a u t h o r i z e d b y U n i v e r s i t y o f I l l i n o i s U r b a n a - C h a m p a i g n a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d S r i d h a r S e s h a d r i A l a n J . a n d J o y c e D . B a l t z E n d o w e d P r o f e s s o r a n d P r o f e s s o r o f B u s i n e s </x:v>
@@ -6567,11 +6685,17 @@
       <x:c r="I163" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J163" s="33"/>
-      <x:c r="K163" s="33"/>
-      <x:c r="L163" s="33"/>
+      <x:c r="J163" s="33" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="K163" s="33" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="L163" s="33" t="n">
+        <x:v>15</x:v>
+      </x:c>
       <x:c r="M163" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/3O4Q2WIWVNSX</x:v>
       </x:c>
     </x:row>
     <x:row r="164">
@@ -6871,10 +6995,10 @@
         <x:v>JHU-Coursera_Analysis of Programs_Certificate 3Z8RM8B5P6LS.pdf</x:v>
       </x:c>
       <x:c r="C173" s="32" t="str">
-        <x:v>JHU</x:v>
+        <x:v>Johns Hopkins University</x:v>
       </x:c>
       <x:c r="D173" s="32" t="str">
-        <x:v>JHU-Coursera_Analysis of Programs_Certificate 3Z8RM8B5P6LS</x:v>
+        <x:v>Analysis and Interpretation of Large-Scale Programs</x:v>
       </x:c>
       <x:c r="E173" s="32" t="str">
         <x:v>A u g 1 0 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o A n a l y s i s a n d I n t e r p r e t a t i o n o f L a r g e - S c a l e P r o g r a m s a n o n l i n e c o u r s e a u t h o r i z e d b y J o h n s H o p k i n s U n i v e r s i t y a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d A g b e s s i A m o u z o u - A s s o c i a t e P r o f e s s o r ; N e f f W a l k e r - S e n i o r S c i e n t i s t ; M e l i n d a M u n o s - A s </x:v>
@@ -6889,11 +7013,17 @@
       <x:c r="I173" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J173" s="33"/>
-      <x:c r="K173" s="33"/>
-      <x:c r="L173" s="33"/>
+      <x:c r="J173" s="33" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="K173" s="33" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="L173" s="33" t="n">
+        <x:v>21</x:v>
+      </x:c>
       <x:c r="M173" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/3Z8RM8B5P6LS</x:v>
       </x:c>
     </x:row>
     <x:row r="174">
@@ -6904,10 +7034,10 @@
         <x:v>JHU-Coursera_Biostatistics in PH_4XIVGLM9A4VF.pdf</x:v>
       </x:c>
       <x:c r="C174" s="32" t="str">
-        <x:v>JHU</x:v>
+        <x:v>Johns Hopkins University</x:v>
       </x:c>
       <x:c r="D174" s="32" t="str">
-        <x:v>JHU-Coursera_Biostatistics in PH_4XIVGLM9A4VF</x:v>
+        <x:v>Biostatistics in Public Health</x:v>
       </x:c>
       <x:c r="E174" s="32" t="str">
         <x:v>4 C o u r s e s S u m m a r y S t a t i s t i c s i n P u b l i c H e a l t h H y p o t h e s i s T e s t i n g i n P u b l i c H e a l t h S i m p l e R e g r e s s i o n A n a l y s i s i n P u b l i c H e a l t h M u l t i p l e R e g r e s s i o n A n a l y s i s i n P u b l i c H e a l t h J o h n M c G r e a d y , P h D , M S A s s o c i a t e S c i e n t i s t D e p a r t m e n t o f B i o s t a t i s t i c s A u g 8 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o h a s s u c c e s s </x:v>
@@ -6926,7 +7056,7 @@
       <x:c r="K174" s="33"/>
       <x:c r="L174" s="33"/>
       <x:c r="M174" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/4XIVGLM9A4VF</x:v>
       </x:c>
     </x:row>
     <x:row r="175">
@@ -6937,10 +7067,10 @@
         <x:v>JHU-Coursera_Evaluating Health Programs_Specializatin Certificate_9LMUYO3P4H4E.pdf</x:v>
       </x:c>
       <x:c r="C175" s="32" t="str">
-        <x:v>JHU</x:v>
+        <x:v>Johns Hopkins University</x:v>
       </x:c>
       <x:c r="D175" s="32" t="str">
-        <x:v>JHU-Coursera_Evaluating Health Programs_Specializatin Certificate_9LMUYO3P4H4E</x:v>
+        <x:v>Evaluating Large-Scale Health Programs</x:v>
       </x:c>
       <x:c r="E175" s="32" t="str">
         <x:v>6 C o u r s e s E v a l u a t i n g P u b l i c H e a l t h P r o g r a m s a t S c a l e P r o g r a m D e s i g n &amp; E v a l u a t i o n f o r H e a l t h S y s t e m s S t r e n g t h e n i n g A s s e s s i n g H e a l t h P r o g r a m D e l i v e r y H o u s e h o l d S u r v e y s f o r P r o g r a m E v a l u a t i o n i n L M I C s M e a s u r i n g a n d M o d e l i n g I m p a c t i n E v a l u a t i o n s A n a l y s i s a n d I n t e r p r e t a t i o n o f L a r g e - S c a l e P r </x:v>
@@ -6956,15 +7086,17 @@
         <x:v>Extraído do documento</x:v>
       </x:c>
       <x:c r="J175" s="33" t="n">
-        <x:v>4</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="K175" s="33" t="n">
-        <x:v>4</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="L175" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="M175" s="32" t="str"/>
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="M175" s="32" t="str">
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/specialization/9LMUYO3P4H4E; estimativa derivada do tempo exibido: 6 meses com 3 por semana para concluir</x:v>
+      </x:c>
     </x:row>
     <x:row r="176">
       <x:c r="A176" s="32" t="n">
@@ -6974,10 +7106,10 @@
         <x:v>JHU-Coursera_Health Program Delivery_Certificate 47FKHSCQYH5D.pdf</x:v>
       </x:c>
       <x:c r="C176" s="32" t="str">
-        <x:v>JHU</x:v>
+        <x:v>Johns Hopkins University</x:v>
       </x:c>
       <x:c r="D176" s="32" t="str">
-        <x:v>JHU-Coursera_Health Program Delivery_Certificate 47FKHSCQYH5D</x:v>
+        <x:v>Assessing Health Program Delivery</x:v>
       </x:c>
       <x:c r="E176" s="32" t="str">
         <x:v>A u g 1 0 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o A s s e s s i n g H e a l t h P r o g r a m D e l i v e r y a n o n l i n e c o u r s e a u t h o r i z e d b y J o h n s H o p k i n s U n i v e r s i t y a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d E l i z a b e t h H a z e l , A s s i s t a n t S c i e n t i s t , I n t e r n a t i o n a l H e a l t h | D i w a k a r M o h a n , A s s i s t a n t S c i e n t i s t , I n t e r n </x:v>
@@ -6992,11 +7124,17 @@
       <x:c r="I176" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J176" s="33"/>
-      <x:c r="K176" s="33"/>
-      <x:c r="L176" s="33"/>
+      <x:c r="J176" s="33" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="K176" s="33" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="L176" s="33" t="n">
+        <x:v>19</x:v>
+      </x:c>
       <x:c r="M176" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/47FKHSCQYH5D</x:v>
       </x:c>
     </x:row>
     <x:row r="177">
@@ -7007,10 +7145,10 @@
         <x:v>JHU-Coursera_PH Programs Evaluation_Certificate URX3MO9G7TX7.pdf</x:v>
       </x:c>
       <x:c r="C177" s="32" t="str">
-        <x:v>JHU</x:v>
+        <x:v>Johns Hopkins University</x:v>
       </x:c>
       <x:c r="D177" s="32" t="str">
-        <x:v>JHU-Coursera_PH Programs Evaluation_Certificate URX3MO9G7TX7</x:v>
+        <x:v>Evaluating Public Health Programs at Scale</x:v>
       </x:c>
       <x:c r="E177" s="32" t="str">
         <x:v>A u g 8 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o E v a l u a t i n g P u b l i c H e a l t h P r o g r a m s a t S c a l e a n o n l i n e c o u r s e a u t h o r i z e d b y J o h n s H o p k i n s U n i v e r s i t y a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d A g b e s s i A m o u z o u , P h D , M H S A s s o c i a t e P r o f e s s o r I n t e r n a t i o n a l H e a l t h N e f f W a l k e r , P h D S e n i o r S c i e n t i </x:v>
@@ -7025,11 +7163,17 @@
       <x:c r="I177" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J177" s="33"/>
-      <x:c r="K177" s="33"/>
-      <x:c r="L177" s="33"/>
+      <x:c r="J177" s="33" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="K177" s="33" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="L177" s="33" t="n">
+        <x:v>18</x:v>
+      </x:c>
       <x:c r="M177" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/URX3MO9G7TX7</x:v>
       </x:c>
     </x:row>
     <x:row r="178">
@@ -7040,10 +7184,10 @@
         <x:v>JHU-Coursera_Program Design and Evaluation_Certificate_N5X42IZWTN22.pdf</x:v>
       </x:c>
       <x:c r="C178" s="32" t="str">
-        <x:v>JHU</x:v>
+        <x:v>Johns Hopkins University</x:v>
       </x:c>
       <x:c r="D178" s="32" t="str">
-        <x:v>JHU-Coursera_Program Design and Evaluation_Certificate_N5X42IZWTN22</x:v>
+        <x:v>Program Design &amp; Evaluation for Health Systems Strengthening</x:v>
       </x:c>
       <x:c r="E178" s="32" t="str">
         <x:v>A u g 9 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o P r o g r a m D e s i g n &amp; E v a l u a t i o n f o r H e a l t h S y s t e m s S t r e n g t h e n i n g a n o n l i n e c o u r s e a u t h o r i z e d b y J o h n s H o p k i n s U n i v e r s i t y a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d T i m o t h y R o b e r t o n , D r P H , A s s i s t a n t S c i e n t i s t | J a y a G u p t a , P h D , H e a l t h S y s t e m s R e s </x:v>
@@ -7058,11 +7202,17 @@
       <x:c r="I178" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J178" s="33"/>
-      <x:c r="K178" s="33"/>
-      <x:c r="L178" s="33"/>
+      <x:c r="J178" s="33" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="K178" s="33" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="L178" s="33" t="n">
+        <x:v>7</x:v>
+      </x:c>
       <x:c r="M178" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/N5X42IZWTN22</x:v>
       </x:c>
     </x:row>
     <x:row r="179">
@@ -7417,10 +7567,10 @@
         <x:v>MichiganU-Coursera_Intro to Translational Science_Certificate_AI712ZU1D9CZ.pdf</x:v>
       </x:c>
       <x:c r="C189" s="32" t="str">
-        <x:v>MichiganU</x:v>
+        <x:v>University of Michigan</x:v>
       </x:c>
       <x:c r="D189" s="32" t="str">
-        <x:v>MichiganU-Coursera_Intro to Translational Science_Certificate_AI712ZU1D9CZ</x:v>
+        <x:v>Introduction to Translational Science</x:v>
       </x:c>
       <x:c r="E189" s="32" t="str">
         <x:v>A u g 4 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o I n t r o d u c t i o n t o T r a n s l a t i o n a l S c i e n c e a n o n l i n e c o u r s e a u t h o r i z e d b y U n i v e r s i t y o f M i c h i g a n a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d V i c k i E l l i n g r o d S e n i o r A s s o c i a t e D e a n C o l l e g e o f P h a r m a c y V e r i f y a t : h t t p s : / / c o u r s e r a . o r g / v e r i f y / A I 7 1 </x:v>
@@ -7435,11 +7585,17 @@
       <x:c r="I189" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J189" s="33"/>
-      <x:c r="K189" s="33"/>
-      <x:c r="L189" s="33"/>
+      <x:c r="J189" s="33" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="K189" s="33" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="L189" s="33" t="n">
+        <x:v>12</x:v>
+      </x:c>
       <x:c r="M189" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/AI712ZU1D9CZ</x:v>
       </x:c>
     </x:row>
     <x:row r="190">
@@ -8370,10 +8526,10 @@
         <x:v>Penn-Coursera_Healthcare Law Specialization Certificate VOUZB1AZBVL4.pdf</x:v>
       </x:c>
       <x:c r="C218" s="32" t="str">
-        <x:v>Penn</x:v>
+        <x:v>University of Pennsylvania</x:v>
       </x:c>
       <x:c r="D218" s="32" t="str">
-        <x:v>Penn-Coursera_Healthcare Law Specialization Certificate VOUZB1AZBVL4</x:v>
+        <x:v>Healthcare Law</x:v>
       </x:c>
       <x:c r="E218" s="32" t="str">
         <x:v>4 C o u r s e s U . S . H e a l t h L a w F u n d a m e n t a l s P r i v a c y L a w a n d H I P A A I n t e l l e c t u a l P r o p e r t y i n t h e H e a l t h c a r e I n d u s t r y C o m p a r a t i v e H e a l t h S y s t e m s T h e o d o r e R u g e r , J D D e a n a n d B e r n a r d G . S e g a l P r o f e s s o r o f L a w P e n n L a w L a u r e n S t e i n f e l d L e c t u r e r i n L a w R . P o l k W a g n e r P r o f e s s o r o f L a w A n g u s C o r b e t t A d j u n c t P </x:v>
@@ -8388,11 +8544,17 @@
       <x:c r="I218" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J218" s="33"/>
-      <x:c r="K218" s="33"/>
-      <x:c r="L218" s="33"/>
+      <x:c r="J218" s="33" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="K218" s="33" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="L218" s="33" t="n">
+        <x:v>40</x:v>
+      </x:c>
       <x:c r="M218" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/specialization/VOUZB1AZBVL4; estimativa derivada do tempo exibido: 1 meses com 10 por semana para concluir</x:v>
       </x:c>
     </x:row>
     <x:row r="219">
@@ -8403,10 +8565,10 @@
         <x:v>Penn-Coursera_Intellectual Property in Healthcare_Certificate_ME8EBTCWCKTS.pdf</x:v>
       </x:c>
       <x:c r="C219" s="32" t="str">
-        <x:v>Penn</x:v>
+        <x:v>University of Pennsylvania</x:v>
       </x:c>
       <x:c r="D219" s="32" t="str">
-        <x:v>Penn-Coursera_Intellectual Property in Healthcare_Certificate_ME8EBTCWCKTS</x:v>
+        <x:v>Intellectual Property in the Healthcare Industry</x:v>
       </x:c>
       <x:c r="E219" s="32" t="str">
         <x:v>A u g 7 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o I n t e l l e c t u a l P r o p e r t y i n t h e H e a l t h c a r e I n d u s t r y a n o n l i n e n o n - c r e d i t c o u r s e a u t h o r i z e d b y U n i v e r s i t y o f P e n n s y l v a n i a a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d R . P o l k W a g n e r P r o f e s s o r o f L a w V e r i f y a t : h t t p s : / / c o u r s e r a . o r g / v e r i f y / M E 8 E B </x:v>
@@ -8421,11 +8583,17 @@
       <x:c r="I219" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J219" s="33"/>
-      <x:c r="K219" s="33"/>
-      <x:c r="L219" s="33"/>
+      <x:c r="J219" s="33" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="K219" s="33" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="L219" s="33" t="n">
+        <x:v>13</x:v>
+      </x:c>
       <x:c r="M219" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/ME8EBTCWCKTS</x:v>
       </x:c>
     </x:row>
     <x:row r="220">
@@ -9681,10 +9849,10 @@
         <x:v>Said-Oxford-Coursera_Agentic and GenAI_Certificate5YR8YBKNEOIC.pdf</x:v>
       </x:c>
       <x:c r="C257" s="32" t="str">
-        <x:v>Said</x:v>
+        <x:v>Saïd Business School, University of Oxford</x:v>
       </x:c>
       <x:c r="D257" s="32" t="str">
-        <x:v>Said-Oxford-Coursera_Agentic and GenAI_Certificate5YR8YBKNEOIC</x:v>
+        <x:v>Generative and Agentic AI</x:v>
       </x:c>
       <x:c r="E257" s="32" t="str">
         <x:v>A u g 1 4 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o G e n e r a t i v e a n d A g e n t i c A I a n o n l i n e c o u r s e a u t h o r i z e d b y S a ï d B u s i n e s s S c h o o l , U n i v e r s i t y o f O x f o r d a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d M a t t h i a s H o l w e g A m e r i c a n S t a n d a r d C o m p a n i e s P r o f e s s o r o f O p e r a t i o n s M a n a g e m e n t S a ï d B u s i n e s s S c h </x:v>
@@ -9699,11 +9867,17 @@
       <x:c r="I257" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J257" s="33"/>
-      <x:c r="K257" s="33"/>
-      <x:c r="L257" s="33"/>
+      <x:c r="J257" s="33" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="K257" s="33" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="L257" s="33" t="n">
+        <x:v>13</x:v>
+      </x:c>
       <x:c r="M257" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/5YR8YBKNEOIC</x:v>
       </x:c>
     </x:row>
     <x:row r="258">
@@ -9714,10 +9888,10 @@
         <x:v>Said-Oxford-Coursera_AI Essentials_Certificate EN2VCPK6A775.pdf</x:v>
       </x:c>
       <x:c r="C258" s="32" t="str">
-        <x:v>Said</x:v>
+        <x:v>Saïd Business School, University of Oxford</x:v>
       </x:c>
       <x:c r="D258" s="32" t="str">
-        <x:v>Said-Oxford-Coursera_AI Essentials_Certificate EN2VCPK6A775</x:v>
+        <x:v>AI Essentials</x:v>
       </x:c>
       <x:c r="E258" s="32" t="str">
         <x:v>A u g 1 3 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o A I E s s e n t i a l s a n o n l i n e c o u r s e a u t h o r i z e d b y S a ï d B u s i n e s s S c h o o l , U n i v e r s i t y o f O x f o r d a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d M a t t h i a s H o l w e g A m e r i c a n S t a n d a r d C o m p a n i e s P r o f e s s o r o f O p e r a t i o n s M a n a g e m e n t S a ï d B u s i n e s s S c h o o l U n i v e r s </x:v>
@@ -9732,11 +9906,17 @@
       <x:c r="I258" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J258" s="33"/>
-      <x:c r="K258" s="33"/>
-      <x:c r="L258" s="33"/>
+      <x:c r="J258" s="33" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="K258" s="33" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="L258" s="33" t="n">
+        <x:v>13</x:v>
+      </x:c>
       <x:c r="M258" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/EN2VCPK6A775</x:v>
       </x:c>
     </x:row>
     <x:row r="259">
@@ -9747,10 +9927,10 @@
         <x:v>Said-Oxford-Coursera_AI Governance_Certificate_FWGA4AWODSM4.pdf</x:v>
       </x:c>
       <x:c r="C259" s="32" t="str">
-        <x:v>Said</x:v>
+        <x:v>Saïd Business School, University of Oxford</x:v>
       </x:c>
       <x:c r="D259" s="32" t="str">
-        <x:v>Said-Oxford-Coursera_AI Governance_Certificate_FWGA4AWODSM4</x:v>
+        <x:v>AI Governance</x:v>
       </x:c>
       <x:c r="E259" s="32" t="str">
         <x:v>A u g 1 4 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o A I G o v e r n a n c e a n o n l i n e c o u r s e a u t h o r i z e d b y S a ï d B u s i n e s s S c h o o l , U n i v e r s i t y o f O x f o r d a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d M a t t h i a s H o l w e g A m e r i c a n S t a n d a r d C o m p a n i e s P r o f e s s o r o f O p e r a t i o n s M a n a g e m e n t S a ï d B u s i n e s s S c h o o l U n i v e r s </x:v>
@@ -9765,11 +9945,17 @@
       <x:c r="I259" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J259" s="33"/>
-      <x:c r="K259" s="33"/>
-      <x:c r="L259" s="33"/>
+      <x:c r="J259" s="33" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="K259" s="33" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="L259" s="33" t="n">
+        <x:v>15</x:v>
+      </x:c>
       <x:c r="M259" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/FWGA4AWODSM4</x:v>
       </x:c>
     </x:row>
     <x:row r="260">
@@ -9780,10 +9966,10 @@
         <x:v>Said-Oxford-Coursera_Specialization AI for Business_Certificate_FWGA4AWODSM4.pdf</x:v>
       </x:c>
       <x:c r="C260" s="32" t="str">
-        <x:v>Said</x:v>
+        <x:v>Saïd Business School, University of Oxford</x:v>
       </x:c>
       <x:c r="D260" s="32" t="str">
-        <x:v>Said-Oxford-Coursera_Specialization AI for Business_Certificate_FWGA4AWODSM4</x:v>
+        <x:v>AI for Business</x:v>
       </x:c>
       <x:c r="E260" s="32" t="str">
         <x:v>3 C o u r s e s A I E s s e n t i a l s G e n e r a t i v e a n d A g e n t i c A I A I G o v e r n a n c e M a t t h i a s H o l w e g A m e r i c a n S t a n d a r d C o m p a n i e s P r o f e s s o r o f O p e r a t i o n s M a n a g e m e n t S a ï d B u s i n e s s S c h o o l U n i v e r s i t y o f O x f o r d A u g 1 4 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o h a s s u c c e s s f u l l y c o m p l e t e d t h e o n l i n e S p e c i a l i z a t i o n A I F o u n d a t i o n </x:v>
@@ -9802,7 +9988,7 @@
       <x:c r="K260" s="33"/>
       <x:c r="L260" s="33"/>
       <x:c r="M260" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/specialization/FWGA4AWODSM4</x:v>
       </x:c>
     </x:row>
     <x:row r="261">
@@ -10397,10 +10583,10 @@
         <x:v>Stanford-Coursera RYUIMPUS3ZLR_Intro to Healthcare_Certificate.pdf</x:v>
       </x:c>
       <x:c r="C277" s="32" t="str">
-        <x:v>Stanford</x:v>
+        <x:v>Stanford Online / Stanford Medicine</x:v>
       </x:c>
       <x:c r="D277" s="32" t="str">
-        <x:v>Stanford-Coursera RYUIMPUS3ZLR_Intro to Healthcare_Certificate</x:v>
+        <x:v>Introduction to Healthcare</x:v>
       </x:c>
       <x:c r="E277" s="32" t="str">
         <x:v>J u l 2 8 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o I n t r o d u c t i o n t o H e a l t h c a r e a n o n l i n e c o u r s e a u t h o r i z e d b y S t a n f o r d U n i v e r s i t y a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d L a u r e n c e B a k e r , M i l d r e d C h o , N i g a m S h a h V e r i f y a t : h t t p s : / / c o u r s e r a . o r g / v e r i f y / R Y U I M P U S 3 Z L R C o u r s e r a h a s c o n f i r m e </x:v>
@@ -10415,11 +10601,17 @@
       <x:c r="I277" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J277" s="33"/>
-      <x:c r="K277" s="33"/>
-      <x:c r="L277" s="33"/>
+      <x:c r="J277" s="33" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="K277" s="33" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="L277" s="33" t="n">
+        <x:v>12</x:v>
+      </x:c>
       <x:c r="M277" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/RYUIMPUS3ZLR</x:v>
       </x:c>
     </x:row>
     <x:row r="278">
@@ -10430,10 +10622,10 @@
         <x:v>Stanford-Coursera_AI in Healthcare Capstone Certificate_9L3NBFUCKU4Q.pdf</x:v>
       </x:c>
       <x:c r="C278" s="32" t="str">
-        <x:v>Stanford</x:v>
+        <x:v>Stanford Online / Stanford Medicine</x:v>
       </x:c>
       <x:c r="D278" s="32" t="str">
-        <x:v>Stanford-Coursera_AI in Healthcare Capstone Certificate_9L3NBFUCKU4Q</x:v>
+        <x:v>AI in Healthcare Capstone</x:v>
       </x:c>
       <x:c r="E278" s="32" t="str">
         <x:v>A u g 2 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o A I i n H e a l t h c a r e C a p s t o n e a n o n l i n e c o u r s e a u t h o r i z e d b y S t a n f o r d U n i v e r s i t y a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d L a u r e n c e B a k e r , M a t t h e w L u n g r e n , N i g a m S h a h , S e r e n a Y e u n g a n d T i n a H e r n a n d e z - B o u s s a r d V e r i f y a t : h t t p s : / / c o u r s e r a . o r g / </x:v>
@@ -10448,11 +10640,17 @@
       <x:c r="I278" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J278" s="33"/>
-      <x:c r="K278" s="33"/>
-      <x:c r="L278" s="33"/>
+      <x:c r="J278" s="33" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K278" s="33" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L278" s="33" t="n">
+        <x:v>10</x:v>
+      </x:c>
       <x:c r="M278" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/9L3NBFUCKU4Q</x:v>
       </x:c>
     </x:row>
     <x:row r="279">
@@ -10463,10 +10661,10 @@
         <x:v>Stanford-Coursera_AI in Healthcare Specialization Certificate_7GM7A9EIJ9W4.pdf</x:v>
       </x:c>
       <x:c r="C279" s="32" t="str">
-        <x:v>Stanford</x:v>
+        <x:v>Stanford Online / Stanford Medicine</x:v>
       </x:c>
       <x:c r="D279" s="32" t="str">
-        <x:v>Stanford-Coursera_AI in Healthcare Specialization Certificate_7GM7A9EIJ9W4</x:v>
+        <x:v>AI in Healthcare</x:v>
       </x:c>
       <x:c r="E279" s="32" t="str">
         <x:v>5 C o u r s e s I n t r o d u c t i o n t o H e a l t h c a r e I n t r o d u c t i o n t o C l i n i c a l D a t a F u n d a m e n t a l s o f M a c h i n e L e a r n i n g f o r H e a l t h c a r e E v a l u a t i o n s o f A I A p p l i c a t i o n s i n H e a l t h c a r e A I i n H e a l t h c a r e C a p s t o n e N i g a m H . S h a h , M B B S , P h D A s s o c i a t e P r o f e s s o r o f M e d i c i n e ( B i o m e d i c a l I n f o r m a t i c s ) A u g 2 , 2 0 2 6 P e d r o L a m o </x:v>
@@ -10481,11 +10679,17 @@
       <x:c r="I279" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J279" s="33"/>
-      <x:c r="K279" s="33"/>
-      <x:c r="L279" s="33"/>
+      <x:c r="J279" s="33" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="K279" s="33" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="L279" s="33" t="n">
+        <x:v>40</x:v>
+      </x:c>
       <x:c r="M279" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/specialization/7GM7A9EIJ9W4; estimativa derivada do tempo exibido: 1 meses com 10 por semana para concluir</x:v>
       </x:c>
     </x:row>
     <x:row r="280">
@@ -10496,10 +10700,10 @@
         <x:v>Stanford-Coursera_Certificate_Fundamentals of ML in HC_MYZ6GPXEFO5H.pdf</x:v>
       </x:c>
       <x:c r="C280" s="32" t="str">
-        <x:v>Stanford</x:v>
+        <x:v>Stanford Online / Stanford Medicine</x:v>
       </x:c>
       <x:c r="D280" s="32" t="str">
-        <x:v>Stanford-Coursera_Certificate_Fundamentals of ML in HC_MYZ6GPXEFO5H</x:v>
+        <x:v>Fundamentals of Machine Learning for Healthcare</x:v>
       </x:c>
       <x:c r="E280" s="32" t="str">
         <x:v>A u g 1 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o F u n d a m e n t a l s o f M a c h i n e L e a r n i n g f o r H e a l t h c a r e a n o n l i n e c o u r s e a u t h o r i z e d b y S t a n f o r d U n i v e r s i t y a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d M a t t h e w L u n g r e n A s s o c i a t e P r o f e s s o r D e p a r t m e n t o f R a d i o l o g y S e r e n a Y e u n g A s s i s t a n t P r o f e s s o r B i o </x:v>
@@ -10515,15 +10719,17 @@
         <x:v>Extraído do documento</x:v>
       </x:c>
       <x:c r="J280" s="33" t="n">
-        <x:v>5</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K280" s="33" t="n">
-        <x:v>5</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="L280" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="M280" s="32" t="str"/>
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="M280" s="32" t="str">
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/MYZ6GPXEFO5H</x:v>
+      </x:c>
     </x:row>
     <x:row r="281">
       <x:c r="A281" s="32" t="n">
@@ -10533,10 +10739,10 @@
         <x:v>Stanford-Coursera_Evaluations of AI in HC_Certificate_DW8FFD7QA2IZ.pdf</x:v>
       </x:c>
       <x:c r="C281" s="32" t="str">
-        <x:v>Stanford</x:v>
+        <x:v>Stanford Online / Stanford Medicine</x:v>
       </x:c>
       <x:c r="D281" s="32" t="str">
-        <x:v>Stanford-Coursera_Evaluations of AI in HC_Certificate_DW8FFD7QA2IZ</x:v>
+        <x:v>Evaluations of AI Applications in Healthcare</x:v>
       </x:c>
       <x:c r="E281" s="32" t="str">
         <x:v>A u g 1 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o E v a l u a t i o n s o f A I A p p l i c a t i o n s i n H e a l t h c a r e a n o n l i n e c o u r s e a u t h o r i z e d b y S t a n f o r d U n i v e r s i t y a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d T i n a H e r n a n d e z - B o u s s a r d A s s o c i a t e P r o f e s s o r M e d i c i n e ( B i o m e d i c a l I n f o r m a t i c s ) , o f B i o m e d i c a l D a t a </x:v>
@@ -10551,11 +10757,17 @@
       <x:c r="I281" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J281" s="33"/>
-      <x:c r="K281" s="33"/>
-      <x:c r="L281" s="33"/>
+      <x:c r="J281" s="33" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="K281" s="33" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L281" s="33" t="n">
+        <x:v>11</x:v>
+      </x:c>
       <x:c r="M281" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/DW8FFD7QA2IZ</x:v>
       </x:c>
     </x:row>
     <x:row r="282">
@@ -10636,10 +10848,10 @@
         <x:v>Stanford-Coursera_PCA Specialization Certificate E8700K9GB2WD.pdf</x:v>
       </x:c>
       <x:c r="C284" s="32" t="str">
-        <x:v>Stanford</x:v>
+        <x:v>Stanford Online / Stanford Medicine</x:v>
       </x:c>
       <x:c r="D284" s="32" t="str">
-        <x:v>Stanford-Coursera_PCA Specialization Certificate E8700K9GB2WD</x:v>
+        <x:v>Palliative Care Always</x:v>
       </x:c>
       <x:c r="E284" s="32" t="str">
         <x:v>5 C o u r s e s E s s e n t i a l s o f P a l l i a t i v e C a r e S y m p t o m M a n a g e m e n t i n P a l l i a t i v e C a r e T r a n s i t i o n s i n C a r e f r o m S u r v i v o r s h i p t o H o s p i c e S u p p o r t i n g F a m i l i e s a n d C a r e g i v e r s P a l l i a t i v e C a r e A l w a y s C a p s t o n e C o u r s e K a v i t h a R a m c h a n d r a n M D , C l i n i c a l A s s o c i a t e P r o f e s s o r , S t a n f o r d M e d i c i n e A u g 3 0 , 2 0 2 6 P e </x:v>
@@ -10654,11 +10866,17 @@
       <x:c r="I284" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J284" s="33"/>
-      <x:c r="K284" s="33"/>
-      <x:c r="L284" s="33"/>
+      <x:c r="J284" s="33" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="K284" s="33" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="L284" s="33" t="n">
+        <x:v>40</x:v>
+      </x:c>
       <x:c r="M284" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/specialization/E8700K9GB2WD; estimativa derivada do tempo exibido: 1 meses com 10 por semana para concluir</x:v>
       </x:c>
     </x:row>
     <x:row r="285">
@@ -10669,10 +10887,10 @@
         <x:v>Stanford-Coursera_Supporting Caregiver Health_Certificate_O8W0ZHG0J5II.pdf</x:v>
       </x:c>
       <x:c r="C285" s="32" t="str">
-        <x:v>Stanford</x:v>
+        <x:v>Stanford Online / Stanford Medicine</x:v>
       </x:c>
       <x:c r="D285" s="32" t="str">
-        <x:v>Stanford-Coursera_Supporting Caregiver Health_Certificate_O8W0ZHG0J5II</x:v>
+        <x:v>Supporting Families and Caregivers</x:v>
       </x:c>
       <x:c r="E285" s="32" t="str">
         <x:v>A u g 3 0 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o S u p p o r t i n g F a m i l i e s a n d C a r e g i v e r s a n o n l i n e c o u r s e a u t h o r i z e d b y S t a n f o r d O n l i n e a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d K a v i t h a R a m c h a n d r a n C l i n i c a l A s s o c i a t e P r o f e s s o r O n c o l o g y J a n D e N o f r i o P h D P r o g r a m M a n a g e r P a l l i a t i v e C a r e A l w a y </x:v>
@@ -10687,11 +10905,17 @@
       <x:c r="I285" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J285" s="33"/>
-      <x:c r="K285" s="33"/>
-      <x:c r="L285" s="33"/>
+      <x:c r="J285" s="33" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K285" s="33" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L285" s="33" t="n">
+        <x:v>10</x:v>
+      </x:c>
       <x:c r="M285" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/O8W0ZHG0J5II</x:v>
       </x:c>
     </x:row>
     <x:row r="286">
@@ -10702,10 +10926,10 @@
         <x:v>Stanford-Coursera_Symptom Management_CertificateLYD5V9AWXRXS.pdf</x:v>
       </x:c>
       <x:c r="C286" s="32" t="str">
-        <x:v>Stanford</x:v>
+        <x:v>Stanford Online / Stanford Medicine</x:v>
       </x:c>
       <x:c r="D286" s="32" t="str">
-        <x:v>Stanford-Coursera_Symptom Management_CertificateLYD5V9AWXRXS</x:v>
+        <x:v>Symptom Management in Palliative Care</x:v>
       </x:c>
       <x:c r="E286" s="32" t="str">
         <x:v>A u g 2 9 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o S y m p t o m M a n a g e m e n t i n P a l l i a t i v e C a r e a n o n l i n e c o u r s e a u t h o r i z e d b y S t a n f o r d O n l i n e a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d J a n D e N o f r i o , J o s h u a F r o n k , K a v i t h a R a m c h a n d r a n , M a n u e l a K o g o n V e r i f y a t : h t t p s : / / c o u r s e r a . o r g / v e r i f y / L Y D 5 V </x:v>
@@ -10720,11 +10944,17 @@
       <x:c r="I286" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J286" s="33"/>
-      <x:c r="K286" s="33"/>
-      <x:c r="L286" s="33"/>
+      <x:c r="J286" s="33" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K286" s="33" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="L286" s="33" t="n">
+        <x:v>9</x:v>
+      </x:c>
       <x:c r="M286" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/LYD5V9AWXRXS</x:v>
       </x:c>
     </x:row>
     <x:row r="287">
@@ -10805,10 +11035,10 @@
         <x:v>Stanfrod-Coursera_Supporting families and caregivers Certificate_O8W0ZHG0J5II.pdf</x:v>
       </x:c>
       <x:c r="C289" s="32" t="str">
-        <x:v>Stanfrod</x:v>
+        <x:v>Stanford Online / Stanford Medicine</x:v>
       </x:c>
       <x:c r="D289" s="32" t="str">
-        <x:v>Stanfrod-Coursera_Supporting families and caregivers Certificate_O8W0ZHG0J5II</x:v>
+        <x:v>Supporting Families and Caregivers</x:v>
       </x:c>
       <x:c r="E289" s="32" t="str">
         <x:v>A u g 3 0 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o S u p p o r t i n g F a m i l i e s a n d C a r e g i v e r s a n o n l i n e c o u r s e a u t h o r i z e d b y S t a n f o r d O n l i n e a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d K a v i t h a R a m c h a n d r a n C l i n i c a l A s s o c i a t e P r o f e s s o r O n c o l o g y J a n D e N o f r i o P h D P r o g r a m M a n a g e r P a l l i a t i v e C a r e A l w a y </x:v>
@@ -10823,11 +11053,17 @@
       <x:c r="I289" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J289" s="33"/>
-      <x:c r="K289" s="33"/>
-      <x:c r="L289" s="33"/>
+      <x:c r="J289" s="33" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K289" s="33" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L289" s="33" t="n">
+        <x:v>10</x:v>
+      </x:c>
       <x:c r="M289" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/O8W0ZHG0J5II</x:v>
       </x:c>
     </x:row>
     <x:row r="290">
@@ -11234,10 +11470,10 @@
         <x:v>U-M-Coursera_Translating Research to communities Certificate_WWZOYLD9AB26.pdf</x:v>
       </x:c>
       <x:c r="C302" s="32" t="str">
-        <x:v>U</x:v>
+        <x:v>University of Michigan</x:v>
       </x:c>
       <x:c r="D302" s="32" t="str">
-        <x:v>U-M-Coursera_Translating Research to communities Certificate_WWZOYLD9AB26</x:v>
+        <x:v>Translating Research to Communities</x:v>
       </x:c>
       <x:c r="E302" s="32" t="str">
         <x:v>A u g 2 9 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o T r a n s l a t i n g R e s e a r c h t o C o m m u n i t i e s a n o n l i n e c o u r s e a u t h o r i z e d b y U n i v e r s i t y o f M i c h i g a n a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d V i c k i E l l i n g r o d J o h n G i d e o n S e a r l e P r o f e s s o r o f P h a r m a c y , D e a n ; P r o f e s s o r o f P s y c h i a t r y C o l l e g e o f P h a r m a c </x:v>
@@ -11252,11 +11488,17 @@
       <x:c r="I302" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J302" s="33"/>
-      <x:c r="K302" s="33"/>
-      <x:c r="L302" s="33"/>
+      <x:c r="J302" s="33" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K302" s="33" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L302" s="33" t="n">
+        <x:v>6</x:v>
+      </x:c>
       <x:c r="M302" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/WWZOYLD9AB26</x:v>
       </x:c>
     </x:row>
     <x:row r="303">
@@ -11267,10 +11509,10 @@
         <x:v>U-M-Coursera_Translating Research to Patients Certificate_IKDNWXUCALFA.pdf</x:v>
       </x:c>
       <x:c r="C303" s="32" t="str">
-        <x:v>U</x:v>
+        <x:v>University of Michigan</x:v>
       </x:c>
       <x:c r="D303" s="32" t="str">
-        <x:v>U-M-Coursera_Translating Research to Patients Certificate_IKDNWXUCALFA</x:v>
+        <x:v>Translating Research to Patients</x:v>
       </x:c>
       <x:c r="E303" s="32" t="str">
         <x:v>A u g 2 9 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o T r a n s l a t i n g R e s e a r c h t o P a t i e n t s a n o n l i n e c o u r s e a u t h o r i z e d b y U n i v e r s i t y o f M i c h i g a n a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d V i c k i E l l i n g r o d J o h n G i d e o n S e a r l e P r o f e s s o r o f P h a r m a c y , D e a n ; P r o f e s s o r o f P s y c h i a t r y C o l l e g e o f P h a r m a c y , M </x:v>
@@ -11285,11 +11527,17 @@
       <x:c r="I303" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J303" s="33"/>
-      <x:c r="K303" s="33"/>
-      <x:c r="L303" s="33"/>
+      <x:c r="J303" s="33" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K303" s="33" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L303" s="33" t="n">
+        <x:v>6</x:v>
+      </x:c>
       <x:c r="M303" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/IKDNWXUCALFA</x:v>
       </x:c>
     </x:row>
     <x:row r="304">
@@ -11300,10 +11548,10 @@
         <x:v>U-M-Coursera_Translating Research to Policy Certificate_0HXUUQIWD1P7.pdf</x:v>
       </x:c>
       <x:c r="C304" s="32" t="str">
-        <x:v>U</x:v>
+        <x:v>University of Michigan</x:v>
       </x:c>
       <x:c r="D304" s="32" t="str">
-        <x:v>U-M-Coursera_Translating Research to Policy Certificate_0HXUUQIWD1P7</x:v>
+        <x:v>Translating Research to Healthcare Policy</x:v>
       </x:c>
       <x:c r="E304" s="32" t="str">
         <x:v>A u g 2 9 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o T r a n s l a t i n g R e s e a r c h t o H e a l t h c a r e P o l i c y a n o n l i n e c o u r s e a u t h o r i z e d b y U n i v e r s i t y o f M i c h i g a n a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d V i c k i E l l i n g r o d J o h n G i d e o n S e a r l e P r o f e s s o r o f P h a r m a c y , D e a n ; P r o f e s s o r o f P s y c h i a t r y C o l l e g e o f P h </x:v>
@@ -11319,15 +11567,17 @@
         <x:v>Extraído do documento</x:v>
       </x:c>
       <x:c r="J304" s="33" t="n">
-        <x:v>0</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="K304" s="33" t="n">
-        <x:v>0</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="L304" s="33" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M304" s="32" t="str"/>
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="M304" s="32" t="str">
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/0HXUUQIWD1P7</x:v>
+      </x:c>
     </x:row>
     <x:row r="305">
       <x:c r="A305" s="32" t="n">
@@ -11337,10 +11587,10 @@
         <x:v>U-M-Coursera_Translational Research for humans_Certificate 7MIVPFC1VTQR.pdf</x:v>
       </x:c>
       <x:c r="C305" s="32" t="str">
-        <x:v>U</x:v>
+        <x:v>University of Michigan</x:v>
       </x:c>
       <x:c r="D305" s="32" t="str">
-        <x:v>U-M-Coursera_Translational Research for humans_Certificate 7MIVPFC1VTQR</x:v>
+        <x:v>Translating Basic Research into Research for Humans</x:v>
       </x:c>
       <x:c r="E305" s="32" t="str">
         <x:v>A u g 1 3 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o T r a n s l a t i n g B a s i c R e s e a r c h i n t o R e s e a r c h f o r H u m a n s a n o n l i n e c o u r s e a u t h o r i z e d b y U n i v e r s i t y o f M i c h i g a n a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d V i c k i E l l i n g r o d S e n i o r A s s o c i a t e D e a n C o l l e g e o f P h a r m a c y V e r i f y a t : h t t p s : / / c o u r s e r a . o r g </x:v>
@@ -11355,11 +11605,17 @@
       <x:c r="I305" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J305" s="33"/>
-      <x:c r="K305" s="33"/>
-      <x:c r="L305" s="33"/>
+      <x:c r="J305" s="33" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K305" s="33" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="L305" s="33" t="n">
+        <x:v>4</x:v>
+      </x:c>
       <x:c r="M305" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/7MIVPFC1VTQR</x:v>
       </x:c>
     </x:row>
     <x:row r="306">
@@ -11370,10 +11626,10 @@
         <x:v>U-M-Coursera_Translational Science Specialization Certificate_IXQRUXCLXP3K.pdf</x:v>
       </x:c>
       <x:c r="C306" s="32" t="str">
-        <x:v>U</x:v>
+        <x:v>University of Michigan</x:v>
       </x:c>
       <x:c r="D306" s="32" t="str">
-        <x:v>U-M-Coursera_Translational Science Specialization Certificate_IXQRUXCLXP3K</x:v>
+        <x:v>Translational Science</x:v>
       </x:c>
       <x:c r="E306" s="32" t="str">
         <x:v>5 C o u r s e s I n t r o d u c t i o n t o T r a n s l a t i o n a l S c i e n c e T r a n s l a t i n g B a s i c R e s e a r c h i n t o R e s e a r c h f o r H u m a n s T r a n s l a t i n g R e s e a r c h t o P a t i e n t s T r a n s l a t i n g R e s e a r c h t o C o m m u n i t i e s T r a n s l a t i n g R e s e a r c h t o H e a l t h c a r e P o l i c y V i c k i E l l i n g r o d S e n i o r A s s o c i a t e D e a n C o l l e g e o f P h a r m a c y A u g 2 9 , 2 0 2 6 P e d r o </x:v>
@@ -11388,11 +11644,17 @@
       <x:c r="I306" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J306" s="33"/>
-      <x:c r="K306" s="33"/>
-      <x:c r="L306" s="33"/>
+      <x:c r="J306" s="33" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="K306" s="33" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="L306" s="33" t="n">
+        <x:v>40</x:v>
+      </x:c>
       <x:c r="M306" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/specialization/IXQRUXCLXP3K; estimativa derivada do tempo exibido: 1 meses com 10 por semana para concluir</x:v>
       </x:c>
     </x:row>
     <x:row r="307">
@@ -12020,10 +12282,10 @@
         <x:v>Yale-Coursera_Global Health Essentials_Certificate_YJ26WLVD3O3K.pdf</x:v>
       </x:c>
       <x:c r="C326" s="32" t="str">
-        <x:v>Yale</x:v>
+        <x:v>Yale University</x:v>
       </x:c>
       <x:c r="D326" s="32" t="str">
-        <x:v>Yale-Coursera_Global Health Essentials_Certificate_YJ26WLVD3O3K</x:v>
+        <x:v>Essentials of Global Health</x:v>
       </x:c>
       <x:c r="E326" s="32" t="str">
         <x:v>A u g 5 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o E s s e n t i a l s o f G l o b a l H e a l t h a n o n l i n e c o u r s e a u t h o r i z e d b y Y a l e U n i v e r s i t y a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d R i c h a r d S k o l n i k F o r m e r L e c t u r e r , D e p a r t m e n t o f H e a l t h P o l i c y a n d M a n a g e m e n t , Y a l e S c h o o l o f P u b l i c H e a l t h a n d L e c t u r e r i n t h e </x:v>
@@ -12038,11 +12300,17 @@
       <x:c r="I326" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J326" s="33"/>
-      <x:c r="K326" s="33"/>
-      <x:c r="L326" s="33"/>
+      <x:c r="J326" s="33" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="K326" s="33" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="L326" s="33" t="n">
+        <x:v>39</x:v>
+      </x:c>
       <x:c r="M326" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/YJ26WLVD3O3K</x:v>
       </x:c>
     </x:row>
     <x:row r="327">
@@ -12084,7 +12352,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R04c05768bace4641"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5633b7ec466c4e6b"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/ACG_UNIFENAS_Medicina.xlsx
+++ b/ACG_UNIFENAS_Medicina.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo" sheetId="1" r:id="Rbcb49d509f77490b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regras UNIFENAS" sheetId="2" r:id="R27aab66ab4c64650"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Certificados" sheetId="3" r:id="Rcf6dbe21f640464a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Excluídos" sheetId="4" r:id="R17671312f80c41f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pendências" sheetId="5" r:id="R4a2acac1b43f46e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo" sheetId="1" r:id="Ra631a2d5b6394eb0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regras UNIFENAS" sheetId="2" r:id="R5a707d50ea9847da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Certificados" sheetId="3" r:id="Rfcbc544967a34355"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Excluídos" sheetId="4" r:id="R4adeef002cf248c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pendências" sheetId="5" r:id="Rd7e2c3b14c65472e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -203,7 +203,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CertificadosTable" displayName="CertificadosTable" ref="A2:M327" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CertificadosTable" displayName="CertificadosTable" ref="A2:M326" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="Controle"/>
     <x:tableColumn id="2" name="Arquivo original"/>
@@ -466,7 +466,7 @@
       </x:c>
       <x:c r="B6" s="16" t="n">
         <x:f>SUM('Certificados'!$J$2:$J$389)</x:f>
-        <x:v>2084.5</x:v>
+        <x:v>2110.5</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -475,7 +475,7 @@
       </x:c>
       <x:c r="B7" s="16" t="n">
         <x:f>SUM('Certificados'!$K$2:$K$389)</x:f>
-        <x:v>2084.5</x:v>
+        <x:v>2110.5</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -484,7 +484,7 @@
       </x:c>
       <x:c r="B8" s="16" t="n">
         <x:f>B3-B7</x:f>
-        <x:v>-1634.5</x:v>
+        <x:v>-1660.5</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -493,7 +493,7 @@
       </x:c>
       <x:c r="B9" s="16" t="n">
         <x:f>COUNTIF('Certificados'!$G$2:$G$389,"&lt;&gt;")</x:f>
-        <x:v>326</x:v>
+        <x:v>325</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -519,11 +519,11 @@
       </x:c>
       <x:c r="C12" s="30" t="n">
         <x:f>SUMIF('Certificados'!$G$2:$G$389,A12,'Certificados'!$J$2:$J$389)</x:f>
-        <x:v>1410.25</x:v>
+        <x:v>1436.25</x:v>
       </x:c>
       <x:c r="D12" s="30" t="n">
         <x:f>SUMIF('Certificados'!$G$2:$G$389,A12,'Certificados'!$K$2:$K$389)</x:f>
-        <x:v>1410.25</x:v>
+        <x:v>1436.25</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -8201,17 +8201,15 @@
         <x:v>206</x:v>
       </x:c>
       <x:c r="B208" s="32" t="str">
-        <x:v>Pedido de Restituição Coursera 2026.07.pdf</x:v>
+        <x:v>Pedro Lamounier Sampaio - CV 2.pdf</x:v>
       </x:c>
       <x:c r="C208" s="32" t="str">
-        <x:v>Pedido de Restituição Coursera 2026.07</x:v>
+        <x:v>Pedro Lamounier Sampaio</x:v>
       </x:c>
       <x:c r="D208" s="32" t="str">
-        <x:v>Pedido de Restituição Coursera 2026.07</x:v>
-      </x:c>
-      <x:c r="E208" s="32" t="str">
-        <x:v>You're all setYou're all setYou're all setYou're all set You’ve submitted Case 06393611 (/s/my-cases?caseId=500VN00000ztsrDYAQ) to Coursera Support. View your case, get updates, and reply from your My Support Cases page. ( ( ( (/s/s/s/s)))) Go to My Support CasesGo to My Support CasesGo to My Support CasesGo to My Support Cases</x:v>
-      </x:c>
+        <x:v>Pedro Lamounier Sampaio - CV 2</x:v>
+      </x:c>
+      <x:c r="E208" s="32" t="str"/>
       <x:c r="F208" s="32" t="str"/>
       <x:c r="G208" s="32" t="str">
         <x:v>Grupo 1 — Ensino</x:v>
@@ -8220,7 +8218,7 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="I208" s="32" t="str">
-        <x:v>Extraído do documento</x:v>
+        <x:v>Sem texto extraível — revisão manual</x:v>
       </x:c>
       <x:c r="J208" s="33"/>
       <x:c r="K208" s="33"/>
@@ -8234,15 +8232,17 @@
         <x:v>207</x:v>
       </x:c>
       <x:c r="B209" s="32" t="str">
-        <x:v>Pedro Lamounier Sampaio - CV 2.pdf</x:v>
+        <x:v>Pedro Lamounier Sampaio - PDF Certificate (ISO 19011 Lead Auditor).pdf</x:v>
       </x:c>
       <x:c r="C209" s="32" t="str">
         <x:v>Pedro Lamounier Sampaio</x:v>
       </x:c>
       <x:c r="D209" s="32" t="str">
-        <x:v>Pedro Lamounier Sampaio - CV 2</x:v>
-      </x:c>
-      <x:c r="E209" s="32" t="str"/>
+        <x:v>Pedro Lamounier Sampaio - PDF Certificate (ISO 19011 Lead Auditor)</x:v>
+      </x:c>
+      <x:c r="E209" s="32" t="str">
+        <x:v>This is to certify that Pedro Lamounier Sampaio has successfully demonstrated proficient comprehension in the course of ISO 19011 Lead Auditor and is therefore awarded this qualification with Distinction on 15th June, 2026.</x:v>
+      </x:c>
       <x:c r="F209" s="32" t="str"/>
       <x:c r="G209" s="32" t="str">
         <x:v>Grupo 1 — Ensino</x:v>
@@ -8251,7 +8251,7 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="I209" s="32" t="str">
-        <x:v>Sem texto extraível — revisão manual</x:v>
+        <x:v>Extraído do documento</x:v>
       </x:c>
       <x:c r="J209" s="33"/>
       <x:c r="K209" s="33"/>
@@ -8265,17 +8265,15 @@
         <x:v>208</x:v>
       </x:c>
       <x:c r="B210" s="32" t="str">
-        <x:v>Pedro Lamounier Sampaio - PDF Certificate (ISO 19011 Lead Auditor).pdf</x:v>
+        <x:v>Pedro Lamounier Sampaio _ LinkedIn_Duolingo LVL128.pdf</x:v>
       </x:c>
       <x:c r="C210" s="32" t="str">
         <x:v>Pedro Lamounier Sampaio</x:v>
       </x:c>
       <x:c r="D210" s="32" t="str">
-        <x:v>Pedro Lamounier Sampaio - PDF Certificate (ISO 19011 Lead Auditor)</x:v>
-      </x:c>
-      <x:c r="E210" s="32" t="str">
-        <x:v>This is to certify that Pedro Lamounier Sampaio has successfully demonstrated proficient comprehension in the course of ISO 19011 Lead Auditor and is therefore awarded this qualification with Distinction on 15th June, 2026.</x:v>
-      </x:c>
+        <x:v>Pedro Lamounier Sampaio _ LinkedIn_Duolingo LVL128</x:v>
+      </x:c>
+      <x:c r="E210" s="32" t="str"/>
       <x:c r="F210" s="32" t="str"/>
       <x:c r="G210" s="32" t="str">
         <x:v>Grupo 1 — Ensino</x:v>
@@ -8284,7 +8282,7 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="I210" s="32" t="str">
-        <x:v>Extraído do documento</x:v>
+        <x:v>Sem texto extraível — revisão manual</x:v>
       </x:c>
       <x:c r="J210" s="33"/>
       <x:c r="K210" s="33"/>
@@ -8298,15 +8296,17 @@
         <x:v>209</x:v>
       </x:c>
       <x:c r="B211" s="32" t="str">
-        <x:v>Pedro Lamounier Sampaio _ LinkedIn_Duolingo LVL128.pdf</x:v>
+        <x:v>Pedro Lamounier Sampaio ACLS (Advanced Cardiac Life Support) Online Course Completion Certificate 2026.pdf</x:v>
       </x:c>
       <x:c r="C211" s="32" t="str">
-        <x:v>Pedro Lamounier Sampaio</x:v>
+        <x:v>Pedro Lamounier Sampaio ACLS (Advanced Cardiac Life Support) Online Course Completion Certificate 2026</x:v>
       </x:c>
       <x:c r="D211" s="32" t="str">
-        <x:v>Pedro Lamounier Sampaio _ LinkedIn_Duolingo LVL128</x:v>
-      </x:c>
-      <x:c r="E211" s="32" t="str"/>
+        <x:v>Pedro Lamounier Sampaio ACLS (Advanced Cardiac Life Support) Online Course Completion Certificate 2026</x:v>
+      </x:c>
+      <x:c r="E211" s="32" t="str">
+        <x:v>A D V A N C E D C A R D I A C L I F E S U P P O R T A d v a n c e d M e d i c a l C e r t i f i c a t i o n ™ T r a i n i n g O r g a n i z a t i o n N a m e A d v a n c e d M e d i c a l C e r t i f i c a t i o n T r a i n i n g O r g a n i z a t i o n C i t y , S t a t e J e f f e r s o n v i l l e , I n d i a n a T r a i n i n g O r g a n i z a t i o n T e l e p h o n e ( 8 6 6 ) 3 5 2 - 1 4 2 0 I n s t r u c t o r N a m e K a r l F . D i s q u e D . O . R P h I n s t r u c t o r S i g n a t </x:v>
+      </x:c>
       <x:c r="F211" s="32" t="str"/>
       <x:c r="G211" s="32" t="str">
         <x:v>Grupo 1 — Ensino</x:v>
@@ -8315,7 +8315,7 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="I211" s="32" t="str">
-        <x:v>Sem texto extraível — revisão manual</x:v>
+        <x:v>Extraído do documento</x:v>
       </x:c>
       <x:c r="J211" s="33"/>
       <x:c r="K211" s="33"/>
@@ -8329,16 +8329,16 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="B212" s="32" t="str">
-        <x:v>Pedro Lamounier Sampaio ACLS (Advanced Cardiac Life Support) Online Course Completion Certificate 2026.pdf</x:v>
+        <x:v>Pedro Lamounier Sampaio ACLS Course Completion Certificate.pdf</x:v>
       </x:c>
       <x:c r="C212" s="32" t="str">
-        <x:v>Pedro Lamounier Sampaio ACLS (Advanced Cardiac Life Support) Online Course Completion Certificate 2026</x:v>
+        <x:v>Pedro Lamounier Sampaio ACLS Course Completion Certificate</x:v>
       </x:c>
       <x:c r="D212" s="32" t="str">
-        <x:v>Pedro Lamounier Sampaio ACLS (Advanced Cardiac Life Support) Online Course Completion Certificate 2026</x:v>
+        <x:v>Pedro Lamounier Sampaio ACLS Course Completion Certificate</x:v>
       </x:c>
       <x:c r="E212" s="32" t="str">
-        <x:v>A D V A N C E D C A R D I A C L I F E S U P P O R T A d v a n c e d M e d i c a l C e r t i f i c a t i o n ™ T r a i n i n g O r g a n i z a t i o n N a m e A d v a n c e d M e d i c a l C e r t i f i c a t i o n T r a i n i n g O r g a n i z a t i o n C i t y , S t a t e J e f f e r s o n v i l l e , I n d i a n a T r a i n i n g O r g a n i z a t i o n T e l e p h o n e ( 8 6 6 ) 3 5 2 - 1 4 2 0 I n s t r u c t o r N a m e K a r l F . D i s q u e D . O . R P h I n s t r u c t o r S i g n a t </x:v>
+        <x:v>C o m p l e t i o n d a t e : K a r l F . D i s q u e D . O . R P h A d v a n c e d C a r d i a c L i f e S u p p o r t C o u r s e T h i s c e r t i f i c a t e c e r t i f i e s t h a t t h e i n d i v i d u a l l i s t e d a b o v e h a s s u c c e s s f u l l y c o m p l e t e d t h e A d v a n c e d C a r d i a c L i f e S u p p o r t ( A C L S ) C o u r s e i n a c c o r d a n c e w i t h t h e c u r r i c u l u m o f S a v e a L i f e . c o m , e m p o w e r e d b y A d v a n c e d M e d </x:v>
       </x:c>
       <x:c r="F212" s="32" t="str"/>
       <x:c r="G212" s="32" t="str">
@@ -8362,16 +8362,16 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B213" s="32" t="str">
-        <x:v>Pedro Lamounier Sampaio ACLS Course Completion Certificate.pdf</x:v>
+        <x:v>Pedro Lamounier Sampaio BLS (Basic Life Support) Online Course Completion Certificate 2026.pdf</x:v>
       </x:c>
       <x:c r="C213" s="32" t="str">
-        <x:v>Pedro Lamounier Sampaio ACLS Course Completion Certificate</x:v>
+        <x:v>Pedro Lamounier Sampaio BLS (Basic Life Support) Online Course Completion Certificate 2026</x:v>
       </x:c>
       <x:c r="D213" s="32" t="str">
-        <x:v>Pedro Lamounier Sampaio ACLS Course Completion Certificate</x:v>
+        <x:v>Pedro Lamounier Sampaio BLS (Basic Life Support) Online Course Completion Certificate 2026</x:v>
       </x:c>
       <x:c r="E213" s="32" t="str">
-        <x:v>C o m p l e t i o n d a t e : K a r l F . D i s q u e D . O . R P h A d v a n c e d C a r d i a c L i f e S u p p o r t C o u r s e T h i s c e r t i f i c a t e c e r t i f i e s t h a t t h e i n d i v i d u a l l i s t e d a b o v e h a s s u c c e s s f u l l y c o m p l e t e d t h e A d v a n c e d C a r d i a c L i f e S u p p o r t ( A C L S ) C o u r s e i n a c c o r d a n c e w i t h t h e c u r r i c u l u m o f S a v e a L i f e . c o m , e m p o w e r e d b y A d v a n c e d M e d </x:v>
+        <x:v>A d v a n c e d M e d i c a l C e r t i f i c a t i o n ™ T r a i n i n g O r g a n i z a t i o n N a m e A d v a n c e d M e d i c a l C e r t i f i c a t i o n T r a i n i n g O r g a n i z a t i o n C i t y , S t a t e J e f f e r s o n v i l l e , I n d i a n a T r a i n i n g O r g a n i z a t i o n T e l e p h o n e ( 8 6 6 ) 3 5 2 - 1 4 2 0 I n s t r u c t o r N a m e K a r l F . D i s q u e D . O . R P h I n s t r u c t o r S i g n a t u r e I s s u e D a t e R e n e w B y BLS Provider h</x:v>
       </x:c>
       <x:c r="F213" s="32" t="str"/>
       <x:c r="G213" s="32" t="str">
@@ -8395,16 +8395,16 @@
         <x:v>212</x:v>
       </x:c>
       <x:c r="B214" s="32" t="str">
-        <x:v>Pedro Lamounier Sampaio BLS (Basic Life Support) Online Course Completion Certificate 2026.pdf</x:v>
+        <x:v>Pedro Lamounier Sampaio- PDF Certificate (Advanced Cardiac Life Support (ACLS)).pdf</x:v>
       </x:c>
       <x:c r="C214" s="32" t="str">
-        <x:v>Pedro Lamounier Sampaio BLS (Basic Life Support) Online Course Completion Certificate 2026</x:v>
+        <x:v>Pedro Lamounier Sampaio</x:v>
       </x:c>
       <x:c r="D214" s="32" t="str">
-        <x:v>Pedro Lamounier Sampaio BLS (Basic Life Support) Online Course Completion Certificate 2026</x:v>
+        <x:v>Pedro Lamounier Sampaio- PDF Certificate (Advanced Cardiac Life Support (ACLS))</x:v>
       </x:c>
       <x:c r="E214" s="32" t="str">
-        <x:v>A d v a n c e d M e d i c a l C e r t i f i c a t i o n ™ T r a i n i n g O r g a n i z a t i o n N a m e A d v a n c e d M e d i c a l C e r t i f i c a t i o n T r a i n i n g O r g a n i z a t i o n C i t y , S t a t e J e f f e r s o n v i l l e , I n d i a n a T r a i n i n g O r g a n i z a t i o n T e l e p h o n e ( 8 6 6 ) 3 5 2 - 1 4 2 0 I n s t r u c t o r N a m e K a r l F . D i s q u e D . O . R P h I n s t r u c t o r S i g n a t u r e I s s u e D a t e R e n e w B y BLS Provider h</x:v>
+        <x:v>This is to certify that Pedro Lamounier Sampaio has successfully demonstrated proficient comprehension in the course of Advanced Cardiac Life Support (ACLS) and is therefore awarded this qualification with Distinction on 10th June, 2026.</x:v>
       </x:c>
       <x:c r="F214" s="32" t="str"/>
       <x:c r="G214" s="32" t="str">
@@ -8428,17 +8428,15 @@
         <x:v>213</x:v>
       </x:c>
       <x:c r="B215" s="32" t="str">
-        <x:v>Pedro Lamounier Sampaio- PDF Certificate (Advanced Cardiac Life Support (ACLS)).pdf</x:v>
+        <x:v>PEDRO_LAMOUNIER_SAMPAIO_Cybersecurity_Awareness_-_Production.pdf</x:v>
       </x:c>
       <x:c r="C215" s="32" t="str">
-        <x:v>Pedro Lamounier Sampaio</x:v>
+        <x:v>PEDRO</x:v>
       </x:c>
       <x:c r="D215" s="32" t="str">
-        <x:v>Pedro Lamounier Sampaio- PDF Certificate (Advanced Cardiac Life Support (ACLS))</x:v>
-      </x:c>
-      <x:c r="E215" s="32" t="str">
-        <x:v>This is to certify that Pedro Lamounier Sampaio has successfully demonstrated proficient comprehension in the course of Advanced Cardiac Life Support (ACLS) and is therefore awarded this qualification with Distinction on 10th June, 2026.</x:v>
-      </x:c>
+        <x:v>PEDRO_LAMOUNIER_SAMPAIO_Cybersecurity_Awareness_-_Production</x:v>
+      </x:c>
+      <x:c r="E215" s="32" t="str"/>
       <x:c r="F215" s="32" t="str"/>
       <x:c r="G215" s="32" t="str">
         <x:v>Grupo 1 — Ensino</x:v>
@@ -8447,7 +8445,7 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="I215" s="32" t="str">
-        <x:v>Extraído do documento</x:v>
+        <x:v>Sem texto extraível — revisão manual</x:v>
       </x:c>
       <x:c r="J215" s="33"/>
       <x:c r="K215" s="33"/>
@@ -8461,13 +8459,13 @@
         <x:v>214</x:v>
       </x:c>
       <x:c r="B216" s="32" t="str">
-        <x:v>PEDRO_LAMOUNIER_SAMPAIO_Cybersecurity_Awareness_-_Production.pdf</x:v>
+        <x:v>PEDRO_LAMOUNIER_SAMPAIO_Project_Management_Essentials_-_Production.pdf</x:v>
       </x:c>
       <x:c r="C216" s="32" t="str">
         <x:v>PEDRO</x:v>
       </x:c>
       <x:c r="D216" s="32" t="str">
-        <x:v>PEDRO_LAMOUNIER_SAMPAIO_Cybersecurity_Awareness_-_Production</x:v>
+        <x:v>PEDRO_LAMOUNIER_SAMPAIO_Project_Management_Essentials_-_Production</x:v>
       </x:c>
       <x:c r="E216" s="32" t="str"/>
       <x:c r="F216" s="32" t="str"/>
@@ -8492,15 +8490,17 @@
         <x:v>215</x:v>
       </x:c>
       <x:c r="B217" s="32" t="str">
-        <x:v>PEDRO_LAMOUNIER_SAMPAIO_Project_Management_Essentials_-_Production.pdf</x:v>
+        <x:v>Penn-Coursera_Healthcare Law Specialization Certificate VOUZB1AZBVL4.pdf</x:v>
       </x:c>
       <x:c r="C217" s="32" t="str">
-        <x:v>PEDRO</x:v>
+        <x:v>University of Pennsylvania</x:v>
       </x:c>
       <x:c r="D217" s="32" t="str">
-        <x:v>PEDRO_LAMOUNIER_SAMPAIO_Project_Management_Essentials_-_Production</x:v>
-      </x:c>
-      <x:c r="E217" s="32" t="str"/>
+        <x:v>Healthcare Law</x:v>
+      </x:c>
+      <x:c r="E217" s="32" t="str">
+        <x:v>4 C o u r s e s U . S . H e a l t h L a w F u n d a m e n t a l s P r i v a c y L a w a n d H I P A A I n t e l l e c t u a l P r o p e r t y i n t h e H e a l t h c a r e I n d u s t r y C o m p a r a t i v e H e a l t h S y s t e m s T h e o d o r e R u g e r , J D D e a n a n d B e r n a r d G . S e g a l P r o f e s s o r o f L a w P e n n L a w L a u r e n S t e i n f e l d L e c t u r e r i n L a w R . P o l k W a g n e r P r o f e s s o r o f L a w A n g u s C o r b e t t A d j u n c t P </x:v>
+      </x:c>
       <x:c r="F217" s="32" t="str"/>
       <x:c r="G217" s="32" t="str">
         <x:v>Grupo 1 — Ensino</x:v>
@@ -8509,13 +8509,19 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="I217" s="32" t="str">
-        <x:v>Sem texto extraível — revisão manual</x:v>
-      </x:c>
-      <x:c r="J217" s="33"/>
-      <x:c r="K217" s="33"/>
-      <x:c r="L217" s="33"/>
+        <x:v>Extraído do documento</x:v>
+      </x:c>
+      <x:c r="J217" s="33" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="K217" s="33" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="L217" s="33" t="n">
+        <x:v>40</x:v>
+      </x:c>
       <x:c r="M217" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/specialization/VOUZB1AZBVL4; estimativa derivada do tempo exibido: 1 meses com 10 por semana para concluir</x:v>
       </x:c>
     </x:row>
     <x:row r="218">
@@ -8523,16 +8529,16 @@
         <x:v>216</x:v>
       </x:c>
       <x:c r="B218" s="32" t="str">
-        <x:v>Penn-Coursera_Healthcare Law Specialization Certificate VOUZB1AZBVL4.pdf</x:v>
+        <x:v>Penn-Coursera_Intellectual Property in Healthcare_Certificate_ME8EBTCWCKTS.pdf</x:v>
       </x:c>
       <x:c r="C218" s="32" t="str">
         <x:v>University of Pennsylvania</x:v>
       </x:c>
       <x:c r="D218" s="32" t="str">
-        <x:v>Healthcare Law</x:v>
+        <x:v>Intellectual Property in the Healthcare Industry</x:v>
       </x:c>
       <x:c r="E218" s="32" t="str">
-        <x:v>4 C o u r s e s U . S . H e a l t h L a w F u n d a m e n t a l s P r i v a c y L a w a n d H I P A A I n t e l l e c t u a l P r o p e r t y i n t h e H e a l t h c a r e I n d u s t r y C o m p a r a t i v e H e a l t h S y s t e m s T h e o d o r e R u g e r , J D D e a n a n d B e r n a r d G . S e g a l P r o f e s s o r o f L a w P e n n L a w L a u r e n S t e i n f e l d L e c t u r e r i n L a w R . P o l k W a g n e r P r o f e s s o r o f L a w A n g u s C o r b e t t A d j u n c t P </x:v>
+        <x:v>A u g 7 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o I n t e l l e c t u a l P r o p e r t y i n t h e H e a l t h c a r e I n d u s t r y a n o n l i n e n o n - c r e d i t c o u r s e a u t h o r i z e d b y U n i v e r s i t y o f P e n n s y l v a n i a a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d R . P o l k W a g n e r P r o f e s s o r o f L a w V e r i f y a t : h t t p s : / / c o u r s e r a . o r g / v e r i f y / M E 8 E B </x:v>
       </x:c>
       <x:c r="F218" s="32" t="str"/>
       <x:c r="G218" s="32" t="str">
@@ -8545,16 +8551,16 @@
         <x:v>Extraído do documento</x:v>
       </x:c>
       <x:c r="J218" s="33" t="n">
-        <x:v>40</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="K218" s="33" t="n">
-        <x:v>40</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="L218" s="33" t="n">
-        <x:v>40</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="M218" s="32" t="str">
-        <x:v>Coursera: https://www.coursera.org/account/accomplishments/specialization/VOUZB1AZBVL4; estimativa derivada do tempo exibido: 1 meses com 10 por semana para concluir</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/ME8EBTCWCKTS</x:v>
       </x:c>
     </x:row>
     <x:row r="219">
@@ -8562,16 +8568,16 @@
         <x:v>217</x:v>
       </x:c>
       <x:c r="B219" s="32" t="str">
-        <x:v>Penn-Coursera_Intellectual Property in Healthcare_Certificate_ME8EBTCWCKTS.pdf</x:v>
+        <x:v>Personalidade INTP (Lógico) _ 16Personalities.pdf</x:v>
       </x:c>
       <x:c r="C219" s="32" t="str">
-        <x:v>University of Pennsylvania</x:v>
+        <x:v>Personalidade INTP (Lógico)</x:v>
       </x:c>
       <x:c r="D219" s="32" t="str">
-        <x:v>Intellectual Property in the Healthcare Industry</x:v>
+        <x:v>Personalidade INTP (Lógico) _ 16Personalities</x:v>
       </x:c>
       <x:c r="E219" s="32" t="str">
-        <x:v>A u g 7 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o I n t e l l e c t u a l P r o p e r t y i n t h e H e a l t h c a r e I n d u s t r y a n o n l i n e n o n - c r e d i t c o u r s e a u t h o r i z e d b y U n i v e r s i t y o f P e n n s y l v a n i a a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d R . P o l k W a g n e r P r o f e s s o r o f L a w V e r i f y a t : h t t p s : / / c o u r s e r a . o r g / v e r i f y / M E 8 E B </x:v>
+        <x:v>Sendo um INTP (Lógico), você possui uma combinação única de curiosidade intelectual, habilidade analítica e inclinação para o pensamento abstrato. Sua mente brinca com as ideias, constantemente explorando conceitos complexos e buscando entender os princípios que vão além do mundo ao redor. Você enxerga a vida com uma mentalidade racional e lógica, confiando mais nos fatos e na razão do que nas emoções ou no senso comum. Sua sede insaciável de conhecimento faz com que você mergulhe profundamente </x:v>
       </x:c>
       <x:c r="F219" s="32" t="str"/>
       <x:c r="G219" s="32" t="str">
@@ -8583,17 +8589,11 @@
       <x:c r="I219" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J219" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="K219" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="L219" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
+      <x:c r="J219" s="33"/>
+      <x:c r="K219" s="33"/>
+      <x:c r="L219" s="33"/>
       <x:c r="M219" s="32" t="str">
-        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/ME8EBTCWCKTS</x:v>
+        <x:v>Carga horária não localizada</x:v>
       </x:c>
     </x:row>
     <x:row r="220">
@@ -8601,17 +8601,15 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="B220" s="32" t="str">
-        <x:v>Personalidade INTP (Lógico) _ 16Personalities.pdf</x:v>
+        <x:v>PET_ESOL Entry 3 Certificate.pdf</x:v>
       </x:c>
       <x:c r="C220" s="32" t="str">
-        <x:v>Personalidade INTP (Lógico)</x:v>
+        <x:v>PET</x:v>
       </x:c>
       <x:c r="D220" s="32" t="str">
-        <x:v>Personalidade INTP (Lógico) _ 16Personalities</x:v>
-      </x:c>
-      <x:c r="E220" s="32" t="str">
-        <x:v>Sendo um INTP (Lógico), você possui uma combinação única de curiosidade intelectual, habilidade analítica e inclinação para o pensamento abstrato. Sua mente brinca com as ideias, constantemente explorando conceitos complexos e buscando entender os princípios que vão além do mundo ao redor. Você enxerga a vida com uma mentalidade racional e lógica, confiando mais nos fatos e na razão do que nas emoções ou no senso comum. Sua sede insaciável de conhecimento faz com que você mergulhe profundamente </x:v>
-      </x:c>
+        <x:v>PET_ESOL Entry 3 Certificate</x:v>
+      </x:c>
+      <x:c r="E220" s="32" t="str"/>
       <x:c r="F220" s="32" t="str"/>
       <x:c r="G220" s="32" t="str">
         <x:v>Grupo 1 — Ensino</x:v>
@@ -8620,7 +8618,7 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="I220" s="32" t="str">
-        <x:v>Extraído do documento</x:v>
+        <x:v>Sem texto extraível — revisão manual</x:v>
       </x:c>
       <x:c r="J220" s="33"/>
       <x:c r="K220" s="33"/>
@@ -8634,15 +8632,17 @@
         <x:v>219</x:v>
       </x:c>
       <x:c r="B221" s="32" t="str">
-        <x:v>PET_ESOL Entry 3 Certificate.pdf</x:v>
+        <x:v>PHC Course - WHO Academy.pdf</x:v>
       </x:c>
       <x:c r="C221" s="32" t="str">
-        <x:v>PET</x:v>
+        <x:v>PHC Course</x:v>
       </x:c>
       <x:c r="D221" s="32" t="str">
-        <x:v>PET_ESOL Entry 3 Certificate</x:v>
-      </x:c>
-      <x:c r="E221" s="32" t="str"/>
+        <x:v>PHC Course - WHO Academy</x:v>
+      </x:c>
+      <x:c r="E221" s="32" t="str">
+        <x:v>Award of completionPRESENTED TO Pedro Lamounier Sampaio for the successful completion of the course “The primary health care approach: A short course" Issued by WHO Academy More information Issued on 23/06/2026 Admission Criteria None Course description Learners engaged in activities to learn about how to equip health professionals, health system leaders, community representatives and partners with a practical overview of the primary health care (PHC) approach. Course activities Learners success</x:v>
+      </x:c>
       <x:c r="F221" s="32" t="str"/>
       <x:c r="G221" s="32" t="str">
         <x:v>Grupo 1 — Ensino</x:v>
@@ -8651,7 +8651,7 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="I221" s="32" t="str">
-        <x:v>Sem texto extraível — revisão manual</x:v>
+        <x:v>Extraído do documento</x:v>
       </x:c>
       <x:c r="J221" s="33"/>
       <x:c r="K221" s="33"/>
@@ -8665,16 +8665,16 @@
         <x:v>220</x:v>
       </x:c>
       <x:c r="B222" s="32" t="str">
-        <x:v>PHC Course - WHO Academy.pdf</x:v>
+        <x:v>pjrtraining _ ISO 9001-2015 Clause-by-Clau... (CBC9000) _ Final Exam.pdf</x:v>
       </x:c>
       <x:c r="C222" s="32" t="str">
-        <x:v>PHC Course</x:v>
+        <x:v>pjrtraining</x:v>
       </x:c>
       <x:c r="D222" s="32" t="str">
-        <x:v>PHC Course - WHO Academy</x:v>
+        <x:v>pjrtraining _ ISO 9001-2015 Clause-by-Clau... (CBC9000) _ Final Exam</x:v>
       </x:c>
       <x:c r="E222" s="32" t="str">
-        <x:v>Award of completionPRESENTED TO Pedro Lamounier Sampaio for the successful completion of the course “The primary health care approach: A short course" Issued by WHO Academy More information Issued on 23/06/2026 Admission Criteria None Course description Learners engaged in activities to learn about how to equip health professionals, health system leaders, community representatives and partners with a practical overview of the primary health care (PHC) approach. Course activities Learners success</x:v>
+        <x:v>ISO 9001:2015 Clause-by-Clau... (CBC9000) (https://pjrtraining.talentlms.com/dashboard) You completed this test on You completed this test on You completed this test on You completed this test on 07/03/2026, 00:2207/03/2026, 00:2207/03/2026, 00:2207/03/2026, 00:22 Your score is 50.00%Your score is 50.00%Your score is 50.00%Your score is 50.00% Unfortunately your score was insu!cient to pass this exam - please try again. INCORRECTINCORRECTINCORRECTINCORRECT Which of the following documents are r</x:v>
       </x:c>
       <x:c r="F222" s="32" t="str"/>
       <x:c r="G222" s="32" t="str">
@@ -8690,7 +8690,7 @@
       <x:c r="K222" s="33"/>
       <x:c r="L222" s="33"/>
       <x:c r="M222" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>https://pjrtraining.talentlms.com/dashboard | https://pjrtraining.talentlms.com/unit/viewtestsurvey/id:1746,mode:test</x:v>
       </x:c>
     </x:row>
     <x:row r="223">
@@ -8698,16 +8698,16 @@
         <x:v>221</x:v>
       </x:c>
       <x:c r="B223" s="32" t="str">
-        <x:v>pjrtraining _ ISO 9001-2015 Clause-by-Clau... (CBC9000) _ Final Exam.pdf</x:v>
+        <x:v>PMI-LinkedIn Certificate - Six Sigma Black Belt.pdf</x:v>
       </x:c>
       <x:c r="C223" s="32" t="str">
-        <x:v>pjrtraining</x:v>
+        <x:v>PMI</x:v>
       </x:c>
       <x:c r="D223" s="32" t="str">
-        <x:v>pjrtraining _ ISO 9001-2015 Clause-by-Clau... (CBC9000) _ Final Exam</x:v>
+        <x:v>PMI-LinkedIn Certificate - Six Sigma Black Belt</x:v>
       </x:c>
       <x:c r="E223" s="32" t="str">
-        <x:v>ISO 9001:2015 Clause-by-Clau... (CBC9000) (https://pjrtraining.talentlms.com/dashboard) You completed this test on You completed this test on You completed this test on You completed this test on 07/03/2026, 00:2207/03/2026, 00:2207/03/2026, 00:2207/03/2026, 00:22 Your score is 50.00%Your score is 50.00%Your score is 50.00%Your score is 50.00% Unfortunately your score was insu!cient to pass this exam - please try again. INCORRECTINCORRECTINCORRECTINCORRECT Which of the following documents are r</x:v>
+        <x:v>L i n k e d I n L e a r n i n g Six Sigma: Black Belt Curso concluído por Pedro Lamounier Sampaio Jul 24, 2026 at 05:34AM UTC Principais competências abordadas Six Sigma Black Belt Shea Hanson, Líder de Estratégia de Conteúdos do Learning O logo da PMI Registered Education Provider é marca registrada do Project Management Institute, Inc. Programa: PMI® Registered Education Provider Provider ID: nº4101 Activity #: 41011Y0KUW PDUs/ContactHours: 2.50 Código do certificado: 2ecec5f30121e7b2d0daaabee</x:v>
       </x:c>
       <x:c r="F223" s="32" t="str"/>
       <x:c r="G223" s="32" t="str">
@@ -8723,7 +8723,7 @@
       <x:c r="K223" s="33"/>
       <x:c r="L223" s="33"/>
       <x:c r="M223" s="32" t="str">
-        <x:v>https://pjrtraining.talentlms.com/dashboard | https://pjrtraining.talentlms.com/unit/viewtestsurvey/id:1746,mode:test</x:v>
+        <x:v>Carga horária não localizada</x:v>
       </x:c>
     </x:row>
     <x:row r="224">
@@ -8731,16 +8731,16 @@
         <x:v>222</x:v>
       </x:c>
       <x:c r="B224" s="32" t="str">
-        <x:v>PMI-LinkedIn Certificate - Six Sigma Black Belt.pdf</x:v>
+        <x:v>PMI-LinkedIn Certificate_Problem Solving for Leadership.pdf</x:v>
       </x:c>
       <x:c r="C224" s="32" t="str">
         <x:v>PMI</x:v>
       </x:c>
       <x:c r="D224" s="32" t="str">
-        <x:v>PMI-LinkedIn Certificate - Six Sigma Black Belt</x:v>
+        <x:v>PMI-LinkedIn Certificate_Problem Solving for Leadership</x:v>
       </x:c>
       <x:c r="E224" s="32" t="str">
-        <x:v>L i n k e d I n L e a r n i n g Six Sigma: Black Belt Curso concluído por Pedro Lamounier Sampaio Jul 24, 2026 at 05:34AM UTC Principais competências abordadas Six Sigma Black Belt Shea Hanson, Líder de Estratégia de Conteúdos do Learning O logo da PMI Registered Education Provider é marca registrada do Project Management Institute, Inc. Programa: PMI® Registered Education Provider Provider ID: nº4101 Activity #: 41011Y0KUW PDUs/ContactHours: 2.50 Código do certificado: 2ecec5f30121e7b2d0daaabee</x:v>
+        <x:v>L i n k e d I n L e a r n i n g Problem-Solving for Founders Curso concluído por Pedro Lamounier Sampaio Jul 25, 2026 at 11:04AM UTC Principais competências abordadas Problem Solving Shea Hanson, Líder de Estratégia de Conteúdos do Learning O logo da PMI Registered Education Provider é marca registrada do Project Management Institute, Inc. Programa: PMI® Registered Education Provider Provider ID: nº4101 Activity #: 4101XQIJ9F PDUs/ContactHours: 0.25 Código do certificado: 63b8d513cadfa027da164e5</x:v>
       </x:c>
       <x:c r="F224" s="32" t="str"/>
       <x:c r="G224" s="32" t="str">
@@ -8764,16 +8764,16 @@
         <x:v>223</x:v>
       </x:c>
       <x:c r="B225" s="32" t="str">
-        <x:v>PMI-LinkedIn Certificate_Problem Solving for Leadership.pdf</x:v>
+        <x:v>PMI-LinkedIn Certificate_Project Management Foundations.pdf</x:v>
       </x:c>
       <x:c r="C225" s="32" t="str">
         <x:v>PMI</x:v>
       </x:c>
       <x:c r="D225" s="32" t="str">
-        <x:v>PMI-LinkedIn Certificate_Problem Solving for Leadership</x:v>
+        <x:v>PMI-LinkedIn Certificate_Project Management Foundations</x:v>
       </x:c>
       <x:c r="E225" s="32" t="str">
-        <x:v>L i n k e d I n L e a r n i n g Problem-Solving for Founders Curso concluído por Pedro Lamounier Sampaio Jul 25, 2026 at 11:04AM UTC Principais competências abordadas Problem Solving Shea Hanson, Líder de Estratégia de Conteúdos do Learning O logo da PMI Registered Education Provider é marca registrada do Project Management Institute, Inc. Programa: PMI® Registered Education Provider Provider ID: nº4101 Activity #: 4101XQIJ9F PDUs/ContactHours: 0.25 Código do certificado: 63b8d513cadfa027da164e5</x:v>
+        <x:v>L i n k e d I n L e a r n i n g Project Management Foundations Curso concluído por Pedro Lamounier Sampaio Jul 25, 2026 at 03:58PM UTC Principais competências abordadas Project Management Shea Hanson, Líder de Estratégia de Conteúdos do Learning O logo da PMI Registered Education Provider é marca registrada do Project Management Institute, Inc. Programa: PMI® Registered Education Provider Provider ID: nº4101 Activity #: 41015ZTOKN PDUs/ContactHours: 3.25 Código do certificado: cd554373d8d1aa1395</x:v>
       </x:c>
       <x:c r="F225" s="32" t="str"/>
       <x:c r="G225" s="32" t="str">
@@ -8797,16 +8797,16 @@
         <x:v>224</x:v>
       </x:c>
       <x:c r="B226" s="32" t="str">
-        <x:v>PMI-LinkedIn Certificate_Project Management Foundations.pdf</x:v>
+        <x:v>PMI-LinkedIn Learning Certificate_Healthcare Projects.pdf</x:v>
       </x:c>
       <x:c r="C226" s="32" t="str">
         <x:v>PMI</x:v>
       </x:c>
       <x:c r="D226" s="32" t="str">
-        <x:v>PMI-LinkedIn Certificate_Project Management Foundations</x:v>
+        <x:v>PMI-LinkedIn Learning Certificate_Healthcare Projects</x:v>
       </x:c>
       <x:c r="E226" s="32" t="str">
-        <x:v>L i n k e d I n L e a r n i n g Project Management Foundations Curso concluído por Pedro Lamounier Sampaio Jul 25, 2026 at 03:58PM UTC Principais competências abordadas Project Management Shea Hanson, Líder de Estratégia de Conteúdos do Learning O logo da PMI Registered Education Provider é marca registrada do Project Management Institute, Inc. Programa: PMI® Registered Education Provider Provider ID: nº4101 Activity #: 41015ZTOKN PDUs/ContactHours: 3.25 Código do certificado: cd554373d8d1aa1395</x:v>
+        <x:v>L i n k e d I n L e a r n i n g Project Management: Healthcare Projects Curso concluído por Pedro Lamounier Sampaio Jul 24, 2026 at 08:28AM UTC Principais competências abordadas Project Management Shea Hanson, Líder de Estratégia de Conteúdos do Learning O logo da PMI Registered Education Provider é marca registrada do Project Management Institute, Inc. Programa: PMI® Registered Education Provider Provider ID: nº4101 Activity #: 4101065F43 PDUs/ContactHours: 1.00 Código do certificado: 1b87915ea</x:v>
       </x:c>
       <x:c r="F226" s="32" t="str"/>
       <x:c r="G226" s="32" t="str">
@@ -8830,16 +8830,16 @@
         <x:v>225</x:v>
       </x:c>
       <x:c r="B227" s="32" t="str">
-        <x:v>PMI-LinkedIn Learning Certificate_Healthcare Projects.pdf</x:v>
+        <x:v>PMI-LinkedIn_Certificate_PM Foundations Requirements.pdf</x:v>
       </x:c>
       <x:c r="C227" s="32" t="str">
         <x:v>PMI</x:v>
       </x:c>
       <x:c r="D227" s="32" t="str">
-        <x:v>PMI-LinkedIn Learning Certificate_Healthcare Projects</x:v>
+        <x:v>PMI-LinkedIn_Certificate_PM Foundations Requirements</x:v>
       </x:c>
       <x:c r="E227" s="32" t="str">
-        <x:v>L i n k e d I n L e a r n i n g Project Management: Healthcare Projects Curso concluído por Pedro Lamounier Sampaio Jul 24, 2026 at 08:28AM UTC Principais competências abordadas Project Management Shea Hanson, Líder de Estratégia de Conteúdos do Learning O logo da PMI Registered Education Provider é marca registrada do Project Management Institute, Inc. Programa: PMI® Registered Education Provider Provider ID: nº4101 Activity #: 4101065F43 PDUs/ContactHours: 1.00 Código do certificado: 1b87915ea</x:v>
+        <x:v>L i n k e d I n L e a r n i n g Project Management Foundations: Requirements Curso concluído por Pedro Lamounier Sampaio Jul 26, 2026 at 06:02AM UTC Principais competências abordadas Requirements Management Project Management Shea Hanson, Líder de Estratégia de Conteúdos do Learning O logo da PMI Registered Education Provider é marca registrada do Project Management Institute, Inc. Programa: PMI® Registered Education Provider Provider ID: nº4101 Activity #: 4101ZQ76OD PDUs/ContactHours: 0.25 Cód</x:v>
       </x:c>
       <x:c r="F227" s="32" t="str"/>
       <x:c r="G227" s="32" t="str">
@@ -8863,16 +8863,16 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="B228" s="32" t="str">
-        <x:v>PMI-LinkedIn_Certificate_PM Foundations Requirements.pdf</x:v>
+        <x:v>PMI-LinkedIn_Certificate_PM Foundations_Ethics.pdf</x:v>
       </x:c>
       <x:c r="C228" s="32" t="str">
         <x:v>PMI</x:v>
       </x:c>
       <x:c r="D228" s="32" t="str">
-        <x:v>PMI-LinkedIn_Certificate_PM Foundations Requirements</x:v>
+        <x:v>PMI-LinkedIn_Certificate_PM Foundations_Ethics</x:v>
       </x:c>
       <x:c r="E228" s="32" t="str">
-        <x:v>L i n k e d I n L e a r n i n g Project Management Foundations: Requirements Curso concluído por Pedro Lamounier Sampaio Jul 26, 2026 at 06:02AM UTC Principais competências abordadas Requirements Management Project Management Shea Hanson, Líder de Estratégia de Conteúdos do Learning O logo da PMI Registered Education Provider é marca registrada do Project Management Institute, Inc. Programa: PMI® Registered Education Provider Provider ID: nº4101 Activity #: 4101ZQ76OD PDUs/ContactHours: 0.25 Cód</x:v>
+        <x:v>L i n k e d I n L e a r n i n g Project Management Foundations: Ethics Curso concluído por Pedro Lamounier Sampaio Jul 26, 2026 at 04:14AM UTC Principais competências abordadas Business Ethics Project Management Shea Hanson, Líder de Estratégia de Conteúdos do Learning O logo da PMI Registered Education Provider é marca registrada do Project Management Institute, Inc. Programa: PMI® Registered Education Provider Provider ID: nº4101 Activity #: 41012JV605 PDUs/ContactHours: 1.00 Código do certifi</x:v>
       </x:c>
       <x:c r="F228" s="32" t="str"/>
       <x:c r="G228" s="32" t="str">
@@ -8896,16 +8896,16 @@
         <x:v>227</x:v>
       </x:c>
       <x:c r="B229" s="32" t="str">
-        <x:v>PMI-LinkedIn_Certificate_PM Foundations_Ethics.pdf</x:v>
+        <x:v>PMI-LinkedIn_Certificate_PME_Budgets.pdf</x:v>
       </x:c>
       <x:c r="C229" s="32" t="str">
         <x:v>PMI</x:v>
       </x:c>
       <x:c r="D229" s="32" t="str">
-        <x:v>PMI-LinkedIn_Certificate_PM Foundations_Ethics</x:v>
+        <x:v>PMI-LinkedIn_Certificate_PME_Budgets</x:v>
       </x:c>
       <x:c r="E229" s="32" t="str">
-        <x:v>L i n k e d I n L e a r n i n g Project Management Foundations: Ethics Curso concluído por Pedro Lamounier Sampaio Jul 26, 2026 at 04:14AM UTC Principais competências abordadas Business Ethics Project Management Shea Hanson, Líder de Estratégia de Conteúdos do Learning O logo da PMI Registered Education Provider é marca registrada do Project Management Institute, Inc. Programa: PMI® Registered Education Provider Provider ID: nº4101 Activity #: 41012JV605 PDUs/ContactHours: 1.00 Código do certifi</x:v>
+        <x:v>L i n k e d I n L e a r n i n g Project Management Foundations: Budgets Curso concluído por Pedro Lamounier Sampaio Jul 26, 2026 at 09:46PM UTC Principais competências abordadas Budget Development Project Management Shea Hanson, Líder de Estratégia de Conteúdos do Learning O logo da PMI Registered Education Provider é marca registrada do Project Management Institute, Inc. Programa: PMI® Registered Education Provider Provider ID: nº4101 Activity #: 4101J2GRWT PDUs/ContactHours: 0.75 Código do cer</x:v>
       </x:c>
       <x:c r="F229" s="32" t="str"/>
       <x:c r="G229" s="32" t="str">
@@ -8929,16 +8929,16 @@
         <x:v>228</x:v>
       </x:c>
       <x:c r="B230" s="32" t="str">
-        <x:v>PMI-LinkedIn_Certificate_PME_Budgets.pdf</x:v>
+        <x:v>PMI-LinkedIn_Certificate_PME_Schedules.pdf</x:v>
       </x:c>
       <x:c r="C230" s="32" t="str">
         <x:v>PMI</x:v>
       </x:c>
       <x:c r="D230" s="32" t="str">
-        <x:v>PMI-LinkedIn_Certificate_PME_Budgets</x:v>
+        <x:v>PMI-LinkedIn_Certificate_PME_Schedules</x:v>
       </x:c>
       <x:c r="E230" s="32" t="str">
-        <x:v>L i n k e d I n L e a r n i n g Project Management Foundations: Budgets Curso concluído por Pedro Lamounier Sampaio Jul 26, 2026 at 09:46PM UTC Principais competências abordadas Budget Development Project Management Shea Hanson, Líder de Estratégia de Conteúdos do Learning O logo da PMI Registered Education Provider é marca registrada do Project Management Institute, Inc. Programa: PMI® Registered Education Provider Provider ID: nº4101 Activity #: 4101J2GRWT PDUs/ContactHours: 0.75 Código do cer</x:v>
+        <x:v>L i n k e d I n L e a r n i n g Project Management Foundations: Schedules Curso concluído por Pedro Lamounier Sampaio Jul 26, 2026 at 01:21PM UTC Principais competências abordadas Project Scheduling Project Management Shea Hanson, Líder de Estratégia de Conteúdos do Learning O logo da PMI Registered Education Provider é marca registrada do Project Management Institute, Inc. Programa: PMI® Registered Education Provider Provider ID: nº4101 Activity #: 41012Q4G32 PDUs/ContactHours: 2.00 Código do c</x:v>
       </x:c>
       <x:c r="F230" s="32" t="str"/>
       <x:c r="G230" s="32" t="str">
@@ -8962,16 +8962,16 @@
         <x:v>229</x:v>
       </x:c>
       <x:c r="B231" s="32" t="str">
-        <x:v>PMI-LinkedIn_Certificate_PME_Schedules.pdf</x:v>
+        <x:v>PMI-LinkedIn_Certificate_PMF_Teams.pdf</x:v>
       </x:c>
       <x:c r="C231" s="32" t="str">
         <x:v>PMI</x:v>
       </x:c>
       <x:c r="D231" s="32" t="str">
-        <x:v>PMI-LinkedIn_Certificate_PME_Schedules</x:v>
+        <x:v>PMI-LinkedIn_Certificate_PMF_Teams</x:v>
       </x:c>
       <x:c r="E231" s="32" t="str">
-        <x:v>L i n k e d I n L e a r n i n g Project Management Foundations: Schedules Curso concluído por Pedro Lamounier Sampaio Jul 26, 2026 at 01:21PM UTC Principais competências abordadas Project Scheduling Project Management Shea Hanson, Líder de Estratégia de Conteúdos do Learning O logo da PMI Registered Education Provider é marca registrada do Project Management Institute, Inc. Programa: PMI® Registered Education Provider Provider ID: nº4101 Activity #: 41012Q4G32 PDUs/ContactHours: 2.00 Código do c</x:v>
+        <x:v>L i n k e d I n L e a r n i n g Project Management Foundations: Teams Curso concluído por Pedro Lamounier Sampaio Jul 27, 2026 at 12:32AM UTC Principais competências abordadas Project Team Management Project Management Shea Hanson, Líder de Estratégia de Conteúdos do Learning O logo da PMI Registered Education Provider é marca registrada do Project Management Institute, Inc. Programa: PMI® Registered Education Provider Provider ID: nº4101 Activity #: 41016UXEQ0 PDUs/ContactHours: 0.25 Código do </x:v>
       </x:c>
       <x:c r="F231" s="32" t="str"/>
       <x:c r="G231" s="32" t="str">
@@ -8995,16 +8995,16 @@
         <x:v>230</x:v>
       </x:c>
       <x:c r="B232" s="32" t="str">
-        <x:v>PMI-LinkedIn_Certificate_PMF_Teams.pdf</x:v>
+        <x:v>PMI-LinkedIn_Leveraging AI_GRC_Certificate.pdf</x:v>
       </x:c>
       <x:c r="C232" s="32" t="str">
         <x:v>PMI</x:v>
       </x:c>
       <x:c r="D232" s="32" t="str">
-        <x:v>PMI-LinkedIn_Certificate_PMF_Teams</x:v>
+        <x:v>PMI-LinkedIn_Leveraging AI_GRC_Certificate</x:v>
       </x:c>
       <x:c r="E232" s="32" t="str">
-        <x:v>L i n k e d I n L e a r n i n g Project Management Foundations: Teams Curso concluído por Pedro Lamounier Sampaio Jul 27, 2026 at 12:32AM UTC Principais competências abordadas Project Team Management Project Management Shea Hanson, Líder de Estratégia de Conteúdos do Learning O logo da PMI Registered Education Provider é marca registrada do Project Management Institute, Inc. Programa: PMI® Registered Education Provider Provider ID: nº4101 Activity #: 41016UXEQ0 PDUs/ContactHours: 0.25 Código do </x:v>
+        <x:v>L i n k e d I n L e a r n i n g Leveraging AI for Governance, Risk, and Compliance Curso concluído por Pedro Lamounier Sampaio Jul 24, 2026 at 08:53AM UTC Principais competências abordadas Governance, Risk Management, and Compliance (GRC) AI Governance Shea Hanson, Líder de Estratégia de Conteúdos do Learning O logo da PMI Registered Education Provider é marca registrada do Project Management Institute, Inc. Programa: PMI® Registered Education Provider Provider ID: nº4101 Activity #: 4101JJM5UB </x:v>
       </x:c>
       <x:c r="F232" s="32" t="str"/>
       <x:c r="G232" s="32" t="str">
@@ -9028,16 +9028,16 @@
         <x:v>231</x:v>
       </x:c>
       <x:c r="B233" s="32" t="str">
-        <x:v>PMI-LinkedIn_Leveraging AI_GRC_Certificate.pdf</x:v>
+        <x:v>PMI-LinkedIn_MicrosoftMPM_Certificate.pdf</x:v>
       </x:c>
       <x:c r="C233" s="32" t="str">
         <x:v>PMI</x:v>
       </x:c>
       <x:c r="D233" s="32" t="str">
-        <x:v>PMI-LinkedIn_Leveraging AI_GRC_Certificate</x:v>
+        <x:v>PMI-LinkedIn_MicrosoftMPM_Certificate</x:v>
       </x:c>
       <x:c r="E233" s="32" t="str">
-        <x:v>L i n k e d I n L e a r n i n g Leveraging AI for Governance, Risk, and Compliance Curso concluído por Pedro Lamounier Sampaio Jul 24, 2026 at 08:53AM UTC Principais competências abordadas Governance, Risk Management, and Compliance (GRC) AI Governance Shea Hanson, Líder de Estratégia de Conteúdos do Learning O logo da PMI Registered Education Provider é marca registrada do Project Management Institute, Inc. Programa: PMI® Registered Education Provider Provider ID: nº4101 Activity #: 4101JJM5UB </x:v>
+        <x:v>L i n k e d I n L e a r n i n g Modern Project Management in Microsoft 365 Curso concluído por Pedro Lamounier Sampaio Jul 28, 2026 at 02:51PM UTC Principais competências abordadas Microsoft 365 Project Management Shea Hanson, Líder de Estratégia de Conteúdos do Learning O logo da PMI Registered Education Provider é marca registrada do Project Management Institute, Inc. Programa: PMI® Registered Education Provider Provider ID: nº4101 Activity #: 4101115EPB PDUs/ContactHours: 2.00 Código do certi</x:v>
       </x:c>
       <x:c r="F233" s="32" t="str"/>
       <x:c r="G233" s="32" t="str">
@@ -9061,16 +9061,16 @@
         <x:v>232</x:v>
       </x:c>
       <x:c r="B234" s="32" t="str">
-        <x:v>PMI-LinkedIn_MicrosoftMPM_Certificate.pdf</x:v>
+        <x:v>PMI-LinkedIn_PMF_Communication_Certificate.pdf</x:v>
       </x:c>
       <x:c r="C234" s="32" t="str">
         <x:v>PMI</x:v>
       </x:c>
       <x:c r="D234" s="32" t="str">
-        <x:v>PMI-LinkedIn_MicrosoftMPM_Certificate</x:v>
+        <x:v>PMI-LinkedIn_PMF_Communication_Certificate</x:v>
       </x:c>
       <x:c r="E234" s="32" t="str">
-        <x:v>L i n k e d I n L e a r n i n g Modern Project Management in Microsoft 365 Curso concluído por Pedro Lamounier Sampaio Jul 28, 2026 at 02:51PM UTC Principais competências abordadas Microsoft 365 Project Management Shea Hanson, Líder de Estratégia de Conteúdos do Learning O logo da PMI Registered Education Provider é marca registrada do Project Management Institute, Inc. Programa: PMI® Registered Education Provider Provider ID: nº4101 Activity #: 4101115EPB PDUs/ContactHours: 2.00 Código do certi</x:v>
+        <x:v>L i n k e d I n L e a r n i n g Project Management Foundations: Communication Curso concluído por Pedro Lamounier Sampaio Jul 27, 2026 at 10:45PM UTC Principais competências abordadas Project Management Project Communications Shea Hanson, Líder de Estratégia de Conteúdos do Learning O logo da PMI Registered Education Provider é marca registrada do Project Management Institute, Inc. Programa: PMI® Registered Education Provider Provider ID: nº4101 Activity #: 4101QGFARX PDUs/ContactHours: 1.00 Cód</x:v>
       </x:c>
       <x:c r="F234" s="32" t="str"/>
       <x:c r="G234" s="32" t="str">
@@ -9094,16 +9094,16 @@
         <x:v>233</x:v>
       </x:c>
       <x:c r="B235" s="32" t="str">
-        <x:v>PMI-LinkedIn_PMF_Communication_Certificate.pdf</x:v>
+        <x:v>PMI-LinkedIn_PMF_Risks_Certificate.pdf</x:v>
       </x:c>
       <x:c r="C235" s="32" t="str">
         <x:v>PMI</x:v>
       </x:c>
       <x:c r="D235" s="32" t="str">
-        <x:v>PMI-LinkedIn_PMF_Communication_Certificate</x:v>
+        <x:v>PMI-LinkedIn_PMF_Risks_Certificate</x:v>
       </x:c>
       <x:c r="E235" s="32" t="str">
-        <x:v>L i n k e d I n L e a r n i n g Project Management Foundations: Communication Curso concluído por Pedro Lamounier Sampaio Jul 27, 2026 at 10:45PM UTC Principais competências abordadas Project Management Project Communications Shea Hanson, Líder de Estratégia de Conteúdos do Learning O logo da PMI Registered Education Provider é marca registrada do Project Management Institute, Inc. Programa: PMI® Registered Education Provider Provider ID: nº4101 Activity #: 4101QGFARX PDUs/ContactHours: 1.00 Cód</x:v>
+        <x:v>L i n k e d I n L e a r n i n g Project Management Foundations: Risk Curso concluído por Pedro Lamounier Sampaio Jul 28, 2026 at 12:32PM UTC Principais competências abordadas Project Management Risk Management Shea Hanson, Líder de Estratégia de Conteúdos do Learning O logo da PMI Registered Education Provider é marca registrada do Project Management Institute, Inc. Programa: PMI® Registered Education Provider Provider ID: nº4101 Activity #: 4101RLET5X PDUs/ContactHours: 1.25 Código do certifica</x:v>
       </x:c>
       <x:c r="F235" s="32" t="str"/>
       <x:c r="G235" s="32" t="str">
@@ -9127,16 +9127,16 @@
         <x:v>234</x:v>
       </x:c>
       <x:c r="B236" s="32" t="str">
-        <x:v>PMI-LinkedIn_PMF_Risks_Certificate.pdf</x:v>
+        <x:v>PMI-LinkedIn_PMF_Stakeholders_Certificate.pdf</x:v>
       </x:c>
       <x:c r="C236" s="32" t="str">
         <x:v>PMI</x:v>
       </x:c>
       <x:c r="D236" s="32" t="str">
-        <x:v>PMI-LinkedIn_PMF_Risks_Certificate</x:v>
+        <x:v>PMI-LinkedIn_PMF_Stakeholders_Certificate</x:v>
       </x:c>
       <x:c r="E236" s="32" t="str">
-        <x:v>L i n k e d I n L e a r n i n g Project Management Foundations: Risk Curso concluído por Pedro Lamounier Sampaio Jul 28, 2026 at 12:32PM UTC Principais competências abordadas Project Management Risk Management Shea Hanson, Líder de Estratégia de Conteúdos do Learning O logo da PMI Registered Education Provider é marca registrada do Project Management Institute, Inc. Programa: PMI® Registered Education Provider Provider ID: nº4101 Activity #: 4101RLET5X PDUs/ContactHours: 1.25 Código do certifica</x:v>
+        <x:v>L i n k e d I n L e a r n i n g Managing Project Stakeholders Curso concluído por Pedro Lamounier Sampaio Jul 28, 2026 at 01:10PM UTC Principais competências abordadas Stakeholder Management Shea Hanson, Líder de Estratégia de Conteúdos do Learning O logo da PMI Registered Education Provider é marca registrada do Project Management Institute, Inc. Programa: PMI® Registered Education Provider Provider ID: nº4101 Activity #: 41013CHZXH PDUs/ContactHours: 0.25 Código do certificado: 6848af3d65e04dd</x:v>
       </x:c>
       <x:c r="F236" s="32" t="str"/>
       <x:c r="G236" s="32" t="str">
@@ -9160,16 +9160,16 @@
         <x:v>235</x:v>
       </x:c>
       <x:c r="B237" s="32" t="str">
-        <x:v>PMI-LinkedIn_PMF_Stakeholders_Certificate.pdf</x:v>
+        <x:v>PMI_LinkedIn_Certificate_AI_Projects.pdf</x:v>
       </x:c>
       <x:c r="C237" s="32" t="str">
         <x:v>PMI</x:v>
       </x:c>
       <x:c r="D237" s="32" t="str">
-        <x:v>PMI-LinkedIn_PMF_Stakeholders_Certificate</x:v>
+        <x:v>PMI_LinkedIn_Certificate_AI_Projects</x:v>
       </x:c>
       <x:c r="E237" s="32" t="str">
-        <x:v>L i n k e d I n L e a r n i n g Managing Project Stakeholders Curso concluído por Pedro Lamounier Sampaio Jul 28, 2026 at 01:10PM UTC Principais competências abordadas Stakeholder Management Shea Hanson, Líder de Estratégia de Conteúdos do Learning O logo da PMI Registered Education Provider é marca registrada do Project Management Institute, Inc. Programa: PMI® Registered Education Provider Provider ID: nº4101 Activity #: 41013CHZXH PDUs/ContactHours: 0.25 Código do certificado: 6848af3d65e04dd</x:v>
+        <x:v>L i n k e d I n L e a r n i n g Leveraging AI for Governance, Risk, and Compliance Curso concluído por Pedro Lamounier Sampaio Jul 24, 2026 at 08:53AM UTC Principais competências abordadas Governance, Risk Management, and Compliance (GRC) AI Governance Shea Hanson, Líder de Estratégia de Conteúdos do Learning O logo da PMI Registered Education Provider é marca registrada do Project Management Institute, Inc. Programa: PMI® Registered Education Provider Provider ID: nº4101 Activity #: 4101JJM5UB </x:v>
       </x:c>
       <x:c r="F237" s="32" t="str"/>
       <x:c r="G237" s="32" t="str">
@@ -9193,16 +9193,16 @@
         <x:v>236</x:v>
       </x:c>
       <x:c r="B238" s="32" t="str">
-        <x:v>PMI_LinkedIn_Certificate_AI_Projects.pdf</x:v>
+        <x:v>PMP ExamPrep1_Project Management Institute (PMI)®.pdf</x:v>
       </x:c>
       <x:c r="C238" s="32" t="str">
-        <x:v>PMI</x:v>
+        <x:v>PMP ExamPrep1</x:v>
       </x:c>
       <x:c r="D238" s="32" t="str">
-        <x:v>PMI_LinkedIn_Certificate_AI_Projects</x:v>
+        <x:v>PMP ExamPrep1_Project Management Institute (PMI)®</x:v>
       </x:c>
       <x:c r="E238" s="32" t="str">
-        <x:v>L i n k e d I n L e a r n i n g Leveraging AI for Governance, Risk, and Compliance Curso concluído por Pedro Lamounier Sampaio Jul 24, 2026 at 08:53AM UTC Principais competências abordadas Governance, Risk Management, and Compliance (GRC) AI Governance Shea Hanson, Líder de Estratégia de Conteúdos do Learning O logo da PMI Registered Education Provider é marca registrada do Project Management Institute, Inc. Programa: PMI® Registered Education Provider Provider ID: nº4101 Activity #: 4101JJM5UB </x:v>
+        <x:v>L i n k e d I n L e a r n i n g Practice Exam 1 for PMI: Project Management Professional (PMP)® Curso concluído por Pedro Lamounier Sampaio Jul 23, 2026 at 05:48PM UTC Principais competências abordadas Project Management Training Project Management Shea Hanson, Líder de Estratégia de Conteúdos do Learning O logo da PMI Registered Education Provider é marca registrada do Project Management Institute, Inc. Programa: PMI® Registered Education Provider Provider ID: nº4101 Activity #: 4101M89TUP PDUs</x:v>
       </x:c>
       <x:c r="F238" s="32" t="str"/>
       <x:c r="G238" s="32" t="str">
@@ -9226,16 +9226,16 @@
         <x:v>237</x:v>
       </x:c>
       <x:c r="B239" s="32" t="str">
-        <x:v>PMP ExamPrep1_Project Management Institute (PMI)®.pdf</x:v>
+        <x:v>Podcast APS_CME answers certificate-2026-7-12_1735.pdf</x:v>
       </x:c>
       <x:c r="C239" s="32" t="str">
-        <x:v>PMP ExamPrep1</x:v>
+        <x:v>Podcast APS</x:v>
       </x:c>
       <x:c r="D239" s="32" t="str">
-        <x:v>PMP ExamPrep1_Project Management Institute (PMI)®</x:v>
+        <x:v>Podcast APS_CME answers certificate-2026-7-12_1735</x:v>
       </x:c>
       <x:c r="E239" s="32" t="str">
-        <x:v>L i n k e d I n L e a r n i n g Practice Exam 1 for PMI: Project Management Professional (PMP)® Curso concluído por Pedro Lamounier Sampaio Jul 23, 2026 at 05:48PM UTC Principais competências abordadas Project Management Training Project Management Shea Hanson, Líder de Estratégia de Conteúdos do Learning O logo da PMI Registered Education Provider é marca registrada do Project Management Institute, Inc. Programa: PMI® Registered Education Provider Provider ID: nº4101 Activity #: 4101M89TUP PDUs</x:v>
+        <x:v>Answers in CME certiﬁes that Pedro Lamounier Sampaio, MD has participated in the enduring activity titled Mastering Evolving Standards in Resectable HNSCC: A Case-Based Discussion to Elevate Pre- and Postoperative Care on July 12, 2026 and is awarded 0.5 AMA PRA Category 1 Credit(s)™. Answers in CME is accredited by the Accreditation Council for Continuing Medical Education (ACCME) to provide continuing medical education for physicians. Answers in CME designates this enduring material for a maxi</x:v>
       </x:c>
       <x:c r="F239" s="32" t="str"/>
       <x:c r="G239" s="32" t="str">
@@ -9251,7 +9251,7 @@
       <x:c r="K239" s="33"/>
       <x:c r="L239" s="33"/>
       <x:c r="M239" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>https://answersincme.com/DDT</x:v>
       </x:c>
     </x:row>
     <x:row r="240">
@@ -9259,16 +9259,16 @@
         <x:v>238</x:v>
       </x:c>
       <x:c r="B240" s="32" t="str">
-        <x:v>Podcast APS_CME answers certificate-2026-7-12_1735.pdf</x:v>
+        <x:v>POP-Q-DVMC-007.pdf</x:v>
       </x:c>
       <x:c r="C240" s="32" t="str">
-        <x:v>Podcast APS</x:v>
+        <x:v>POP</x:v>
       </x:c>
       <x:c r="D240" s="32" t="str">
-        <x:v>Podcast APS_CME answers certificate-2026-7-12_1735</x:v>
+        <x:v>POP-Q-DVMC-007</x:v>
       </x:c>
       <x:c r="E240" s="32" t="str">
-        <x:v>Answers in CME certiﬁes that Pedro Lamounier Sampaio, MD has participated in the enduring activity titled Mastering Evolving Standards in Resectable HNSCC: A Case-Based Discussion to Elevate Pre- and Postoperative Care on July 12, 2026 and is awarded 0.5 AMA PRA Category 1 Credit(s)™. Answers in CME is accredited by the Accreditation Council for Continuing Medical Education (ACCME) to provide continuing medical education for physicians. Answers in CME designates this enduring material for a maxi</x:v>
+        <x:v>CÓPIA INFORMATIVA VÁLIDA POR 24 HORAS APÓS IMPRESSÃO. A INUTILIZAÇÃO É RESPONSABILIDADE DO USUÁRIO. Impresso em: 01/03/2023 13:14 SUPERINTENDÊNCIA DE VIGILÂNCIA SANITÁRIA/SES- MG PROCEDIMENTO OPERACIONAL PADRÃO Número: POP-Q-DVMC-007 Revisão: 05 Página: 1/9 Vigência: Título: Procedimento de Auditoria Interna 1. INTRODUÇÃO Este documento descreve os passos para auditoria interna dos processos de trabalho de competência da Diretoria de Vigilância em Medicamentos e Congêneres da Superintendência de</x:v>
       </x:c>
       <x:c r="F240" s="32" t="str"/>
       <x:c r="G240" s="32" t="str">
@@ -9280,28 +9280,32 @@
       <x:c r="I240" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J240" s="33"/>
-      <x:c r="K240" s="33"/>
-      <x:c r="L240" s="33"/>
-      <x:c r="M240" s="32" t="str">
-        <x:v>https://answersincme.com/DDT</x:v>
-      </x:c>
+      <x:c r="J240" s="33" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K240" s="33" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="L240" s="33" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="M240" s="32" t="str"/>
     </x:row>
     <x:row r="241">
       <x:c r="A241" s="32" t="n">
         <x:v>239</x:v>
       </x:c>
       <x:c r="B241" s="32" t="str">
-        <x:v>POP-Q-DVMC-007.pdf</x:v>
+        <x:v>pop-q-svs-012-ver-00-auditoria-interna-da-qualidade.pdf</x:v>
       </x:c>
       <x:c r="C241" s="32" t="str">
-        <x:v>POP</x:v>
+        <x:v>pop</x:v>
       </x:c>
       <x:c r="D241" s="32" t="str">
-        <x:v>POP-Q-DVMC-007</x:v>
+        <x:v>pop-q-svs-012-ver-00-auditoria-interna-da-qualidade</x:v>
       </x:c>
       <x:c r="E241" s="32" t="str">
-        <x:v>CÓPIA INFORMATIVA VÁLIDA POR 24 HORAS APÓS IMPRESSÃO. A INUTILIZAÇÃO É RESPONSABILIDADE DO USUÁRIO. Impresso em: 01/03/2023 13:14 SUPERINTENDÊNCIA DE VIGILÂNCIA SANITÁRIA/SES- MG PROCEDIMENTO OPERACIONAL PADRÃO Número: POP-Q-DVMC-007 Revisão: 05 Página: 1/9 Vigência: Título: Procedimento de Auditoria Interna 1. INTRODUÇÃO Este documento descreve os passos para auditoria interna dos processos de trabalho de competência da Diretoria de Vigilância em Medicamentos e Congêneres da Superintendência de</x:v>
+        <x:v>SUPERINTENDÊNCIA DE VIGILÂNCIA SANITÁRIA/SES-MG PROCEDIMENTO OPERACIONAL PADRÃO Número: POP-Q-SVS-012 Versão: 01 Início da Vigência: 18/05/2026 Página 1/11 Título: Auditoria Interna da Qualidade CÓPIA INFORMATIVA VÁLIDA POR 24 HORAS APÓS IMPRESSÃO. A INUTILIZAÇÃO É RESPONSABILIDADE DO USUÁRIO. Impresso em: 04/05/2026 10:54 1. INTRODUÇÃO A Organização deve conduzir auditorias internas em Sistemas de Gestão da Qualidade (SGQ), a intervalos planejados, para prover informação sobre sua conformidade </x:v>
       </x:c>
       <x:c r="F241" s="32" t="str"/>
       <x:c r="G241" s="32" t="str">
@@ -9329,16 +9333,16 @@
         <x:v>240</x:v>
       </x:c>
       <x:c r="B242" s="32" t="str">
-        <x:v>pop-q-svs-012-ver-00-auditoria-interna-da-qualidade.pdf</x:v>
+        <x:v>POP_Q_SVS_001___Gerenciamento_de_Documentos_da_Qualidade___versão_05-POP_Q_SVS_001,_versão_05_43746.pdf</x:v>
       </x:c>
       <x:c r="C242" s="32" t="str">
-        <x:v>pop</x:v>
+        <x:v>POP</x:v>
       </x:c>
       <x:c r="D242" s="32" t="str">
-        <x:v>pop-q-svs-012-ver-00-auditoria-interna-da-qualidade</x:v>
+        <x:v>POP_Q_SVS_001___Gerenciamento_de_Documentos_da_Qualidade___versão_05-POP_Q_SVS_001,_versão_05_43746</x:v>
       </x:c>
       <x:c r="E242" s="32" t="str">
-        <x:v>SUPERINTENDÊNCIA DE VIGILÂNCIA SANITÁRIA/SES-MG PROCEDIMENTO OPERACIONAL PADRÃO Número: POP-Q-SVS-012 Versão: 01 Início da Vigência: 18/05/2026 Página 1/11 Título: Auditoria Interna da Qualidade CÓPIA INFORMATIVA VÁLIDA POR 24 HORAS APÓS IMPRESSÃO. A INUTILIZAÇÃO É RESPONSABILIDADE DO USUÁRIO. Impresso em: 04/05/2026 10:54 1. INTRODUÇÃO A Organização deve conduzir auditorias internas em Sistemas de Gestão da Qualidade (SGQ), a intervalos planejados, para prover informação sobre sua conformidade </x:v>
+        <x:v>Certificamos que Pedro Lamounier Sampaio participou do Curso "POP-Q-SVS-001 - Gerenciamento de Documentos da Qualidade, versão 05", promovido pela Subsecretaria de Vigilância em Saúde por meio da Superintendência de Vigilância Sanitária, com carga horária total de 4 horas/aula, concluído no dia 25 de junho de 2026.</x:v>
       </x:c>
       <x:c r="F242" s="32" t="str"/>
       <x:c r="G242" s="32" t="str">
@@ -9351,13 +9355,13 @@
         <x:v>Extraído do documento</x:v>
       </x:c>
       <x:c r="J242" s="33" t="n">
-        <x:v>24</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K242" s="33" t="n">
-        <x:v>24</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L242" s="33" t="n">
-        <x:v>24</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="M242" s="32" t="str"/>
     </x:row>
@@ -9366,16 +9370,16 @@
         <x:v>241</x:v>
       </x:c>
       <x:c r="B243" s="32" t="str">
-        <x:v>POP_Q_SVS_001___Gerenciamento_de_Documentos_da_Qualidade___versão_05-POP_Q_SVS_001,_versão_05_43746.pdf</x:v>
+        <x:v>problem_solving_skills_turma_ago2026_certificado.pdf</x:v>
       </x:c>
       <x:c r="C243" s="32" t="str">
-        <x:v>POP</x:v>
+        <x:v>problem</x:v>
       </x:c>
       <x:c r="D243" s="32" t="str">
-        <x:v>POP_Q_SVS_001___Gerenciamento_de_Documentos_da_Qualidade___versão_05-POP_Q_SVS_001,_versão_05_43746</x:v>
+        <x:v>problem_solving_skills_turma_ago2026_certificado</x:v>
       </x:c>
       <x:c r="E243" s="32" t="str">
-        <x:v>Certificamos que Pedro Lamounier Sampaio participou do Curso "POP-Q-SVS-001 - Gerenciamento de Documentos da Qualidade, versão 05", promovido pela Subsecretaria de Vigilância em Saúde por meio da Superintendência de Vigilância Sanitária, com carga horária total de 4 horas/aula, concluído no dia 25 de junho de 2026.</x:v>
+        <x:v>The National School of Public Administration - Enap certifies that PEDRO LAMOUNIER SAMPAIO completed the course Problem-Solving Skills (Turma AGO/2026), with workload of 25 hours, beginning in 13/08/2026, end in 16/08/2026 and final grade 93.89.</x:v>
       </x:c>
       <x:c r="F243" s="32" t="str"/>
       <x:c r="G243" s="32" t="str">
@@ -9388,13 +9392,13 @@
         <x:v>Extraído do documento</x:v>
       </x:c>
       <x:c r="J243" s="33" t="n">
-        <x:v>4</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="K243" s="33" t="n">
-        <x:v>4</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="L243" s="33" t="n">
-        <x:v>4</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="M243" s="32" t="str"/>
     </x:row>
@@ -9403,16 +9407,16 @@
         <x:v>242</x:v>
       </x:c>
       <x:c r="B244" s="32" t="str">
-        <x:v>problem_solving_skills_turma_ago2026_certificado.pdf</x:v>
+        <x:v>Processo Civil no pós-pandemia - Certificado ESAOAB.pdf</x:v>
       </x:c>
       <x:c r="C244" s="32" t="str">
-        <x:v>problem</x:v>
+        <x:v>Processo Civil no pós</x:v>
       </x:c>
       <x:c r="D244" s="32" t="str">
-        <x:v>problem_solving_skills_turma_ago2026_certificado</x:v>
+        <x:v>Processo Civil no pós-pandemia - Certificado ESAOAB</x:v>
       </x:c>
       <x:c r="E244" s="32" t="str">
-        <x:v>The National School of Public Administration - Enap certifies that PEDRO LAMOUNIER SAMPAIO completed the course Problem-Solving Skills (Turma AGO/2026), with workload of 25 hours, beginning in 13/08/2026, end in 16/08/2026 and final grade 93.89.</x:v>
+        <x:v>Certiﬁcado O Conselho Federal da Ordem dos Advogados do Brasil certiﬁca que Pedro Lamounier Sampaio concluiu o curso OS DESAFIOS DO PROCESSO CIVIL E O NOVO PANORAMA ECONÔMICO PÓS PANDEMIA, realizado na modalidade à distância, com a carga horária total equivalente a 30 minutos(trinta minutos). Brasília/DF, 01 de Julho de 2026. Gedeon Batista Pitaluga Júnior Diretor-Geral da ESA Nacional Gerado em: 01/07/2026</x:v>
       </x:c>
       <x:c r="F244" s="32" t="str"/>
       <x:c r="G244" s="32" t="str">
@@ -9424,32 +9428,28 @@
       <x:c r="I244" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J244" s="33" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="K244" s="33" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="L244" s="33" t="n">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="M244" s="32" t="str"/>
+      <x:c r="J244" s="33"/>
+      <x:c r="K244" s="33"/>
+      <x:c r="L244" s="33"/>
+      <x:c r="M244" s="32" t="str">
+        <x:v>Carga horária não localizada</x:v>
+      </x:c>
     </x:row>
     <x:row r="245">
       <x:c r="A245" s="32" t="n">
         <x:v>243</x:v>
       </x:c>
       <x:c r="B245" s="32" t="str">
-        <x:v>Processo Civil no pós-pandemia - Certificado ESAOAB.pdf</x:v>
+        <x:v>Project Management Institute (PMI)_6S Green Belt.pdf</x:v>
       </x:c>
       <x:c r="C245" s="32" t="str">
-        <x:v>Processo Civil no pós</x:v>
+        <x:v>Project Management Institute (PMI)</x:v>
       </x:c>
       <x:c r="D245" s="32" t="str">
-        <x:v>Processo Civil no pós-pandemia - Certificado ESAOAB</x:v>
+        <x:v>Project Management Institute (PMI)_6S Green Belt</x:v>
       </x:c>
       <x:c r="E245" s="32" t="str">
-        <x:v>Certiﬁcado O Conselho Federal da Ordem dos Advogados do Brasil certiﬁca que Pedro Lamounier Sampaio concluiu o curso OS DESAFIOS DO PROCESSO CIVIL E O NOVO PANORAMA ECONÔMICO PÓS PANDEMIA, realizado na modalidade à distância, com a carga horária total equivalente a 30 minutos(trinta minutos). Brasília/DF, 01 de Julho de 2026. Gedeon Batista Pitaluga Júnior Diretor-Geral da ESA Nacional Gerado em: 01/07/2026</x:v>
+        <x:v>L i n k e d I n L e a r n i n g Six Sigma: Green Belt Curso concluído por Pedro Lamounier Sampaio Jul 22, 2026 at 09:55PM UTC Principais competências abordadas Six Sigma Green Belt Six Sigma Shea Hanson, Líder de Estratégia de Conteúdos do Learning O logo da PMI Registered Education Provider é marca registrada do Project Management Institute, Inc. Programa: PMI® Registered Education Provider Provider ID: nº4101 Activity #: 4101AJTRSU PDUs/ContactHours: 1.75 Código do certificado: d2a3af823a261cc</x:v>
       </x:c>
       <x:c r="F245" s="32" t="str"/>
       <x:c r="G245" s="32" t="str">
@@ -9473,13 +9473,13 @@
         <x:v>244</x:v>
       </x:c>
       <x:c r="B246" s="32" t="str">
-        <x:v>Project Management Institute (PMI)_6S Green Belt.pdf</x:v>
+        <x:v>Project Management Institute (PMI)®.pdf</x:v>
       </x:c>
       <x:c r="C246" s="32" t="str">
-        <x:v>Project Management Institute (PMI)</x:v>
+        <x:v>Project Management Institute (PMI)®</x:v>
       </x:c>
       <x:c r="D246" s="32" t="str">
-        <x:v>Project Management Institute (PMI)_6S Green Belt</x:v>
+        <x:v>Project Management Institute (PMI)®</x:v>
       </x:c>
       <x:c r="E246" s="32" t="str">
         <x:v>L i n k e d I n L e a r n i n g Six Sigma: Green Belt Curso concluído por Pedro Lamounier Sampaio Jul 22, 2026 at 09:55PM UTC Principais competências abordadas Six Sigma Green Belt Six Sigma Shea Hanson, Líder de Estratégia de Conteúdos do Learning O logo da PMI Registered Education Provider é marca registrada do Project Management Institute, Inc. Programa: PMI® Registered Education Provider Provider ID: nº4101 Activity #: 4101AJTRSU PDUs/ContactHours: 1.75 Código do certificado: d2a3af823a261cc</x:v>
@@ -9506,16 +9506,16 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="B247" s="32" t="str">
-        <x:v>Project Management Institute (PMI)®.pdf</x:v>
+        <x:v>Proteção de dados pessoais - Certificado ESAOAB.pdf</x:v>
       </x:c>
       <x:c r="C247" s="32" t="str">
-        <x:v>Project Management Institute (PMI)®</x:v>
+        <x:v>Proteção de dados pessoais</x:v>
       </x:c>
       <x:c r="D247" s="32" t="str">
-        <x:v>Project Management Institute (PMI)®</x:v>
+        <x:v>Proteção de dados pessoais - Certificado ESAOAB</x:v>
       </x:c>
       <x:c r="E247" s="32" t="str">
-        <x:v>L i n k e d I n L e a r n i n g Six Sigma: Green Belt Curso concluído por Pedro Lamounier Sampaio Jul 22, 2026 at 09:55PM UTC Principais competências abordadas Six Sigma Green Belt Six Sigma Shea Hanson, Líder de Estratégia de Conteúdos do Learning O logo da PMI Registered Education Provider é marca registrada do Project Management Institute, Inc. Programa: PMI® Registered Education Provider Provider ID: nº4101 Activity #: 4101AJTRSU PDUs/ContactHours: 1.75 Código do certificado: d2a3af823a261cc</x:v>
+        <x:v>Certiﬁcado O Conselho Federal da Ordem dos Advogados do Brasil certiﬁca que Pedro Lamounier Sampaio concluiu o curso Proteção de Dados Pessoais, realizado na modalidade à distância, com a carga horária total equivalente a 2h(dois horas). Brasília/DF, 02 de Julho de 2026. Gedeon Batista Pitaluga Júnior Diretor-Geral da ESA Nacional Gerado em: 02/07/2026</x:v>
       </x:c>
       <x:c r="F247" s="32" t="str"/>
       <x:c r="G247" s="32" t="str">
@@ -9527,28 +9527,32 @@
       <x:c r="I247" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J247" s="33"/>
-      <x:c r="K247" s="33"/>
-      <x:c r="L247" s="33"/>
-      <x:c r="M247" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
-      </x:c>
+      <x:c r="J247" s="33" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K247" s="33" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L247" s="33" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M247" s="32" t="str"/>
     </x:row>
     <x:row r="248">
       <x:c r="A248" s="32" t="n">
         <x:v>246</x:v>
       </x:c>
       <x:c r="B248" s="32" t="str">
-        <x:v>Proteção de dados pessoais - Certificado ESAOAB.pdf</x:v>
+        <x:v>Public Health Law Academy_Certificate.pdf</x:v>
       </x:c>
       <x:c r="C248" s="32" t="str">
-        <x:v>Proteção de dados pessoais</x:v>
+        <x:v>Public Health Law Academy</x:v>
       </x:c>
       <x:c r="D248" s="32" t="str">
-        <x:v>Proteção de dados pessoais - Certificado ESAOAB</x:v>
+        <x:v>Public Health Law Academy_Certificate</x:v>
       </x:c>
       <x:c r="E248" s="32" t="str">
-        <x:v>Certiﬁcado O Conselho Federal da Ordem dos Advogados do Brasil certiﬁca que Pedro Lamounier Sampaio concluiu o curso Proteção de Dados Pessoais, realizado na modalidade à distância, com a carga horária total equivalente a 2h(dois horas). Brasília/DF, 02 de Julho de 2026. Gedeon Batista Pitaluga Júnior Diretor-Geral da ESA Nacional Gerado em: 02/07/2026</x:v>
+        <x:v>Pedro Lamounier Sampaio 07/30/2026</x:v>
       </x:c>
       <x:c r="F248" s="32" t="str"/>
       <x:c r="G248" s="32" t="str">
@@ -9560,33 +9564,27 @@
       <x:c r="I248" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J248" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="K248" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="L248" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="M248" s="32" t="str"/>
+      <x:c r="J248" s="33"/>
+      <x:c r="K248" s="33"/>
+      <x:c r="L248" s="33"/>
+      <x:c r="M248" s="32" t="str">
+        <x:v>Carga horária não localizada</x:v>
+      </x:c>
     </x:row>
     <x:row r="249">
       <x:c r="A249" s="32" t="n">
         <x:v>247</x:v>
       </x:c>
       <x:c r="B249" s="32" t="str">
-        <x:v>Public Health Law Academy_Certificate.pdf</x:v>
+        <x:v>Python.pdf</x:v>
       </x:c>
       <x:c r="C249" s="32" t="str">
-        <x:v>Public Health Law Academy</x:v>
+        <x:v>Python</x:v>
       </x:c>
       <x:c r="D249" s="32" t="str">
-        <x:v>Public Health Law Academy_Certificate</x:v>
-      </x:c>
-      <x:c r="E249" s="32" t="str">
-        <x:v>Pedro Lamounier Sampaio 07/30/2026</x:v>
-      </x:c>
+        <x:v>Python</x:v>
+      </x:c>
+      <x:c r="E249" s="32" t="str"/>
       <x:c r="F249" s="32" t="str"/>
       <x:c r="G249" s="32" t="str">
         <x:v>Grupo 1 — Ensino</x:v>
@@ -9595,7 +9593,7 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="I249" s="32" t="str">
-        <x:v>Extraído do documento</x:v>
+        <x:v>Sem texto extraível — revisão manual</x:v>
       </x:c>
       <x:c r="J249" s="33"/>
       <x:c r="K249" s="33"/>
@@ -9609,47 +9607,53 @@
         <x:v>248</x:v>
       </x:c>
       <x:c r="B250" s="32" t="str">
-        <x:v>Python.pdf</x:v>
+        <x:v>Q1 Basics Certificate_554362_48978_3.pdf</x:v>
       </x:c>
       <x:c r="C250" s="32" t="str">
-        <x:v>Python</x:v>
+        <x:v>Q1 Basics Certificate</x:v>
       </x:c>
       <x:c r="D250" s="32" t="str">
-        <x:v>Python</x:v>
-      </x:c>
-      <x:c r="E250" s="32" t="str"/>
+        <x:v>Q1 Basics Certificate_554362_48978_3</x:v>
+      </x:c>
+      <x:c r="E250" s="32" t="str">
+        <x:v>Stanford Center for Continuing Medical Education | cme.stanford.edu | Email: StanfordCME@stanford.edu Event ID 48978 Stanford University School of Medicine certifies that Pedro Lamounier Sampaio, LL.M. has participated for 1.00 hours in the Enduring Material titled SafetyQuest: Level One - QI Basics on 07/06/2026 This Activity was designated for 2.00 AMA PRA Category 1 Credit(s)™ Accreditation In support of improving patient care, Stanford Medicine is jointly accredited by the Accreditation Coun</x:v>
+      </x:c>
       <x:c r="F250" s="32" t="str"/>
       <x:c r="G250" s="32" t="str">
-        <x:v>Grupo 1 — Ensino</x:v>
+        <x:v>Grupo 3 — Extensão</x:v>
       </x:c>
       <x:c r="H250" s="32" t="str">
-        <x:v>1.5</x:v>
+        <x:v>3.1</x:v>
       </x:c>
       <x:c r="I250" s="32" t="str">
-        <x:v>Sem texto extraível — revisão manual</x:v>
-      </x:c>
-      <x:c r="J250" s="33"/>
-      <x:c r="K250" s="33"/>
-      <x:c r="L250" s="33"/>
-      <x:c r="M250" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
-      </x:c>
+        <x:v>Extraído do documento</x:v>
+      </x:c>
+      <x:c r="J250" s="33" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K250" s="33" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L250" s="33" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M250" s="32" t="str"/>
     </x:row>
     <x:row r="251">
       <x:c r="A251" s="32" t="n">
         <x:v>249</x:v>
       </x:c>
       <x:c r="B251" s="32" t="str">
-        <x:v>Q1 Basics Certificate_554362_48978_3.pdf</x:v>
+        <x:v>Q1 Basics_Certificate_CE_554362_48978_3.pdf</x:v>
       </x:c>
       <x:c r="C251" s="32" t="str">
-        <x:v>Q1 Basics Certificate</x:v>
+        <x:v>Q1 Basics</x:v>
       </x:c>
       <x:c r="D251" s="32" t="str">
-        <x:v>Q1 Basics Certificate_554362_48978_3</x:v>
+        <x:v>Q1 Basics_Certificate_CE_554362_48978_3</x:v>
       </x:c>
       <x:c r="E251" s="32" t="str">
-        <x:v>Stanford Center for Continuing Medical Education | cme.stanford.edu | Email: StanfordCME@stanford.edu Event ID 48978 Stanford University School of Medicine certifies that Pedro Lamounier Sampaio, LL.M. has participated for 1.00 hours in the Enduring Material titled SafetyQuest: Level One - QI Basics on 07/06/2026 This Activity was designated for 2.00 AMA PRA Category 1 Credit(s)™ Accreditation In support of improving patient care, Stanford Medicine is jointly accredited by the Accreditation Coun</x:v>
+        <x:v>Stanford Center for Continuing Medical Education | cme.stanford.edu | Email: StanfordCME@stanford.edu Event ID 48978 Stanford University School of Medicine certifies that Pedro Lamounier Sampaio, LL.M. has participated for 2.00 hours in the Enduring Material titled SafetyQuest: Level One - QI Basics on 07/06/2026 This Activity was designated for 2.00 AMA PRA Category 1 Credit(s)™ Accreditation In support of improving patient care, Stanford Medicine is jointly accredited by the Accreditation Coun</x:v>
       </x:c>
       <x:c r="F251" s="32" t="str"/>
       <x:c r="G251" s="32" t="str">
@@ -9662,13 +9666,13 @@
         <x:v>Extraído do documento</x:v>
       </x:c>
       <x:c r="J251" s="33" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K251" s="33" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L251" s="33" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="M251" s="32" t="str"/>
     </x:row>
@@ -9677,60 +9681,56 @@
         <x:v>250</x:v>
       </x:c>
       <x:c r="B252" s="32" t="str">
-        <x:v>Q1 Basics_Certificate_CE_554362_48978_3.pdf</x:v>
+        <x:v>QMS_ISO 19011-2026_Fundamentos_Certificado 0014912.pdf</x:v>
       </x:c>
       <x:c r="C252" s="32" t="str">
-        <x:v>Q1 Basics</x:v>
+        <x:v>QMS</x:v>
       </x:c>
       <x:c r="D252" s="32" t="str">
-        <x:v>Q1 Basics_Certificate_CE_554362_48978_3</x:v>
+        <x:v>QMS_ISO 19011-2026_Fundamentos_Certificado 0014912</x:v>
       </x:c>
       <x:c r="E252" s="32" t="str">
-        <x:v>Stanford Center for Continuing Medical Education | cme.stanford.edu | Email: StanfordCME@stanford.edu Event ID 48978 Stanford University School of Medicine certifies that Pedro Lamounier Sampaio, LL.M. has participated for 2.00 hours in the Enduring Material titled SafetyQuest: Level One - QI Basics on 07/06/2026 This Activity was designated for 2.00 AMA PRA Category 1 Credit(s)™ Accreditation In support of improving patient care, Stanford Medicine is jointly accredited by the Accreditation Coun</x:v>
+        <x:v>PEDRO LAMOUNIER SAMPAIO Fundamentos da ISO 19011:2026 Diretrizes para Auditorias de Sistemas de Gestão</x:v>
       </x:c>
       <x:c r="F252" s="32" t="str"/>
       <x:c r="G252" s="32" t="str">
-        <x:v>Grupo 3 — Extensão</x:v>
+        <x:v>Grupo 1 — Ensino</x:v>
       </x:c>
       <x:c r="H252" s="32" t="str">
-        <x:v>3.1</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="I252" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J252" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="K252" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="L252" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="M252" s="32" t="str"/>
+      <x:c r="J252" s="33"/>
+      <x:c r="K252" s="33"/>
+      <x:c r="L252" s="33"/>
+      <x:c r="M252" s="32" t="str">
+        <x:v>Carga horária não localizada</x:v>
+      </x:c>
     </x:row>
     <x:row r="253">
       <x:c r="A253" s="32" t="n">
         <x:v>251</x:v>
       </x:c>
       <x:c r="B253" s="32" t="str">
-        <x:v>QMS_ISO 19011-2026_Fundamentos_Certificado 0014912.pdf</x:v>
+        <x:v>Relatório_Extensao_CEPROC.pdf</x:v>
       </x:c>
       <x:c r="C253" s="32" t="str">
-        <x:v>QMS</x:v>
+        <x:v>Relatório</x:v>
       </x:c>
       <x:c r="D253" s="32" t="str">
-        <x:v>QMS_ISO 19011-2026_Fundamentos_Certificado 0014912</x:v>
+        <x:v>Relatório_Extensao_CEPROC</x:v>
       </x:c>
       <x:c r="E253" s="32" t="str">
-        <x:v>PEDRO LAMOUNIER SAMPAIO Fundamentos da ISO 19011:2026 Diretrizes para Auditorias de Sistemas de Gestão</x:v>
+        <x:v>1 IDENTIFICAÇÃO Registro 203797 Aprovado pelo CENEX 28/05/2019 - Faculdade de Direito Status Atividade em desenvolvimento Título Fundamentação das Decisões Judiciais:desafios e perspectivas Data de início 05/06/2019 Previsão de término 05/06/2019 Prazo de vigência 05/06/2019 CARACTERIZAÇÃO Ano em que se iniciou a atividade 2019 Unidade/Órgão de execução Faculdade de Direito Departamento/Setor de execução Departamento de Direito e Processo Civil e Comercial Caracterização Seminários e Eventos Aná</x:v>
       </x:c>
       <x:c r="F253" s="32" t="str"/>
       <x:c r="G253" s="32" t="str">
-        <x:v>Grupo 1 — Ensino</x:v>
+        <x:v>Grupo 3 — Extensão</x:v>
       </x:c>
       <x:c r="H253" s="32" t="str">
-        <x:v>1.5</x:v>
+        <x:v>3.1</x:v>
       </x:c>
       <x:c r="I253" s="32" t="str">
         <x:v>Extraído do documento</x:v>
@@ -9747,16 +9747,16 @@
         <x:v>252</x:v>
       </x:c>
       <x:c r="B254" s="32" t="str">
-        <x:v>Receipt for Order 394583203.pdf</x:v>
+        <x:v>revivr-CPR_certificate_2026.08.22.pdf</x:v>
       </x:c>
       <x:c r="C254" s="32" t="str">
-        <x:v>Receipt for Order 394583203</x:v>
+        <x:v>revivr</x:v>
       </x:c>
       <x:c r="D254" s="32" t="str">
-        <x:v>Receipt for Order 394583203</x:v>
+        <x:v>revivr-CPR_certificate_2026.08.22</x:v>
       </x:c>
       <x:c r="E254" s="32" t="str">
-        <x:v>Pedro Lamounier Sampaio &lt;plamouniersampaio55@gmail.com&gt; Your Receipt for Order #394583203 Coursera &lt;no-reply@t.learn.coursera.org&gt; seg., 20 de jul., 04:38 Para: &lt;plamouniersampaio55@gmail.com&gt; Dear Pedro Lamounier Sampaio, Thank you for your purchase RECEIPT Coursera Inc. 381 E. Evelyn Avenue Mountain View, CA 94041 USA 07/09/2025 Order Number: 394583203 Product Details Price Qty Professional Certificate Subscription: Johns Hopkins Medical Office Manager USD 49.001 TOTAL (USD): 49.00 Please keep</x:v>
+        <x:v>/C_ertifica/t_e of RevivR comp/l_etionBritish Heart Foundation certifies that has completed lifesaving CPR training with RevivR. Together, we’ll help increase the survival rate of out-of-hospital cardiac arrests. Date: bhf.org.uk/revivr Dr Charmaine Griffiths Chief Executive, British Heart Foundation © British Heart Foundation 2023, a registered charity in England and Wales (225971) and Scotland (SC039426). Re/m_ember re/f_resh your CPR skills every six mon/t_hs using RevivR. 23 Aug 2026 Pedro L</x:v>
       </x:c>
       <x:c r="F254" s="32" t="str"/>
       <x:c r="G254" s="32" t="str">
@@ -9780,32 +9780,38 @@
         <x:v>253</x:v>
       </x:c>
       <x:c r="B255" s="32" t="str">
-        <x:v>Relatório_Extensao_CEPROC.pdf</x:v>
+        <x:v>Said-Oxford-Coursera_Agentic and GenAI_Certificate5YR8YBKNEOIC.pdf</x:v>
       </x:c>
       <x:c r="C255" s="32" t="str">
-        <x:v>Relatório</x:v>
+        <x:v>Saïd Business School, University of Oxford</x:v>
       </x:c>
       <x:c r="D255" s="32" t="str">
-        <x:v>Relatório_Extensao_CEPROC</x:v>
+        <x:v>Generative and Agentic AI</x:v>
       </x:c>
       <x:c r="E255" s="32" t="str">
-        <x:v>1 IDENTIFICAÇÃO Registro 203797 Aprovado pelo CENEX 28/05/2019 - Faculdade de Direito Status Atividade em desenvolvimento Título Fundamentação das Decisões Judiciais:desafios e perspectivas Data de início 05/06/2019 Previsão de término 05/06/2019 Prazo de vigência 05/06/2019 CARACTERIZAÇÃO Ano em que se iniciou a atividade 2019 Unidade/Órgão de execução Faculdade de Direito Departamento/Setor de execução Departamento de Direito e Processo Civil e Comercial Caracterização Seminários e Eventos Aná</x:v>
+        <x:v>A u g 1 4 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o G e n e r a t i v e a n d A g e n t i c A I a n o n l i n e c o u r s e a u t h o r i z e d b y S a ï d B u s i n e s s S c h o o l , U n i v e r s i t y o f O x f o r d a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d M a t t h i a s H o l w e g A m e r i c a n S t a n d a r d C o m p a n i e s P r o f e s s o r o f O p e r a t i o n s M a n a g e m e n t S a ï d B u s i n e s s S c h </x:v>
       </x:c>
       <x:c r="F255" s="32" t="str"/>
       <x:c r="G255" s="32" t="str">
-        <x:v>Grupo 3 — Extensão</x:v>
+        <x:v>Grupo 1 — Ensino</x:v>
       </x:c>
       <x:c r="H255" s="32" t="str">
-        <x:v>3.1</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="I255" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J255" s="33"/>
-      <x:c r="K255" s="33"/>
-      <x:c r="L255" s="33"/>
+      <x:c r="J255" s="33" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="K255" s="33" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="L255" s="33" t="n">
+        <x:v>13</x:v>
+      </x:c>
       <x:c r="M255" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/5YR8YBKNEOIC</x:v>
       </x:c>
     </x:row>
     <x:row r="256">
@@ -9813,16 +9819,16 @@
         <x:v>254</x:v>
       </x:c>
       <x:c r="B256" s="32" t="str">
-        <x:v>revivr-CPR_certificate_2026.08.22.pdf</x:v>
+        <x:v>Said-Oxford-Coursera_AI Essentials_Certificate EN2VCPK6A775.pdf</x:v>
       </x:c>
       <x:c r="C256" s="32" t="str">
-        <x:v>revivr</x:v>
+        <x:v>Saïd Business School, University of Oxford</x:v>
       </x:c>
       <x:c r="D256" s="32" t="str">
-        <x:v>revivr-CPR_certificate_2026.08.22</x:v>
+        <x:v>AI Essentials</x:v>
       </x:c>
       <x:c r="E256" s="32" t="str">
-        <x:v>/C_ertifica/t_e of RevivR comp/l_etionBritish Heart Foundation certifies that has completed lifesaving CPR training with RevivR. Together, we’ll help increase the survival rate of out-of-hospital cardiac arrests. Date: bhf.org.uk/revivr Dr Charmaine Griffiths Chief Executive, British Heart Foundation © British Heart Foundation 2023, a registered charity in England and Wales (225971) and Scotland (SC039426). Re/m_ember re/f_resh your CPR skills every six mon/t_hs using RevivR. 23 Aug 2026 Pedro L</x:v>
+        <x:v>A u g 1 3 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o A I E s s e n t i a l s a n o n l i n e c o u r s e a u t h o r i z e d b y S a ï d B u s i n e s s S c h o o l , U n i v e r s i t y o f O x f o r d a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d M a t t h i a s H o l w e g A m e r i c a n S t a n d a r d C o m p a n i e s P r o f e s s o r o f O p e r a t i o n s M a n a g e m e n t S a ï d B u s i n e s s S c h o o l U n i v e r s </x:v>
       </x:c>
       <x:c r="F256" s="32" t="str"/>
       <x:c r="G256" s="32" t="str">
@@ -9834,11 +9840,17 @@
       <x:c r="I256" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J256" s="33"/>
-      <x:c r="K256" s="33"/>
-      <x:c r="L256" s="33"/>
+      <x:c r="J256" s="33" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="K256" s="33" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="L256" s="33" t="n">
+        <x:v>13</x:v>
+      </x:c>
       <x:c r="M256" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/EN2VCPK6A775</x:v>
       </x:c>
     </x:row>
     <x:row r="257">
@@ -9846,16 +9858,16 @@
         <x:v>255</x:v>
       </x:c>
       <x:c r="B257" s="32" t="str">
-        <x:v>Said-Oxford-Coursera_Agentic and GenAI_Certificate5YR8YBKNEOIC.pdf</x:v>
+        <x:v>Said-Oxford-Coursera_AI Governance_Certificate_FWGA4AWODSM4.pdf</x:v>
       </x:c>
       <x:c r="C257" s="32" t="str">
         <x:v>Saïd Business School, University of Oxford</x:v>
       </x:c>
       <x:c r="D257" s="32" t="str">
-        <x:v>Generative and Agentic AI</x:v>
+        <x:v>AI Governance</x:v>
       </x:c>
       <x:c r="E257" s="32" t="str">
-        <x:v>A u g 1 4 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o G e n e r a t i v e a n d A g e n t i c A I a n o n l i n e c o u r s e a u t h o r i z e d b y S a ï d B u s i n e s s S c h o o l , U n i v e r s i t y o f O x f o r d a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d M a t t h i a s H o l w e g A m e r i c a n S t a n d a r d C o m p a n i e s P r o f e s s o r o f O p e r a t i o n s M a n a g e m e n t S a ï d B u s i n e s s S c h </x:v>
+        <x:v>A u g 1 4 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o A I G o v e r n a n c e a n o n l i n e c o u r s e a u t h o r i z e d b y S a ï d B u s i n e s s S c h o o l , U n i v e r s i t y o f O x f o r d a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d M a t t h i a s H o l w e g A m e r i c a n S t a n d a r d C o m p a n i e s P r o f e s s o r o f O p e r a t i o n s M a n a g e m e n t S a ï d B u s i n e s s S c h o o l U n i v e r s </x:v>
       </x:c>
       <x:c r="F257" s="32" t="str"/>
       <x:c r="G257" s="32" t="str">
@@ -9868,16 +9880,16 @@
         <x:v>Extraído do documento</x:v>
       </x:c>
       <x:c r="J257" s="33" t="n">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K257" s="33" t="n">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="L257" s="33" t="n">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="M257" s="32" t="str">
-        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/5YR8YBKNEOIC</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/FWGA4AWODSM4</x:v>
       </x:c>
     </x:row>
     <x:row r="258">
@@ -9885,16 +9897,16 @@
         <x:v>256</x:v>
       </x:c>
       <x:c r="B258" s="32" t="str">
-        <x:v>Said-Oxford-Coursera_AI Essentials_Certificate EN2VCPK6A775.pdf</x:v>
+        <x:v>Said-Oxford-Coursera_Specialization AI for Business_Certificate_FWGA4AWODSM4.pdf</x:v>
       </x:c>
       <x:c r="C258" s="32" t="str">
         <x:v>Saïd Business School, University of Oxford</x:v>
       </x:c>
       <x:c r="D258" s="32" t="str">
-        <x:v>AI Essentials</x:v>
+        <x:v>AI for Business</x:v>
       </x:c>
       <x:c r="E258" s="32" t="str">
-        <x:v>A u g 1 3 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o A I E s s e n t i a l s a n o n l i n e c o u r s e a u t h o r i z e d b y S a ï d B u s i n e s s S c h o o l , U n i v e r s i t y o f O x f o r d a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d M a t t h i a s H o l w e g A m e r i c a n S t a n d a r d C o m p a n i e s P r o f e s s o r o f O p e r a t i o n s M a n a g e m e n t S a ï d B u s i n e s s S c h o o l U n i v e r s </x:v>
+        <x:v>3 C o u r s e s A I E s s e n t i a l s G e n e r a t i v e a n d A g e n t i c A I A I G o v e r n a n c e M a t t h i a s H o l w e g A m e r i c a n S t a n d a r d C o m p a n i e s P r o f e s s o r o f O p e r a t i o n s M a n a g e m e n t S a ï d B u s i n e s s S c h o o l U n i v e r s i t y o f O x f o r d A u g 1 4 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o h a s s u c c e s s f u l l y c o m p l e t e d t h e o n l i n e S p e c i a l i z a t i o n A I F o u n d a t i o n </x:v>
       </x:c>
       <x:c r="F258" s="32" t="str"/>
       <x:c r="G258" s="32" t="str">
@@ -9906,17 +9918,11 @@
       <x:c r="I258" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J258" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="K258" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="L258" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
+      <x:c r="J258" s="33"/>
+      <x:c r="K258" s="33"/>
+      <x:c r="L258" s="33"/>
       <x:c r="M258" s="32" t="str">
-        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/EN2VCPK6A775</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/specialization/FWGA4AWODSM4</x:v>
       </x:c>
     </x:row>
     <x:row r="259">
@@ -9924,16 +9930,16 @@
         <x:v>257</x:v>
       </x:c>
       <x:c r="B259" s="32" t="str">
-        <x:v>Said-Oxford-Coursera_AI Governance_Certificate_FWGA4AWODSM4.pdf</x:v>
+        <x:v>SkillFront-ISO 9001_Associate_Certificate_SFE0232f5d549bbc-96337181584206.pdf</x:v>
       </x:c>
       <x:c r="C259" s="32" t="str">
-        <x:v>Saïd Business School, University of Oxford</x:v>
+        <x:v>SkillFront</x:v>
       </x:c>
       <x:c r="D259" s="32" t="str">
-        <x:v>AI Governance</x:v>
+        <x:v>SkillFront-ISO 9001_Associate_Certificate_SFE0232f5d549bbc-96337181584206</x:v>
       </x:c>
       <x:c r="E259" s="32" t="str">
-        <x:v>A u g 1 4 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o A I G o v e r n a n c e a n o n l i n e c o u r s e a u t h o r i z e d b y S a ï d B u s i n e s s S c h o o l , U n i v e r s i t y o f O x f o r d a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d M a t t h i a s H o l w e g A m e r i c a n S t a n d a r d C o m p a n i e s P r o f e s s o r o f O p e r a t i o n s M a n a g e m e n t S a ï d B u s i n e s s S c h o o l U n i v e r s </x:v>
+        <x:v>ISO 9001 QUALITY MANAGEMENT SYSTEMS ASSOCIATE™ PEDRO LAMOUNIER SAMPAIO 9633718158420629 AUGUST 2026</x:v>
       </x:c>
       <x:c r="F259" s="32" t="str"/>
       <x:c r="G259" s="32" t="str">
@@ -9945,17 +9951,11 @@
       <x:c r="I259" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J259" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="K259" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="L259" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
+      <x:c r="J259" s="33"/>
+      <x:c r="K259" s="33"/>
+      <x:c r="L259" s="33"/>
       <x:c r="M259" s="32" t="str">
-        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/FWGA4AWODSM4</x:v>
+        <x:v>Carga horária não localizada</x:v>
       </x:c>
     </x:row>
     <x:row r="260">
@@ -9963,16 +9963,16 @@
         <x:v>258</x:v>
       </x:c>
       <x:c r="B260" s="32" t="str">
-        <x:v>Said-Oxford-Coursera_Specialization AI for Business_Certificate_FWGA4AWODSM4.pdf</x:v>
+        <x:v>SkillFront_ISO 27001 ISMS Associate SFE0166da11827fd-47327192991292_Certificate.pdf</x:v>
       </x:c>
       <x:c r="C260" s="32" t="str">
-        <x:v>Saïd Business School, University of Oxford</x:v>
+        <x:v>SkillFront</x:v>
       </x:c>
       <x:c r="D260" s="32" t="str">
-        <x:v>AI for Business</x:v>
+        <x:v>SkillFront_ISO 27001 ISMS Associate SFE0166da11827fd-47327192991292_Certificate</x:v>
       </x:c>
       <x:c r="E260" s="32" t="str">
-        <x:v>3 C o u r s e s A I E s s e n t i a l s G e n e r a t i v e a n d A g e n t i c A I A I G o v e r n a n c e M a t t h i a s H o l w e g A m e r i c a n S t a n d a r d C o m p a n i e s P r o f e s s o r o f O p e r a t i o n s M a n a g e m e n t S a ï d B u s i n e s s S c h o o l U n i v e r s i t y o f O x f o r d A u g 1 4 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o h a s s u c c e s s f u l l y c o m p l e t e d t h e o n l i n e S p e c i a l i z a t i o n A I F o u n d a t i o n </x:v>
+        <x:v>ISO/IEC 27001:2022 INFORMATION SECURITY ASSOCIATE™ PEDRO LAMOUNIER SAMPAIO 4732719299129218 AUGUST 2026</x:v>
       </x:c>
       <x:c r="F260" s="32" t="str"/>
       <x:c r="G260" s="32" t="str">
@@ -9988,7 +9988,7 @@
       <x:c r="K260" s="33"/>
       <x:c r="L260" s="33"/>
       <x:c r="M260" s="32" t="str">
-        <x:v>Coursera: https://www.coursera.org/account/accomplishments/specialization/FWGA4AWODSM4</x:v>
+        <x:v>Carga horária não localizada</x:v>
       </x:c>
     </x:row>
     <x:row r="261">
@@ -9996,82 +9996,90 @@
         <x:v>259</x:v>
       </x:c>
       <x:c r="B261" s="32" t="str">
-        <x:v>SkillFront-ISO 9001_Associate_Certificate_SFE0232f5d549bbc-96337181584206.pdf</x:v>
+        <x:v>Stanford CME-CE - AI thinking in healthcare_554362_56997_3.pdf</x:v>
       </x:c>
       <x:c r="C261" s="32" t="str">
-        <x:v>SkillFront</x:v>
+        <x:v>Stanford CME</x:v>
       </x:c>
       <x:c r="D261" s="32" t="str">
-        <x:v>SkillFront-ISO 9001_Associate_Certificate_SFE0232f5d549bbc-96337181584206</x:v>
+        <x:v>Stanford CME-CE - AI thinking in healthcare_554362_56997_3</x:v>
       </x:c>
       <x:c r="E261" s="32" t="str">
-        <x:v>ISO 9001 QUALITY MANAGEMENT SYSTEMS ASSOCIATE™ PEDRO LAMOUNIER SAMPAIO 9633718158420629 AUGUST 2026</x:v>
+        <x:v>Stanford Center for Continuing Medical Education | cme.stanford.edu | Email: StanfordCME@stanford.edu Event ID 56997 Stanford University School of Medicine certifies that Pedro Lamounier Sampaio, LL.M. has participated for 0.50 hours in the Enduring Material titled Stanford Medcast Episode 114: Emerging Technology Mini-Series: AI as a Thinking Partner in Medicine on 08/10/2026 This Activity was designated for 0.50 AMA PRA Category 1 Credit(s)™ Accreditation In support of improving patient care, </x:v>
       </x:c>
       <x:c r="F261" s="32" t="str"/>
       <x:c r="G261" s="32" t="str">
-        <x:v>Grupo 1 — Ensino</x:v>
+        <x:v>Grupo 3 — Extensão</x:v>
       </x:c>
       <x:c r="H261" s="32" t="str">
-        <x:v>1.5</x:v>
+        <x:v>3.1</x:v>
       </x:c>
       <x:c r="I261" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J261" s="33"/>
-      <x:c r="K261" s="33"/>
-      <x:c r="L261" s="33"/>
-      <x:c r="M261" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
-      </x:c>
+      <x:c r="J261" s="33" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="K261" s="33" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="L261" s="33" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="M261" s="32" t="str"/>
     </x:row>
     <x:row r="262">
       <x:c r="A262" s="32" t="n">
         <x:v>260</x:v>
       </x:c>
       <x:c r="B262" s="32" t="str">
-        <x:v>SkillFront_ISO 27001 ISMS Associate SFE0166da11827fd-47327192991292_Certificate.pdf</x:v>
+        <x:v>Stanford CME_Trends in Precision Medicine Certificate_554362_56922_3.pdf</x:v>
       </x:c>
       <x:c r="C262" s="32" t="str">
-        <x:v>SkillFront</x:v>
+        <x:v>Stanford CME</x:v>
       </x:c>
       <x:c r="D262" s="32" t="str">
-        <x:v>SkillFront_ISO 27001 ISMS Associate SFE0166da11827fd-47327192991292_Certificate</x:v>
+        <x:v>Stanford CME_Trends in Precision Medicine Certificate_554362_56922_3</x:v>
       </x:c>
       <x:c r="E262" s="32" t="str">
-        <x:v>ISO/IEC 27001:2022 INFORMATION SECURITY ASSOCIATE™ PEDRO LAMOUNIER SAMPAIO 4732719299129218 AUGUST 2026</x:v>
+        <x:v>Stanford Center for Continuing Medical Education | cme.stanford.edu | Email: StanfordCME@stanford.edu Event ID 56922 Stanford University School of Medicine certifies that Pedro Lamounier Sampaio, LL.M. has participated for 0.50 hours in the Enduring Material titled Stanford Medcast Episode 113: From Data to Decisions: The Future of Precision Medicine in Practice on 08/25/2026 This Activity was designated for 0.50 AMA PRA Category 1 Credit(s)™ Accreditation In support of improving patient care, S</x:v>
       </x:c>
       <x:c r="F262" s="32" t="str"/>
       <x:c r="G262" s="32" t="str">
-        <x:v>Grupo 1 — Ensino</x:v>
+        <x:v>Grupo 3 — Extensão</x:v>
       </x:c>
       <x:c r="H262" s="32" t="str">
-        <x:v>1.5</x:v>
+        <x:v>3.1</x:v>
       </x:c>
       <x:c r="I262" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J262" s="33"/>
-      <x:c r="K262" s="33"/>
-      <x:c r="L262" s="33"/>
-      <x:c r="M262" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
-      </x:c>
+      <x:c r="J262" s="33" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="K262" s="33" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="L262" s="33" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="M262" s="32" t="str"/>
     </x:row>
     <x:row r="263">
       <x:c r="A263" s="32" t="n">
         <x:v>261</x:v>
       </x:c>
       <x:c r="B263" s="32" t="str">
-        <x:v>Stanford CME-CE - AI thinking in healthcare_554362_56997_3.pdf</x:v>
+        <x:v>Stanford Med_AI in Healthcare Capstone_554362_39163_3.pdf</x:v>
       </x:c>
       <x:c r="C263" s="32" t="str">
-        <x:v>Stanford CME</x:v>
+        <x:v>Stanford Med</x:v>
       </x:c>
       <x:c r="D263" s="32" t="str">
-        <x:v>Stanford CME-CE - AI thinking in healthcare_554362_56997_3</x:v>
+        <x:v>Stanford Med_AI in Healthcare Capstone_554362_39163_3</x:v>
       </x:c>
       <x:c r="E263" s="32" t="str">
-        <x:v>Stanford Center for Continuing Medical Education | cme.stanford.edu | Email: StanfordCME@stanford.edu Event ID 56997 Stanford University School of Medicine certifies that Pedro Lamounier Sampaio, LL.M. has participated for 0.50 hours in the Enduring Material titled Stanford Medcast Episode 114: Emerging Technology Mini-Series: AI as a Thinking Partner in Medicine on 08/10/2026 This Activity was designated for 0.50 AMA PRA Category 1 Credit(s)™ Accreditation In support of improving patient care, </x:v>
+        <x:v>Stanford Center for Continuing Medical Education | cme.stanford.edu | Email: StanfordCME@stanford.edu Event ID 39163 Stanford University School of Medicine certifies that Pedro Lamounier Sampaio, LL.M. has participated for 11.00 hours in the Enduring Material titled AI Series: AI in Healthcare Capstone Project on 08/01/2026 This Activity was designated for 11.00 AMA PRA Category 1 Credit(s)™ Accreditation In support of improving patient care, Stanford Medicine is jointly accredited by the Accred</x:v>
       </x:c>
       <x:c r="F263" s="32" t="str"/>
       <x:c r="G263" s="32" t="str">
@@ -10084,13 +10092,13 @@
         <x:v>Extraído do documento</x:v>
       </x:c>
       <x:c r="J263" s="33" t="n">
-        <x:v>0.5</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="K263" s="33" t="n">
-        <x:v>0.5</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L263" s="33" t="n">
-        <x:v>0.5</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="M263" s="32" t="str"/>
     </x:row>
@@ -10099,16 +10107,16 @@
         <x:v>262</x:v>
       </x:c>
       <x:c r="B264" s="32" t="str">
-        <x:v>Stanford CME_Trends in Precision Medicine Certificate_554362_56922_3.pdf</x:v>
+        <x:v>Stanford Medicine_554362_47051_3_AI in Healthcare Certificate.pdf</x:v>
       </x:c>
       <x:c r="C264" s="32" t="str">
-        <x:v>Stanford CME</x:v>
+        <x:v>Stanford Medicine</x:v>
       </x:c>
       <x:c r="D264" s="32" t="str">
-        <x:v>Stanford CME_Trends in Precision Medicine Certificate_554362_56922_3</x:v>
+        <x:v>Stanford Medicine_554362_47051_3_AI in Healthcare Certificate</x:v>
       </x:c>
       <x:c r="E264" s="32" t="str">
-        <x:v>Stanford Center for Continuing Medical Education | cme.stanford.edu | Email: StanfordCME@stanford.edu Event ID 56922 Stanford University School of Medicine certifies that Pedro Lamounier Sampaio, LL.M. has participated for 0.50 hours in the Enduring Material titled Stanford Medcast Episode 113: From Data to Decisions: The Future of Precision Medicine in Practice on 08/25/2026 This Activity was designated for 0.50 AMA PRA Category 1 Credit(s)™ Accreditation In support of improving patient care, S</x:v>
+        <x:v>Stanford Center for Continuing Medical Education | cme.stanford.edu | Email: StanfordCME@stanford.edu Event ID 47051 Stanford University School of Medicine certifies that Pedro Lamounier Sampaio, LL.M. has participated for 12.00 hours in the Enduring Material titled AI Series: Introduction to Healthcare on 07/28/2026 This Activity was designated for 12.00 AMA PRA Category 1 Credit(s)™ Accreditation In support of improving patient care, Stanford Medicine is jointly accredited by the Accreditation</x:v>
       </x:c>
       <x:c r="F264" s="32" t="str"/>
       <x:c r="G264" s="32" t="str">
@@ -10121,13 +10129,13 @@
         <x:v>Extraído do documento</x:v>
       </x:c>
       <x:c r="J264" s="33" t="n">
-        <x:v>0.5</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="K264" s="33" t="n">
-        <x:v>0.5</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L264" s="33" t="n">
-        <x:v>0.5</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="M264" s="32" t="str"/>
     </x:row>
@@ -10136,13 +10144,13 @@
         <x:v>263</x:v>
       </x:c>
       <x:c r="B265" s="32" t="str">
-        <x:v>Stanford Med_AI in Healthcare Capstone_554362_39163_3.pdf</x:v>
+        <x:v>Stanford Medicine_AI in Healthcare Capstone Project Certificate_554362_39163_3.pdf</x:v>
       </x:c>
       <x:c r="C265" s="32" t="str">
-        <x:v>Stanford Med</x:v>
+        <x:v>Stanford Medicine</x:v>
       </x:c>
       <x:c r="D265" s="32" t="str">
-        <x:v>Stanford Med_AI in Healthcare Capstone_554362_39163_3</x:v>
+        <x:v>Stanford Medicine_AI in Healthcare Capstone Project Certificate_554362_39163_3</x:v>
       </x:c>
       <x:c r="E265" s="32" t="str">
         <x:v>Stanford Center for Continuing Medical Education | cme.stanford.edu | Email: StanfordCME@stanford.edu Event ID 39163 Stanford University School of Medicine certifies that Pedro Lamounier Sampaio, LL.M. has participated for 11.00 hours in the Enduring Material titled AI Series: AI in Healthcare Capstone Project on 08/01/2026 This Activity was designated for 11.00 AMA PRA Category 1 Credit(s)™ Accreditation In support of improving patient care, Stanford Medicine is jointly accredited by the Accred</x:v>
@@ -10173,16 +10181,16 @@
         <x:v>264</x:v>
       </x:c>
       <x:c r="B266" s="32" t="str">
-        <x:v>Stanford Medicine_554362_47051_3_AI in Healthcare Certificate.pdf</x:v>
+        <x:v>Stanford Medicine_Antimicrobial Stewardship_CME-CE Certificate_554362_49027_3.pdf</x:v>
       </x:c>
       <x:c r="C266" s="32" t="str">
         <x:v>Stanford Medicine</x:v>
       </x:c>
       <x:c r="D266" s="32" t="str">
-        <x:v>Stanford Medicine_554362_47051_3_AI in Healthcare Certificate</x:v>
+        <x:v>Stanford Medicine_Antimicrobial Stewardship_CME-CE Certificate_554362_49027_3</x:v>
       </x:c>
       <x:c r="E266" s="32" t="str">
-        <x:v>Stanford Center for Continuing Medical Education | cme.stanford.edu | Email: StanfordCME@stanford.edu Event ID 47051 Stanford University School of Medicine certifies that Pedro Lamounier Sampaio, LL.M. has participated for 12.00 hours in the Enduring Material titled AI Series: Introduction to Healthcare on 07/28/2026 This Activity was designated for 12.00 AMA PRA Category 1 Credit(s)™ Accreditation In support of improving patient care, Stanford Medicine is jointly accredited by the Accreditation</x:v>
+        <x:v>Stanford Center for Continuing Medical Education | cme.stanford.edu | Email: StanfordCME@stanford.edu Event ID 49027 Stanford University School of Medicine certifies that Pedro Lamounier Sampaio, LL.M. has participated for 7.00 hours in the Enduring Material titled Antimicrobial Stewardship: Improving Clinical Outcomes by Optimization of Antibiotic Practices on 08/30/2026 This Activity was designated for 7.00 AMA PRA Category 1 Credit(s)™ Accreditation In support of improving patient care, Stanf</x:v>
       </x:c>
       <x:c r="F266" s="32" t="str"/>
       <x:c r="G266" s="32" t="str">
@@ -10195,13 +10203,13 @@
         <x:v>Extraído do documento</x:v>
       </x:c>
       <x:c r="J266" s="33" t="n">
-        <x:v>12</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="K266" s="33" t="n">
-        <x:v>12</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="L266" s="33" t="n">
-        <x:v>12</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="M266" s="32" t="str"/>
     </x:row>
@@ -10210,16 +10218,16 @@
         <x:v>265</x:v>
       </x:c>
       <x:c r="B267" s="32" t="str">
-        <x:v>Stanford Medicine_AI in Healthcare Capstone Project Certificate_554362_39163_3.pdf</x:v>
+        <x:v>Stanford Medicine_CME_RECAP Health Podcast_Certificate_554362_53806_3.pdf</x:v>
       </x:c>
       <x:c r="C267" s="32" t="str">
         <x:v>Stanford Medicine</x:v>
       </x:c>
       <x:c r="D267" s="32" t="str">
-        <x:v>Stanford Medicine_AI in Healthcare Capstone Project Certificate_554362_39163_3</x:v>
+        <x:v>Stanford Medicine_CME_RECAP Health Podcast_Certificate_554362_53806_3</x:v>
       </x:c>
       <x:c r="E267" s="32" t="str">
-        <x:v>Stanford Center for Continuing Medical Education | cme.stanford.edu | Email: StanfordCME@stanford.edu Event ID 39163 Stanford University School of Medicine certifies that Pedro Lamounier Sampaio, LL.M. has participated for 11.00 hours in the Enduring Material titled AI Series: AI in Healthcare Capstone Project on 08/01/2026 This Activity was designated for 11.00 AMA PRA Category 1 Credit(s)™ Accreditation In support of improving patient care, Stanford Medicine is jointly accredited by the Accred</x:v>
+        <x:v>Stanford Center for Continuing Medical Education | cme.stanford.edu | Email: StanfordCME@stanford.edu Event ID 53806 Stanford University School of Medicine certifies that Pedro Lamounier Sampaio, LL.M. has participated for 0.25 hours in the Enduring Material titled Episode 109: Season Recap – Human-Centered Medicine in an Age of Innovation on 08/25/2026 This Activity was designated for 0.25 AMA PRA Category 1 Credit(s)™ Accreditation In support of improving patient care, Stanford Medicine is joi</x:v>
       </x:c>
       <x:c r="F267" s="32" t="str"/>
       <x:c r="G267" s="32" t="str">
@@ -10232,13 +10240,13 @@
         <x:v>Extraído do documento</x:v>
       </x:c>
       <x:c r="J267" s="33" t="n">
-        <x:v>11</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="K267" s="33" t="n">
-        <x:v>11</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="L267" s="33" t="n">
-        <x:v>11</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="M267" s="32" t="str"/>
     </x:row>
@@ -10247,16 +10255,16 @@
         <x:v>266</x:v>
       </x:c>
       <x:c r="B268" s="32" t="str">
-        <x:v>Stanford Medicine_Antimicrobial Stewardship_CME-CE Certificate_554362_49027_3.pdf</x:v>
+        <x:v>Stanford Medicine_Essentials of Palliative Care_CE_554362_47068_3.pdf</x:v>
       </x:c>
       <x:c r="C268" s="32" t="str">
         <x:v>Stanford Medicine</x:v>
       </x:c>
       <x:c r="D268" s="32" t="str">
-        <x:v>Stanford Medicine_Antimicrobial Stewardship_CME-CE Certificate_554362_49027_3</x:v>
+        <x:v>Stanford Medicine_Essentials of Palliative Care_CE_554362_47068_3</x:v>
       </x:c>
       <x:c r="E268" s="32" t="str">
-        <x:v>Stanford Center for Continuing Medical Education | cme.stanford.edu | Email: StanfordCME@stanford.edu Event ID 49027 Stanford University School of Medicine certifies that Pedro Lamounier Sampaio, LL.M. has participated for 7.00 hours in the Enduring Material titled Antimicrobial Stewardship: Improving Clinical Outcomes by Optimization of Antibiotic Practices on 08/30/2026 This Activity was designated for 7.00 AMA PRA Category 1 Credit(s)™ Accreditation In support of improving patient care, Stanf</x:v>
+        <x:v>Stanford Center for Continuing Medical Education | cme.stanford.edu | Email: StanfordCME@stanford.edu Event ID 47068 Stanford University School of Medicine certifies that Pedro Lamounier Sampaio, LL.M. has participated for 11.50 hours in the Enduring Material titled Essentials of Palliative Care on 08/17/2026 This Activity was designated for 11.50 AMA PRA Category 1 Credit(s)™ Accreditation In support of improving patient care, Stanford Medicine is jointly accredited by the Accreditation Council</x:v>
       </x:c>
       <x:c r="F268" s="32" t="str"/>
       <x:c r="G268" s="32" t="str">
@@ -10269,13 +10277,13 @@
         <x:v>Extraído do documento</x:v>
       </x:c>
       <x:c r="J268" s="33" t="n">
-        <x:v>7</x:v>
+        <x:v>11.5</x:v>
       </x:c>
       <x:c r="K268" s="33" t="n">
-        <x:v>7</x:v>
+        <x:v>11.5</x:v>
       </x:c>
       <x:c r="L268" s="33" t="n">
-        <x:v>7</x:v>
+        <x:v>11.5</x:v>
       </x:c>
       <x:c r="M268" s="32" t="str"/>
     </x:row>
@@ -10284,16 +10292,16 @@
         <x:v>267</x:v>
       </x:c>
       <x:c r="B269" s="32" t="str">
-        <x:v>Stanford Medicine_CME_RECAP Health Podcast_Certificate_554362_53806_3.pdf</x:v>
+        <x:v>Stanford Medicine_Evaluation of AI in healthcare Certificate_554362_47063_3.pdf</x:v>
       </x:c>
       <x:c r="C269" s="32" t="str">
         <x:v>Stanford Medicine</x:v>
       </x:c>
       <x:c r="D269" s="32" t="str">
-        <x:v>Stanford Medicine_CME_RECAP Health Podcast_Certificate_554362_53806_3</x:v>
+        <x:v>Stanford Medicine_Evaluation of AI in healthcare Certificate_554362_47063_3</x:v>
       </x:c>
       <x:c r="E269" s="32" t="str">
-        <x:v>Stanford Center for Continuing Medical Education | cme.stanford.edu | Email: StanfordCME@stanford.edu Event ID 53806 Stanford University School of Medicine certifies that Pedro Lamounier Sampaio, LL.M. has participated for 0.25 hours in the Enduring Material titled Episode 109: Season Recap – Human-Centered Medicine in an Age of Innovation on 08/25/2026 This Activity was designated for 0.25 AMA PRA Category 1 Credit(s)™ Accreditation In support of improving patient care, Stanford Medicine is joi</x:v>
+        <x:v>Stanford Center for Continuing Medical Education | cme.stanford.edu | Email: StanfordCME@stanford.edu Event ID 47063 Stanford University School of Medicine certifies that Pedro Lamounier Sampaio, LL.M. has participated for 9.50 hours in the Enduring Material titled AI Series: Evaluations of AI Applications in Healthcare on 08/01/2026 This Activity was designated for 9.50 AMA PRA Category 1 Credit(s)™ Accreditation In support of improving patient care, Stanford Medicine is jointly accredited by t</x:v>
       </x:c>
       <x:c r="F269" s="32" t="str"/>
       <x:c r="G269" s="32" t="str">
@@ -10306,13 +10314,13 @@
         <x:v>Extraído do documento</x:v>
       </x:c>
       <x:c r="J269" s="33" t="n">
-        <x:v>0.25</x:v>
+        <x:v>9.5</x:v>
       </x:c>
       <x:c r="K269" s="33" t="n">
-        <x:v>0.25</x:v>
+        <x:v>9.5</x:v>
       </x:c>
       <x:c r="L269" s="33" t="n">
-        <x:v>0.25</x:v>
+        <x:v>9.5</x:v>
       </x:c>
       <x:c r="M269" s="32" t="str"/>
     </x:row>
@@ -10321,16 +10329,16 @@
         <x:v>268</x:v>
       </x:c>
       <x:c r="B270" s="32" t="str">
-        <x:v>Stanford Medicine_Essentials of Palliative Care_CE_554362_47068_3.pdf</x:v>
+        <x:v>Stanford Medicine_Fundamentals in AI and MLin HC_Certificate.CE_554362_47055_3.pdf</x:v>
       </x:c>
       <x:c r="C270" s="32" t="str">
         <x:v>Stanford Medicine</x:v>
       </x:c>
       <x:c r="D270" s="32" t="str">
-        <x:v>Stanford Medicine_Essentials of Palliative Care_CE_554362_47068_3</x:v>
+        <x:v>Stanford Medicine_Fundamentals in AI and MLin HC_Certificate.CE_554362_47055_3</x:v>
       </x:c>
       <x:c r="E270" s="32" t="str">
-        <x:v>Stanford Center for Continuing Medical Education | cme.stanford.edu | Email: StanfordCME@stanford.edu Event ID 47068 Stanford University School of Medicine certifies that Pedro Lamounier Sampaio, LL.M. has participated for 11.50 hours in the Enduring Material titled Essentials of Palliative Care on 08/17/2026 This Activity was designated for 11.50 AMA PRA Category 1 Credit(s)™ Accreditation In support of improving patient care, Stanford Medicine is jointly accredited by the Accreditation Council</x:v>
+        <x:v>Stanford Center for Continuing Medical Education | cme.stanford.edu | Email: StanfordCME@stanford.edu Event ID 47055 Stanford University School of Medicine certifies that Pedro Lamounier Sampaio, LL.M. has participated for 11.00 hours in the Enduring Material titled AI Series: Fundamentals of AI and Machine Learning in Healthcare on 07/31/2026 This Activity was designated for 11.00 AMA PRA Category 1 Credit(s)™ Accreditation In support of improving patient care, Stanford Medicine is jointly accr</x:v>
       </x:c>
       <x:c r="F270" s="32" t="str"/>
       <x:c r="G270" s="32" t="str">
@@ -10343,13 +10351,13 @@
         <x:v>Extraído do documento</x:v>
       </x:c>
       <x:c r="J270" s="33" t="n">
-        <x:v>11.5</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="K270" s="33" t="n">
-        <x:v>11.5</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L270" s="33" t="n">
-        <x:v>11.5</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="M270" s="32" t="str"/>
     </x:row>
@@ -10358,16 +10366,16 @@
         <x:v>269</x:v>
       </x:c>
       <x:c r="B271" s="32" t="str">
-        <x:v>Stanford Medicine_Evaluation of AI in healthcare Certificate_554362_47063_3.pdf</x:v>
+        <x:v>Stanford Medicine_Supporting Caregivers in PCA_Certificate-CE_554362_47065_3.pdf</x:v>
       </x:c>
       <x:c r="C271" s="32" t="str">
         <x:v>Stanford Medicine</x:v>
       </x:c>
       <x:c r="D271" s="32" t="str">
-        <x:v>Stanford Medicine_Evaluation of AI in healthcare Certificate_554362_47063_3</x:v>
+        <x:v>Stanford Medicine_Supporting Caregivers in PCA_Certificate-CE_554362_47065_3</x:v>
       </x:c>
       <x:c r="E271" s="32" t="str">
-        <x:v>Stanford Center for Continuing Medical Education | cme.stanford.edu | Email: StanfordCME@stanford.edu Event ID 47063 Stanford University School of Medicine certifies that Pedro Lamounier Sampaio, LL.M. has participated for 9.50 hours in the Enduring Material titled AI Series: Evaluations of AI Applications in Healthcare on 08/01/2026 This Activity was designated for 9.50 AMA PRA Category 1 Credit(s)™ Accreditation In support of improving patient care, Stanford Medicine is jointly accredited by t</x:v>
+        <x:v>Stanford Center for Continuing Medical Education | cme.stanford.edu | Email: StanfordCME@stanford.edu Event ID 47065 Stanford University School of Medicine certifies that Pedro Lamounier Sampaio, LL.M. has participated for 10.00 hours in the Enduring Material titled Supporting Families and Caregivers on 08/29/2026 This Activity was designated for 10.00 AMA PRA Category 1 Credit(s)™ Accreditation In support of improving patient care, Stanford Medicine is jointly accredited by the Accreditation Co</x:v>
       </x:c>
       <x:c r="F271" s="32" t="str"/>
       <x:c r="G271" s="32" t="str">
@@ -10380,13 +10388,13 @@
         <x:v>Extraído do documento</x:v>
       </x:c>
       <x:c r="J271" s="33" t="n">
-        <x:v>9.5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="K271" s="33" t="n">
-        <x:v>9.5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L271" s="33" t="n">
-        <x:v>9.5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="M271" s="32" t="str"/>
     </x:row>
@@ -10395,16 +10403,16 @@
         <x:v>270</x:v>
       </x:c>
       <x:c r="B272" s="32" t="str">
-        <x:v>Stanford Medicine_Fundamentals in AI and MLin HC_Certificate.CE_554362_47055_3.pdf</x:v>
+        <x:v>Stanford Medicine_Symptom Management Certificate.pdf</x:v>
       </x:c>
       <x:c r="C272" s="32" t="str">
         <x:v>Stanford Medicine</x:v>
       </x:c>
       <x:c r="D272" s="32" t="str">
-        <x:v>Stanford Medicine_Fundamentals in AI and MLin HC_Certificate.CE_554362_47055_3</x:v>
+        <x:v>Stanford Medicine_Symptom Management Certificate</x:v>
       </x:c>
       <x:c r="E272" s="32" t="str">
-        <x:v>Stanford Center for Continuing Medical Education | cme.stanford.edu | Email: StanfordCME@stanford.edu Event ID 47055 Stanford University School of Medicine certifies that Pedro Lamounier Sampaio, LL.M. has participated for 11.00 hours in the Enduring Material titled AI Series: Fundamentals of AI and Machine Learning in Healthcare on 07/31/2026 This Activity was designated for 11.00 AMA PRA Category 1 Credit(s)™ Accreditation In support of improving patient care, Stanford Medicine is jointly accr</x:v>
+        <x:v>Stanford Center for Continuing Medical Education | cme.stanford.edu | Email: StanfordCME@stanford.edu Event ID 47067 Stanford University School of Medicine certifies that Pedro Lamounier Sampaio, LL.M. has participated for 9.75 hours in the Enduring Material titled Symptom Management in Palliative Care on 08/25/2026 This Activity was designated for 9.75 AMA PRA Category 1 Credit(s)™ Accreditation In support of improving patient care, Stanford Medicine is jointly accredited by the Accreditation C</x:v>
       </x:c>
       <x:c r="F272" s="32" t="str"/>
       <x:c r="G272" s="32" t="str">
@@ -10417,13 +10425,13 @@
         <x:v>Extraído do documento</x:v>
       </x:c>
       <x:c r="J272" s="33" t="n">
-        <x:v>11</x:v>
+        <x:v>9.75</x:v>
       </x:c>
       <x:c r="K272" s="33" t="n">
-        <x:v>11</x:v>
+        <x:v>9.75</x:v>
       </x:c>
       <x:c r="L272" s="33" t="n">
-        <x:v>11</x:v>
+        <x:v>9.75</x:v>
       </x:c>
       <x:c r="M272" s="32" t="str"/>
     </x:row>
@@ -10432,16 +10440,16 @@
         <x:v>271</x:v>
       </x:c>
       <x:c r="B273" s="32" t="str">
-        <x:v>Stanford Medicine_Supporting Caregivers in PCA_Certificate-CE_554362_47065_3.pdf</x:v>
+        <x:v>Stanford Medicine_Transitioning care in palliative care_Certificate-CME-CE_554362_47066_3.pdf</x:v>
       </x:c>
       <x:c r="C273" s="32" t="str">
         <x:v>Stanford Medicine</x:v>
       </x:c>
       <x:c r="D273" s="32" t="str">
-        <x:v>Stanford Medicine_Supporting Caregivers in PCA_Certificate-CE_554362_47065_3</x:v>
+        <x:v>Stanford Medicine_Transitioning care in palliative care_Certificate-CME-CE_554362_47066_3</x:v>
       </x:c>
       <x:c r="E273" s="32" t="str">
-        <x:v>Stanford Center for Continuing Medical Education | cme.stanford.edu | Email: StanfordCME@stanford.edu Event ID 47065 Stanford University School of Medicine certifies that Pedro Lamounier Sampaio, LL.M. has participated for 10.00 hours in the Enduring Material titled Supporting Families and Caregivers on 08/29/2026 This Activity was designated for 10.00 AMA PRA Category 1 Credit(s)™ Accreditation In support of improving patient care, Stanford Medicine is jointly accredited by the Accreditation Co</x:v>
+        <x:v>Stanford Center for Continuing Medical Education | cme.stanford.edu | Email: StanfordCME@stanford.edu Event ID 47066 Stanford University School of Medicine certifies that Pedro Lamounier Sampaio, LL.M. has participated for 10.00 hours in the Enduring Material titled Transitions in Care from Survivorship to Hospice on 08/29/2026 This Activity was designated for 10.00 AMA PRA Category 1 Credit(s)™ Accreditation In support of improving patient care, Stanford Medicine is jointly accredited by the Ac</x:v>
       </x:c>
       <x:c r="F273" s="32" t="str"/>
       <x:c r="G273" s="32" t="str">
@@ -10469,16 +10477,16 @@
         <x:v>272</x:v>
       </x:c>
       <x:c r="B274" s="32" t="str">
-        <x:v>Stanford Medicine_Symptom Management Certificate.pdf</x:v>
+        <x:v>Stanford Medicine_Women Health_Menopause and Care Management_Certificate_554362_56761_3.pdf</x:v>
       </x:c>
       <x:c r="C274" s="32" t="str">
         <x:v>Stanford Medicine</x:v>
       </x:c>
       <x:c r="D274" s="32" t="str">
-        <x:v>Stanford Medicine_Symptom Management Certificate</x:v>
+        <x:v>Stanford Medicine_Women Health_Menopause and Care Management_Certificate_554362_56761_3</x:v>
       </x:c>
       <x:c r="E274" s="32" t="str">
-        <x:v>Stanford Center for Continuing Medical Education | cme.stanford.edu | Email: StanfordCME@stanford.edu Event ID 47067 Stanford University School of Medicine certifies that Pedro Lamounier Sampaio, LL.M. has participated for 9.75 hours in the Enduring Material titled Symptom Management in Palliative Care on 08/25/2026 This Activity was designated for 9.75 AMA PRA Category 1 Credit(s)™ Accreditation In support of improving patient care, Stanford Medicine is jointly accredited by the Accreditation C</x:v>
+        <x:v>Stanford Center for Continuing Medical Education | cme.stanford.edu | Email: StanfordCME@stanford.edu Event ID 56761 Stanford University School of Medicine certifies that Pedro Lamounier Sampaio, LL.M. has participated for 0.75 hours in the Enduring Material titled Stanford Medcast Episode 111: Menopause Matters: Myths, Management, and Meaningful Care on 08/26/2026 This Activity was designated for 0.75 AMA PRA Category 1 Credit(s)™ Accreditation In support of improving patient care, Stanford Med</x:v>
       </x:c>
       <x:c r="F274" s="32" t="str"/>
       <x:c r="G274" s="32" t="str">
@@ -10491,13 +10499,13 @@
         <x:v>Extraído do documento</x:v>
       </x:c>
       <x:c r="J274" s="33" t="n">
-        <x:v>9.75</x:v>
+        <x:v>0.75</x:v>
       </x:c>
       <x:c r="K274" s="33" t="n">
-        <x:v>9.75</x:v>
+        <x:v>0.75</x:v>
       </x:c>
       <x:c r="L274" s="33" t="n">
-        <x:v>9.75</x:v>
+        <x:v>0.75</x:v>
       </x:c>
       <x:c r="M274" s="32" t="str"/>
     </x:row>
@@ -10506,90 +10514,94 @@
         <x:v>273</x:v>
       </x:c>
       <x:c r="B275" s="32" t="str">
-        <x:v>Stanford Medicine_Transitioning care in palliative care_Certificate-CME-CE_554362_47066_3.pdf</x:v>
+        <x:v>Stanford-Coursera RYUIMPUS3ZLR_Intro to Healthcare_Certificate.pdf</x:v>
       </x:c>
       <x:c r="C275" s="32" t="str">
-        <x:v>Stanford Medicine</x:v>
+        <x:v>Stanford Online / Stanford Medicine</x:v>
       </x:c>
       <x:c r="D275" s="32" t="str">
-        <x:v>Stanford Medicine_Transitioning care in palliative care_Certificate-CME-CE_554362_47066_3</x:v>
+        <x:v>Introduction to Healthcare</x:v>
       </x:c>
       <x:c r="E275" s="32" t="str">
-        <x:v>Stanford Center for Continuing Medical Education | cme.stanford.edu | Email: StanfordCME@stanford.edu Event ID 47066 Stanford University School of Medicine certifies that Pedro Lamounier Sampaio, LL.M. has participated for 10.00 hours in the Enduring Material titled Transitions in Care from Survivorship to Hospice on 08/29/2026 This Activity was designated for 10.00 AMA PRA Category 1 Credit(s)™ Accreditation In support of improving patient care, Stanford Medicine is jointly accredited by the Ac</x:v>
+        <x:v>J u l 2 8 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o I n t r o d u c t i o n t o H e a l t h c a r e a n o n l i n e c o u r s e a u t h o r i z e d b y S t a n f o r d U n i v e r s i t y a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d L a u r e n c e B a k e r , M i l d r e d C h o , N i g a m S h a h V e r i f y a t : h t t p s : / / c o u r s e r a . o r g / v e r i f y / R Y U I M P U S 3 Z L R C o u r s e r a h a s c o n f i r m e </x:v>
       </x:c>
       <x:c r="F275" s="32" t="str"/>
       <x:c r="G275" s="32" t="str">
-        <x:v>Grupo 3 — Extensão</x:v>
+        <x:v>Grupo 1 — Ensino</x:v>
       </x:c>
       <x:c r="H275" s="32" t="str">
-        <x:v>3.1</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="I275" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
       <x:c r="J275" s="33" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="K275" s="33" t="n">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="L275" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="M275" s="32" t="str"/>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M275" s="32" t="str">
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/RYUIMPUS3ZLR</x:v>
+      </x:c>
     </x:row>
     <x:row r="276">
       <x:c r="A276" s="32" t="n">
         <x:v>274</x:v>
       </x:c>
       <x:c r="B276" s="32" t="str">
-        <x:v>Stanford Medicine_Women Health_Menopause and Care Management_Certificate_554362_56761_3.pdf</x:v>
+        <x:v>Stanford-Coursera_AI in Healthcare Capstone Certificate_9L3NBFUCKU4Q.pdf</x:v>
       </x:c>
       <x:c r="C276" s="32" t="str">
-        <x:v>Stanford Medicine</x:v>
+        <x:v>Stanford Online / Stanford Medicine</x:v>
       </x:c>
       <x:c r="D276" s="32" t="str">
-        <x:v>Stanford Medicine_Women Health_Menopause and Care Management_Certificate_554362_56761_3</x:v>
+        <x:v>AI in Healthcare Capstone</x:v>
       </x:c>
       <x:c r="E276" s="32" t="str">
-        <x:v>Stanford Center for Continuing Medical Education | cme.stanford.edu | Email: StanfordCME@stanford.edu Event ID 56761 Stanford University School of Medicine certifies that Pedro Lamounier Sampaio, LL.M. has participated for 0.75 hours in the Enduring Material titled Stanford Medcast Episode 111: Menopause Matters: Myths, Management, and Meaningful Care on 08/26/2026 This Activity was designated for 0.75 AMA PRA Category 1 Credit(s)™ Accreditation In support of improving patient care, Stanford Med</x:v>
+        <x:v>A u g 2 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o A I i n H e a l t h c a r e C a p s t o n e a n o n l i n e c o u r s e a u t h o r i z e d b y S t a n f o r d U n i v e r s i t y a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d L a u r e n c e B a k e r , M a t t h e w L u n g r e n , N i g a m S h a h , S e r e n a Y e u n g a n d T i n a H e r n a n d e z - B o u s s a r d V e r i f y a t : h t t p s : / / c o u r s e r a . o r g / </x:v>
       </x:c>
       <x:c r="F276" s="32" t="str"/>
       <x:c r="G276" s="32" t="str">
-        <x:v>Grupo 3 — Extensão</x:v>
+        <x:v>Grupo 1 — Ensino</x:v>
       </x:c>
       <x:c r="H276" s="32" t="str">
-        <x:v>3.1</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="I276" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
       <x:c r="J276" s="33" t="n">
-        <x:v>0.75</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="K276" s="33" t="n">
-        <x:v>0.75</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L276" s="33" t="n">
-        <x:v>0.75</x:v>
-      </x:c>
-      <x:c r="M276" s="32" t="str"/>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="M276" s="32" t="str">
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/9L3NBFUCKU4Q</x:v>
+      </x:c>
     </x:row>
     <x:row r="277">
       <x:c r="A277" s="32" t="n">
         <x:v>275</x:v>
       </x:c>
       <x:c r="B277" s="32" t="str">
-        <x:v>Stanford-Coursera RYUIMPUS3ZLR_Intro to Healthcare_Certificate.pdf</x:v>
+        <x:v>Stanford-Coursera_AI in Healthcare Specialization Certificate_7GM7A9EIJ9W4.pdf</x:v>
       </x:c>
       <x:c r="C277" s="32" t="str">
         <x:v>Stanford Online / Stanford Medicine</x:v>
       </x:c>
       <x:c r="D277" s="32" t="str">
-        <x:v>Introduction to Healthcare</x:v>
+        <x:v>AI in Healthcare</x:v>
       </x:c>
       <x:c r="E277" s="32" t="str">
-        <x:v>J u l 2 8 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o I n t r o d u c t i o n t o H e a l t h c a r e a n o n l i n e c o u r s e a u t h o r i z e d b y S t a n f o r d U n i v e r s i t y a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d L a u r e n c e B a k e r , M i l d r e d C h o , N i g a m S h a h V e r i f y a t : h t t p s : / / c o u r s e r a . o r g / v e r i f y / R Y U I M P U S 3 Z L R C o u r s e r a h a s c o n f i r m e </x:v>
+        <x:v>5 C o u r s e s I n t r o d u c t i o n t o H e a l t h c a r e I n t r o d u c t i o n t o C l i n i c a l D a t a F u n d a m e n t a l s o f M a c h i n e L e a r n i n g f o r H e a l t h c a r e E v a l u a t i o n s o f A I A p p l i c a t i o n s i n H e a l t h c a r e A I i n H e a l t h c a r e C a p s t o n e N i g a m H . S h a h , M B B S , P h D A s s o c i a t e P r o f e s s o r o f M e d i c i n e ( B i o m e d i c a l I n f o r m a t i c s ) A u g 2 , 2 0 2 6 P e d r o L a m o </x:v>
       </x:c>
       <x:c r="F277" s="32" t="str"/>
       <x:c r="G277" s="32" t="str">
@@ -10602,16 +10614,16 @@
         <x:v>Extraído do documento</x:v>
       </x:c>
       <x:c r="J277" s="33" t="n">
-        <x:v>12</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="K277" s="33" t="n">
-        <x:v>12</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="L277" s="33" t="n">
-        <x:v>12</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="M277" s="32" t="str">
-        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/RYUIMPUS3ZLR</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/specialization/7GM7A9EIJ9W4; estimativa derivada do tempo exibido: 1 meses com 10 por semana para concluir</x:v>
       </x:c>
     </x:row>
     <x:row r="278">
@@ -10619,16 +10631,16 @@
         <x:v>276</x:v>
       </x:c>
       <x:c r="B278" s="32" t="str">
-        <x:v>Stanford-Coursera_AI in Healthcare Capstone Certificate_9L3NBFUCKU4Q.pdf</x:v>
+        <x:v>Stanford-Coursera_Antibiotic Stewardship Certificate.pdf</x:v>
       </x:c>
       <x:c r="C278" s="32" t="str">
         <x:v>Stanford Online / Stanford Medicine</x:v>
       </x:c>
       <x:c r="D278" s="32" t="str">
-        <x:v>AI in Healthcare Capstone</x:v>
+        <x:v>Antibiotic Stewardship</x:v>
       </x:c>
       <x:c r="E278" s="32" t="str">
-        <x:v>A u g 2 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o A I i n H e a l t h c a r e C a p s t o n e a n o n l i n e c o u r s e a u t h o r i z e d b y S t a n f o r d U n i v e r s i t y a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d L a u r e n c e B a k e r , M a t t h e w L u n g r e n , N i g a m S h a h , S e r e n a Y e u n g a n d T i n a H e r n a n d e z - B o u s s a r d V e r i f y a t : h t t p s : / / c o u r s e r a . o r g / </x:v>
+        <x:v>Uso responsável de antimicrobianos; doenças infecciosas; farmacologia e farmacoterapia; controle de infecções; práticas clínicas e avaliação do paciente.</x:v>
       </x:c>
       <x:c r="F278" s="32" t="str"/>
       <x:c r="G278" s="32" t="str">
@@ -10641,16 +10653,16 @@
         <x:v>Extraído do documento</x:v>
       </x:c>
       <x:c r="J278" s="33" t="n">
-        <x:v>10</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K278" s="33" t="n">
-        <x:v>10</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L278" s="33" t="n">
-        <x:v>10</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="M278" s="32" t="str">
-        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/9L3NBFUCKU4Q</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/FZV2SBU6I8NI; estimativa derivada do tempo exibido: 5 horas (aproximadamente)</x:v>
       </x:c>
     </x:row>
     <x:row r="279">
@@ -10658,16 +10670,16 @@
         <x:v>277</x:v>
       </x:c>
       <x:c r="B279" s="32" t="str">
-        <x:v>Stanford-Coursera_AI in Healthcare Specialization Certificate_7GM7A9EIJ9W4.pdf</x:v>
+        <x:v>Stanford-Coursera_Certificate_Fundamentals of ML in HC_MYZ6GPXEFO5H.pdf</x:v>
       </x:c>
       <x:c r="C279" s="32" t="str">
         <x:v>Stanford Online / Stanford Medicine</x:v>
       </x:c>
       <x:c r="D279" s="32" t="str">
-        <x:v>AI in Healthcare</x:v>
+        <x:v>Fundamentals of Machine Learning for Healthcare</x:v>
       </x:c>
       <x:c r="E279" s="32" t="str">
-        <x:v>5 C o u r s e s I n t r o d u c t i o n t o H e a l t h c a r e I n t r o d u c t i o n t o C l i n i c a l D a t a F u n d a m e n t a l s o f M a c h i n e L e a r n i n g f o r H e a l t h c a r e E v a l u a t i o n s o f A I A p p l i c a t i o n s i n H e a l t h c a r e A I i n H e a l t h c a r e C a p s t o n e N i g a m H . S h a h , M B B S , P h D A s s o c i a t e P r o f e s s o r o f M e d i c i n e ( B i o m e d i c a l I n f o r m a t i c s ) A u g 2 , 2 0 2 6 P e d r o L a m o </x:v>
+        <x:v>A u g 1 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o F u n d a m e n t a l s o f M a c h i n e L e a r n i n g f o r H e a l t h c a r e a n o n l i n e c o u r s e a u t h o r i z e d b y S t a n f o r d U n i v e r s i t y a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d M a t t h e w L u n g r e n A s s o c i a t e P r o f e s s o r D e p a r t m e n t o f R a d i o l o g y S e r e n a Y e u n g A s s i s t a n t P r o f e s s o r B i o </x:v>
       </x:c>
       <x:c r="F279" s="32" t="str"/>
       <x:c r="G279" s="32" t="str">
@@ -10680,16 +10692,16 @@
         <x:v>Extraído do documento</x:v>
       </x:c>
       <x:c r="J279" s="33" t="n">
-        <x:v>40</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K279" s="33" t="n">
-        <x:v>40</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="L279" s="33" t="n">
-        <x:v>40</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="M279" s="32" t="str">
-        <x:v>Coursera: https://www.coursera.org/account/accomplishments/specialization/7GM7A9EIJ9W4; estimativa derivada do tempo exibido: 1 meses com 10 por semana para concluir</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/MYZ6GPXEFO5H</x:v>
       </x:c>
     </x:row>
     <x:row r="280">
@@ -10697,16 +10709,16 @@
         <x:v>278</x:v>
       </x:c>
       <x:c r="B280" s="32" t="str">
-        <x:v>Stanford-Coursera_Certificate_Fundamentals of ML in HC_MYZ6GPXEFO5H.pdf</x:v>
+        <x:v>Stanford-Coursera_Evaluations of AI in HC_Certificate_DW8FFD7QA2IZ.pdf</x:v>
       </x:c>
       <x:c r="C280" s="32" t="str">
         <x:v>Stanford Online / Stanford Medicine</x:v>
       </x:c>
       <x:c r="D280" s="32" t="str">
-        <x:v>Fundamentals of Machine Learning for Healthcare</x:v>
+        <x:v>Evaluations of AI Applications in Healthcare</x:v>
       </x:c>
       <x:c r="E280" s="32" t="str">
-        <x:v>A u g 1 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o F u n d a m e n t a l s o f M a c h i n e L e a r n i n g f o r H e a l t h c a r e a n o n l i n e c o u r s e a u t h o r i z e d b y S t a n f o r d U n i v e r s i t y a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d M a t t h e w L u n g r e n A s s o c i a t e P r o f e s s o r D e p a r t m e n t o f R a d i o l o g y S e r e n a Y e u n g A s s i s t a n t P r o f e s s o r B i o </x:v>
+        <x:v>A u g 1 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o E v a l u a t i o n s o f A I A p p l i c a t i o n s i n H e a l t h c a r e a n o n l i n e c o u r s e a u t h o r i z e d b y S t a n f o r d U n i v e r s i t y a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d T i n a H e r n a n d e z - B o u s s a r d A s s o c i a t e P r o f e s s o r M e d i c i n e ( B i o m e d i c a l I n f o r m a t i c s ) , o f B i o m e d i c a l D a t a </x:v>
       </x:c>
       <x:c r="F280" s="32" t="str"/>
       <x:c r="G280" s="32" t="str">
@@ -10719,16 +10731,16 @@
         <x:v>Extraído do documento</x:v>
       </x:c>
       <x:c r="J280" s="33" t="n">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="K280" s="33" t="n">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="L280" s="33" t="n">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="M280" s="32" t="str">
-        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/MYZ6GPXEFO5H</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/DW8FFD7QA2IZ</x:v>
       </x:c>
     </x:row>
     <x:row r="281">
@@ -10736,16 +10748,16 @@
         <x:v>279</x:v>
       </x:c>
       <x:c r="B281" s="32" t="str">
-        <x:v>Stanford-Coursera_Evaluations of AI in HC_Certificate_DW8FFD7QA2IZ.pdf</x:v>
+        <x:v>Stanford-Coursera_Intro to Clinical Data Certificate.pdf</x:v>
       </x:c>
       <x:c r="C281" s="32" t="str">
         <x:v>Stanford Online / Stanford Medicine</x:v>
       </x:c>
       <x:c r="D281" s="32" t="str">
-        <x:v>Evaluations of AI Applications in Healthcare</x:v>
+        <x:v>Introduction to Clinical Data</x:v>
       </x:c>
       <x:c r="E281" s="32" t="str">
-        <x:v>A u g 1 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o E v a l u a t i o n s o f A I A p p l i c a t i o n s i n H e a l t h c a r e a n o n l i n e c o u r s e a u t h o r i z e d b y S t a n f o r d U n i v e r s i t y a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d T i n a H e r n a n d e z - B o u s s a r d A s s o c i a t e P r o f e s s o r M e d i c i n e ( B i o m e d i c a l I n f o r m a t i c s ) , o f B i o m e d i c a l D a t a </x:v>
+        <x:v>Aplicação de uma estrutura para mineração de dados médicos; uso ético de dados em decisões de saúde; tratamento de dados sistematicamente imprecisos; formulação de perguntas de pesquisa e construção de fluxo de trabalho de mineração de dados.</x:v>
       </x:c>
       <x:c r="F281" s="32" t="str"/>
       <x:c r="G281" s="32" t="str">
@@ -10767,7 +10779,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="M281" s="32" t="str">
-        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/DW8FFD7QA2IZ</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/WFZW6W7MXCAN; estimativa derivada do tempo exibido: 11 horas (aproximadamente)</x:v>
       </x:c>
     </x:row>
     <x:row r="282">
@@ -10775,32 +10787,38 @@
         <x:v>280</x:v>
       </x:c>
       <x:c r="B282" s="32" t="str">
-        <x:v>Stanford-Coursera_Intro to Clinical Data Certificate.pdf</x:v>
+        <x:v>Stanford-Coursera_Intro to Clinical Data Certificate_554362_47057_3_CME.pdf</x:v>
       </x:c>
       <x:c r="C282" s="32" t="str">
-        <x:v>Stanford</x:v>
+        <x:v>Stanford University School of Medicine / Stanford Medicine CME</x:v>
       </x:c>
       <x:c r="D282" s="32" t="str">
-        <x:v>Stanford-Coursera_Intro to Clinical Data Certificate</x:v>
+        <x:v>AI Series: Introduction to Clinical Data</x:v>
       </x:c>
       <x:c r="E282" s="32" t="str">
-        <x:v>J u l 3 1 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o I n t r o d u c t i o n t o C l i n i c a l D a t a a n o n l i n e c o u r s e a u t h o r i z e d b y S t a n f o r d U n i v e r s i t y a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d D a v i d M a g n u s , N i g a m S h a h , S t e v e n B a g l e y V e r i f y a t : h t t p s : / / c o u r s e r a . o r g / v e r i f y / W F Z W 6 W 7 M X C A N C o u r s e r a h a s c o n f i r </x:v>
+        <x:v>Material educacional continuado sobre introdução a dados clínicos, conforme certificado CME da Stanford Medicine.</x:v>
       </x:c>
       <x:c r="F282" s="32" t="str"/>
       <x:c r="G282" s="32" t="str">
-        <x:v>Grupo 1 — Ensino</x:v>
+        <x:v>Grupo 3 — Extensão</x:v>
       </x:c>
       <x:c r="H282" s="32" t="str">
-        <x:v>1.5</x:v>
+        <x:v>3.1</x:v>
       </x:c>
       <x:c r="I282" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J282" s="33"/>
-      <x:c r="K282" s="33"/>
-      <x:c r="L282" s="33"/>
+      <x:c r="J282" s="33" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="K282" s="33" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L282" s="33" t="n">
+        <x:v>11</x:v>
+      </x:c>
       <x:c r="M282" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>Certificado CME declara participação por 11,00 horas; atividade educacional continuada.</x:v>
       </x:c>
     </x:row>
     <x:row r="283">
@@ -10808,53 +10826,55 @@
         <x:v>281</x:v>
       </x:c>
       <x:c r="B283" s="32" t="str">
-        <x:v>Stanford-Coursera_Intro to Clinical Data Certificate_554362_47057_3_CME.pdf</x:v>
+        <x:v>Stanford-Coursera_PCA Specialization Certificate E8700K9GB2WD.pdf</x:v>
       </x:c>
       <x:c r="C283" s="32" t="str">
-        <x:v>Stanford</x:v>
+        <x:v>Stanford Online / Stanford Medicine</x:v>
       </x:c>
       <x:c r="D283" s="32" t="str">
-        <x:v>Stanford-Coursera_Intro to Clinical Data Certificate_554362_47057_3_CME</x:v>
+        <x:v>Palliative Care Always</x:v>
       </x:c>
       <x:c r="E283" s="32" t="str">
-        <x:v>Stanford Center for Continuing Medical Education | cme.stanford.edu | Email: StanfordCME@stanford.edu Event ID 47057 Stanford University School of Medicine certifies that Pedro Lamounier Sampaio, LL.M. has participated for 11.00 hours in the Enduring Material titled AI Series: Introduction to Clinical Data on 07/30/2026 This Activity was designated for 11.00 AMA PRA Category 1 Credit(s)™ Accreditation In support of improving patient care, Stanford Medicine is jointly accredited by the Accreditat</x:v>
+        <x:v>5 C o u r s e s E s s e n t i a l s o f P a l l i a t i v e C a r e S y m p t o m M a n a g e m e n t i n P a l l i a t i v e C a r e T r a n s i t i o n s i n C a r e f r o m S u r v i v o r s h i p t o H o s p i c e S u p p o r t i n g F a m i l i e s a n d C a r e g i v e r s P a l l i a t i v e C a r e A l w a y s C a p s t o n e C o u r s e K a v i t h a R a m c h a n d r a n M D , C l i n i c a l A s s o c i a t e P r o f e s s o r , S t a n f o r d M e d i c i n e A u g 3 0 , 2 0 2 6 P e </x:v>
       </x:c>
       <x:c r="F283" s="32" t="str"/>
       <x:c r="G283" s="32" t="str">
-        <x:v>Grupo 3 — Extensão</x:v>
+        <x:v>Grupo 1 — Ensino</x:v>
       </x:c>
       <x:c r="H283" s="32" t="str">
-        <x:v>3.1</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="I283" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
       <x:c r="J283" s="33" t="n">
-        <x:v>11</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="K283" s="33" t="n">
-        <x:v>11</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="L283" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M283" s="32" t="str"/>
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="M283" s="32" t="str">
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/specialization/E8700K9GB2WD; estimativa derivada do tempo exibido: 1 meses com 10 por semana para concluir</x:v>
+      </x:c>
     </x:row>
     <x:row r="284">
       <x:c r="A284" s="32" t="n">
         <x:v>282</x:v>
       </x:c>
       <x:c r="B284" s="32" t="str">
-        <x:v>Stanford-Coursera_PCA Specialization Certificate E8700K9GB2WD.pdf</x:v>
+        <x:v>Stanford-Coursera_Supporting Caregiver Health_Certificate_O8W0ZHG0J5II.pdf</x:v>
       </x:c>
       <x:c r="C284" s="32" t="str">
         <x:v>Stanford Online / Stanford Medicine</x:v>
       </x:c>
       <x:c r="D284" s="32" t="str">
-        <x:v>Palliative Care Always</x:v>
+        <x:v>Supporting Families and Caregivers</x:v>
       </x:c>
       <x:c r="E284" s="32" t="str">
-        <x:v>5 C o u r s e s E s s e n t i a l s o f P a l l i a t i v e C a r e S y m p t o m M a n a g e m e n t i n P a l l i a t i v e C a r e T r a n s i t i o n s i n C a r e f r o m S u r v i v o r s h i p t o H o s p i c e S u p p o r t i n g F a m i l i e s a n d C a r e g i v e r s P a l l i a t i v e C a r e A l w a y s C a p s t o n e C o u r s e K a v i t h a R a m c h a n d r a n M D , C l i n i c a l A s s o c i a t e P r o f e s s o r , S t a n f o r d M e d i c i n e A u g 3 0 , 2 0 2 6 P e </x:v>
+        <x:v>A u g 3 0 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o S u p p o r t i n g F a m i l i e s a n d C a r e g i v e r s a n o n l i n e c o u r s e a u t h o r i z e d b y S t a n f o r d O n l i n e a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d K a v i t h a R a m c h a n d r a n C l i n i c a l A s s o c i a t e P r o f e s s o r O n c o l o g y J a n D e N o f r i o P h D P r o g r a m M a n a g e r P a l l i a t i v e C a r e A l w a y </x:v>
       </x:c>
       <x:c r="F284" s="32" t="str"/>
       <x:c r="G284" s="32" t="str">
@@ -10867,16 +10887,16 @@
         <x:v>Extraído do documento</x:v>
       </x:c>
       <x:c r="J284" s="33" t="n">
-        <x:v>40</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="K284" s="33" t="n">
-        <x:v>40</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L284" s="33" t="n">
-        <x:v>40</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="M284" s="32" t="str">
-        <x:v>Coursera: https://www.coursera.org/account/accomplishments/specialization/E8700K9GB2WD; estimativa derivada do tempo exibido: 1 meses com 10 por semana para concluir</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/O8W0ZHG0J5II</x:v>
       </x:c>
     </x:row>
     <x:row r="285">
@@ -10884,16 +10904,16 @@
         <x:v>283</x:v>
       </x:c>
       <x:c r="B285" s="32" t="str">
-        <x:v>Stanford-Coursera_Supporting Caregiver Health_Certificate_O8W0ZHG0J5II.pdf</x:v>
+        <x:v>Stanford-Coursera_Symptom Management_CertificateLYD5V9AWXRXS.pdf</x:v>
       </x:c>
       <x:c r="C285" s="32" t="str">
         <x:v>Stanford Online / Stanford Medicine</x:v>
       </x:c>
       <x:c r="D285" s="32" t="str">
-        <x:v>Supporting Families and Caregivers</x:v>
+        <x:v>Symptom Management in Palliative Care</x:v>
       </x:c>
       <x:c r="E285" s="32" t="str">
-        <x:v>A u g 3 0 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o S u p p o r t i n g F a m i l i e s a n d C a r e g i v e r s a n o n l i n e c o u r s e a u t h o r i z e d b y S t a n f o r d O n l i n e a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d K a v i t h a R a m c h a n d r a n C l i n i c a l A s s o c i a t e P r o f e s s o r O n c o l o g y J a n D e N o f r i o P h D P r o g r a m M a n a g e r P a l l i a t i v e C a r e A l w a y </x:v>
+        <x:v>A u g 2 9 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o S y m p t o m M a n a g e m e n t i n P a l l i a t i v e C a r e a n o n l i n e c o u r s e a u t h o r i z e d b y S t a n f o r d O n l i n e a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d J a n D e N o f r i o , J o s h u a F r o n k , K a v i t h a R a m c h a n d r a n , M a n u e l a K o g o n V e r i f y a t : h t t p s : / / c o u r s e r a . o r g / v e r i f y / L Y D 5 V </x:v>
       </x:c>
       <x:c r="F285" s="32" t="str"/>
       <x:c r="G285" s="32" t="str">
@@ -10906,16 +10926,16 @@
         <x:v>Extraído do documento</x:v>
       </x:c>
       <x:c r="J285" s="33" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="K285" s="33" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="L285" s="33" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="M285" s="32" t="str">
-        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/O8W0ZHG0J5II</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/LYD5V9AWXRXS</x:v>
       </x:c>
     </x:row>
     <x:row r="286">
@@ -10923,16 +10943,16 @@
         <x:v>284</x:v>
       </x:c>
       <x:c r="B286" s="32" t="str">
-        <x:v>Stanford-Coursera_Symptom Management_CertificateLYD5V9AWXRXS.pdf</x:v>
+        <x:v>Stanford-Coursera_Transitioning care in palliative care_Certificate_554362_47066_3.pdf</x:v>
       </x:c>
       <x:c r="C286" s="32" t="str">
         <x:v>Stanford Online / Stanford Medicine</x:v>
       </x:c>
       <x:c r="D286" s="32" t="str">
-        <x:v>Symptom Management in Palliative Care</x:v>
+        <x:v>Transitions in Care from Survivorship to Hospice</x:v>
       </x:c>
       <x:c r="E286" s="32" t="str">
-        <x:v>A u g 2 9 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o S y m p t o m M a n a g e m e n t i n P a l l i a t i v e C a r e a n o n l i n e c o u r s e a u t h o r i z e d b y S t a n f o r d O n l i n e a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d J a n D e N o f r i o , J o s h u a F r o n k , K a v i t h a R a m c h a n d r a n , M a n u e l a K o g o n V e r i f y a t : h t t p s : / / c o u r s e r a . o r g / v e r i f y / L Y D 5 V </x:v>
+        <x:v>Mudanças nas necessidades do paciente conforme o prognóstico; triagem e avaliação espiritual; sobrevivência e necessidades específicas; cuidados hospice e diferenças em relação aos cuidados paliativos.</x:v>
       </x:c>
       <x:c r="F286" s="32" t="str"/>
       <x:c r="G286" s="32" t="str">
@@ -10945,16 +10965,16 @@
         <x:v>Extraído do documento</x:v>
       </x:c>
       <x:c r="J286" s="33" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="K286" s="33" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L286" s="33" t="n">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="M286" s="32" t="str">
-        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/LYD5V9AWXRXS</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/OYTO0JAKNOFA; estimativa derivada do tempo exibido: 10 horas (aproximadamente)</x:v>
       </x:c>
     </x:row>
     <x:row r="287">
@@ -10962,86 +10982,92 @@
         <x:v>285</x:v>
       </x:c>
       <x:c r="B287" s="32" t="str">
-        <x:v>Stanford-Coursera_Transitioning care in palliative care_Certificate_554362_47066_3.pdf</x:v>
+        <x:v>Stanfprd Medicine_Medcast 95_CME Certificate.pdf</x:v>
       </x:c>
       <x:c r="C287" s="32" t="str">
-        <x:v>Stanford</x:v>
+        <x:v>Stanfprd Medicine</x:v>
       </x:c>
       <x:c r="D287" s="32" t="str">
-        <x:v>Stanford-Coursera_Transitioning care in palliative care_Certificate_554362_47066_3</x:v>
+        <x:v>Stanfprd Medicine_Medcast 95_CME Certificate</x:v>
       </x:c>
       <x:c r="E287" s="32" t="str">
-        <x:v>A u g 2 9 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o T r a n s i t i o n s i n C a r e f r o m S u r v i v o r s h i p t o H o s p i c e a n o n l i n e c o u r s e a u t h o r i z e d b y S t a n f o r d O n l i n e a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d K a v i t h a R a m c h a n d r a n C l i n i c a l A s s o c i a t e P r o f e s s o r O n c o l o g y J a n D e N o f r i o P h D P r o g r a m M a n a g e r P a l l i a t i </x:v>
+        <x:v>Stanford Center for Continuing Medical Education | cme.stanford.edu | Email: StanfordCME@stanford.edu Event ID 53645 Stanford University School of Medicine certifies that Pedro Lamounier Sampaio, LL.M. has participated for 0.50 hours in the Enduring Material titled Stanford Medcast Episode 106: Hot Topics Mini-Series - Laser Focused: Innovations and Equity in Dermatology on 08/30/2026 This Activity was designated for 0.50 AMA PRA Category 1 Credit(s)™ Accreditation In support of improving patien</x:v>
       </x:c>
       <x:c r="F287" s="32" t="str"/>
       <x:c r="G287" s="32" t="str">
-        <x:v>Grupo 1 — Ensino</x:v>
+        <x:v>Grupo 3 — Extensão</x:v>
       </x:c>
       <x:c r="H287" s="32" t="str">
-        <x:v>1.5</x:v>
+        <x:v>3.1</x:v>
       </x:c>
       <x:c r="I287" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J287" s="33"/>
-      <x:c r="K287" s="33"/>
-      <x:c r="L287" s="33"/>
-      <x:c r="M287" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
-      </x:c>
+      <x:c r="J287" s="33" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="K287" s="33" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="L287" s="33" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="M287" s="32" t="str"/>
     </x:row>
     <x:row r="288">
       <x:c r="A288" s="32" t="n">
         <x:v>286</x:v>
       </x:c>
       <x:c r="B288" s="32" t="str">
-        <x:v>Stanfprd Medicine_Medcast 95_CME Certificate.pdf</x:v>
+        <x:v>Stanfrod-Coursera_Supporting families and caregivers Certificate_O8W0ZHG0J5II.pdf</x:v>
       </x:c>
       <x:c r="C288" s="32" t="str">
-        <x:v>Stanfprd Medicine</x:v>
+        <x:v>Stanford Online / Stanford Medicine</x:v>
       </x:c>
       <x:c r="D288" s="32" t="str">
-        <x:v>Stanfprd Medicine_Medcast 95_CME Certificate</x:v>
+        <x:v>Supporting Families and Caregivers</x:v>
       </x:c>
       <x:c r="E288" s="32" t="str">
-        <x:v>Stanford Center for Continuing Medical Education | cme.stanford.edu | Email: StanfordCME@stanford.edu Event ID 53645 Stanford University School of Medicine certifies that Pedro Lamounier Sampaio, LL.M. has participated for 0.50 hours in the Enduring Material titled Stanford Medcast Episode 106: Hot Topics Mini-Series - Laser Focused: Innovations and Equity in Dermatology on 08/30/2026 This Activity was designated for 0.50 AMA PRA Category 1 Credit(s)™ Accreditation In support of improving patien</x:v>
+        <x:v>A u g 3 0 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o S u p p o r t i n g F a m i l i e s a n d C a r e g i v e r s a n o n l i n e c o u r s e a u t h o r i z e d b y S t a n f o r d O n l i n e a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d K a v i t h a R a m c h a n d r a n C l i n i c a l A s s o c i a t e P r o f e s s o r O n c o l o g y J a n D e N o f r i o P h D P r o g r a m M a n a g e r P a l l i a t i v e C a r e A l w a y </x:v>
       </x:c>
       <x:c r="F288" s="32" t="str"/>
       <x:c r="G288" s="32" t="str">
-        <x:v>Grupo 3 — Extensão</x:v>
+        <x:v>Grupo 1 — Ensino</x:v>
       </x:c>
       <x:c r="H288" s="32" t="str">
-        <x:v>3.1</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="I288" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
       <x:c r="J288" s="33" t="n">
-        <x:v>0.5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="K288" s="33" t="n">
-        <x:v>0.5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="L288" s="33" t="n">
-        <x:v>0.5</x:v>
-      </x:c>
-      <x:c r="M288" s="32" t="str"/>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="M288" s="32" t="str">
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/O8W0ZHG0J5II</x:v>
+      </x:c>
     </x:row>
     <x:row r="289">
       <x:c r="A289" s="32" t="n">
         <x:v>287</x:v>
       </x:c>
       <x:c r="B289" s="32" t="str">
-        <x:v>Stanfrod-Coursera_Supporting families and caregivers Certificate_O8W0ZHG0J5II.pdf</x:v>
+        <x:v>texto 2.txt</x:v>
       </x:c>
       <x:c r="C289" s="32" t="str">
-        <x:v>Stanford Online / Stanford Medicine</x:v>
+        <x:v>texto 2</x:v>
       </x:c>
       <x:c r="D289" s="32" t="str">
-        <x:v>Supporting Families and Caregivers</x:v>
+        <x:v>texto 2</x:v>
       </x:c>
       <x:c r="E289" s="32" t="str">
-        <x:v>A u g 3 0 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o S u p p o r t i n g F a m i l i e s a n d C a r e g i v e r s a n o n l i n e c o u r s e a u t h o r i z e d b y S t a n f o r d O n l i n e a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d K a v i t h a R a m c h a n d r a n C l i n i c a l A s s o c i a t e P r o f e s s o r O n c o l o g y J a n D e N o f r i o P h D P r o g r a m M a n a g e r P a l l i a t i v e C a r e A l w a y </x:v>
+        <x:v>Anato_Cert-692737-01935-3059043.pdf</x:v>
       </x:c>
       <x:c r="F289" s="32" t="str"/>
       <x:c r="G289" s="32" t="str">
@@ -11053,17 +11079,11 @@
       <x:c r="I289" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J289" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="K289" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L289" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
+      <x:c r="J289" s="33"/>
+      <x:c r="K289" s="33"/>
+      <x:c r="L289" s="33"/>
       <x:c r="M289" s="32" t="str">
-        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/O8W0ZHG0J5II</x:v>
+        <x:v>Carga horária não localizada</x:v>
       </x:c>
     </x:row>
     <x:row r="290">
@@ -11071,16 +11091,16 @@
         <x:v>288</x:v>
       </x:c>
       <x:c r="B290" s="32" t="str">
-        <x:v>texto 2.txt</x:v>
+        <x:v>texto 3.txt</x:v>
       </x:c>
       <x:c r="C290" s="32" t="str">
-        <x:v>texto 2</x:v>
+        <x:v>texto 3</x:v>
       </x:c>
       <x:c r="D290" s="32" t="str">
-        <x:v>texto 2</x:v>
+        <x:v>texto 3</x:v>
       </x:c>
       <x:c r="E290" s="32" t="str">
-        <x:v>Anato_Cert-692737-01935-3059043.pdf</x:v>
+        <x:v># Definindo a lista de dados estruturada apenas com Hidroquinona e Arbutin dados_expandidos = { "Produto / Rótulo Comercial": [ # Iniciais (da lista anterior) "Hidroquinona 5% + Ácido Retinoico 0,025% + Dexametasona 0,05%", "Hidroquinona 4% + Alfa Bisabolol 1%", "Hidroquinona 40mg/g (4%) Creme Genérico (EMS)", "Vitacid Plus Creme (40mg/g)", "Suavicid Creme", "Hormoskin Creme", "Hidroquinona 5% Pura Creme Base", "Hidroquinona 4% Gel-Creme Hidratante", "Creme Gel para Peeling Noturno (Hidroquinona</x:v>
       </x:c>
       <x:c r="F290" s="32" t="str"/>
       <x:c r="G290" s="32" t="str">
@@ -11096,7 +11116,7 @@
       <x:c r="K290" s="33"/>
       <x:c r="L290" s="33"/>
       <x:c r="M290" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>https://produto.mercadolivre.com.br/MLB-3554868073-creme-despigmentante-alfa-arbutin-7-40g-_JM", | https://shopee.com.br/search?keyword=Alfa+Arbutin+Axilas", | https://shopee.com.br/search?keyword=Alfa+Arbutin+Formulab",</x:v>
       </x:c>
     </x:row>
     <x:row r="291">
@@ -11104,16 +11124,16 @@
         <x:v>289</x:v>
       </x:c>
       <x:c r="B291" s="32" t="str">
-        <x:v>texto 3.txt</x:v>
+        <x:v>texto.txt</x:v>
       </x:c>
       <x:c r="C291" s="32" t="str">
-        <x:v>texto 3</x:v>
+        <x:v>texto</x:v>
       </x:c>
       <x:c r="D291" s="32" t="str">
-        <x:v>texto 3</x:v>
+        <x:v>texto</x:v>
       </x:c>
       <x:c r="E291" s="32" t="str">
-        <x:v># Definindo a lista de dados estruturada apenas com Hidroquinona e Arbutin dados_expandidos = { "Produto / Rótulo Comercial": [ # Iniciais (da lista anterior) "Hidroquinona 5% + Ácido Retinoico 0,025% + Dexametasona 0,05%", "Hidroquinona 4% + Alfa Bisabolol 1%", "Hidroquinona 40mg/g (4%) Creme Genérico (EMS)", "Vitacid Plus Creme (40mg/g)", "Suavicid Creme", "Hormoskin Creme", "Hidroquinona 5% Pura Creme Base", "Hidroquinona 4% Gel-Creme Hidratante", "Creme Gel para Peeling Noturno (Hidroquinona</x:v>
+        <x:v>Quer fazer cursos gratuitos com certificados também? Baixe o app em https://cursa.app/pt/downapp</x:v>
       </x:c>
       <x:c r="F291" s="32" t="str"/>
       <x:c r="G291" s="32" t="str">
@@ -11129,7 +11149,7 @@
       <x:c r="K291" s="33"/>
       <x:c r="L291" s="33"/>
       <x:c r="M291" s="32" t="str">
-        <x:v>https://produto.mercadolivre.com.br/MLB-3554868073-creme-despigmentante-alfa-arbutin-7-40g-_JM", | https://shopee.com.br/search?keyword=Alfa+Arbutin+Axilas", | https://shopee.com.br/search?keyword=Alfa+Arbutin+Formulab",</x:v>
+        <x:v>https://cursa.app/pt/downapp</x:v>
       </x:c>
     </x:row>
     <x:row r="292">
@@ -11137,16 +11157,16 @@
         <x:v>290</x:v>
       </x:c>
       <x:c r="B292" s="32" t="str">
-        <x:v>texto.txt</x:v>
+        <x:v>TRREE (2023)_Certificate of completion for module 1_Intro to Research.pdf</x:v>
       </x:c>
       <x:c r="C292" s="32" t="str">
-        <x:v>texto</x:v>
+        <x:v>TRREE (2023)</x:v>
       </x:c>
       <x:c r="D292" s="32" t="str">
-        <x:v>texto</x:v>
+        <x:v>TRREE (2023)_Certificate of completion for module 1_Intro to Research</x:v>
       </x:c>
       <x:c r="E292" s="32" t="str">
-        <x:v>Quer fazer cursos gratuitos com certificados também? Baixe o app em https://cursa.app/pt/downapp</x:v>
+        <x:v>Zertifikat Certificado Certificat Certificate Promouvoir les plus hauts standards éthiques dans la protection des participants à la recherche biomédicale Promoting the highest ethical standards in the protection of biomedical research participants Professeur Dominique Sprumont Coordinateur TRREE Coordinator Certificat de formation - Training Certificate Ce document atteste que - this document certifies that Pedro Lamounier Sampaio a complété avec succès - has successfully completed Module 1 (202</x:v>
       </x:c>
       <x:c r="F292" s="32" t="str"/>
       <x:c r="G292" s="32" t="str">
@@ -11162,7 +11182,7 @@
       <x:c r="K292" s="33"/>
       <x:c r="L292" s="33"/>
       <x:c r="M292" s="32" t="str">
-        <x:v>https://cursa.app/pt/downapp</x:v>
+        <x:v>http://www.cihr-irsc.gc.ca/e/2891.html</x:v>
       </x:c>
     </x:row>
     <x:row r="293">
@@ -11170,16 +11190,16 @@
         <x:v>291</x:v>
       </x:c>
       <x:c r="B293" s="32" t="str">
-        <x:v>TRREE (2023)_Certificate of completion for module 1_Intro to Research.pdf</x:v>
+        <x:v>TRREE (2023)_Certificate of completion for module 2_Ethics Evaluation in Research.pdf</x:v>
       </x:c>
       <x:c r="C293" s="32" t="str">
         <x:v>TRREE (2023)</x:v>
       </x:c>
       <x:c r="D293" s="32" t="str">
-        <x:v>TRREE (2023)_Certificate of completion for module 1_Intro to Research</x:v>
+        <x:v>TRREE (2023)_Certificate of completion for module 2_Ethics Evaluation in Research</x:v>
       </x:c>
       <x:c r="E293" s="32" t="str">
-        <x:v>Zertifikat Certificado Certificat Certificate Promouvoir les plus hauts standards éthiques dans la protection des participants à la recherche biomédicale Promoting the highest ethical standards in the protection of biomedical research participants Professeur Dominique Sprumont Coordinateur TRREE Coordinator Certificat de formation - Training Certificate Ce document atteste que - this document certifies that Pedro Lamounier Sampaio a complété avec succès - has successfully completed Module 1 (202</x:v>
+        <x:v>Zertifikat Certificado Certificat Certificate Promouvoir les plus hauts standards éthiques dans la protection des participants à la recherche biomédicale Promoting the highest ethical standards in the protection of biomedical research participants Professeur Dominique Sprumont Coordinateur TRREE Coordinator Certificat de formation - Training Certificate Ce document atteste que - this document certifies that Pedro Lamounier Sampaio a complété avec succès - has successfully completed Module 2 (202</x:v>
       </x:c>
       <x:c r="F293" s="32" t="str"/>
       <x:c r="G293" s="32" t="str">
@@ -11203,16 +11223,16 @@
         <x:v>292</x:v>
       </x:c>
       <x:c r="B294" s="32" t="str">
-        <x:v>TRREE (2023)_Certificate of completion for module 2_Ethics Evaluation in Research.pdf</x:v>
+        <x:v>TRREE (2023)_Certificate of completion for module 3_Informed Consent_Certificate.pdf</x:v>
       </x:c>
       <x:c r="C294" s="32" t="str">
         <x:v>TRREE (2023)</x:v>
       </x:c>
       <x:c r="D294" s="32" t="str">
-        <x:v>TRREE (2023)_Certificate of completion for module 2_Ethics Evaluation in Research</x:v>
+        <x:v>TRREE (2023)_Certificate of completion for module 3_Informed Consent_Certificate</x:v>
       </x:c>
       <x:c r="E294" s="32" t="str">
-        <x:v>Zertifikat Certificado Certificat Certificate Promouvoir les plus hauts standards éthiques dans la protection des participants à la recherche biomédicale Promoting the highest ethical standards in the protection of biomedical research participants Professeur Dominique Sprumont Coordinateur TRREE Coordinator Certificat de formation - Training Certificate Ce document atteste que - this document certifies that Pedro Lamounier Sampaio a complété avec succès - has successfully completed Module 2 (202</x:v>
+        <x:v>Zertifikat Certificado Certificat Certificate Promouvoir les plus hauts standards éthiques dans la protection des participants à la recherche biomédicale Promoting the highest ethical standards in the protection of biomedical research participants Professeur Dominique Sprumont Coordinateur TRREE Coordinator Certificat de formation - Training Certificate Ce document atteste que - this document certifies that Pedro Lamounier Sampaio a complété avec succès - has successfully completed Module 3 (202</x:v>
       </x:c>
       <x:c r="F294" s="32" t="str"/>
       <x:c r="G294" s="32" t="str">
@@ -11236,16 +11256,16 @@
         <x:v>293</x:v>
       </x:c>
       <x:c r="B295" s="32" t="str">
-        <x:v>TRREE (2023)_Certificate of completion for module 3_Informed Consent_Certificate.pdf</x:v>
+        <x:v>TRREE_Module 4_R3_GCP_Certificate.pdf</x:v>
       </x:c>
       <x:c r="C295" s="32" t="str">
-        <x:v>TRREE (2023)</x:v>
+        <x:v>TRREE</x:v>
       </x:c>
       <x:c r="D295" s="32" t="str">
-        <x:v>TRREE (2023)_Certificate of completion for module 3_Informed Consent_Certificate</x:v>
+        <x:v>TRREE_Module 4_R3_GCP_Certificate</x:v>
       </x:c>
       <x:c r="E295" s="32" t="str">
-        <x:v>Zertifikat Certificado Certificat Certificate Promouvoir les plus hauts standards éthiques dans la protection des participants à la recherche biomédicale Promoting the highest ethical standards in the protection of biomedical research participants Professeur Dominique Sprumont Coordinateur TRREE Coordinator Certificat de formation - Training Certificate Ce document atteste que - this document certifies that Pedro Lamounier Sampaio a complété avec succès - has successfully completed Module 3 (202</x:v>
+        <x:v>Zertifikat Certificado Certificat Certificate Promouvoir les plus hauts standards éthiques dans la protection des participants à la recherche biomédicale Promoting the highest ethical standards in the protection of biomedical research participants Professeur Dominique Sprumont Coordinateur TRREE Coordinator Certificat de formation - Training Certificate Ce document atteste que - this document certifies that Pedro Lamounier Sampaio a complété avec succès - has successfully completed Module 4 - Go</x:v>
       </x:c>
       <x:c r="F295" s="32" t="str"/>
       <x:c r="G295" s="32" t="str">
@@ -11269,13 +11289,13 @@
         <x:v>294</x:v>
       </x:c>
       <x:c r="B296" s="32" t="str">
-        <x:v>TRREE_Module 4_R3_GCP_Certificate.pdf</x:v>
+        <x:v>TRREE_Module 4R2_GCP_Certificate.pdf</x:v>
       </x:c>
       <x:c r="C296" s="32" t="str">
         <x:v>TRREE</x:v>
       </x:c>
       <x:c r="D296" s="32" t="str">
-        <x:v>TRREE_Module 4_R3_GCP_Certificate</x:v>
+        <x:v>TRREE_Module 4R2_GCP_Certificate</x:v>
       </x:c>
       <x:c r="E296" s="32" t="str">
         <x:v>Zertifikat Certificado Certificat Certificate Promouvoir les plus hauts standards éthiques dans la protection des participants à la recherche biomédicale Promoting the highest ethical standards in the protection of biomedical research participants Professeur Dominique Sprumont Coordinateur TRREE Coordinator Certificat de formation - Training Certificate Ce document atteste que - this document certifies that Pedro Lamounier Sampaio a complété avec succès - has successfully completed Module 4 - Go</x:v>
@@ -11302,16 +11322,16 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="B297" s="32" t="str">
-        <x:v>TRREE_Module 4R2_GCP_Certificate.pdf</x:v>
+        <x:v>TRREE_Module 5.1 HIV Vaccine TrialsTraining certificate.pdf</x:v>
       </x:c>
       <x:c r="C297" s="32" t="str">
         <x:v>TRREE</x:v>
       </x:c>
       <x:c r="D297" s="32" t="str">
-        <x:v>TRREE_Module 4R2_GCP_Certificate</x:v>
+        <x:v>TRREE_Module 5.1 HIV Vaccine TrialsTraining certificate</x:v>
       </x:c>
       <x:c r="E297" s="32" t="str">
-        <x:v>Zertifikat Certificado Certificat Certificate Promouvoir les plus hauts standards éthiques dans la protection des participants à la recherche biomédicale Promoting the highest ethical standards in the protection of biomedical research participants Professeur Dominique Sprumont Coordinateur TRREE Coordinator Certificat de formation - Training Certificate Ce document atteste que - this document certifies that Pedro Lamounier Sampaio a complété avec succès - has successfully completed Module 4 - Go</x:v>
+        <x:v>Zertifikat Certificado Certificat Certificate Promouvoir les plus hauts standards éthiques dans la protection des participants à la recherche biomédicale Promoting the highest ethical standards in the protection of biomedical research participants Professeur Dominique Sprumont Coordinateur TRREE Coordinator Certificat de formation - Training Certificate Ce document atteste que - this document certifies that Pedro Lamounier Sampaio a complété avec succès - has successfully completed Module 5.1 - </x:v>
       </x:c>
       <x:c r="F297" s="32" t="str"/>
       <x:c r="G297" s="32" t="str">
@@ -11335,16 +11355,16 @@
         <x:v>296</x:v>
       </x:c>
       <x:c r="B298" s="32" t="str">
-        <x:v>TRREE_Module 5.1 HIV Vaccine TrialsTraining certificate.pdf</x:v>
+        <x:v>TRREE_Module 5.2_Adolescent participants in HIV Trials_Training certificate - Module 5.2.pdf</x:v>
       </x:c>
       <x:c r="C298" s="32" t="str">
         <x:v>TRREE</x:v>
       </x:c>
       <x:c r="D298" s="32" t="str">
-        <x:v>TRREE_Module 5.1 HIV Vaccine TrialsTraining certificate</x:v>
+        <x:v>TRREE_Module 5.2_Adolescent participants in HIV Trials_Training certificate - Module 5.2</x:v>
       </x:c>
       <x:c r="E298" s="32" t="str">
-        <x:v>Zertifikat Certificado Certificat Certificate Promouvoir les plus hauts standards éthiques dans la protection des participants à la recherche biomédicale Promoting the highest ethical standards in the protection of biomedical research participants Professeur Dominique Sprumont Coordinateur TRREE Coordinator Certificat de formation - Training Certificate Ce document atteste que - this document certifies that Pedro Lamounier Sampaio a complété avec succès - has successfully completed Module 5.1 - </x:v>
+        <x:v>Zertifikat Certificado Certificat Certificate Promouvoir les plus hauts standards éthiques dans la protection des participants à la recherche biomédicale Promoting the highest ethical standards in the protection of biomedical research participants Professeur Dominique Sprumont Coordinateur TRREE Coordinator Certificat de formation - Training Certificate Ce document atteste que - this document certifies that Pedro Lamounier Sampaio a complété avec succès - has successfully completed Module 5.2 - </x:v>
       </x:c>
       <x:c r="F298" s="32" t="str"/>
       <x:c r="G298" s="32" t="str">
@@ -11368,16 +11388,16 @@
         <x:v>297</x:v>
       </x:c>
       <x:c r="B299" s="32" t="str">
-        <x:v>TRREE_Module 5.2_Adolescent participants in HIV Trials_Training certificate - Module 5.2.pdf</x:v>
+        <x:v>TRREE_Module 5.3_Ethics in PH Research_Training Certificate.pdf</x:v>
       </x:c>
       <x:c r="C299" s="32" t="str">
         <x:v>TRREE</x:v>
       </x:c>
       <x:c r="D299" s="32" t="str">
-        <x:v>TRREE_Module 5.2_Adolescent participants in HIV Trials_Training certificate - Module 5.2</x:v>
+        <x:v>TRREE_Module 5.3_Ethics in PH Research_Training Certificate</x:v>
       </x:c>
       <x:c r="E299" s="32" t="str">
-        <x:v>Zertifikat Certificado Certificat Certificate Promouvoir les plus hauts standards éthiques dans la protection des participants à la recherche biomédicale Promoting the highest ethical standards in the protection of biomedical research participants Professeur Dominique Sprumont Coordinateur TRREE Coordinator Certificat de formation - Training Certificate Ce document atteste que - this document certifies that Pedro Lamounier Sampaio a complété avec succès - has successfully completed Module 5.2 - </x:v>
+        <x:v>Zertifikat Certificado Certificat Certificate Promouvoir les plus hauts standards éthiques dans la protection des participants à la recherche biomédicale Promoting the highest ethical standards in the protection of biomedical research participants Professeur Dominique Sprumont Coordinateur TRREE Coordinator Certificat de formation - Training Certificate Ce document atteste que - this document certifies that Pedro Lamounier Sampaio a complété avec succès - has successfully completed Module 5.3 - </x:v>
       </x:c>
       <x:c r="F299" s="32" t="str"/>
       <x:c r="G299" s="32" t="str">
@@ -11401,16 +11421,16 @@
         <x:v>298</x:v>
       </x:c>
       <x:c r="B300" s="32" t="str">
-        <x:v>TRREE_Module 5.3_Ethics in PH Research_Training Certificate.pdf</x:v>
+        <x:v>TRREE_Reg. Frameworks_Suisse-2025_Certificate.pdf</x:v>
       </x:c>
       <x:c r="C300" s="32" t="str">
         <x:v>TRREE</x:v>
       </x:c>
       <x:c r="D300" s="32" t="str">
-        <x:v>TRREE_Module 5.3_Ethics in PH Research_Training Certificate</x:v>
+        <x:v>TRREE_Reg. Frameworks_Suisse-2025_Certificate</x:v>
       </x:c>
       <x:c r="E300" s="32" t="str">
-        <x:v>Zertifikat Certificado Certificat Certificate Promouvoir les plus hauts standards éthiques dans la protection des participants à la recherche biomédicale Promoting the highest ethical standards in the protection of biomedical research participants Professeur Dominique Sprumont Coordinateur TRREE Coordinator Certificat de formation - Training Certificate Ce document atteste que - this document certifies that Pedro Lamounier Sampaio a complété avec succès - has successfully completed Module 5.3 - </x:v>
+        <x:v>Zertifikat Certificado Certificat Certificate Promouvoir les plus hauts standards éthiques dans la protection des participants à la recherche biomédicale Promoting the highest ethical standards in the protection of biomedical research participants Professeur Dominique Sprumont Coordinateur TRREE Coordinator Certificat de formation - Training Certificate Ce document atteste que - this document certifies that Pedro Lamounier Sampaio a complété avec succès - has successfully completed Swiss Nationa</x:v>
       </x:c>
       <x:c r="F300" s="32" t="str"/>
       <x:c r="G300" s="32" t="str">
@@ -11434,16 +11454,16 @@
         <x:v>299</x:v>
       </x:c>
       <x:c r="B301" s="32" t="str">
-        <x:v>TRREE_Reg. Frameworks_Suisse-2025_Certificate.pdf</x:v>
+        <x:v>U-M-Coursera_Translating Research to communities Certificate_WWZOYLD9AB26.pdf</x:v>
       </x:c>
       <x:c r="C301" s="32" t="str">
-        <x:v>TRREE</x:v>
+        <x:v>University of Michigan</x:v>
       </x:c>
       <x:c r="D301" s="32" t="str">
-        <x:v>TRREE_Reg. Frameworks_Suisse-2025_Certificate</x:v>
+        <x:v>Translating Research to Communities</x:v>
       </x:c>
       <x:c r="E301" s="32" t="str">
-        <x:v>Zertifikat Certificado Certificat Certificate Promouvoir les plus hauts standards éthiques dans la protection des participants à la recherche biomédicale Promoting the highest ethical standards in the protection of biomedical research participants Professeur Dominique Sprumont Coordinateur TRREE Coordinator Certificat de formation - Training Certificate Ce document atteste que - this document certifies that Pedro Lamounier Sampaio a complété avec succès - has successfully completed Swiss Nationa</x:v>
+        <x:v>A u g 2 9 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o T r a n s l a t i n g R e s e a r c h t o C o m m u n i t i e s a n o n l i n e c o u r s e a u t h o r i z e d b y U n i v e r s i t y o f M i c h i g a n a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d V i c k i E l l i n g r o d J o h n G i d e o n S e a r l e P r o f e s s o r o f P h a r m a c y , D e a n ; P r o f e s s o r o f P s y c h i a t r y C o l l e g e o f P h a r m a c </x:v>
       </x:c>
       <x:c r="F301" s="32" t="str"/>
       <x:c r="G301" s="32" t="str">
@@ -11455,11 +11475,17 @@
       <x:c r="I301" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J301" s="33"/>
-      <x:c r="K301" s="33"/>
-      <x:c r="L301" s="33"/>
+      <x:c r="J301" s="33" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K301" s="33" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="L301" s="33" t="n">
+        <x:v>6</x:v>
+      </x:c>
       <x:c r="M301" s="32" t="str">
-        <x:v>http://www.cihr-irsc.gc.ca/e/2891.html</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/WWZOYLD9AB26</x:v>
       </x:c>
     </x:row>
     <x:row r="302">
@@ -11467,16 +11493,16 @@
         <x:v>300</x:v>
       </x:c>
       <x:c r="B302" s="32" t="str">
-        <x:v>U-M-Coursera_Translating Research to communities Certificate_WWZOYLD9AB26.pdf</x:v>
+        <x:v>U-M-Coursera_Translating Research to Patients Certificate_IKDNWXUCALFA.pdf</x:v>
       </x:c>
       <x:c r="C302" s="32" t="str">
         <x:v>University of Michigan</x:v>
       </x:c>
       <x:c r="D302" s="32" t="str">
-        <x:v>Translating Research to Communities</x:v>
+        <x:v>Translating Research to Patients</x:v>
       </x:c>
       <x:c r="E302" s="32" t="str">
-        <x:v>A u g 2 9 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o T r a n s l a t i n g R e s e a r c h t o C o m m u n i t i e s a n o n l i n e c o u r s e a u t h o r i z e d b y U n i v e r s i t y o f M i c h i g a n a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d V i c k i E l l i n g r o d J o h n G i d e o n S e a r l e P r o f e s s o r o f P h a r m a c y , D e a n ; P r o f e s s o r o f P s y c h i a t r y C o l l e g e o f P h a r m a c </x:v>
+        <x:v>A u g 2 9 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o T r a n s l a t i n g R e s e a r c h t o P a t i e n t s a n o n l i n e c o u r s e a u t h o r i z e d b y U n i v e r s i t y o f M i c h i g a n a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d V i c k i E l l i n g r o d J o h n G i d e o n S e a r l e P r o f e s s o r o f P h a r m a c y , D e a n ; P r o f e s s o r o f P s y c h i a t r y C o l l e g e o f P h a r m a c y , M </x:v>
       </x:c>
       <x:c r="F302" s="32" t="str"/>
       <x:c r="G302" s="32" t="str">
@@ -11498,7 +11524,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="M302" s="32" t="str">
-        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/WWZOYLD9AB26</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/IKDNWXUCALFA</x:v>
       </x:c>
     </x:row>
     <x:row r="303">
@@ -11506,16 +11532,16 @@
         <x:v>301</x:v>
       </x:c>
       <x:c r="B303" s="32" t="str">
-        <x:v>U-M-Coursera_Translating Research to Patients Certificate_IKDNWXUCALFA.pdf</x:v>
+        <x:v>U-M-Coursera_Translating Research to Policy Certificate_0HXUUQIWD1P7.pdf</x:v>
       </x:c>
       <x:c r="C303" s="32" t="str">
         <x:v>University of Michigan</x:v>
       </x:c>
       <x:c r="D303" s="32" t="str">
-        <x:v>Translating Research to Patients</x:v>
+        <x:v>Translating Research to Healthcare Policy</x:v>
       </x:c>
       <x:c r="E303" s="32" t="str">
-        <x:v>A u g 2 9 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o T r a n s l a t i n g R e s e a r c h t o P a t i e n t s a n o n l i n e c o u r s e a u t h o r i z e d b y U n i v e r s i t y o f M i c h i g a n a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d V i c k i E l l i n g r o d J o h n G i d e o n S e a r l e P r o f e s s o r o f P h a r m a c y , D e a n ; P r o f e s s o r o f P s y c h i a t r y C o l l e g e o f P h a r m a c y , M </x:v>
+        <x:v>A u g 2 9 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o T r a n s l a t i n g R e s e a r c h t o H e a l t h c a r e P o l i c y a n o n l i n e c o u r s e a u t h o r i z e d b y U n i v e r s i t y o f M i c h i g a n a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d V i c k i E l l i n g r o d J o h n G i d e o n S e a r l e P r o f e s s o r o f P h a r m a c y , D e a n ; P r o f e s s o r o f P s y c h i a t r y C o l l e g e o f P h </x:v>
       </x:c>
       <x:c r="F303" s="32" t="str"/>
       <x:c r="G303" s="32" t="str">
@@ -11528,16 +11554,16 @@
         <x:v>Extraído do documento</x:v>
       </x:c>
       <x:c r="J303" s="33" t="n">
-        <x:v>6</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="K303" s="33" t="n">
-        <x:v>6</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="L303" s="33" t="n">
-        <x:v>6</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="M303" s="32" t="str">
-        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/IKDNWXUCALFA</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/0HXUUQIWD1P7</x:v>
       </x:c>
     </x:row>
     <x:row r="304">
@@ -11545,16 +11571,16 @@
         <x:v>302</x:v>
       </x:c>
       <x:c r="B304" s="32" t="str">
-        <x:v>U-M-Coursera_Translating Research to Policy Certificate_0HXUUQIWD1P7.pdf</x:v>
+        <x:v>U-M-Coursera_Translational Research for humans_Certificate 7MIVPFC1VTQR.pdf</x:v>
       </x:c>
       <x:c r="C304" s="32" t="str">
         <x:v>University of Michigan</x:v>
       </x:c>
       <x:c r="D304" s="32" t="str">
-        <x:v>Translating Research to Healthcare Policy</x:v>
+        <x:v>Translating Basic Research into Research for Humans</x:v>
       </x:c>
       <x:c r="E304" s="32" t="str">
-        <x:v>A u g 2 9 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o T r a n s l a t i n g R e s e a r c h t o H e a l t h c a r e P o l i c y a n o n l i n e c o u r s e a u t h o r i z e d b y U n i v e r s i t y o f M i c h i g a n a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d V i c k i E l l i n g r o d J o h n G i d e o n S e a r l e P r o f e s s o r o f P h a r m a c y , D e a n ; P r o f e s s o r o f P s y c h i a t r y C o l l e g e o f P h </x:v>
+        <x:v>A u g 1 3 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o T r a n s l a t i n g B a s i c R e s e a r c h i n t o R e s e a r c h f o r H u m a n s a n o n l i n e c o u r s e a u t h o r i z e d b y U n i v e r s i t y o f M i c h i g a n a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d V i c k i E l l i n g r o d S e n i o r A s s o c i a t e D e a n C o l l e g e o f P h a r m a c y V e r i f y a t : h t t p s : / / c o u r s e r a . o r g </x:v>
       </x:c>
       <x:c r="F304" s="32" t="str"/>
       <x:c r="G304" s="32" t="str">
@@ -11567,16 +11593,16 @@
         <x:v>Extraído do documento</x:v>
       </x:c>
       <x:c r="J304" s="33" t="n">
-        <x:v>9</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K304" s="33" t="n">
-        <x:v>9</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L304" s="33" t="n">
-        <x:v>9</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="M304" s="32" t="str">
-        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/0HXUUQIWD1P7</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/7MIVPFC1VTQR</x:v>
       </x:c>
     </x:row>
     <x:row r="305">
@@ -11584,16 +11610,16 @@
         <x:v>303</x:v>
       </x:c>
       <x:c r="B305" s="32" t="str">
-        <x:v>U-M-Coursera_Translational Research for humans_Certificate 7MIVPFC1VTQR.pdf</x:v>
+        <x:v>U-M-Coursera_Translational Science Specialization Certificate_IXQRUXCLXP3K.pdf</x:v>
       </x:c>
       <x:c r="C305" s="32" t="str">
         <x:v>University of Michigan</x:v>
       </x:c>
       <x:c r="D305" s="32" t="str">
-        <x:v>Translating Basic Research into Research for Humans</x:v>
+        <x:v>Translational Science</x:v>
       </x:c>
       <x:c r="E305" s="32" t="str">
-        <x:v>A u g 1 3 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o T r a n s l a t i n g B a s i c R e s e a r c h i n t o R e s e a r c h f o r H u m a n s a n o n l i n e c o u r s e a u t h o r i z e d b y U n i v e r s i t y o f M i c h i g a n a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d V i c k i E l l i n g r o d S e n i o r A s s o c i a t e D e a n C o l l e g e o f P h a r m a c y V e r i f y a t : h t t p s : / / c o u r s e r a . o r g </x:v>
+        <x:v>5 C o u r s e s I n t r o d u c t i o n t o T r a n s l a t i o n a l S c i e n c e T r a n s l a t i n g B a s i c R e s e a r c h i n t o R e s e a r c h f o r H u m a n s T r a n s l a t i n g R e s e a r c h t o P a t i e n t s T r a n s l a t i n g R e s e a r c h t o C o m m u n i t i e s T r a n s l a t i n g R e s e a r c h t o H e a l t h c a r e P o l i c y V i c k i E l l i n g r o d S e n i o r A s s o c i a t e D e a n C o l l e g e o f P h a r m a c y A u g 2 9 , 2 0 2 6 P e d r o </x:v>
       </x:c>
       <x:c r="F305" s="32" t="str"/>
       <x:c r="G305" s="32" t="str">
@@ -11606,16 +11632,16 @@
         <x:v>Extraído do documento</x:v>
       </x:c>
       <x:c r="J305" s="33" t="n">
-        <x:v>4</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="K305" s="33" t="n">
-        <x:v>4</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="L305" s="33" t="n">
-        <x:v>4</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="M305" s="32" t="str">
-        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/7MIVPFC1VTQR</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/specialization/IXQRUXCLXP3K; estimativa derivada do tempo exibido: 1 meses com 10 por semana para concluir</x:v>
       </x:c>
     </x:row>
     <x:row r="306">
@@ -11623,17 +11649,15 @@
         <x:v>304</x:v>
       </x:c>
       <x:c r="B306" s="32" t="str">
-        <x:v>U-M-Coursera_Translational Science Specialization Certificate_IXQRUXCLXP3K.pdf</x:v>
+        <x:v>UFMA_DRC na APS_Certificafdo de Curso.pdf</x:v>
       </x:c>
       <x:c r="C306" s="32" t="str">
-        <x:v>University of Michigan</x:v>
+        <x:v>UFMA</x:v>
       </x:c>
       <x:c r="D306" s="32" t="str">
-        <x:v>Translational Science</x:v>
-      </x:c>
-      <x:c r="E306" s="32" t="str">
-        <x:v>5 C o u r s e s I n t r o d u c t i o n t o T r a n s l a t i o n a l S c i e n c e T r a n s l a t i n g B a s i c R e s e a r c h i n t o R e s e a r c h f o r H u m a n s T r a n s l a t i n g R e s e a r c h t o P a t i e n t s T r a n s l a t i n g R e s e a r c h t o C o m m u n i t i e s T r a n s l a t i n g R e s e a r c h t o H e a l t h c a r e P o l i c y V i c k i E l l i n g r o d S e n i o r A s s o c i a t e D e a n C o l l e g e o f P h a r m a c y A u g 2 9 , 2 0 2 6 P e d r o </x:v>
-      </x:c>
+        <x:v>UFMA_DRC na APS_Certificafdo de Curso</x:v>
+      </x:c>
+      <x:c r="E306" s="32" t="str"/>
       <x:c r="F306" s="32" t="str"/>
       <x:c r="G306" s="32" t="str">
         <x:v>Grupo 1 — Ensino</x:v>
@@ -11642,19 +11666,13 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="I306" s="32" t="str">
-        <x:v>Extraído do documento</x:v>
-      </x:c>
-      <x:c r="J306" s="33" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="K306" s="33" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="L306" s="33" t="n">
-        <x:v>40</x:v>
-      </x:c>
+        <x:v>Sem texto extraível — revisão manual</x:v>
+      </x:c>
+      <x:c r="J306" s="33"/>
+      <x:c r="K306" s="33"/>
+      <x:c r="L306" s="33"/>
       <x:c r="M306" s="32" t="str">
-        <x:v>Coursera: https://www.coursera.org/account/accomplishments/specialization/IXQRUXCLXP3K; estimativa derivada do tempo exibido: 1 meses com 10 por semana para concluir</x:v>
+        <x:v>Carga horária não localizada</x:v>
       </x:c>
     </x:row>
     <x:row r="307">
@@ -11662,15 +11680,17 @@
         <x:v>305</x:v>
       </x:c>
       <x:c r="B307" s="32" t="str">
-        <x:v>UFMA_DRC na APS_Certificafdo de Curso.pdf</x:v>
+        <x:v>UFMG-UNA-SUS_M1_Atributos da APS_certificado_1f198775-dbe8-6290-b71e-85b8bf09b5ac.pdf</x:v>
       </x:c>
       <x:c r="C307" s="32" t="str">
-        <x:v>UFMA</x:v>
+        <x:v>UFMG</x:v>
       </x:c>
       <x:c r="D307" s="32" t="str">
-        <x:v>UFMA_DRC na APS_Certificafdo de Curso</x:v>
-      </x:c>
-      <x:c r="E307" s="32" t="str"/>
+        <x:v>UFMG-UNA-SUS_M1_Atributos da APS_certificado_1f198775-dbe8-6290-b71e-85b8bf09b5ac</x:v>
+      </x:c>
+      <x:c r="E307" s="32" t="str">
+        <x:v>/gid00003/gid00032/gid00039/gid00042/gid00001/gid00009/gid00042/gid00045/gid00036/gid00053/gid00042/gid00041/gid00047/gid00032/gid01142/gid00001 /gid00002/gid00001/gid00022/gid00041/gid00036/gid00049/gid00032/gid00045/gid00046/gid00036/gid00031/gid00028/gid00031/gid00032/gid00001/gid00007/gid00032/gid00031/gid00032/gid00045/gid00028/gid00039/gid00001/gid00031/gid00032/gid00001/gid00014/gid00036/gid00041/gid00028/gid00046/gid00001/gid00008/gid00032/gid00045/gid00028/gid00036/gid00046/gid00001/gid</x:v>
+      </x:c>
       <x:c r="F307" s="32" t="str"/>
       <x:c r="G307" s="32" t="str">
         <x:v>Grupo 1 — Ensino</x:v>
@@ -11679,7 +11699,7 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="I307" s="32" t="str">
-        <x:v>Sem texto extraível — revisão manual</x:v>
+        <x:v>Extraído do documento</x:v>
       </x:c>
       <x:c r="J307" s="33"/>
       <x:c r="K307" s="33"/>
@@ -11693,16 +11713,16 @@
         <x:v>306</x:v>
       </x:c>
       <x:c r="B308" s="32" t="str">
-        <x:v>UFMG-UNA-SUS_M1_Atributos da APS_certificado_1f198775-dbe8-6290-b71e-85b8bf09b5ac.pdf</x:v>
+        <x:v>UFMG_Aceleracao Saude Digital APS_Certificado2406162535PL.pdf</x:v>
       </x:c>
       <x:c r="C308" s="32" t="str">
         <x:v>UFMG</x:v>
       </x:c>
       <x:c r="D308" s="32" t="str">
-        <x:v>UFMG-UNA-SUS_M1_Atributos da APS_certificado_1f198775-dbe8-6290-b71e-85b8bf09b5ac</x:v>
+        <x:v>UFMG_Aceleracao Saude Digital APS_Certificado2406162535PL</x:v>
       </x:c>
       <x:c r="E308" s="32" t="str">
-        <x:v>/gid00003/gid00032/gid00039/gid00042/gid00001/gid00009/gid00042/gid00045/gid00036/gid00053/gid00042/gid00041/gid00047/gid00032/gid01142/gid00001 /gid00002/gid00001/gid00022/gid00041/gid00036/gid00049/gid00032/gid00045/gid00046/gid00036/gid00031/gid00028/gid00031/gid00032/gid00001/gid00007/gid00032/gid00031/gid00032/gid00045/gid00028/gid00039/gid00001/gid00031/gid00032/gid00001/gid00014/gid00036/gid00041/gid00028/gid00046/gid00001/gid00008/gid00032/gid00045/gid00028/gid00036/gid00046/gid00001/gid</x:v>
+        <x:v>Certificamos que 30 de agosto de 2026Belo Horizonte, PEDRO LAMOUNIER SAMPAIO concluiu o Curso Aceleração para Saúde Digital na Atenção Primária à Saúde, que faz parte da trilha formativa para Profissionais de Saúde. O curso, realizado na modalidade EaD autoinstrucional, teve carga horária de 25 horas. Educa e-SUS APS é uma parceria da Coordenação-Geral de Projetos e Inovação da Secretaria de Atenção Primária à Saúde do Ministério da Saúde com a Universidade Federal de Minas Gerais. RODRIGO ANDRÉ</x:v>
       </x:c>
       <x:c r="F308" s="32" t="str"/>
       <x:c r="G308" s="32" t="str">
@@ -11714,11 +11734,17 @@
       <x:c r="I308" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J308" s="33"/>
-      <x:c r="K308" s="33"/>
-      <x:c r="L308" s="33"/>
+      <x:c r="J308" s="33" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="K308" s="33" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="L308" s="33" t="n">
+        <x:v>25</x:v>
+      </x:c>
       <x:c r="M308" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>https://educaesusaps.medicina.ufmg.br</x:v>
       </x:c>
     </x:row>
     <x:row r="309">
@@ -11726,38 +11752,38 @@
         <x:v>307</x:v>
       </x:c>
       <x:c r="B309" s="32" t="str">
-        <x:v>UFMG_Aceleracao Saude Digital APS_Certificado2406162535PL.pdf</x:v>
+        <x:v>UNA-SUS-UFMA_Aperfeiçoamento em DRC_Certificado.pdf</x:v>
       </x:c>
       <x:c r="C309" s="32" t="str">
-        <x:v>UFMG</x:v>
+        <x:v>Ministério da Saúde / UFMA VIRTUAL-STED</x:v>
       </x:c>
       <x:c r="D309" s="32" t="str">
-        <x:v>UFMG_Aceleracao Saude Digital APS_Certificado2406162535PL</x:v>
+        <x:v>Curso de Aperfeiçoamento em Nefrologia Interdisciplinar para Profissionais do SUS</x:v>
       </x:c>
       <x:c r="E309" s="32" t="str">
-        <x:v>Certificamos que 30 de agosto de 2026Belo Horizonte, PEDRO LAMOUNIER SAMPAIO concluiu o Curso Aceleração para Saúde Digital na Atenção Primária à Saúde, que faz parte da trilha formativa para Profissionais de Saúde. O curso, realizado na modalidade EaD autoinstrucional, teve carga horária de 25 horas. Educa e-SUS APS é uma parceria da Coordenação-Geral de Projetos e Inovação da Secretaria de Atenção Primária à Saúde do Ministério da Saúde com a Universidade Federal de Minas Gerais. RODRIGO ANDRÉ</x:v>
+        <x:v>Introdução ao estudo da DRC (45 h); abordagem da DRC na APS (30 h); manejo clínico da DRC (60 h); diálise peritoneal (30 h); atendimento interdisciplinar da DRC (30 h).</x:v>
       </x:c>
       <x:c r="F309" s="32" t="str"/>
       <x:c r="G309" s="32" t="str">
-        <x:v>Grupo 1 — Ensino</x:v>
+        <x:v>Grupo 3 — Extensão</x:v>
       </x:c>
       <x:c r="H309" s="32" t="str">
-        <x:v>1.5</x:v>
+        <x:v>3.5</x:v>
       </x:c>
       <x:c r="I309" s="32" t="str">
-        <x:v>Extraído do documento</x:v>
+        <x:v>Sem texto extraível — revisão manual</x:v>
       </x:c>
       <x:c r="J309" s="33" t="n">
-        <x:v>25</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="K309" s="33" t="n">
-        <x:v>25</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="L309" s="33" t="n">
-        <x:v>25</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="M309" s="32" t="str">
-        <x:v>https://educaesusaps.medicina.ufmg.br</x:v>
+        <x:v>Certificado e verso detalham cinco módulos e total de 195 h.</x:v>
       </x:c>
     </x:row>
     <x:row r="310">
@@ -11765,38 +11791,30 @@
         <x:v>308</x:v>
       </x:c>
       <x:c r="B310" s="32" t="str">
-        <x:v>UNA-SUS-UFMA_Aperfeiçoamento em DRC_Certificado.pdf</x:v>
+        <x:v>UNA-SUS-UFMA_Atendimento Interdisciplinar DRC_M5_Certificado.pdf</x:v>
       </x:c>
       <x:c r="C310" s="32" t="str">
-        <x:v>Ministério da Saúde / UFMA VIRTUAL-STED</x:v>
+        <x:v>UNA</x:v>
       </x:c>
       <x:c r="D310" s="32" t="str">
-        <x:v>Curso de Aperfeiçoamento em Nefrologia Interdisciplinar para Profissionais do SUS</x:v>
-      </x:c>
-      <x:c r="E310" s="32" t="str">
-        <x:v>Introdução ao estudo da DRC (45 h); abordagem da DRC na APS (30 h); manejo clínico da DRC (60 h); diálise peritoneal (30 h); atendimento interdisciplinar da DRC (30 h).</x:v>
-      </x:c>
+        <x:v>UNA-SUS-UFMA_Atendimento Interdisciplinar DRC_M5_Certificado</x:v>
+      </x:c>
+      <x:c r="E310" s="32" t="str"/>
       <x:c r="F310" s="32" t="str"/>
       <x:c r="G310" s="32" t="str">
-        <x:v>Grupo 3 — Extensão</x:v>
+        <x:v>Grupo 1 — Ensino</x:v>
       </x:c>
       <x:c r="H310" s="32" t="str">
-        <x:v>3.5</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="I310" s="32" t="str">
         <x:v>Sem texto extraível — revisão manual</x:v>
       </x:c>
-      <x:c r="J310" s="33" t="n">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="K310" s="33" t="n">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="L310" s="33" t="n">
-        <x:v>195</x:v>
-      </x:c>
+      <x:c r="J310" s="33"/>
+      <x:c r="K310" s="33"/>
+      <x:c r="L310" s="33"/>
       <x:c r="M310" s="32" t="str">
-        <x:v>Certificado e verso detalham cinco módulos e total de 195 h.</x:v>
+        <x:v>Carga horária não localizada</x:v>
       </x:c>
     </x:row>
     <x:row r="311">
@@ -11804,13 +11822,13 @@
         <x:v>309</x:v>
       </x:c>
       <x:c r="B311" s="32" t="str">
-        <x:v>UNA-SUS-UFMA_Atendimento Interdisciplinar DRC_M5_Certificado.pdf</x:v>
+        <x:v>UNA-SUS-UFMA_Diálise Peritoneal_M4_Certificado.pdf</x:v>
       </x:c>
       <x:c r="C311" s="32" t="str">
         <x:v>UNA</x:v>
       </x:c>
       <x:c r="D311" s="32" t="str">
-        <x:v>UNA-SUS-UFMA_Atendimento Interdisciplinar DRC_M5_Certificado</x:v>
+        <x:v>UNA-SUS-UFMA_Diálise Peritoneal_M4_Certificado</x:v>
       </x:c>
       <x:c r="E311" s="32" t="str"/>
       <x:c r="F311" s="32" t="str"/>
@@ -11835,13 +11853,13 @@
         <x:v>310</x:v>
       </x:c>
       <x:c r="B312" s="32" t="str">
-        <x:v>UNA-SUS-UFMA_Diálise Peritoneal_M4_Certificado.pdf</x:v>
+        <x:v>UNA-SUS-UFMA_IA na Saúde_Extensão_Certificado.pdf</x:v>
       </x:c>
       <x:c r="C312" s="32" t="str">
         <x:v>UNA</x:v>
       </x:c>
       <x:c r="D312" s="32" t="str">
-        <x:v>UNA-SUS-UFMA_Diálise Peritoneal_M4_Certificado</x:v>
+        <x:v>UNA-SUS-UFMA_IA na Saúde_Extensão_Certificado</x:v>
       </x:c>
       <x:c r="E312" s="32" t="str"/>
       <x:c r="F312" s="32" t="str"/>
@@ -11866,13 +11884,13 @@
         <x:v>311</x:v>
       </x:c>
       <x:c r="B313" s="32" t="str">
-        <x:v>UNA-SUS-UFMA_IA na Saúde_Extensão_Certificado.pdf</x:v>
+        <x:v>UNA-SUS-UFMA_Introdução à DRC_M1_Certificado.pdf</x:v>
       </x:c>
       <x:c r="C313" s="32" t="str">
         <x:v>UNA</x:v>
       </x:c>
       <x:c r="D313" s="32" t="str">
-        <x:v>UNA-SUS-UFMA_IA na Saúde_Extensão_Certificado</x:v>
+        <x:v>UNA-SUS-UFMA_Introdução à DRC_M1_Certificado</x:v>
       </x:c>
       <x:c r="E313" s="32" t="str"/>
       <x:c r="F313" s="32" t="str"/>
@@ -11897,13 +11915,13 @@
         <x:v>312</x:v>
       </x:c>
       <x:c r="B314" s="32" t="str">
-        <x:v>UNA-SUS-UFMA_Introdução à DRC_M1_Certificado.pdf</x:v>
+        <x:v>UNA-SUS-UFMA_Manejo clínico da DRC_M3_Certificado.pdf</x:v>
       </x:c>
       <x:c r="C314" s="32" t="str">
         <x:v>UNA</x:v>
       </x:c>
       <x:c r="D314" s="32" t="str">
-        <x:v>UNA-SUS-UFMA_Introdução à DRC_M1_Certificado</x:v>
+        <x:v>UNA-SUS-UFMA_Manejo clínico da DRC_M3_Certificado</x:v>
       </x:c>
       <x:c r="E314" s="32" t="str"/>
       <x:c r="F314" s="32" t="str"/>
@@ -11928,13 +11946,13 @@
         <x:v>313</x:v>
       </x:c>
       <x:c r="B315" s="32" t="str">
-        <x:v>UNA-SUS-UFMA_Manejo clínico da DRC_M3_Certificado.pdf</x:v>
+        <x:v>UNA-SUS-UFMA_Registros e Qualidade na Saúde Digital_Certificado de Conclusao_.pdf</x:v>
       </x:c>
       <x:c r="C315" s="32" t="str">
         <x:v>UNA</x:v>
       </x:c>
       <x:c r="D315" s="32" t="str">
-        <x:v>UNA-SUS-UFMA_Manejo clínico da DRC_M3_Certificado</x:v>
+        <x:v>UNA-SUS-UFMA_Registros e Qualidade na Saúde Digital_Certificado de Conclusao_</x:v>
       </x:c>
       <x:c r="E315" s="32" t="str"/>
       <x:c r="F315" s="32" t="str"/>
@@ -11959,13 +11977,13 @@
         <x:v>314</x:v>
       </x:c>
       <x:c r="B316" s="32" t="str">
-        <x:v>UNA-SUS-UFMA_Registros e Qualidade na Saúde Digital_Certificado de Conclusao_.pdf</x:v>
+        <x:v>UNA-SUS-UFMA_Saude Digital e SUS_Certificado Extensão.pdf</x:v>
       </x:c>
       <x:c r="C316" s="32" t="str">
         <x:v>UNA</x:v>
       </x:c>
       <x:c r="D316" s="32" t="str">
-        <x:v>UNA-SUS-UFMA_Registros e Qualidade na Saúde Digital_Certificado de Conclusao_</x:v>
+        <x:v>UNA-SUS-UFMA_Saude Digital e SUS_Certificado Extensão</x:v>
       </x:c>
       <x:c r="E316" s="32" t="str"/>
       <x:c r="F316" s="32" t="str"/>
@@ -11990,13 +12008,13 @@
         <x:v>315</x:v>
       </x:c>
       <x:c r="B317" s="32" t="str">
-        <x:v>UNA-SUS-UFMA_Saude Digital e SUS_Certificado Extensão.pdf</x:v>
+        <x:v>UNA-SUS-UFMA_Saúde Digital Inclusiva_Certificado.pdf</x:v>
       </x:c>
       <x:c r="C317" s="32" t="str">
         <x:v>UNA</x:v>
       </x:c>
       <x:c r="D317" s="32" t="str">
-        <x:v>UNA-SUS-UFMA_Saude Digital e SUS_Certificado Extensão</x:v>
+        <x:v>UNA-SUS-UFMA_Saúde Digital Inclusiva_Certificado</x:v>
       </x:c>
       <x:c r="E317" s="32" t="str"/>
       <x:c r="F317" s="32" t="str"/>
@@ -12021,13 +12039,13 @@
         <x:v>316</x:v>
       </x:c>
       <x:c r="B318" s="32" t="str">
-        <x:v>UNA-SUS-UFMA_Saúde Digital Inclusiva_Certificado.pdf</x:v>
+        <x:v>UNA-SUS-UFMA_Saúde Digital Noções fundamentais_Certificado.pdf</x:v>
       </x:c>
       <x:c r="C318" s="32" t="str">
         <x:v>UNA</x:v>
       </x:c>
       <x:c r="D318" s="32" t="str">
-        <x:v>UNA-SUS-UFMA_Saúde Digital Inclusiva_Certificado</x:v>
+        <x:v>UNA-SUS-UFMA_Saúde Digital Noções fundamentais_Certificado</x:v>
       </x:c>
       <x:c r="E318" s="32" t="str"/>
       <x:c r="F318" s="32" t="str"/>
@@ -12052,13 +12070,13 @@
         <x:v>317</x:v>
       </x:c>
       <x:c r="B319" s="32" t="str">
-        <x:v>UNA-SUS-UFMA_Saúde Digital Noções fundamentais_Certificado.pdf</x:v>
+        <x:v>UNA-SUS-UFMA_Transf Digital_Extensao_Certificado.pdf</x:v>
       </x:c>
       <x:c r="C319" s="32" t="str">
         <x:v>UNA</x:v>
       </x:c>
       <x:c r="D319" s="32" t="str">
-        <x:v>UNA-SUS-UFMA_Saúde Digital Noções fundamentais_Certificado</x:v>
+        <x:v>UNA-SUS-UFMA_Transf Digital_Extensao_Certificado</x:v>
       </x:c>
       <x:c r="E319" s="32" t="str"/>
       <x:c r="F319" s="32" t="str"/>
@@ -12083,13 +12101,13 @@
         <x:v>318</x:v>
       </x:c>
       <x:c r="B320" s="32" t="str">
-        <x:v>UNA-SUS-UFMA_Transf Digital_Extensao_Certificado.pdf</x:v>
+        <x:v>UNA-SUS_Certificado_Introducao Saúde Digital.pdf</x:v>
       </x:c>
       <x:c r="C320" s="32" t="str">
         <x:v>UNA</x:v>
       </x:c>
       <x:c r="D320" s="32" t="str">
-        <x:v>UNA-SUS-UFMA_Transf Digital_Extensao_Certificado</x:v>
+        <x:v>UNA-SUS_Certificado_Introducao Saúde Digital</x:v>
       </x:c>
       <x:c r="E320" s="32" t="str"/>
       <x:c r="F320" s="32" t="str"/>
@@ -12114,13 +12132,13 @@
         <x:v>319</x:v>
       </x:c>
       <x:c r="B321" s="32" t="str">
-        <x:v>UNA-SUS_Certificado_Introducao Saúde Digital.pdf</x:v>
+        <x:v>UNA-SUS_UFMA_Cultura da Saúde Digital_Certificado de Extensão_.pdf</x:v>
       </x:c>
       <x:c r="C321" s="32" t="str">
         <x:v>UNA</x:v>
       </x:c>
       <x:c r="D321" s="32" t="str">
-        <x:v>UNA-SUS_Certificado_Introducao Saúde Digital</x:v>
+        <x:v>UNA-SUS_UFMA_Cultura da Saúde Digital_Certificado de Extensão_</x:v>
       </x:c>
       <x:c r="E321" s="32" t="str"/>
       <x:c r="F321" s="32" t="str"/>
@@ -12145,13 +12163,13 @@
         <x:v>320</x:v>
       </x:c>
       <x:c r="B322" s="32" t="str">
-        <x:v>UNA-SUS_UFMA_Cultura da Saúde Digital_Certificado de Extensão_.pdf</x:v>
+        <x:v>UNA-SUS_UFMA_Etica e Responsabilidade_Saude Digital_Certificado Extensão.pdf</x:v>
       </x:c>
       <x:c r="C322" s="32" t="str">
         <x:v>UNA</x:v>
       </x:c>
       <x:c r="D322" s="32" t="str">
-        <x:v>UNA-SUS_UFMA_Cultura da Saúde Digital_Certificado de Extensão_</x:v>
+        <x:v>UNA-SUS_UFMA_Etica e Responsabilidade_Saude Digital_Certificado Extensão</x:v>
       </x:c>
       <x:c r="E322" s="32" t="str"/>
       <x:c r="F322" s="32" t="str"/>
@@ -12176,30 +12194,38 @@
         <x:v>321</x:v>
       </x:c>
       <x:c r="B323" s="32" t="str">
-        <x:v>UNA-SUS_UFMA_Etica e Responsabilidade_Saude Digital_Certificado Extensão.pdf</x:v>
+        <x:v>UNA-SUS_UFMA_Programa_Aperfeicoamento_Saude Digital_Certificado.pdf</x:v>
       </x:c>
       <x:c r="C323" s="32" t="str">
-        <x:v>UNA</x:v>
+        <x:v>Universidade Aberta do SUS / Universidade Federal do Maranhão (UNA-SUS/UFMA)</x:v>
       </x:c>
       <x:c r="D323" s="32" t="str">
-        <x:v>UNA-SUS_UFMA_Etica e Responsabilidade_Saude Digital_Certificado Extensão</x:v>
-      </x:c>
-      <x:c r="E323" s="32" t="str"/>
+        <x:v>Programa de Aperfeiçoamento em Saúde Digital I</x:v>
+      </x:c>
+      <x:c r="E323" s="32" t="str">
+        <x:v>Segurança da Informação em Saúde Digital; Cultura de Saúde Digital; Ética e responsabilidade social em Saúde Digital; Registros Eletrônicos e Qualidade da Informação em Saúde; Introdução à Saúde Digital; Saúde Digital aplicada ao SUS.</x:v>
+      </x:c>
       <x:c r="F323" s="32" t="str"/>
       <x:c r="G323" s="32" t="str">
-        <x:v>Grupo 1 — Ensino</x:v>
+        <x:v>Grupo 3 — Extensão</x:v>
       </x:c>
       <x:c r="H323" s="32" t="str">
-        <x:v>1.5</x:v>
+        <x:v>3.5</x:v>
       </x:c>
       <x:c r="I323" s="32" t="str">
         <x:v>Sem texto extraível — revisão manual</x:v>
       </x:c>
-      <x:c r="J323" s="33"/>
-      <x:c r="K323" s="33"/>
-      <x:c r="L323" s="33"/>
+      <x:c r="J323" s="33" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="K323" s="33" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="L323" s="33" t="n">
+        <x:v>180</x:v>
+      </x:c>
       <x:c r="M323" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>Código de autenticação e validação constam no certificado.</x:v>
       </x:c>
     </x:row>
     <x:row r="324">
@@ -12207,38 +12233,32 @@
         <x:v>322</x:v>
       </x:c>
       <x:c r="B324" s="32" t="str">
-        <x:v>UNA-SUS_UFMA_Programa_Aperfeicoamento_Saude Digital_Certificado.pdf</x:v>
+        <x:v>VMEdu_SFC_PedroLamounierSampaio-1182483.pdf</x:v>
       </x:c>
       <x:c r="C324" s="32" t="str">
-        <x:v>Universidade Aberta do SUS / Universidade Federal do Maranhão (UNA-SUS/UFMA)</x:v>
+        <x:v>VMEdu</x:v>
       </x:c>
       <x:c r="D324" s="32" t="str">
-        <x:v>Programa de Aperfeiçoamento em Saúde Digital I</x:v>
+        <x:v>VMEdu_SFC_PedroLamounierSampaio-1182483</x:v>
       </x:c>
       <x:c r="E324" s="32" t="str">
-        <x:v>Segurança da Informação em Saúde Digital; Cultura de Saúde Digital; Ética e responsabilidade social em Saúde Digital; Registros Eletrônicos e Qualidade da Informação em Saúde; Introdução à Saúde Digital; Saúde Digital aplicada ao SUS.</x:v>
+        <x:v>Pedro Lamounier Sampaio Granted Date : August 17, 2026 1182483</x:v>
       </x:c>
       <x:c r="F324" s="32" t="str"/>
       <x:c r="G324" s="32" t="str">
-        <x:v>Grupo 3 — Extensão</x:v>
+        <x:v>Grupo 1 — Ensino</x:v>
       </x:c>
       <x:c r="H324" s="32" t="str">
-        <x:v>3.5</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="I324" s="32" t="str">
-        <x:v>Sem texto extraível — revisão manual</x:v>
-      </x:c>
-      <x:c r="J324" s="33" t="n">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="K324" s="33" t="n">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="L324" s="33" t="n">
-        <x:v>180</x:v>
-      </x:c>
+        <x:v>Extraído do documento</x:v>
+      </x:c>
+      <x:c r="J324" s="33"/>
+      <x:c r="K324" s="33"/>
+      <x:c r="L324" s="33"/>
       <x:c r="M324" s="32" t="str">
-        <x:v>Código de autenticação e validação constam no certificado.</x:v>
+        <x:v>Carga horária não localizada</x:v>
       </x:c>
     </x:row>
     <x:row r="325">
@@ -12246,16 +12266,16 @@
         <x:v>323</x:v>
       </x:c>
       <x:c r="B325" s="32" t="str">
-        <x:v>VMEdu_SFC_PedroLamounierSampaio-1182483.pdf</x:v>
+        <x:v>Yale-Coursera_Global Health Essentials_Certificate_YJ26WLVD3O3K.pdf</x:v>
       </x:c>
       <x:c r="C325" s="32" t="str">
-        <x:v>VMEdu</x:v>
+        <x:v>Yale University</x:v>
       </x:c>
       <x:c r="D325" s="32" t="str">
-        <x:v>VMEdu_SFC_PedroLamounierSampaio-1182483</x:v>
+        <x:v>Essentials of Global Health</x:v>
       </x:c>
       <x:c r="E325" s="32" t="str">
-        <x:v>Pedro Lamounier Sampaio Granted Date : August 17, 2026 1182483</x:v>
+        <x:v>A u g 5 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o E s s e n t i a l s o f G l o b a l H e a l t h a n o n l i n e c o u r s e a u t h o r i z e d b y Y a l e U n i v e r s i t y a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d R i c h a r d S k o l n i k F o r m e r L e c t u r e r , D e p a r t m e n t o f H e a l t h P o l i c y a n d M a n a g e m e n t , Y a l e S c h o o l o f P u b l i c H e a l t h a n d L e c t u r e r i n t h e </x:v>
       </x:c>
       <x:c r="F325" s="32" t="str"/>
       <x:c r="G325" s="32" t="str">
@@ -12267,11 +12287,17 @@
       <x:c r="I325" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J325" s="33"/>
-      <x:c r="K325" s="33"/>
-      <x:c r="L325" s="33"/>
+      <x:c r="J325" s="33" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="K325" s="33" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="L325" s="33" t="n">
+        <x:v>39</x:v>
+      </x:c>
       <x:c r="M325" s="32" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/YJ26WLVD3O3K</x:v>
       </x:c>
     </x:row>
     <x:row r="326">
@@ -12279,16 +12305,16 @@
         <x:v>324</x:v>
       </x:c>
       <x:c r="B326" s="32" t="str">
-        <x:v>Yale-Coursera_Global Health Essentials_Certificate_YJ26WLVD3O3K.pdf</x:v>
+        <x:v>Your D-U-N-S Number is enclosed_.pdf</x:v>
       </x:c>
       <x:c r="C326" s="32" t="str">
-        <x:v>Yale University</x:v>
+        <x:v>Your D</x:v>
       </x:c>
       <x:c r="D326" s="32" t="str">
-        <x:v>Essentials of Global Health</x:v>
+        <x:v>Your D-U-N-S Number is enclosed_</x:v>
       </x:c>
       <x:c r="E326" s="32" t="str">
-        <x:v>A u g 5 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o E s s e n t i a l s o f G l o b a l H e a l t h a n o n l i n e c o u r s e a u t h o r i z e d b y Y a l e U n i v e r s i t y a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d R i c h a r d S k o l n i k F o r m e r L e c t u r e r , D e p a r t m e n t o f H e a l t h P o l i c y a n d M a n a g e m e n t , Y a l e S c h o o l o f P u b l i c H e a l t h a n d L e c t u r e r i n t h e </x:v>
+        <x:v>Dear Pedro Lamounier Sampaio, The D-U-N-S Number for LAMOUNIER SAMPAIO SOCIEDADE INDIVIDUAL DE ADVOCACIA is 583207925. If you have the legal authority to bind your company to Apple Developer Program agreements, you can use this number to enroll for your company. Before enrolling, please ensure that LAMOUNIER SAMPAIO SOCIEDADE INDIVIDUAL DE ADVOCACIA is a legal entity. Enroll now Best regards, Apple Developer Relations TM and © 2026 Apple Inc. One Apple Park Way, MS 301-1TEV, Cupertino, CA 95014.</x:v>
       </x:c>
       <x:c r="F326" s="32" t="str"/>
       <x:c r="G326" s="32" t="str">
@@ -12300,49 +12326,10 @@
       <x:c r="I326" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="J326" s="33" t="n">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="K326" s="33" t="n">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="L326" s="33" t="n">
-        <x:v>39</x:v>
-      </x:c>
+      <x:c r="J326" s="33"/>
+      <x:c r="K326" s="33"/>
+      <x:c r="L326" s="33"/>
       <x:c r="M326" s="32" t="str">
-        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/YJ26WLVD3O3K</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="327">
-      <x:c r="A327" s="32" t="n">
-        <x:v>325</x:v>
-      </x:c>
-      <x:c r="B327" s="32" t="str">
-        <x:v>Your D-U-N-S Number is enclosed_.pdf</x:v>
-      </x:c>
-      <x:c r="C327" s="32" t="str">
-        <x:v>Your D</x:v>
-      </x:c>
-      <x:c r="D327" s="32" t="str">
-        <x:v>Your D-U-N-S Number is enclosed_</x:v>
-      </x:c>
-      <x:c r="E327" s="32" t="str">
-        <x:v>Dear Pedro Lamounier Sampaio, The D-U-N-S Number for LAMOUNIER SAMPAIO SOCIEDADE INDIVIDUAL DE ADVOCACIA is 583207925. If you have the legal authority to bind your company to Apple Developer Program agreements, you can use this number to enroll for your company. Before enrolling, please ensure that LAMOUNIER SAMPAIO SOCIEDADE INDIVIDUAL DE ADVOCACIA is a legal entity. Enroll now Best regards, Apple Developer Relations TM and © 2026 Apple Inc. One Apple Park Way, MS 301-1TEV, Cupertino, CA 95014.</x:v>
-      </x:c>
-      <x:c r="F327" s="32" t="str"/>
-      <x:c r="G327" s="32" t="str">
-        <x:v>Grupo 1 — Ensino</x:v>
-      </x:c>
-      <x:c r="H327" s="32" t="str">
-        <x:v>1.5</x:v>
-      </x:c>
-      <x:c r="I327" s="32" t="str">
-        <x:v>Extraído do documento</x:v>
-      </x:c>
-      <x:c r="J327" s="33"/>
-      <x:c r="K327" s="33"/>
-      <x:c r="L327" s="33"/>
-      <x:c r="M327" s="32" t="str">
         <x:v>Carga horária não localizada</x:v>
       </x:c>
     </x:row>
@@ -12352,7 +12339,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5633b7ec466c4e6b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5425f691b24548e0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12716,13 +12703,13 @@
         <x:v>Coursera+_Subscription Receipts.pdf</x:v>
       </x:c>
       <x:c r="B26" s="24" t="str">
-        <x:v>Título, histórico, matrícula, tese ou documento pessoal detectado</x:v>
+        <x:v>Recibo/pedido administrativo, não comprova atividade acadêmica</x:v>
       </x:c>
       <x:c r="C26" s="24" t="str">
         <x:v>Pedro Lamounier Sampaio &lt;plamouniersampaio55@gmail.com&gt; Suas compras da Apple3 mensagens Apple &lt;no_reply@email.apple.com&gt; seg., 20 de jul., 04:59 Para: &lt;plamouniersampaio55@gmail.com&gt; Recibo CONTA APPLE plamouniersampaio55@gmail.com FATURADO PARA Visa .... 1276 Pedro Lamounier Sampaio ouro preto 1523 Apartamento 802 Belo Horizonte, MG 30170-048 BRA DATA 01/05/2026 ID DO PEDIDO MN7NZT51SG Nº DO DOCUMENTO 760127670022 App Store Coursera Plus Subscription Coursera Plus Subscription (Mensalmente) R$ 183,00 TOTAL R$ 183,00 Privacidade: usamos um ID de assinante para fornecer relatórios a desenvolve</x:v>
       </x:c>
       <x:c r="D26" s="24" t="str">
-        <x:v>Não publicar; manter apenas no acervo privado/pessoal.</x:v>
+        <x:v>Não importar como curso; manter apenas no acervo privado/pessoal.</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -13099,27 +13086,27 @@
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="24" t="str">
-        <x:v>PEDRO LAMOUNIER SAMPAIO.pdf</x:v>
+        <x:v>Pedido de Restituição Coursera 2026.07.pdf</x:v>
       </x:c>
       <x:c r="B54" s="24" t="str">
-        <x:v>Título, histórico, matrícula, tese ou documento pessoal detectado</x:v>
+        <x:v>Recibo/pedido administrativo, não comprova atividade acadêmica</x:v>
       </x:c>
       <x:c r="C54" s="24" t="str">
-        <x:v>FACULDADE FACULESTE EAD 39.974.772/0001-60 RUA LUIZ RODRIGUES DOS SANTOS, nº 44, SALA 202, TODOS OS SANTOS, CORONEL FABRICIANO, MG, 35170-061 DECLARAÇÃO DE CONCLUINTE De acordo com a resolução CNE/CES Nº 01 de 06/04/2018 e Portaria Nº 1640 de 19 de setembro 2019. Declaramos que PEDRO LAMOUNIER SAMPAIO concluiu todas as avaliações do curso de Pós-Graduação em LL.M. DIREITO TRIBUTÁRIO (carga horária total de 360 horas), em nível de especialização pela Faculeste. O(a) aluno(a) ainda não finalizou a disciplina de TCC, pois não completou o tempo mínimo de curso necessário para a avaliação dessa dis</x:v>
+        <x:v>You're all setYou're all setYou're all setYou're all set You’ve submitted Case 06393611 (/s/my-cases?caseId=500VN00000ztsrDYAQ) to Coursera Support. View your case, get updates, and reply from your My Support Cases page. ( ( ( (/s/s/s/s)))) Go to My Support CasesGo to My Support CasesGo to My Support CasesGo to My Support Cases</x:v>
       </x:c>
       <x:c r="D54" s="24" t="str">
-        <x:v>Não publicar; manter apenas no acervo privado/pessoal.</x:v>
+        <x:v>Não importar como curso; manter apenas no acervo privado/pessoal.</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="24" t="str">
-        <x:v>SGA - Declaração de Matrícula.pdf</x:v>
+        <x:v>PEDRO LAMOUNIER SAMPAIO.pdf</x:v>
       </x:c>
       <x:c r="B55" s="24" t="str">
         <x:v>Título, histórico, matrícula, tese ou documento pessoal detectado</x:v>
       </x:c>
       <x:c r="C55" s="24" t="str">
-        <x:v>PONTIFÍCIA UNIVERSIDADE CATÓLICA DE MINAS GERAIS Reconhecida pelo Decreto nº 45.046, de 12 de dezembro de 1958 D E C L A R A Ç Ã O D E M A T R Í C U L A Declaramos para os devidos fins que, PEDRO LAMOUNIER SAMPAIO - matrícula 887284 , é aluno(a) do curso de MEDICINA , turno INTEGRAL , desta Pontifícia Universidade Católica de Minas Gerais - CNPJ 17.178.195/0014-81, regularmente matriculado(a) no 1º semestre de 2026 , até a presente data, conforme especificado abaixo. Disciplinas PeríodoCarga Horária ANATOMIA HUMANA SISTÊMICA 1º 72 BIOLOGIA CELULAR I 2º 80 FISIOLOGIA MÉDICA I 3º 100 INTRODUÇÃO </x:v>
+        <x:v>FACULDADE FACULESTE EAD 39.974.772/0001-60 RUA LUIZ RODRIGUES DOS SANTOS, nº 44, SALA 202, TODOS OS SANTOS, CORONEL FABRICIANO, MG, 35170-061 DECLARAÇÃO DE CONCLUINTE De acordo com a resolução CNE/CES Nº 01 de 06/04/2018 e Portaria Nº 1640 de 19 de setembro 2019. Declaramos que PEDRO LAMOUNIER SAMPAIO concluiu todas as avaliações do curso de Pós-Graduação em LL.M. DIREITO TRIBUTÁRIO (carga horária total de 360 horas), em nível de especialização pela Faculeste. O(a) aluno(a) ainda não finalizou a disciplina de TCC, pois não completou o tempo mínimo de curso necessário para a avaliação dessa dis</x:v>
       </x:c>
       <x:c r="D55" s="24" t="str">
         <x:v>Não publicar; manter apenas no acervo privado/pessoal.</x:v>
@@ -13127,27 +13114,27 @@
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="24" t="str">
-        <x:v>Stanford-Coursera_Antibiotic Stewardship Certificate.pdf</x:v>
+        <x:v>Receipt for Order 394583203.pdf</x:v>
       </x:c>
       <x:c r="B56" s="24" t="str">
-        <x:v>Título, histórico, matrícula, tese ou documento pessoal detectado</x:v>
+        <x:v>Recibo/pedido administrativo, não comprova atividade acadêmica</x:v>
       </x:c>
       <x:c r="C56" s="24" t="str">
-        <x:v>Course Record Aug 6, 2026 Pedro Lamounier Sampaio Antibiotic Stewardship an online course authorized by Stanford University and offered through Coursera has successfully completed Stan Deresinski, MD, Elizabeth Robilotti, Marisa Holubar, Lina Meng, PharmD, BCPS, BCCCP &amp; Emily Mui SOME ONLINE COURSES MAY DRAW ON MATERIAL FROM COURSES TAUGHT ON-CAMPUS BUT THEY ARE NOT EQUIVALENT TO ON-CAMPUS COURSES. THIS STATEMENT DOES NOT AFFIRM THAT THIS PARTICIPANT WAS ENROLLED AS A STUDENT AT STANFORD UNIVERSITY IN ANY WAY. IT DOES NOT CONFER A STANFORD UNIVERSITY GRADE, COURSE CREDIT OR DEGREE, AND IT DOES</x:v>
+        <x:v>Pedro Lamounier Sampaio &lt;plamouniersampaio55@gmail.com&gt; Your Receipt for Order #394583203 Coursera &lt;no-reply@t.learn.coursera.org&gt; seg., 20 de jul., 04:38 Para: &lt;plamouniersampaio55@gmail.com&gt; Dear Pedro Lamounier Sampaio, Thank you for your purchase RECEIPT Coursera Inc. 381 E. Evelyn Avenue Mountain View, CA 94041 USA 07/09/2025 Order Number: 394583203 Product Details Price Qty Professional Certificate Subscription: Johns Hopkins Medical Office Manager USD 49.001 TOTAL (USD): 49.00 Please keep this receipt as record of your payment. Your subscription starts today. You will be charged 49.00 (</x:v>
       </x:c>
       <x:c r="D56" s="24" t="str">
-        <x:v>Não publicar; manter apenas no acervo privado/pessoal.</x:v>
+        <x:v>Não importar como curso; manter apenas no acervo privado/pessoal.</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="24" t="str">
-        <x:v>stanford_554362_Transcript.pdf</x:v>
+        <x:v>SGA - Declaração de Matrícula.pdf</x:v>
       </x:c>
       <x:c r="B57" s="24" t="str">
         <x:v>Título, histórico, matrícula, tese ou documento pessoal detectado</x:v>
       </x:c>
       <x:c r="C57" s="24" t="str">
-        <x:v>Belo Horizonte, 30170048 Ouro Preto 1523 Pedro Lamounier Sampaio, LL.M. BRAZIL Transcript Period 1/1/2010 to 8/1/2026 Created On: 8/1/2026 Transcript Credit Summary: Non-Physician Participation Credit: 56.50 Credits Activity Name/Date Credits 56.50 Total: ID Non-Physician Participation Credit Credit Type: Session Claim Date Activity Format SafetyQuest: Level One - QI Basics, January 8, 2024 - January 7, 2027 Enduring Material 48978 EDX SafetyQuest: Level 1 - QI Basics , January 8, 2024 - January 7, 2027 2.00 7/6/2026 AI Series: Introduction to Healthcare, August 10, 2023 - August 9, 2026 Endur</x:v>
+        <x:v>PONTIFÍCIA UNIVERSIDADE CATÓLICA DE MINAS GERAIS Reconhecida pelo Decreto nº 45.046, de 12 de dezembro de 1958 D E C L A R A Ç Ã O D E M A T R Í C U L A Declaramos para os devidos fins que, PEDRO LAMOUNIER SAMPAIO - matrícula 887284 , é aluno(a) do curso de MEDICINA , turno INTEGRAL , desta Pontifícia Universidade Católica de Minas Gerais - CNPJ 17.178.195/0014-81, regularmente matriculado(a) no 1º semestre de 2026 , até a presente data, conforme especificado abaixo. Disciplinas PeríodoCarga Horária ANATOMIA HUMANA SISTÊMICA 1º 72 BIOLOGIA CELULAR I 2º 80 FISIOLOGIA MÉDICA I 3º 100 INTRODUÇÃO </x:v>
       </x:c>
       <x:c r="D57" s="24" t="str">
         <x:v>Não publicar; manter apenas no acervo privado/pessoal.</x:v>
@@ -13155,13 +13142,13 @@
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="24" t="str">
-        <x:v>studentmemap200.pdf</x:v>
+        <x:v>Stanford-Coursera_Antibiotic Stewardship Certificate.pdf</x:v>
       </x:c>
       <x:c r="B58" s="24" t="str">
         <x:v>Título, histórico, matrícula, tese ou documento pessoal detectado</x:v>
       </x:c>
       <x:c r="C58" s="24" t="str">
-        <x:v>QUALIFICATIONS FOR MEMBERSHIP Student Associate membership is open to undergraduate students enrolled in at least 9 semester hours (or equivalent), graduate students enrolled in at least 6 semester hours (or equivalent) in an accredited college or university. Proof of enrollment must accompany application (see below). The application fee is non-transferable and is non-refundable once approved. CFE members are not eligible for student membership. ACFE dues are not deductible as a charitable contribution for Federal Income Tax purposes. No portion of ACFE dues are spent on lobbying activities. P</x:v>
+        <x:v>Course Record Aug 6, 2026 Pedro Lamounier Sampaio Antibiotic Stewardship an online course authorized by Stanford University and offered through Coursera has successfully completed Stan Deresinski, MD, Elizabeth Robilotti, Marisa Holubar, Lina Meng, PharmD, BCPS, BCCCP &amp; Emily Mui SOME ONLINE COURSES MAY DRAW ON MATERIAL FROM COURSES TAUGHT ON-CAMPUS BUT THEY ARE NOT EQUIVALENT TO ON-CAMPUS COURSES. THIS STATEMENT DOES NOT AFFIRM THAT THIS PARTICIPANT WAS ENROLLED AS A STUDENT AT STANFORD UNIVERSITY IN ANY WAY. IT DOES NOT CONFER A STANFORD UNIVERSITY GRADE, COURSE CREDIT OR DEGREE, AND IT DOES</x:v>
       </x:c>
       <x:c r="D58" s="24" t="str">
         <x:v>Não publicar; manter apenas no acervo privado/pessoal.</x:v>
@@ -13169,13 +13156,13 @@
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="24" t="str">
-        <x:v>The SQuaRE series.pdf</x:v>
+        <x:v>stanford_554362_Transcript.pdf</x:v>
       </x:c>
       <x:c r="B59" s="24" t="str">
         <x:v>Título, histórico, matrícula, tese ou documento pessoal detectado</x:v>
       </x:c>
       <x:c r="C59" s="24" t="str">
-        <x:v>The SQuaRE series Now, let’s take a closer look at the SquaRE series which promotes an expansive list of characteristics for software and data quality. It distinguishes between the quality of a software product with 8 characteristics and also the quality in use of a software product, data and IT services. It also differentiates cyber and social trust with five characteristics, data quality with 15 characteristics and IT service quality with 8 characteristics. For instance, in terms of ISO/IEC 25010, emerging social requirements fall within the category of "freedom from risk." The standard defi</x:v>
+        <x:v>Belo Horizonte, 30170048 Ouro Preto 1523 Pedro Lamounier Sampaio, LL.M. BRAZIL Transcript Period 1/1/2010 to 8/1/2026 Created On: 8/1/2026 Transcript Credit Summary: Non-Physician Participation Credit: 56.50 Credits Activity Name/Date Credits 56.50 Total: ID Non-Physician Participation Credit Credit Type: Session Claim Date Activity Format SafetyQuest: Level One - QI Basics, January 8, 2024 - January 7, 2027 Enduring Material 48978 EDX SafetyQuest: Level 1 - QI Basics , January 8, 2024 - January 7, 2027 2.00 7/6/2026 AI Series: Introduction to Healthcare, August 10, 2023 - August 9, 2026 Endur</x:v>
       </x:c>
       <x:c r="D59" s="24" t="str">
         <x:v>Não publicar; manter apenas no acervo privado/pessoal.</x:v>
@@ -13183,13 +13170,13 @@
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="24" t="str">
-        <x:v>UFMA_SUS_Saude Digital_Declaracao_Matricular.pdf</x:v>
+        <x:v>studentmemap200.pdf</x:v>
       </x:c>
       <x:c r="B60" s="24" t="str">
         <x:v>Título, histórico, matrícula, tese ou documento pessoal detectado</x:v>
       </x:c>
       <x:c r="C60" s="24" t="str">
-        <x:v>DECLARAÇÃO Declaramos para os devidos fins que o(a) aluno(a) PEDRO LAMOUNIER SAMPAIO, CPF n.º 08831798650, está devidamente matriculado(a) no curso de extensão Saúde Digital aplicada ao SUS , da Universidade Aberta do SUS/Universidade Federal do Maranhão (UNA-SUS/UFMA), na modalidade a distância, com carga horária total de 30 horas e que o(a) referido(a) aluno(a) está desenvolvendo suas atividades didáticas desde o dia 01/04/2026 até a presente data. São Luís, 27 de julho de 2026</x:v>
+        <x:v>QUALIFICATIONS FOR MEMBERSHIP Student Associate membership is open to undergraduate students enrolled in at least 9 semester hours (or equivalent), graduate students enrolled in at least 6 semester hours (or equivalent) in an accredited college or university. Proof of enrollment must accompany application (see below). The application fee is non-transferable and is non-refundable once approved. CFE members are not eligible for student membership. ACFE dues are not deductible as a charitable contribution for Federal Income Tax purposes. No portion of ACFE dues are spent on lobbying activities. P</x:v>
       </x:c>
       <x:c r="D60" s="24" t="str">
         <x:v>Não publicar; manter apenas no acervo privado/pessoal.</x:v>
@@ -13197,13 +13184,13 @@
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="24" t="str">
-        <x:v>UFMG-UNA-SUS_Cuidados da Criança na APS_Certificado_1f19bdf8-15cb-6bc0-afb9-7d41a92de2c8.pdf</x:v>
+        <x:v>The SQuaRE series.pdf</x:v>
       </x:c>
       <x:c r="B61" s="24" t="str">
         <x:v>Título, histórico, matrícula, tese ou documento pessoal detectado</x:v>
       </x:c>
       <x:c r="C61" s="24" t="str">
-        <x:v>Certificado de conclusão A Universidade Federal de Minas Gerais (UFMG), por meio da Universidade Aberta do SUS (UNA-SUS), certifica que CPF nº , concluiu o curso Abordagem Cuidados para o Desenvolvimento da Criança na Atenção Primária à Saúde (APS), produzido pela Universidade Federal de Minas Gerais (UFMG), na c ategoria de curso de qualificação profissional, com carga horária de horas. Belo Horizonte, Claúdia Regina Lindgren Alves Professora e Coordenadora do Curso UFMG 30 08831798650 11 de agosto de 2026 Pedro Lamounier Sampaio</x:v>
+        <x:v>The SQuaRE series Now, let’s take a closer look at the SquaRE series which promotes an expansive list of characteristics for software and data quality. It distinguishes between the quality of a software product with 8 characteristics and also the quality in use of a software product, data and IT services. It also differentiates cyber and social trust with five characteristics, data quality with 15 characteristics and IT service quality with 8 characteristics. For instance, in terms of ISO/IEC 25010, emerging social requirements fall within the category of "freedom from risk." The standard defi</x:v>
       </x:c>
       <x:c r="D61" s="24" t="str">
         <x:v>Não publicar; manter apenas no acervo privado/pessoal.</x:v>
@@ -13211,25 +13198,27 @@
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="24" t="str">
-        <x:v>UFMG_LLB_PLS_WES Degree Equivalency Tool - WES.pdf</x:v>
+        <x:v>UFMA_SUS_Saude Digital_Declaracao_Matricular.pdf</x:v>
       </x:c>
       <x:c r="B62" s="24" t="str">
         <x:v>Título, histórico, matrícula, tese ou documento pessoal detectado</x:v>
       </x:c>
-      <x:c r="C62" s="24" t="str"/>
+      <x:c r="C62" s="24" t="str">
+        <x:v>DECLARAÇÃO Declaramos para os devidos fins que o(a) aluno(a) PEDRO LAMOUNIER SAMPAIO, CPF n.º 08831798650, está devidamente matriculado(a) no curso de extensão Saúde Digital aplicada ao SUS , da Universidade Aberta do SUS/Universidade Federal do Maranhão (UNA-SUS/UFMA), na modalidade a distância, com carga horária total de 30 horas e que o(a) referido(a) aluno(a) está desenvolvendo suas atividades didáticas desde o dia 01/04/2026 até a presente data. São Luís, 27 de julho de 2026</x:v>
+      </x:c>
       <x:c r="D62" s="24" t="str">
         <x:v>Não publicar; manter apenas no acervo privado/pessoal.</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="24" t="str">
-        <x:v>UNA-SUS-UFMA_Registros Eletrônicos e Saúde Digital_Declaracao Matricular.pdf</x:v>
+        <x:v>UFMG-UNA-SUS_Cuidados da Criança na APS_Certificado_1f19bdf8-15cb-6bc0-afb9-7d41a92de2c8.pdf</x:v>
       </x:c>
       <x:c r="B63" s="24" t="str">
         <x:v>Título, histórico, matrícula, tese ou documento pessoal detectado</x:v>
       </x:c>
       <x:c r="C63" s="24" t="str">
-        <x:v>DECLARAÇÃO Declaramos para os devidos fins que o(a) aluno(a) PEDRO LAMOUNIER SAMPAIO, CPF n.º 08831798650, está devidamente matriculado(a) no curso de extensão Registros Eletrônicos e Qualidade da Informação em Saúde , da Universidade Aberta do SUS/Universidade Federal do Maranhão (UNA- SUS/UFMA), na modalidade a distância, com carga horária total de 30 horas e que o(a) referido(a) aluno(a) está desenvolvendo suas atividades didáticas desde o dia 27/05/2026 até a presente data. São Luís, 27 de julho de 2026</x:v>
+        <x:v>Certificado de conclusão A Universidade Federal de Minas Gerais (UFMG), por meio da Universidade Aberta do SUS (UNA-SUS), certifica que CPF nº , concluiu o curso Abordagem Cuidados para o Desenvolvimento da Criança na Atenção Primária à Saúde (APS), produzido pela Universidade Federal de Minas Gerais (UFMG), na c ategoria de curso de qualificação profissional, com carga horária de horas. Belo Horizonte, Claúdia Regina Lindgren Alves Professora e Coordenadora do Curso UFMG 30 08831798650 11 de agosto de 2026 Pedro Lamounier Sampaio</x:v>
       </x:c>
       <x:c r="D63" s="24" t="str">
         <x:v>Não publicar; manter apenas no acervo privado/pessoal.</x:v>
@@ -13237,27 +13226,25 @@
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="24" t="str">
-        <x:v>UNA-SUS-UFMA_Saúde Digital Conceituacao_Certificado.pdf</x:v>
+        <x:v>UFMG_LLB_PLS_WES Degree Equivalency Tool - WES.pdf</x:v>
       </x:c>
       <x:c r="B64" s="24" t="str">
         <x:v>Título, histórico, matrícula, tese ou documento pessoal detectado</x:v>
       </x:c>
-      <x:c r="C64" s="24" t="str">
-        <x:v>DECLARAÇÃO Declaramos para os devidos fins que o(a) aluno(a) PEDRO LAMOUNIER SAMPAIO, CPF n.º 08831798650, está devidamente matriculado(a) no curso de extensão Saúde Digital: conceitos, histórico e principais terminologias , da Universidade Aberta do SUS da Universidade Federal do Maranhão (UNA- SUS/UFMA) na modalidade a distância, com carga horária total de 15 horas e que o(a) referido(a) aluno(a) está desenvolvendo suas atividades didáticas desde o dia 19/03/2026 até a presente data. São Luís, 20 de agosto de 2026</x:v>
-      </x:c>
+      <x:c r="C64" s="24" t="str"/>
       <x:c r="D64" s="24" t="str">
         <x:v>Não publicar; manter apenas no acervo privado/pessoal.</x:v>
       </x:c>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="24" t="str">
-        <x:v>UNA-SUS-UFMA_Transf Digital_Extensao_Declaracao.pdf</x:v>
+        <x:v>UNA-SUS-UFMA_Registros Eletrônicos e Saúde Digital_Declaracao Matricular.pdf</x:v>
       </x:c>
       <x:c r="B65" s="24" t="str">
         <x:v>Título, histórico, matrícula, tese ou documento pessoal detectado</x:v>
       </x:c>
       <x:c r="C65" s="24" t="str">
-        <x:v>DECLARAÇÃO Declaramos para os devidos fins que o(a) aluno(a) PEDRO LAMOUNIER SAMPAIO, CPF n.º 08831798650, está devidamente matriculado(a) no curso de extensão Transformação digital no setor da saúde , da Universidade Aberta do SUS da Universidade Federal do Maranhão (UNA-SUS/UFMA) na modalidade a distância, com carga horária total de 15 horas e que o(a) referido(a) aluno(a) está desenvolvendo suas atividades didáticas desde o dia 19/03/2026 até a presente data. São Luís, 20 de agosto de 2026</x:v>
+        <x:v>DECLARAÇÃO Declaramos para os devidos fins que o(a) aluno(a) PEDRO LAMOUNIER SAMPAIO, CPF n.º 08831798650, está devidamente matriculado(a) no curso de extensão Registros Eletrônicos e Qualidade da Informação em Saúde , da Universidade Aberta do SUS/Universidade Federal do Maranhão (UNA- SUS/UFMA), na modalidade a distância, com carga horária total de 30 horas e que o(a) referido(a) aluno(a) está desenvolvendo suas atividades didáticas desde o dia 27/05/2026 até a presente data. São Luís, 27 de julho de 2026</x:v>
       </x:c>
       <x:c r="D65" s="24" t="str">
         <x:v>Não publicar; manter apenas no acervo privado/pessoal.</x:v>
@@ -13265,13 +13252,13 @@
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="24" t="str">
-        <x:v>UNA-SUS-UFMA_Ética e Responsabilidade na Saúde Digital_Declaracao.pdf</x:v>
+        <x:v>UNA-SUS-UFMA_Saúde Digital Conceituacao_Certificado.pdf</x:v>
       </x:c>
       <x:c r="B66" s="24" t="str">
         <x:v>Título, histórico, matrícula, tese ou documento pessoal detectado</x:v>
       </x:c>
       <x:c r="C66" s="24" t="str">
-        <x:v>DECLARAÇÃO Declaramos para os devidos fins que o(a) aluno(a) PEDRO LAMOUNIER SAMPAIO, CPF n.º 08831798650, está devidamente matriculado(a) no curso de extensão Ética e responsabilidade social em Saúde Digital , da Universidade Aberta do SUS/Universidade Federal do Maranhão (UNA-SUS/UFMA), na modalidade a distância, com carga horária total de 30 horas e que o(a) referido(a) aluno(a) está desenvolvendo suas atividades didáticas desde o dia 05/06/2026 até a presente data São Luís, 27 de julho de 2026</x:v>
+        <x:v>DECLARAÇÃO Declaramos para os devidos fins que o(a) aluno(a) PEDRO LAMOUNIER SAMPAIO, CPF n.º 08831798650, está devidamente matriculado(a) no curso de extensão Saúde Digital: conceitos, histórico e principais terminologias , da Universidade Aberta do SUS da Universidade Federal do Maranhão (UNA- SUS/UFMA) na modalidade a distância, com carga horária total de 15 horas e que o(a) referido(a) aluno(a) está desenvolvendo suas atividades didáticas desde o dia 19/03/2026 até a presente data. São Luís, 20 de agosto de 2026</x:v>
       </x:c>
       <x:c r="D66" s="24" t="str">
         <x:v>Não publicar; manter apenas no acervo privado/pessoal.</x:v>
@@ -13279,15 +13266,43 @@
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="24" t="str">
-        <x:v>UNA-SUS_Saúde da Puerpera eAPS_Qualificacao Profissional_Certificado.pdf</x:v>
+        <x:v>UNA-SUS-UFMA_Transf Digital_Extensao_Declaracao.pdf</x:v>
       </x:c>
       <x:c r="B67" s="24" t="str">
         <x:v>Título, histórico, matrícula, tese ou documento pessoal detectado</x:v>
       </x:c>
       <x:c r="C67" s="24" t="str">
+        <x:v>DECLARAÇÃO Declaramos para os devidos fins que o(a) aluno(a) PEDRO LAMOUNIER SAMPAIO, CPF n.º 08831798650, está devidamente matriculado(a) no curso de extensão Transformação digital no setor da saúde , da Universidade Aberta do SUS da Universidade Federal do Maranhão (UNA-SUS/UFMA) na modalidade a distância, com carga horária total de 15 horas e que o(a) referido(a) aluno(a) está desenvolvendo suas atividades didáticas desde o dia 19/03/2026 até a presente data. São Luís, 20 de agosto de 2026</x:v>
+      </x:c>
+      <x:c r="D67" s="24" t="str">
+        <x:v>Não publicar; manter apenas no acervo privado/pessoal.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" s="24" t="str">
+        <x:v>UNA-SUS-UFMA_Ética e Responsabilidade na Saúde Digital_Declaracao.pdf</x:v>
+      </x:c>
+      <x:c r="B68" s="24" t="str">
+        <x:v>Título, histórico, matrícula, tese ou documento pessoal detectado</x:v>
+      </x:c>
+      <x:c r="C68" s="24" t="str">
+        <x:v>DECLARAÇÃO Declaramos para os devidos fins que o(a) aluno(a) PEDRO LAMOUNIER SAMPAIO, CPF n.º 08831798650, está devidamente matriculado(a) no curso de extensão Ética e responsabilidade social em Saúde Digital , da Universidade Aberta do SUS/Universidade Federal do Maranhão (UNA-SUS/UFMA), na modalidade a distância, com carga horária total de 30 horas e que o(a) referido(a) aluno(a) está desenvolvendo suas atividades didáticas desde o dia 05/06/2026 até a presente data São Luís, 27 de julho de 2026</x:v>
+      </x:c>
+      <x:c r="D68" s="24" t="str">
+        <x:v>Não publicar; manter apenas no acervo privado/pessoal.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" s="24" t="str">
+        <x:v>UNA-SUS_Saúde da Puerpera eAPS_Qualificacao Profissional_Certificado.pdf</x:v>
+      </x:c>
+      <x:c r="B69" s="24" t="str">
+        <x:v>Título, histórico, matrícula, tese ou documento pessoal detectado</x:v>
+      </x:c>
+      <x:c r="C69" s="24" t="str">
         <x:v>CER TIF ICADO DE CON CLUSÃO A Universidade Federal de Santa Catarina (UFSC), por meio da Universidade Aberta do SUS (UNA-SUS), certiﬁca que CPF no , concluiu o curso “Reconhecendo a Norma Brasileira de Comercialização de Alimentos para Lactentes e Crianças de Primeira Infância, Bicos, Chupetas e Mamadeiras (NBCAL): formação para Proﬁssionais da Rede de Atenção à Saúde”, produzido pela Universidade Federal de Santa Catarina (UFSC), na categoria qualiﬁcação proﬁssional, com carga horária de horas. Sheila Rubia Lindner Professora do Departamento de Saúde Pública Universidade Federal de Santa Cata</x:v>
       </x:c>
-      <x:c r="D67" s="24" t="str">
+      <x:c r="D69" s="24" t="str">
         <x:v>Não publicar; manter apenas no acervo privado/pessoal.</x:v>
       </x:c>
     </x:row>
@@ -15984,10 +15999,10 @@
     </x:row>
     <x:row r="179">
       <x:c r="A179" s="24" t="str">
-        <x:v>Pedido de Restituição Coursera 2026.07.pdf</x:v>
+        <x:v>Pedro Lamounier Sampaio - CV 2.pdf</x:v>
       </x:c>
       <x:c r="B179" s="24" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>PDF/imagem sem texto extraível</x:v>
       </x:c>
       <x:c r="C179" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
@@ -15999,10 +16014,10 @@
     </x:row>
     <x:row r="180">
       <x:c r="A180" s="24" t="str">
-        <x:v>Pedro Lamounier Sampaio - CV 2.pdf</x:v>
+        <x:v>Pedro Lamounier Sampaio - PDF Certificate (ISO 19011 Lead Auditor).pdf</x:v>
       </x:c>
       <x:c r="B180" s="24" t="str">
-        <x:v>PDF/imagem sem texto extraível</x:v>
+        <x:v>Carga horária não localizada</x:v>
       </x:c>
       <x:c r="C180" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
@@ -16014,10 +16029,10 @@
     </x:row>
     <x:row r="181">
       <x:c r="A181" s="24" t="str">
-        <x:v>Pedro Lamounier Sampaio - PDF Certificate (ISO 19011 Lead Auditor).pdf</x:v>
+        <x:v>Pedro Lamounier Sampaio _ LinkedIn_Duolingo LVL128.pdf</x:v>
       </x:c>
       <x:c r="B181" s="24" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>PDF/imagem sem texto extraível</x:v>
       </x:c>
       <x:c r="C181" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
@@ -16029,10 +16044,10 @@
     </x:row>
     <x:row r="182">
       <x:c r="A182" s="24" t="str">
-        <x:v>Pedro Lamounier Sampaio _ LinkedIn_Duolingo LVL128.pdf</x:v>
+        <x:v>Pedro Lamounier Sampaio ACLS (Advanced Cardiac Life Support) Online Course Completion Certificate 2026.pdf</x:v>
       </x:c>
       <x:c r="B182" s="24" t="str">
-        <x:v>PDF/imagem sem texto extraível</x:v>
+        <x:v>Carga horária não localizada</x:v>
       </x:c>
       <x:c r="C182" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
@@ -16044,7 +16059,7 @@
     </x:row>
     <x:row r="183">
       <x:c r="A183" s="24" t="str">
-        <x:v>Pedro Lamounier Sampaio ACLS (Advanced Cardiac Life Support) Online Course Completion Certificate 2026.pdf</x:v>
+        <x:v>Pedro Lamounier Sampaio ACLS Course Completion Certificate.pdf</x:v>
       </x:c>
       <x:c r="B183" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16059,7 +16074,7 @@
     </x:row>
     <x:row r="184">
       <x:c r="A184" s="24" t="str">
-        <x:v>Pedro Lamounier Sampaio ACLS Course Completion Certificate.pdf</x:v>
+        <x:v>Pedro Lamounier Sampaio BLS (Basic Life Support) Online Course Completion Certificate 2026.pdf</x:v>
       </x:c>
       <x:c r="B184" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16074,7 +16089,7 @@
     </x:row>
     <x:row r="185">
       <x:c r="A185" s="24" t="str">
-        <x:v>Pedro Lamounier Sampaio BLS (Basic Life Support) Online Course Completion Certificate 2026.pdf</x:v>
+        <x:v>Pedro Lamounier Sampaio- PDF Certificate (Advanced Cardiac Life Support (ACLS)).pdf</x:v>
       </x:c>
       <x:c r="B185" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16089,10 +16104,10 @@
     </x:row>
     <x:row r="186">
       <x:c r="A186" s="24" t="str">
-        <x:v>Pedro Lamounier Sampaio- PDF Certificate (Advanced Cardiac Life Support (ACLS)).pdf</x:v>
+        <x:v>PEDRO_LAMOUNIER_SAMPAIO_Cybersecurity_Awareness_-_Production.pdf</x:v>
       </x:c>
       <x:c r="B186" s="24" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>PDF/imagem sem texto extraível</x:v>
       </x:c>
       <x:c r="C186" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
@@ -16104,7 +16119,7 @@
     </x:row>
     <x:row r="187">
       <x:c r="A187" s="24" t="str">
-        <x:v>PEDRO_LAMOUNIER_SAMPAIO_Cybersecurity_Awareness_-_Production.pdf</x:v>
+        <x:v>PEDRO_LAMOUNIER_SAMPAIO_Project_Management_Essentials_-_Production.pdf</x:v>
       </x:c>
       <x:c r="B187" s="24" t="str">
         <x:v>PDF/imagem sem texto extraível</x:v>
@@ -16119,10 +16134,10 @@
     </x:row>
     <x:row r="188">
       <x:c r="A188" s="24" t="str">
-        <x:v>PEDRO_LAMOUNIER_SAMPAIO_Project_Management_Essentials_-_Production.pdf</x:v>
+        <x:v>Penn-Coursera_Healthcare Law Specialization Certificate VOUZB1AZBVL4.pdf</x:v>
       </x:c>
       <x:c r="B188" s="24" t="str">
-        <x:v>PDF/imagem sem texto extraível</x:v>
+        <x:v>Carga horária não localizada</x:v>
       </x:c>
       <x:c r="C188" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
@@ -16134,7 +16149,7 @@
     </x:row>
     <x:row r="189">
       <x:c r="A189" s="24" t="str">
-        <x:v>Penn-Coursera_Healthcare Law Specialization Certificate VOUZB1AZBVL4.pdf</x:v>
+        <x:v>Penn-Coursera_Intellectual Property in Healthcare_Certificate_ME8EBTCWCKTS.pdf</x:v>
       </x:c>
       <x:c r="B189" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16149,7 +16164,7 @@
     </x:row>
     <x:row r="190">
       <x:c r="A190" s="24" t="str">
-        <x:v>Penn-Coursera_Intellectual Property in Healthcare_Certificate_ME8EBTCWCKTS.pdf</x:v>
+        <x:v>Personalidade INTP (Lógico) _ 16Personalities.pdf</x:v>
       </x:c>
       <x:c r="B190" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16164,10 +16179,10 @@
     </x:row>
     <x:row r="191">
       <x:c r="A191" s="24" t="str">
-        <x:v>Personalidade INTP (Lógico) _ 16Personalities.pdf</x:v>
+        <x:v>PET_ESOL Entry 3 Certificate.pdf</x:v>
       </x:c>
       <x:c r="B191" s="24" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>PDF/imagem sem texto extraível</x:v>
       </x:c>
       <x:c r="C191" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
@@ -16179,10 +16194,10 @@
     </x:row>
     <x:row r="192">
       <x:c r="A192" s="24" t="str">
-        <x:v>PET_ESOL Entry 3 Certificate.pdf</x:v>
+        <x:v>PHC Course - WHO Academy.pdf</x:v>
       </x:c>
       <x:c r="B192" s="24" t="str">
-        <x:v>PDF/imagem sem texto extraível</x:v>
+        <x:v>Carga horária não localizada</x:v>
       </x:c>
       <x:c r="C192" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
@@ -16194,7 +16209,7 @@
     </x:row>
     <x:row r="193">
       <x:c r="A193" s="24" t="str">
-        <x:v>PHC Course - WHO Academy.pdf</x:v>
+        <x:v>pjrtraining _ ISO 9001-2015 Clause-by-Clau... (CBC9000) _ Final Exam.pdf</x:v>
       </x:c>
       <x:c r="B193" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16202,14 +16217,16 @@
       <x:c r="C193" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
       </x:c>
-      <x:c r="D193" s="24" t="str"/>
+      <x:c r="D193" s="24" t="str">
+        <x:v>https://pjrtraining.talentlms.com/dashboard | https://pjrtraining.talentlms.com/unit/viewtestsurvey/id:1746,mode:test</x:v>
+      </x:c>
       <x:c r="E193" s="24" t="str">
         <x:v>Pendente</x:v>
       </x:c>
     </x:row>
     <x:row r="194">
       <x:c r="A194" s="24" t="str">
-        <x:v>pjrtraining _ ISO 9001-2015 Clause-by-Clau... (CBC9000) _ Final Exam.pdf</x:v>
+        <x:v>PMI-LinkedIn Certificate - Six Sigma Black Belt.pdf</x:v>
       </x:c>
       <x:c r="B194" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16217,16 +16234,14 @@
       <x:c r="C194" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
       </x:c>
-      <x:c r="D194" s="24" t="str">
-        <x:v>https://pjrtraining.talentlms.com/dashboard | https://pjrtraining.talentlms.com/unit/viewtestsurvey/id:1746,mode:test</x:v>
-      </x:c>
+      <x:c r="D194" s="24" t="str"/>
       <x:c r="E194" s="24" t="str">
         <x:v>Pendente</x:v>
       </x:c>
     </x:row>
     <x:row r="195">
       <x:c r="A195" s="24" t="str">
-        <x:v>PMI-LinkedIn Certificate - Six Sigma Black Belt.pdf</x:v>
+        <x:v>PMI-LinkedIn Certificate_Problem Solving for Leadership.pdf</x:v>
       </x:c>
       <x:c r="B195" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16241,7 +16256,7 @@
     </x:row>
     <x:row r="196">
       <x:c r="A196" s="24" t="str">
-        <x:v>PMI-LinkedIn Certificate_Problem Solving for Leadership.pdf</x:v>
+        <x:v>PMI-LinkedIn Certificate_Project Management Foundations.pdf</x:v>
       </x:c>
       <x:c r="B196" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16256,7 +16271,7 @@
     </x:row>
     <x:row r="197">
       <x:c r="A197" s="24" t="str">
-        <x:v>PMI-LinkedIn Certificate_Project Management Foundations.pdf</x:v>
+        <x:v>PMI-LinkedIn Learning Certificate_Healthcare Projects.pdf</x:v>
       </x:c>
       <x:c r="B197" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16271,7 +16286,7 @@
     </x:row>
     <x:row r="198">
       <x:c r="A198" s="24" t="str">
-        <x:v>PMI-LinkedIn Learning Certificate_Healthcare Projects.pdf</x:v>
+        <x:v>PMI-LinkedIn_Certificate_PM Foundations Requirements.pdf</x:v>
       </x:c>
       <x:c r="B198" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16286,7 +16301,7 @@
     </x:row>
     <x:row r="199">
       <x:c r="A199" s="24" t="str">
-        <x:v>PMI-LinkedIn_Certificate_PM Foundations Requirements.pdf</x:v>
+        <x:v>PMI-LinkedIn_Certificate_PM Foundations_Ethics.pdf</x:v>
       </x:c>
       <x:c r="B199" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16301,7 +16316,7 @@
     </x:row>
     <x:row r="200">
       <x:c r="A200" s="24" t="str">
-        <x:v>PMI-LinkedIn_Certificate_PM Foundations_Ethics.pdf</x:v>
+        <x:v>PMI-LinkedIn_Certificate_PME_Budgets.pdf</x:v>
       </x:c>
       <x:c r="B200" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16316,7 +16331,7 @@
     </x:row>
     <x:row r="201">
       <x:c r="A201" s="24" t="str">
-        <x:v>PMI-LinkedIn_Certificate_PME_Budgets.pdf</x:v>
+        <x:v>PMI-LinkedIn_Certificate_PME_Schedules.pdf</x:v>
       </x:c>
       <x:c r="B201" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16331,7 +16346,7 @@
     </x:row>
     <x:row r="202">
       <x:c r="A202" s="24" t="str">
-        <x:v>PMI-LinkedIn_Certificate_PME_Schedules.pdf</x:v>
+        <x:v>PMI-LinkedIn_Certificate_PMF_Teams.pdf</x:v>
       </x:c>
       <x:c r="B202" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16346,7 +16361,7 @@
     </x:row>
     <x:row r="203">
       <x:c r="A203" s="24" t="str">
-        <x:v>PMI-LinkedIn_Certificate_PMF_Teams.pdf</x:v>
+        <x:v>PMI-LinkedIn_Leveraging AI_GRC_Certificate.pdf</x:v>
       </x:c>
       <x:c r="B203" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16361,7 +16376,7 @@
     </x:row>
     <x:row r="204">
       <x:c r="A204" s="24" t="str">
-        <x:v>PMI-LinkedIn_Leveraging AI_GRC_Certificate.pdf</x:v>
+        <x:v>PMI-LinkedIn_MicrosoftMPM_Certificate.pdf</x:v>
       </x:c>
       <x:c r="B204" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16376,7 +16391,7 @@
     </x:row>
     <x:row r="205">
       <x:c r="A205" s="24" t="str">
-        <x:v>PMI-LinkedIn_MicrosoftMPM_Certificate.pdf</x:v>
+        <x:v>PMI-LinkedIn_PMF_Communication_Certificate.pdf</x:v>
       </x:c>
       <x:c r="B205" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16391,7 +16406,7 @@
     </x:row>
     <x:row r="206">
       <x:c r="A206" s="24" t="str">
-        <x:v>PMI-LinkedIn_PMF_Communication_Certificate.pdf</x:v>
+        <x:v>PMI-LinkedIn_PMF_Risks_Certificate.pdf</x:v>
       </x:c>
       <x:c r="B206" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16406,7 +16421,7 @@
     </x:row>
     <x:row r="207">
       <x:c r="A207" s="24" t="str">
-        <x:v>PMI-LinkedIn_PMF_Risks_Certificate.pdf</x:v>
+        <x:v>PMI-LinkedIn_PMF_Stakeholders_Certificate.pdf</x:v>
       </x:c>
       <x:c r="B207" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16421,7 +16436,7 @@
     </x:row>
     <x:row r="208">
       <x:c r="A208" s="24" t="str">
-        <x:v>PMI-LinkedIn_PMF_Stakeholders_Certificate.pdf</x:v>
+        <x:v>PMI_LinkedIn_Certificate_AI_Projects.pdf</x:v>
       </x:c>
       <x:c r="B208" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16436,7 +16451,7 @@
     </x:row>
     <x:row r="209">
       <x:c r="A209" s="24" t="str">
-        <x:v>PMI_LinkedIn_Certificate_AI_Projects.pdf</x:v>
+        <x:v>PMP ExamPrep1_Project Management Institute (PMI)®.pdf</x:v>
       </x:c>
       <x:c r="B209" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16451,7 +16466,7 @@
     </x:row>
     <x:row r="210">
       <x:c r="A210" s="24" t="str">
-        <x:v>PMP ExamPrep1_Project Management Institute (PMI)®.pdf</x:v>
+        <x:v>Podcast APS_CME answers certificate-2026-7-12_1735.pdf</x:v>
       </x:c>
       <x:c r="B210" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16459,14 +16474,16 @@
       <x:c r="C210" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
       </x:c>
-      <x:c r="D210" s="24" t="str"/>
+      <x:c r="D210" s="24" t="str">
+        <x:v>https://answersincme.com/DDT</x:v>
+      </x:c>
       <x:c r="E210" s="24" t="str">
         <x:v>Pendente</x:v>
       </x:c>
     </x:row>
     <x:row r="211">
       <x:c r="A211" s="24" t="str">
-        <x:v>Podcast APS_CME answers certificate-2026-7-12_1735.pdf</x:v>
+        <x:v>Processo Civil no pós-pandemia - Certificado ESAOAB.pdf</x:v>
       </x:c>
       <x:c r="B211" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16474,16 +16491,14 @@
       <x:c r="C211" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
       </x:c>
-      <x:c r="D211" s="24" t="str">
-        <x:v>https://answersincme.com/DDT</x:v>
-      </x:c>
+      <x:c r="D211" s="24" t="str"/>
       <x:c r="E211" s="24" t="str">
         <x:v>Pendente</x:v>
       </x:c>
     </x:row>
     <x:row r="212">
       <x:c r="A212" s="24" t="str">
-        <x:v>Processo Civil no pós-pandemia - Certificado ESAOAB.pdf</x:v>
+        <x:v>Project Management Institute (PMI)_6S Green Belt.pdf</x:v>
       </x:c>
       <x:c r="B212" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16498,7 +16513,7 @@
     </x:row>
     <x:row r="213">
       <x:c r="A213" s="24" t="str">
-        <x:v>Project Management Institute (PMI)_6S Green Belt.pdf</x:v>
+        <x:v>Project Management Institute (PMI)®.pdf</x:v>
       </x:c>
       <x:c r="B213" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16513,7 +16528,7 @@
     </x:row>
     <x:row r="214">
       <x:c r="A214" s="24" t="str">
-        <x:v>Project Management Institute (PMI)®.pdf</x:v>
+        <x:v>Public Health Law Academy_Certificate.pdf</x:v>
       </x:c>
       <x:c r="B214" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16528,10 +16543,10 @@
     </x:row>
     <x:row r="215">
       <x:c r="A215" s="24" t="str">
-        <x:v>Public Health Law Academy_Certificate.pdf</x:v>
+        <x:v>Python.pdf</x:v>
       </x:c>
       <x:c r="B215" s="24" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>PDF/imagem sem texto extraível</x:v>
       </x:c>
       <x:c r="C215" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
@@ -16543,10 +16558,10 @@
     </x:row>
     <x:row r="216">
       <x:c r="A216" s="24" t="str">
-        <x:v>Python.pdf</x:v>
+        <x:v>QMS_ISO 19011-2026_Fundamentos_Certificado 0014912.pdf</x:v>
       </x:c>
       <x:c r="B216" s="24" t="str">
-        <x:v>PDF/imagem sem texto extraível</x:v>
+        <x:v>Carga horária não localizada</x:v>
       </x:c>
       <x:c r="C216" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
@@ -16558,7 +16573,7 @@
     </x:row>
     <x:row r="217">
       <x:c r="A217" s="24" t="str">
-        <x:v>QMS_ISO 19011-2026_Fundamentos_Certificado 0014912.pdf</x:v>
+        <x:v>Relatório_Extensao_CEPROC.pdf</x:v>
       </x:c>
       <x:c r="B217" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16573,7 +16588,7 @@
     </x:row>
     <x:row r="218">
       <x:c r="A218" s="24" t="str">
-        <x:v>Receipt for Order 394583203.pdf</x:v>
+        <x:v>revivr-CPR_certificate_2026.08.22.pdf</x:v>
       </x:c>
       <x:c r="B218" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16588,7 +16603,7 @@
     </x:row>
     <x:row r="219">
       <x:c r="A219" s="24" t="str">
-        <x:v>Relatório_Extensao_CEPROC.pdf</x:v>
+        <x:v>Said-Oxford-Coursera_Agentic and GenAI_Certificate5YR8YBKNEOIC.pdf</x:v>
       </x:c>
       <x:c r="B219" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16603,7 +16618,7 @@
     </x:row>
     <x:row r="220">
       <x:c r="A220" s="24" t="str">
-        <x:v>revivr-CPR_certificate_2026.08.22.pdf</x:v>
+        <x:v>Said-Oxford-Coursera_AI Essentials_Certificate EN2VCPK6A775.pdf</x:v>
       </x:c>
       <x:c r="B220" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16618,7 +16633,7 @@
     </x:row>
     <x:row r="221">
       <x:c r="A221" s="24" t="str">
-        <x:v>Said-Oxford-Coursera_Agentic and GenAI_Certificate5YR8YBKNEOIC.pdf</x:v>
+        <x:v>Said-Oxford-Coursera_AI Governance_Certificate_FWGA4AWODSM4.pdf</x:v>
       </x:c>
       <x:c r="B221" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16633,7 +16648,7 @@
     </x:row>
     <x:row r="222">
       <x:c r="A222" s="24" t="str">
-        <x:v>Said-Oxford-Coursera_AI Essentials_Certificate EN2VCPK6A775.pdf</x:v>
+        <x:v>Said-Oxford-Coursera_Specialization AI for Business_Certificate_FWGA4AWODSM4.pdf</x:v>
       </x:c>
       <x:c r="B222" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16648,7 +16663,7 @@
     </x:row>
     <x:row r="223">
       <x:c r="A223" s="24" t="str">
-        <x:v>Said-Oxford-Coursera_AI Governance_Certificate_FWGA4AWODSM4.pdf</x:v>
+        <x:v>SkillFront-ISO 9001_Associate_Certificate_SFE0232f5d549bbc-96337181584206.pdf</x:v>
       </x:c>
       <x:c r="B223" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16663,7 +16678,7 @@
     </x:row>
     <x:row r="224">
       <x:c r="A224" s="24" t="str">
-        <x:v>Said-Oxford-Coursera_Specialization AI for Business_Certificate_FWGA4AWODSM4.pdf</x:v>
+        <x:v>SkillFront_ISO 27001 ISMS Associate SFE0166da11827fd-47327192991292_Certificate.pdf</x:v>
       </x:c>
       <x:c r="B224" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16678,7 +16693,7 @@
     </x:row>
     <x:row r="225">
       <x:c r="A225" s="24" t="str">
-        <x:v>SkillFront-ISO 9001_Associate_Certificate_SFE0232f5d549bbc-96337181584206.pdf</x:v>
+        <x:v>Stanford-Coursera RYUIMPUS3ZLR_Intro to Healthcare_Certificate.pdf</x:v>
       </x:c>
       <x:c r="B225" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16693,7 +16708,7 @@
     </x:row>
     <x:row r="226">
       <x:c r="A226" s="24" t="str">
-        <x:v>SkillFront_ISO 27001 ISMS Associate SFE0166da11827fd-47327192991292_Certificate.pdf</x:v>
+        <x:v>Stanford-Coursera_AI in Healthcare Capstone Certificate_9L3NBFUCKU4Q.pdf</x:v>
       </x:c>
       <x:c r="B226" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16708,7 +16723,7 @@
     </x:row>
     <x:row r="227">
       <x:c r="A227" s="24" t="str">
-        <x:v>Stanford-Coursera RYUIMPUS3ZLR_Intro to Healthcare_Certificate.pdf</x:v>
+        <x:v>Stanford-Coursera_AI in Healthcare Specialization Certificate_7GM7A9EIJ9W4.pdf</x:v>
       </x:c>
       <x:c r="B227" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16723,7 +16738,7 @@
     </x:row>
     <x:row r="228">
       <x:c r="A228" s="24" t="str">
-        <x:v>Stanford-Coursera_AI in Healthcare Capstone Certificate_9L3NBFUCKU4Q.pdf</x:v>
+        <x:v>Stanford-Coursera_Antibiotic Stewardship Certificate.pdf</x:v>
       </x:c>
       <x:c r="B228" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16731,14 +16746,16 @@
       <x:c r="C228" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
       </x:c>
-      <x:c r="D228" s="24" t="str"/>
+      <x:c r="D228" s="24" t="str">
+        <x:v>https://coursera.org/verify/FZV2SBU6I8NI</x:v>
+      </x:c>
       <x:c r="E228" s="24" t="str">
         <x:v>Pendente</x:v>
       </x:c>
     </x:row>
     <x:row r="229">
       <x:c r="A229" s="24" t="str">
-        <x:v>Stanford-Coursera_AI in Healthcare Specialization Certificate_7GM7A9EIJ9W4.pdf</x:v>
+        <x:v>Stanford-Coursera_Evaluations of AI in HC_Certificate_DW8FFD7QA2IZ.pdf</x:v>
       </x:c>
       <x:c r="B229" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16753,7 +16770,7 @@
     </x:row>
     <x:row r="230">
       <x:c r="A230" s="24" t="str">
-        <x:v>Stanford-Coursera_Evaluations of AI in HC_Certificate_DW8FFD7QA2IZ.pdf</x:v>
+        <x:v>Stanford-Coursera_Intro to Clinical Data Certificate.pdf</x:v>
       </x:c>
       <x:c r="B230" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16768,7 +16785,7 @@
     </x:row>
     <x:row r="231">
       <x:c r="A231" s="24" t="str">
-        <x:v>Stanford-Coursera_Intro to Clinical Data Certificate.pdf</x:v>
+        <x:v>Stanford-Coursera_PCA Specialization Certificate E8700K9GB2WD.pdf</x:v>
       </x:c>
       <x:c r="B231" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16783,7 +16800,7 @@
     </x:row>
     <x:row r="232">
       <x:c r="A232" s="24" t="str">
-        <x:v>Stanford-Coursera_PCA Specialization Certificate E8700K9GB2WD.pdf</x:v>
+        <x:v>Stanford-Coursera_Supporting Caregiver Health_Certificate_O8W0ZHG0J5II.pdf</x:v>
       </x:c>
       <x:c r="B232" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16798,7 +16815,7 @@
     </x:row>
     <x:row r="233">
       <x:c r="A233" s="24" t="str">
-        <x:v>Stanford-Coursera_Supporting Caregiver Health_Certificate_O8W0ZHG0J5II.pdf</x:v>
+        <x:v>Stanford-Coursera_Symptom Management_CertificateLYD5V9AWXRXS.pdf</x:v>
       </x:c>
       <x:c r="B233" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16813,7 +16830,7 @@
     </x:row>
     <x:row r="234">
       <x:c r="A234" s="24" t="str">
-        <x:v>Stanford-Coursera_Symptom Management_CertificateLYD5V9AWXRXS.pdf</x:v>
+        <x:v>Stanford-Coursera_Transitioning care in palliative care_Certificate_554362_47066_3.pdf</x:v>
       </x:c>
       <x:c r="B234" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16828,7 +16845,7 @@
     </x:row>
     <x:row r="235">
       <x:c r="A235" s="24" t="str">
-        <x:v>Stanford-Coursera_Transitioning care in palliative care_Certificate_554362_47066_3.pdf</x:v>
+        <x:v>Stanfrod-Coursera_Supporting families and caregivers Certificate_O8W0ZHG0J5II.pdf</x:v>
       </x:c>
       <x:c r="B235" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16843,7 +16860,7 @@
     </x:row>
     <x:row r="236">
       <x:c r="A236" s="24" t="str">
-        <x:v>Stanfrod-Coursera_Supporting families and caregivers Certificate_O8W0ZHG0J5II.pdf</x:v>
+        <x:v>texto 2.txt</x:v>
       </x:c>
       <x:c r="B236" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16858,7 +16875,7 @@
     </x:row>
     <x:row r="237">
       <x:c r="A237" s="24" t="str">
-        <x:v>texto 2.txt</x:v>
+        <x:v>texto 3.txt</x:v>
       </x:c>
       <x:c r="B237" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16866,14 +16883,16 @@
       <x:c r="C237" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
       </x:c>
-      <x:c r="D237" s="24" t="str"/>
+      <x:c r="D237" s="24" t="str">
+        <x:v>https://produto.mercadolivre.com.br/MLB-3554868073-creme-despigmentante-alfa-arbutin-7-40g-_JM", | https://shopee.com.br/search?keyword=Alfa+Arbutin+Axilas", | https://shopee.com.br/search?keyword=Alfa+Arbutin+Formulab", | https://shopee.com.br/search?keyword=Alfa+Arbutin+Locao", | https://shopee.com.br/search?keyword=Alpha+Arbutin", | https://shopee.com.br/search?keyword=Creme%20Gel%20para%20Peeling%20com%20%C3%81cido%20Retin%C3%B3ico%20e%20Hidroquinona", | https://shopee.com.br/search?keyword=Hidroquinona", | https://www.amazon.com.br/alpha-arbutin/s?k=alpha+arbutin", | https://www.amazon.com.br/s?k=Gel+Facial+Alfa+Arbutin", | https://www.belezasaude.com.br/creme-alfa-arbutin-10-vitamina-c-estabilizada-10-40g", | https://www.drogariaminasbrasil.com.br/hidroquinona-5-acid-retinoico-0-025-dexametasona-0-05-creme-30g.html", | https://www.drogariaminasbrasil.com.br/search?q=hidroquinona", | https://www.drogariasaopaulo.com.br/search?w=Melan-Off", | https://www.drogariasaopaulo.com.br/search?w=suavicid", | https://www.drogasil.com.br/search?w=Blancy", | https://www.drogasil.com.br/search?w=Classis%20TX", | https://www.drogasil.com.br/search?w=vitacid%20plus", | https://www.epocacosmeticos.com.br/search?q=Eucerin+Anti+Pigment", | https://www.farmaciabelladona.com.br/search?q=alfa+arbutin", | https://www.farmaciabelladona.com.br/search?q=hidroquinona", | https://www.farmaciabotanica.com.br/search?q=alfa+arbutin", | https://www.farmaciaeficacia.com.br/search?q=alfa+arbutin", | https://www.farmaciaeficacia.com.br/search?q=hidroquinona", | https://www.farmasesi.com.br/produto/5424-hidroquinona--ems-400mg-4-creme-30g", | https://www.farmasite.com.br/hidroquinona-4-alfa-bisabolol-1-creme-30g", | https://www.farmasite.com.br/search?q=hidroquinona", | https://www.manipulart.com.br/search?q=hidroquinona" | https://www.manipulart.com.br/search?q=hidroquinona", | https://www.mercadolivre.com.br/p/MLB39792525", | https://www.mercadolivre.com.br/search?keyword=Arbutin+Creme", | https://www.mercadolivre.com.br/search?keyword=Raavi%20Alfa%20Arbutin", | https://www.naturalforma.com.br/search?q=alfa+arbutin", | https://www.naturalforma.com.br/search?q=hidroquinona", | https://www.panvel.com/search?q=hormoskin", | https://www.rituaria.com.br/produtos/formula-uniformizadora",</x:v>
+      </x:c>
       <x:c r="E237" s="24" t="str">
         <x:v>Pendente</x:v>
       </x:c>
     </x:row>
     <x:row r="238">
       <x:c r="A238" s="24" t="str">
-        <x:v>texto 3.txt</x:v>
+        <x:v>texto.txt</x:v>
       </x:c>
       <x:c r="B238" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16882,7 +16901,7 @@
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
       </x:c>
       <x:c r="D238" s="24" t="str">
-        <x:v>https://produto.mercadolivre.com.br/MLB-3554868073-creme-despigmentante-alfa-arbutin-7-40g-_JM", | https://shopee.com.br/search?keyword=Alfa+Arbutin+Axilas", | https://shopee.com.br/search?keyword=Alfa+Arbutin+Formulab", | https://shopee.com.br/search?keyword=Alfa+Arbutin+Locao", | https://shopee.com.br/search?keyword=Alpha+Arbutin", | https://shopee.com.br/search?keyword=Creme%20Gel%20para%20Peeling%20com%20%C3%81cido%20Retin%C3%B3ico%20e%20Hidroquinona", | https://shopee.com.br/search?keyword=Hidroquinona", | https://www.amazon.com.br/alpha-arbutin/s?k=alpha+arbutin", | https://www.amazon.com.br/s?k=Gel+Facial+Alfa+Arbutin", | https://www.belezasaude.com.br/creme-alfa-arbutin-10-vitamina-c-estabilizada-10-40g", | https://www.drogariaminasbrasil.com.br/hidroquinona-5-acid-retinoico-0-025-dexametasona-0-05-creme-30g.html", | https://www.drogariaminasbrasil.com.br/search?q=hidroquinona", | https://www.drogariasaopaulo.com.br/search?w=Melan-Off", | https://www.drogariasaopaulo.com.br/search?w=suavicid", | https://www.drogasil.com.br/search?w=Blancy", | https://www.drogasil.com.br/search?w=Classis%20TX", | https://www.drogasil.com.br/search?w=vitacid%20plus", | https://www.epocacosmeticos.com.br/search?q=Eucerin+Anti+Pigment", | https://www.farmaciabelladona.com.br/search?q=alfa+arbutin", | https://www.farmaciabelladona.com.br/search?q=hidroquinona", | https://www.farmaciabotanica.com.br/search?q=alfa+arbutin", | https://www.farmaciaeficacia.com.br/search?q=alfa+arbutin", | https://www.farmaciaeficacia.com.br/search?q=hidroquinona", | https://www.farmasesi.com.br/produto/5424-hidroquinona--ems-400mg-4-creme-30g", | https://www.farmasite.com.br/hidroquinona-4-alfa-bisabolol-1-creme-30g", | https://www.farmasite.com.br/search?q=hidroquinona", | https://www.manipulart.com.br/search?q=hidroquinona" | https://www.manipulart.com.br/search?q=hidroquinona", | https://www.mercadolivre.com.br/p/MLB39792525", | https://www.mercadolivre.com.br/search?keyword=Arbutin+Creme", | https://www.mercadolivre.com.br/search?keyword=Raavi%20Alfa%20Arbutin", | https://www.naturalforma.com.br/search?q=alfa+arbutin", | https://www.naturalforma.com.br/search?q=hidroquinona", | https://www.panvel.com/search?q=hormoskin", | https://www.rituaria.com.br/produtos/formula-uniformizadora",</x:v>
+        <x:v>https://cursa.app/pt/downapp</x:v>
       </x:c>
       <x:c r="E238" s="24" t="str">
         <x:v>Pendente</x:v>
@@ -16890,7 +16909,7 @@
     </x:row>
     <x:row r="239">
       <x:c r="A239" s="24" t="str">
-        <x:v>texto.txt</x:v>
+        <x:v>TRREE (2023)_Certificate of completion for module 1_Intro to Research.pdf</x:v>
       </x:c>
       <x:c r="B239" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16899,7 +16918,7 @@
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
       </x:c>
       <x:c r="D239" s="24" t="str">
-        <x:v>https://cursa.app/pt/downapp</x:v>
+        <x:v>http://www.cihr-irsc.gc.ca/e/2891.html</x:v>
       </x:c>
       <x:c r="E239" s="24" t="str">
         <x:v>Pendente</x:v>
@@ -16907,7 +16926,7 @@
     </x:row>
     <x:row r="240">
       <x:c r="A240" s="24" t="str">
-        <x:v>TRREE (2023)_Certificate of completion for module 1_Intro to Research.pdf</x:v>
+        <x:v>TRREE (2023)_Certificate of completion for module 2_Ethics Evaluation in Research.pdf</x:v>
       </x:c>
       <x:c r="B240" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16924,7 +16943,7 @@
     </x:row>
     <x:row r="241">
       <x:c r="A241" s="24" t="str">
-        <x:v>TRREE (2023)_Certificate of completion for module 2_Ethics Evaluation in Research.pdf</x:v>
+        <x:v>TRREE (2023)_Certificate of completion for module 3_Informed Consent_Certificate.pdf</x:v>
       </x:c>
       <x:c r="B241" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16941,7 +16960,7 @@
     </x:row>
     <x:row r="242">
       <x:c r="A242" s="24" t="str">
-        <x:v>TRREE (2023)_Certificate of completion for module 3_Informed Consent_Certificate.pdf</x:v>
+        <x:v>TRREE_Module 4_R3_GCP_Certificate.pdf</x:v>
       </x:c>
       <x:c r="B242" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16958,7 +16977,7 @@
     </x:row>
     <x:row r="243">
       <x:c r="A243" s="24" t="str">
-        <x:v>TRREE_Module 4_R3_GCP_Certificate.pdf</x:v>
+        <x:v>TRREE_Module 4R2_GCP_Certificate.pdf</x:v>
       </x:c>
       <x:c r="B243" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16975,7 +16994,7 @@
     </x:row>
     <x:row r="244">
       <x:c r="A244" s="24" t="str">
-        <x:v>TRREE_Module 4R2_GCP_Certificate.pdf</x:v>
+        <x:v>TRREE_Module 5.1 HIV Vaccine TrialsTraining certificate.pdf</x:v>
       </x:c>
       <x:c r="B244" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16992,7 +17011,7 @@
     </x:row>
     <x:row r="245">
       <x:c r="A245" s="24" t="str">
-        <x:v>TRREE_Module 5.1 HIV Vaccine TrialsTraining certificate.pdf</x:v>
+        <x:v>TRREE_Module 5.2_Adolescent participants in HIV Trials_Training certificate - Module 5.2.pdf</x:v>
       </x:c>
       <x:c r="B245" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -17009,7 +17028,7 @@
     </x:row>
     <x:row r="246">
       <x:c r="A246" s="24" t="str">
-        <x:v>TRREE_Module 5.2_Adolescent participants in HIV Trials_Training certificate - Module 5.2.pdf</x:v>
+        <x:v>TRREE_Module 5.3_Ethics in PH Research_Training Certificate.pdf</x:v>
       </x:c>
       <x:c r="B246" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -17026,7 +17045,7 @@
     </x:row>
     <x:row r="247">
       <x:c r="A247" s="24" t="str">
-        <x:v>TRREE_Module 5.3_Ethics in PH Research_Training Certificate.pdf</x:v>
+        <x:v>TRREE_Reg. Frameworks_Suisse-2025_Certificate.pdf</x:v>
       </x:c>
       <x:c r="B247" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -17043,7 +17062,7 @@
     </x:row>
     <x:row r="248">
       <x:c r="A248" s="24" t="str">
-        <x:v>TRREE_Reg. Frameworks_Suisse-2025_Certificate.pdf</x:v>
+        <x:v>U-M-Coursera_Translating Research to communities Certificate_WWZOYLD9AB26.pdf</x:v>
       </x:c>
       <x:c r="B248" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -17051,16 +17070,14 @@
       <x:c r="C248" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
       </x:c>
-      <x:c r="D248" s="24" t="str">
-        <x:v>http://www.cihr-irsc.gc.ca/e/2891.html</x:v>
-      </x:c>
+      <x:c r="D248" s="24" t="str"/>
       <x:c r="E248" s="24" t="str">
         <x:v>Pendente</x:v>
       </x:c>
     </x:row>
     <x:row r="249">
       <x:c r="A249" s="24" t="str">
-        <x:v>U-M-Coursera_Translating Research to communities Certificate_WWZOYLD9AB26.pdf</x:v>
+        <x:v>U-M-Coursera_Translating Research to Patients Certificate_IKDNWXUCALFA.pdf</x:v>
       </x:c>
       <x:c r="B249" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -17075,7 +17092,7 @@
     </x:row>
     <x:row r="250">
       <x:c r="A250" s="24" t="str">
-        <x:v>U-M-Coursera_Translating Research to Patients Certificate_IKDNWXUCALFA.pdf</x:v>
+        <x:v>U-M-Coursera_Translational Research for humans_Certificate 7MIVPFC1VTQR.pdf</x:v>
       </x:c>
       <x:c r="B250" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -17090,7 +17107,7 @@
     </x:row>
     <x:row r="251">
       <x:c r="A251" s="24" t="str">
-        <x:v>U-M-Coursera_Translational Research for humans_Certificate 7MIVPFC1VTQR.pdf</x:v>
+        <x:v>U-M-Coursera_Translational Science Specialization Certificate_IXQRUXCLXP3K.pdf</x:v>
       </x:c>
       <x:c r="B251" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -17105,10 +17122,10 @@
     </x:row>
     <x:row r="252">
       <x:c r="A252" s="24" t="str">
-        <x:v>U-M-Coursera_Translational Science Specialization Certificate_IXQRUXCLXP3K.pdf</x:v>
+        <x:v>UFMA_DRC na APS_Certificafdo de Curso.pdf</x:v>
       </x:c>
       <x:c r="B252" s="24" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>PDF/imagem sem texto extraível</x:v>
       </x:c>
       <x:c r="C252" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
@@ -17120,10 +17137,10 @@
     </x:row>
     <x:row r="253">
       <x:c r="A253" s="24" t="str">
-        <x:v>UFMA_DRC na APS_Certificafdo de Curso.pdf</x:v>
+        <x:v>UFMG-UNA-SUS_M1_Atributos da APS_certificado_1f198775-dbe8-6290-b71e-85b8bf09b5ac.pdf</x:v>
       </x:c>
       <x:c r="B253" s="24" t="str">
-        <x:v>PDF/imagem sem texto extraível</x:v>
+        <x:v>Carga horária não localizada</x:v>
       </x:c>
       <x:c r="C253" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
@@ -17135,10 +17152,10 @@
     </x:row>
     <x:row r="254">
       <x:c r="A254" s="24" t="str">
-        <x:v>UFMG-UNA-SUS_M1_Atributos da APS_certificado_1f198775-dbe8-6290-b71e-85b8bf09b5ac.pdf</x:v>
+        <x:v>UNA-SUS-UFMA_Aperfeiçoamento em DRC_Certificado.pdf</x:v>
       </x:c>
       <x:c r="B254" s="24" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>PDF/imagem sem texto extraível</x:v>
       </x:c>
       <x:c r="C254" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
@@ -17150,7 +17167,7 @@
     </x:row>
     <x:row r="255">
       <x:c r="A255" s="24" t="str">
-        <x:v>UNA-SUS-UFMA_Aperfeiçoamento em DRC_Certificado.pdf</x:v>
+        <x:v>UNA-SUS-UFMA_Atendimento Interdisciplinar DRC_M5_Certificado.pdf</x:v>
       </x:c>
       <x:c r="B255" s="24" t="str">
         <x:v>PDF/imagem sem texto extraível</x:v>
@@ -17165,7 +17182,7 @@
     </x:row>
     <x:row r="256">
       <x:c r="A256" s="24" t="str">
-        <x:v>UNA-SUS-UFMA_Atendimento Interdisciplinar DRC_M5_Certificado.pdf</x:v>
+        <x:v>UNA-SUS-UFMA_Diálise Peritoneal_M4_Certificado.pdf</x:v>
       </x:c>
       <x:c r="B256" s="24" t="str">
         <x:v>PDF/imagem sem texto extraível</x:v>
@@ -17180,7 +17197,7 @@
     </x:row>
     <x:row r="257">
       <x:c r="A257" s="24" t="str">
-        <x:v>UNA-SUS-UFMA_Diálise Peritoneal_M4_Certificado.pdf</x:v>
+        <x:v>UNA-SUS-UFMA_IA na Saúde_Extensão_Certificado.pdf</x:v>
       </x:c>
       <x:c r="B257" s="24" t="str">
         <x:v>PDF/imagem sem texto extraível</x:v>
@@ -17195,7 +17212,7 @@
     </x:row>
     <x:row r="258">
       <x:c r="A258" s="24" t="str">
-        <x:v>UNA-SUS-UFMA_IA na Saúde_Extensão_Certificado.pdf</x:v>
+        <x:v>UNA-SUS-UFMA_Introdução à DRC_M1_Certificado.pdf</x:v>
       </x:c>
       <x:c r="B258" s="24" t="str">
         <x:v>PDF/imagem sem texto extraível</x:v>
@@ -17210,7 +17227,7 @@
     </x:row>
     <x:row r="259">
       <x:c r="A259" s="24" t="str">
-        <x:v>UNA-SUS-UFMA_Introdução à DRC_M1_Certificado.pdf</x:v>
+        <x:v>UNA-SUS-UFMA_Manejo clínico da DRC_M3_Certificado.pdf</x:v>
       </x:c>
       <x:c r="B259" s="24" t="str">
         <x:v>PDF/imagem sem texto extraível</x:v>
@@ -17225,7 +17242,7 @@
     </x:row>
     <x:row r="260">
       <x:c r="A260" s="24" t="str">
-        <x:v>UNA-SUS-UFMA_Manejo clínico da DRC_M3_Certificado.pdf</x:v>
+        <x:v>UNA-SUS-UFMA_Registros e Qualidade na Saúde Digital_Certificado de Conclusao_.pdf</x:v>
       </x:c>
       <x:c r="B260" s="24" t="str">
         <x:v>PDF/imagem sem texto extraível</x:v>
@@ -17240,7 +17257,7 @@
     </x:row>
     <x:row r="261">
       <x:c r="A261" s="24" t="str">
-        <x:v>UNA-SUS-UFMA_Registros e Qualidade na Saúde Digital_Certificado de Conclusao_.pdf</x:v>
+        <x:v>UNA-SUS-UFMA_Saude Digital e SUS_Certificado Extensão.pdf</x:v>
       </x:c>
       <x:c r="B261" s="24" t="str">
         <x:v>PDF/imagem sem texto extraível</x:v>
@@ -17255,7 +17272,7 @@
     </x:row>
     <x:row r="262">
       <x:c r="A262" s="24" t="str">
-        <x:v>UNA-SUS-UFMA_Saude Digital e SUS_Certificado Extensão.pdf</x:v>
+        <x:v>UNA-SUS-UFMA_Saúde Digital Inclusiva_Certificado.pdf</x:v>
       </x:c>
       <x:c r="B262" s="24" t="str">
         <x:v>PDF/imagem sem texto extraível</x:v>
@@ -17270,7 +17287,7 @@
     </x:row>
     <x:row r="263">
       <x:c r="A263" s="24" t="str">
-        <x:v>UNA-SUS-UFMA_Saúde Digital Inclusiva_Certificado.pdf</x:v>
+        <x:v>UNA-SUS-UFMA_Saúde Digital Noções fundamentais_Certificado.pdf</x:v>
       </x:c>
       <x:c r="B263" s="24" t="str">
         <x:v>PDF/imagem sem texto extraível</x:v>
@@ -17285,7 +17302,7 @@
     </x:row>
     <x:row r="264">
       <x:c r="A264" s="24" t="str">
-        <x:v>UNA-SUS-UFMA_Saúde Digital Noções fundamentais_Certificado.pdf</x:v>
+        <x:v>UNA-SUS-UFMA_Transf Digital_Extensao_Certificado.pdf</x:v>
       </x:c>
       <x:c r="B264" s="24" t="str">
         <x:v>PDF/imagem sem texto extraível</x:v>
@@ -17300,7 +17317,7 @@
     </x:row>
     <x:row r="265">
       <x:c r="A265" s="24" t="str">
-        <x:v>UNA-SUS-UFMA_Transf Digital_Extensao_Certificado.pdf</x:v>
+        <x:v>UNA-SUS_Certificado_Introducao Saúde Digital.pdf</x:v>
       </x:c>
       <x:c r="B265" s="24" t="str">
         <x:v>PDF/imagem sem texto extraível</x:v>
@@ -17315,7 +17332,7 @@
     </x:row>
     <x:row r="266">
       <x:c r="A266" s="24" t="str">
-        <x:v>UNA-SUS_Certificado_Introducao Saúde Digital.pdf</x:v>
+        <x:v>UNA-SUS_UFMA_Cultura da Saúde Digital_Certificado de Extensão_.pdf</x:v>
       </x:c>
       <x:c r="B266" s="24" t="str">
         <x:v>PDF/imagem sem texto extraível</x:v>
@@ -17330,7 +17347,7 @@
     </x:row>
     <x:row r="267">
       <x:c r="A267" s="24" t="str">
-        <x:v>UNA-SUS_UFMA_Cultura da Saúde Digital_Certificado de Extensão_.pdf</x:v>
+        <x:v>UNA-SUS_UFMA_Etica e Responsabilidade_Saude Digital_Certificado Extensão.pdf</x:v>
       </x:c>
       <x:c r="B267" s="24" t="str">
         <x:v>PDF/imagem sem texto extraível</x:v>
@@ -17345,7 +17362,7 @@
     </x:row>
     <x:row r="268">
       <x:c r="A268" s="24" t="str">
-        <x:v>UNA-SUS_UFMA_Etica e Responsabilidade_Saude Digital_Certificado Extensão.pdf</x:v>
+        <x:v>UNA-SUS_UFMA_Programa_Aperfeicoamento_Saude Digital_Certificado.pdf</x:v>
       </x:c>
       <x:c r="B268" s="24" t="str">
         <x:v>PDF/imagem sem texto extraível</x:v>
@@ -17360,10 +17377,10 @@
     </x:row>
     <x:row r="269">
       <x:c r="A269" s="24" t="str">
-        <x:v>UNA-SUS_UFMA_Programa_Aperfeicoamento_Saude Digital_Certificado.pdf</x:v>
+        <x:v>VMEdu_SFC_PedroLamounierSampaio-1182483.pdf</x:v>
       </x:c>
       <x:c r="B269" s="24" t="str">
-        <x:v>PDF/imagem sem texto extraível</x:v>
+        <x:v>Carga horária não localizada</x:v>
       </x:c>
       <x:c r="C269" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
@@ -17375,7 +17392,7 @@
     </x:row>
     <x:row r="270">
       <x:c r="A270" s="24" t="str">
-        <x:v>VMEdu_SFC_PedroLamounierSampaio-1182483.pdf</x:v>
+        <x:v>Yale-Coursera_Global Health Essentials_Certificate_YJ26WLVD3O3K.pdf</x:v>
       </x:c>
       <x:c r="B270" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -17390,7 +17407,7 @@
     </x:row>
     <x:row r="271">
       <x:c r="A271" s="24" t="str">
-        <x:v>Yale-Coursera_Global Health Essentials_Certificate_YJ26WLVD3O3K.pdf</x:v>
+        <x:v>Your D-U-N-S Number is enclosed_.pdf</x:v>
       </x:c>
       <x:c r="B271" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -17400,21 +17417,6 @@
       </x:c>
       <x:c r="D271" s="24" t="str"/>
       <x:c r="E271" s="24" t="str">
-        <x:v>Pendente</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="272">
-      <x:c r="A272" s="24" t="str">
-        <x:v>Your D-U-N-S Number is enclosed_.pdf</x:v>
-      </x:c>
-      <x:c r="B272" s="24" t="str">
-        <x:v>Carga horária não localizada</x:v>
-      </x:c>
-      <x:c r="C272" s="24" t="str">
-        <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
-      </x:c>
-      <x:c r="D272" s="24" t="str"/>
-      <x:c r="E272" s="24" t="str">
         <x:v>Pendente</x:v>
       </x:c>
     </x:row>

--- a/ACG_UNIFENAS_Medicina.xlsx
+++ b/ACG_UNIFENAS_Medicina.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo" sheetId="1" r:id="R21a864e93ff341f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regras UNIFENAS" sheetId="2" r:id="R47d6610fc2e44920"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Certificados" sheetId="3" r:id="R91ad27624040493b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Excluídos" sheetId="4" r:id="R4acaf79ad5f24e18"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pendências" sheetId="5" r:id="R31012f932d1f4daa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo" sheetId="1" r:id="R0a96d4fe3c794ad9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regras UNIFENAS" sheetId="2" r:id="R88288ccc0e96487b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Certificados" sheetId="3" r:id="Rf93a249f3de3485d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Excluídos" sheetId="4" r:id="R439b4e79e4304ccd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pendências" sheetId="5" r:id="Rf6674072e94e46b0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -467,7 +467,7 @@
       </x:c>
       <x:c r="B6" s="16" t="n">
         <x:f>SUM('Certificados'!$K$2:$K$389)</x:f>
-        <x:v>2110.5</x:v>
+        <x:v>2244.5</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -476,7 +476,7 @@
       </x:c>
       <x:c r="B7" s="16" t="n">
         <x:f>SUM('Certificados'!$M$2:$M$389)</x:f>
-        <x:v>2110.5</x:v>
+        <x:v>2244.5</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -485,7 +485,7 @@
       </x:c>
       <x:c r="B8" s="16" t="n">
         <x:f>B3-B7</x:f>
-        <x:v>-1660.5</x:v>
+        <x:v>-1794.5</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -520,11 +520,11 @@
       </x:c>
       <x:c r="C12" s="30" t="n">
         <x:f>SUMIF('Certificados'!$H$2:$H$389,A12,'Certificados'!$K$2:$K$389)</x:f>
-        <x:v>1360.25</x:v>
+        <x:v>1494.25</x:v>
       </x:c>
       <x:c r="D12" s="30" t="n">
         <x:f>SUMIF('Certificados'!$H$2:$H$389,A12,'Certificados'!$M$2:$M$389)</x:f>
-        <x:v>1360.25</x:v>
+        <x:v>1494.25</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -2118,7 +2118,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="N26" s="32" t="str">
-        <x:v>Coursera: https://www.coursera.org/account/accomplishments/specialization/K99N55L2EZNG; estimativa derivada do tempo exibido: 1 meses com 10 por semana para concluir</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/specialization/K99N55L2EZNG; duração exibida: 1 meses com 10 por semana para concluir</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -3501,7 +3501,9 @@
       <x:c r="E64" s="32" t="str">
         <x:v>Revenue Cycle, Billing, and Coding</x:v>
       </x:c>
-      <x:c r="F64" s="32" t="str"/>
+      <x:c r="F64" s="32" t="str">
+        <x:v>Patient registration; revenue cycle management; medical coding; billing; claims processing; and denial management.</x:v>
+      </x:c>
       <x:c r="G64" s="32" t="str"/>
       <x:c r="H64" s="32" t="str">
         <x:v>Grupo 1 — Ensino</x:v>
@@ -3542,7 +3544,7 @@
         <x:v>Revenue Cycle, Billing, and Coding</x:v>
       </x:c>
       <x:c r="F65" s="32" t="str">
-        <x:v>J u n 2 8 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o R e v e n u e C y c l e , B i l l i n g , a n d C o d i n g u m c u r s o o n - l i n e a u t o r i z a d o p e l a J o h n s H o p k i n s U n i v e r s i t y e m i n i s t r a d o a t r a v é s d a C o u r s e r a c o n c l u i u c o m s u c e s s o o P r o g r a m a d e c u r s o s i n t e g r a d o s M a u r a M c G u i r e , M D , C P C , F A C P E x e c u t i v e D i r e c t o r O J H P S t r a t e g i c L e a r n i n g C e n t </x:v>
+        <x:v>Patient registration; revenue cycle management; medical coding; billing; claims processing; and denial management.</x:v>
       </x:c>
       <x:c r="G65" s="32" t="str"/>
       <x:c r="H65" s="32" t="str">
@@ -3606,7 +3608,7 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="N66" s="32" t="str">
-        <x:v>Coursera: https://www.coursera.org/account/accomplishments/professional-cert/P7PRAOBUU4L9; estimativa derivada do tempo exibido: 6 meses com 3 por semana para concluir</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/professional-cert/P7PRAOBUU4L9; duração exibida: 6 meses com 3 por semana para concluir</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
@@ -3648,7 +3650,7 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="N67" s="32" t="str">
-        <x:v>Coursera: https://www.coursera.org/account/accomplishments/professional-cert/P7PRAOBUU4L9; estimativa derivada do tempo exibido: 6 meses com 3 por semana para concluir</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/professional-cert/P7PRAOBUU4L9; duração exibida: 6 meses com 3 por semana para concluir</x:v>
       </x:c>
     </x:row>
     <x:row r="68">
@@ -4616,7 +4618,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="N94" s="32" t="str">
-        <x:v>Coursera: https://www.coursera.org/account/accomplishments/specialization/8BH1XC5QBHPD; estimativa derivada do tempo exibido: 1 meses com 10 por semana para concluir</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/specialization/8BH1XC5QBHPD; duração exibida: 1 meses com 10 por semana para concluir</x:v>
       </x:c>
     </x:row>
     <x:row r="95">
@@ -4634,7 +4636,7 @@
         <x:v>Leading Healthcare Quality and Safety</x:v>
       </x:c>
       <x:c r="F95" s="32" t="str">
-        <x:v>J u l 2 1 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o L e a d i n g H e a l t h c a r e Q u a l i t y a n d S a f e t y a n o n l i n e c o u r s e a u t h o r i z e d b y T h e G e o r g e W a s h i n g t o n U n i v e r s i t y a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d G r e g o r y P a w l s o n C l i n i c a l P r o f e s s o r o f M e d i c i n e a n d E x e c u t i v e C o a c h G W S c h o o l o f N u r s i n g J e a n J o h </x:v>
+        <x:v>Patient safety; health informatics; healthcare administration; measurement systems; change management; and organizational change.</x:v>
       </x:c>
       <x:c r="G95" s="32" t="str"/>
       <x:c r="H95" s="32" t="str">
@@ -4718,7 +4720,7 @@
         <x:v>Quality Improvement in Healthcare</x:v>
       </x:c>
       <x:c r="F97" s="32" t="str">
-        <x:v>3 C o u r s e s I n t r o d u c t i o n t o Q u a l i t y I m p r o v e m e n t i n H e a l t h c a r e U s i n g D a t a f o r H e a l t h c a r e I m p r o v e m e n t Q u a l i t y I m p r o v e m e n t f o r P o p u l a t i o n H e a l t h D r T h o m a s W o o d c o c k S e n i o r R e s e a r c h F e l l o w S c h o o l o f P u b l i c H e a l t h J u l 2 4 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o h a s s u c c e s s f u l l y c o m p l e t e d t h e o n l i n e S p e c i a l i </x:v>
+        <x:v>Introduction to quality improvement in healthcare; using data for healthcare improvement; and quality improvement for population health.</x:v>
       </x:c>
       <x:c r="G97" s="32" t="str"/>
       <x:c r="H97" s="32" t="str">
@@ -4740,7 +4742,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="N97" s="32" t="str">
-        <x:v>Coursera: https://www.coursera.org/account/accomplishments/specialization/2RUAK3DPGYVQ; estimativa derivada do tempo exibido: 1 meses com 10 por semana para concluir</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/specialization/2RUAK3DPGYVQ; duração exibida: 1 meses com 10 por semana para concluir</x:v>
       </x:c>
     </x:row>
     <x:row r="98">
@@ -4760,7 +4762,7 @@
         <x:v>Introduction to Quality Improvement in Healthcare</x:v>
       </x:c>
       <x:c r="F98" s="32" t="str">
-        <x:v>J u l 2 2 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o I n t r o d u c t i o n t o Q u a l i t y I m p r o v e m e n t i n H e a l t h c a r e a n o n l i n e c o u r s e a u t h o r i z e d b y I m p e r i a l C o l l e g e L o n d o n a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d D r T h o m a s W o o d c o c k S e n i o r R e s e a r c h F e l l o w S c h o o l o f P u b l i c H e a l t h V e r i f y a t : h t t p s : / / c o u r s e </x:v>
+        <x:v>Fundamentals of quality improvement in healthcare and methods for initiating improvement projects.</x:v>
       </x:c>
       <x:c r="G98" s="32" t="str"/>
       <x:c r="H98" s="32" t="str">
@@ -4802,7 +4804,7 @@
         <x:v>Using Data for Healthcare Improvement</x:v>
       </x:c>
       <x:c r="F99" s="32" t="str">
-        <x:v>J u l 2 4 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o U s i n g D a t a f o r H e a l t h c a r e I m p r o v e m e n t a n o n l i n e c o u r s e a u t h o r i z e d b y I m p e r i a l C o l l e g e L o n d o n a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d D r T h o m a s W o o d c o c k S e n i o r R e s e a r c h F e l l o w S c h o o l o f P u b l i c H e a l t h V e r i f y a t : h t t p s : / / c o u r s e r a . o r g / v e r i </x:v>
+        <x:v>Using healthcare data to identify problems, measure performance, and guide improvement.</x:v>
       </x:c>
       <x:c r="G99" s="32" t="str"/>
       <x:c r="H99" s="32" t="str">
@@ -5132,7 +5134,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="N107" s="32" t="str">
-        <x:v>Coursera: https://www.coursera.org/account/accomplishments/specialization/DSEV3OLMXEMK; estimativa derivada do tempo exibido: 1 meses com 3 por semana para concluir</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/specialization/DSEV3OLMXEMK; duração exibida: 1 meses com 3 por semana para concluir</x:v>
       </x:c>
     </x:row>
     <x:row r="108">
@@ -5216,7 +5218,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="N109" s="32" t="str">
-        <x:v>Coursera: https://www.coursera.org/account/accomplishments/specialization/CG5I6U6HR05R; estimativa derivada do tempo exibido: 1 meses com 3 por semana para concluir</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/specialization/CG5I6U6HR05R; duração exibida: 1 meses com 3 por semana para concluir</x:v>
       </x:c>
     </x:row>
     <x:row r="110">
@@ -5300,7 +5302,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="N111" s="32" t="str">
-        <x:v>Coursera: https://www.coursera.org/account/accomplishments/specialization/ZVA616EKPRVQ; estimativa derivada do tempo exibido: 1 meses com 3 por semana para concluir</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/specialization/ZVA616EKPRVQ; duração exibida: 1 meses com 3 por semana para concluir</x:v>
       </x:c>
     </x:row>
     <x:row r="112">
@@ -5317,10 +5319,10 @@
         <x:v>Duke University</x:v>
       </x:c>
       <x:c r="E112" s="32" t="str">
-        <x:v>Telehealth: Neurological Exam Course</x:v>
+        <x:v>Telehealth: Neurologic Assessment</x:v>
       </x:c>
       <x:c r="F112" s="32" t="str">
-        <x:v>A u g 1 7 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o T e l e h e a l t h : N e u r o l o g i c A s s e s s m e n t a n o n l i n e c o u r s e a u t h o r i z e d b y D u k e U n i v e r s i t y a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d D a n i e l O s t r o v s k y A s s o c i a t e P r o f e s s o r P e d i a t r i c s K a t h l e e n W a i t e P r o f e s s o r o f M e d i c i n e D i v i s i o n o f G e n e r a l I n t e r n a </x:v>
+        <x:v>Perform a virtual neurological assessment; discuss the advantages and limitations of a virtual neurological assessment; describe the benefits of telehealth visits for patients with neurological concerns or conditions.</x:v>
       </x:c>
       <x:c r="G112" s="32" t="str"/>
       <x:c r="H112" s="32" t="str">
@@ -5332,11 +5334,17 @@
       <x:c r="J112" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="K112" s="33"/>
-      <x:c r="L112" s="33"/>
-      <x:c r="M112" s="33"/>
+      <x:c r="K112" s="33" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L112" s="33" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M112" s="33" t="n">
+        <x:v>2</x:v>
+      </x:c>
       <x:c r="N112" s="32" t="str">
-        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/UCSTLLOAX0QZ</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/UCSTLLOAX0QZ; página do curso: https://www.coursera.org/learn/telehealth-neurologic-assessment; duração exibida: 2 horas para completar</x:v>
       </x:c>
     </x:row>
     <x:row r="113">
@@ -5353,10 +5361,10 @@
         <x:v>Duke University</x:v>
       </x:c>
       <x:c r="E113" s="32" t="str">
-        <x:v>Telehealth: Neurology</x:v>
+        <x:v>Telehealth: Essentials, Teamwork, and Neurologic Exam</x:v>
       </x:c>
       <x:c r="F113" s="32" t="str">
-        <x:v>3 C o u r s e s T e l e h e a l t h C l i n i c a l E s s e n t i a l s T e l e h e a l t h : I n t e r p r o f e s s i o n a l T e a m - B a s e d C a r e T e l e h e a l t h : N e u r o l o g i c A s s e s s m e n t D a n i e l O s t r o v s k y A s s o c i a t e P r o f e s s o r P e d i a t r i c s K a t h l e e n W a i t e P r o f e s s o r o f M e d i c i n e D i v i s i o n o f G e n e r a l I n t e r n a l M e d i c i n e A u g 1 7 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o h a </x:v>
+        <x:v>Prepare and conduct telehealth video visits; describe team-based telehealth care; perform physical neurologic exams remotely; identify the benefits and limitations of telehealth visits.</x:v>
       </x:c>
       <x:c r="G113" s="32" t="str"/>
       <x:c r="H113" s="32" t="str">
@@ -5368,11 +5376,17 @@
       <x:c r="J113" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="K113" s="33"/>
-      <x:c r="L113" s="33"/>
-      <x:c r="M113" s="33"/>
+      <x:c r="K113" s="33" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="L113" s="33" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M113" s="33" t="n">
+        <x:v>12</x:v>
+      </x:c>
       <x:c r="N113" s="32" t="str">
-        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/UCSTLLOAX0QZ</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/UCSTLLOAX0QZ; página do curso: https://www.coursera.org/specializations/telehealth-neurologic-essentials-teamwork; duração exibida: 4 semanas com 3 por semana para concluir</x:v>
       </x:c>
     </x:row>
     <x:row r="114">
@@ -6648,7 +6662,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="N148" s="32" t="str">
-        <x:v>Coursera: https://www.coursera.org/account/accomplishments/specialization/53FFGZD92GQU; estimativa derivada do tempo exibido: 1 meses com 10 por semana para concluir</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/specialization/53FFGZD92GQU; duração exibida: 1 meses com 10 por semana para concluir</x:v>
       </x:c>
     </x:row>
     <x:row r="149">
@@ -7084,7 +7098,7 @@
         <x:v>Digital Health</x:v>
       </x:c>
       <x:c r="F161" s="32" t="str">
-        <x:v>3 C o u r s e s I n t r o d u c t i o n t o D i g i t a l h e a l t h D e s i g n a n d I m p l e m e n t a t i o n o f D i g i t a l H e a l t h I n t e r v e n t i o n s E v a l u a t i o n o f D i g i t a l H e a l t h I n t e r v e n t i o n s A n a L u i s a N e v e s S e n i o r C l i n i c a l L e c t u r e r &amp; D i r e c t o r o f G l o b a l D i g i t a l H e a l t h U n i t S c h o o l o f P u b l i c H e a l t h A u g 7 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o h a s s u c c </x:v>
+        <x:v>Introduction to digital health; design and implementation of digital health interventions; and evaluation of digital health interventions.</x:v>
       </x:c>
       <x:c r="G161" s="32" t="str"/>
       <x:c r="H161" s="32" t="str">
@@ -7106,7 +7120,7 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="N161" s="32" t="str">
-        <x:v>Coursera: https://www.coursera.org/account/accomplishments/specialization/CO5VFFKM5MQ6; estimativa derivada do tempo exibido: 2 meses com 10 por semana para concluir</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/specialization/CO5VFFKM5MQ6; duração exibida: 2 meses com 10 por semana para concluir</x:v>
       </x:c>
     </x:row>
     <x:row r="162">
@@ -7520,7 +7534,7 @@
         <x:v>Analysis and Interpretation of Large-Scale Programs</x:v>
       </x:c>
       <x:c r="F173" s="32" t="str">
-        <x:v>A u g 1 0 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o A n a l y s i s a n d I n t e r p r e t a t i o n o f L a r g e - S c a l e P r o g r a m s a n o n l i n e c o u r s e a u t h o r i z e d b y J o h n s H o p k i n s U n i v e r s i t y a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d A g b e s s i A m o u z o u - A s s o c i a t e P r o f e s s o r ; N e f f W a l k e r - S e n i o r S c i e n t i s t ; M e l i n d a M u n o s - A s </x:v>
+        <x:v>Analysis and interpretation of large-scale health programs and their data.</x:v>
       </x:c>
       <x:c r="G173" s="32" t="str"/>
       <x:c r="H173" s="32" t="str">
@@ -7562,7 +7576,7 @@
         <x:v>Biostatistics in Public Health</x:v>
       </x:c>
       <x:c r="F174" s="32" t="str">
-        <x:v>4 C o u r s e s S u m m a r y S t a t i s t i c s i n P u b l i c H e a l t h H y p o t h e s i s T e s t i n g i n P u b l i c H e a l t h S i m p l e R e g r e s s i o n A n a l y s i s i n P u b l i c H e a l t h M u l t i p l e R e g r e s s i o n A n a l y s i s i n P u b l i c H e a l t h J o h n M c G r e a d y , P h D , M S A s s o c i a t e S c i e n t i s t D e p a r t m e n t o f B i o s t a t i s t i c s A u g 8 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o h a s s u c c e s s </x:v>
+        <x:v>Calculate summary statistics for biomedical and public health data; interpret written and visual presentations of statistical data; evaluate and interpret regression methods; choose the appropriate statistical method for a research question.</x:v>
       </x:c>
       <x:c r="G174" s="32" t="str"/>
       <x:c r="H174" s="32" t="str">
@@ -7574,11 +7588,17 @@
       <x:c r="J174" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="K174" s="33"/>
-      <x:c r="L174" s="33"/>
-      <x:c r="M174" s="33"/>
+      <x:c r="K174" s="33" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="L174" s="33" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="M174" s="33" t="n">
+        <x:v>80</x:v>
+      </x:c>
       <x:c r="N174" s="32" t="str">
-        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/4XIVGLM9A4VF</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/4XIVGLM9A4VF; página do curso: https://www.coursera.org/specializations/biostatistics-public-health; duração exibida: 2 meses com 10 por semana para concluir</x:v>
       </x:c>
     </x:row>
     <x:row r="175">
@@ -7620,7 +7640,7 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="N175" s="32" t="str">
-        <x:v>Coursera: https://www.coursera.org/account/accomplishments/specialization/9LMUYO3P4H4E; estimativa derivada do tempo exibido: 6 meses com 3 por semana para concluir</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/specialization/9LMUYO3P4H4E; duração exibida: 6 meses com 3 por semana para concluir</x:v>
       </x:c>
     </x:row>
     <x:row r="176">
@@ -7640,7 +7660,7 @@
         <x:v>Assessing Health Program Delivery</x:v>
       </x:c>
       <x:c r="F176" s="32" t="str">
-        <x:v>A u g 1 0 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o A s s e s s i n g H e a l t h P r o g r a m D e l i v e r y a n o n l i n e c o u r s e a u t h o r i z e d b y J o h n s H o p k i n s U n i v e r s i t y a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d E l i z a b e t h H a z e l , A s s i s t a n t S c i e n t i s t , I n t e r n a t i o n a l H e a l t h | D i w a k a r M o h a n , A s s i s t a n t S c i e n t i s t , I n t e r n </x:v>
+        <x:v>Assessment of health program delivery, including implementation and program performance.</x:v>
       </x:c>
       <x:c r="G176" s="32" t="str"/>
       <x:c r="H176" s="32" t="str">
@@ -7682,7 +7702,7 @@
         <x:v>Evaluating Public Health Programs at Scale</x:v>
       </x:c>
       <x:c r="F177" s="32" t="str">
-        <x:v>A u g 8 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o E v a l u a t i n g P u b l i c H e a l t h P r o g r a m s a t S c a l e a n o n l i n e c o u r s e a u t h o r i z e d b y J o h n s H o p k i n s U n i v e r s i t y a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d A g b e s s i A m o u z o u , P h D , M H S A s s o c i a t e P r o f e s s o r I n t e r n a t i o n a l H e a l t h N e f f W a l k e r , P h D S e n i o r S c i e n t i </x:v>
+        <x:v>Evaluation of public health programs at scale, using indicators, methods, and evidence to assess results.</x:v>
       </x:c>
       <x:c r="G177" s="32" t="str"/>
       <x:c r="H177" s="32" t="str">
@@ -7724,7 +7744,7 @@
         <x:v>Program Design &amp; Evaluation for Health Systems Strengthening</x:v>
       </x:c>
       <x:c r="F178" s="32" t="str">
-        <x:v>A u g 9 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o P r o g r a m D e s i g n &amp; E v a l u a t i o n f o r H e a l t h S y s t e m s S t r e n g t h e n i n g a n o n l i n e c o u r s e a u t h o r i z e d b y J o h n s H o p k i n s U n i v e r s i t y a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d T i m o t h y R o b e r t o n , D r P H , A s s i s t a n t S c i e n t i s t | J a y a G u p t a , P h D , H e a l t h S y s t e m s R e s </x:v>
+        <x:v>Program design and evaluation for health systems strengthening; planning, measurement, and interpretation of program results.</x:v>
       </x:c>
       <x:c r="G178" s="32" t="str"/>
       <x:c r="H178" s="32" t="str">
@@ -9172,7 +9192,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="N217" s="32" t="str">
-        <x:v>Coursera: https://www.coursera.org/account/accomplishments/specialization/VOUZB1AZBVL4; estimativa derivada do tempo exibido: 1 meses com 10 por semana para concluir</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/specialization/VOUZB1AZBVL4; duração exibida: 1 meses com 10 por semana para concluir</x:v>
       </x:c>
     </x:row>
     <x:row r="218">
@@ -10677,10 +10697,10 @@
         <x:v>Saïd Business School, University of Oxford</x:v>
       </x:c>
       <x:c r="E258" s="32" t="str">
-        <x:v>AI for Business</x:v>
+        <x:v>AI Foundations for Business Professionals</x:v>
       </x:c>
       <x:c r="F258" s="32" t="str">
-        <x:v>3 C o u r s e s A I E s s e n t i a l s G e n e r a t i v e a n d A g e n t i c A I A I G o v e r n a n c e M a t t h i a s H o l w e g A m e r i c a n S t a n d a r d C o m p a n i e s P r o f e s s o r o f O p e r a t i o n s M a n a g e m e n t S a ï d B u s i n e s s S c h o o l U n i v e r s i t y o f O x f o r d A u g 1 4 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o h a s s u c c e s s f u l l y c o m p l e t e d t h e o n l i n e S p e c i a l i z a t i o n A I F o u n d a t i o n </x:v>
+        <x:v>Understand core concepts of AI, machine learning, and deep learning and their strategic business value; distinguish generative and agentic AI from traditional models; apply ethical considerations and governance strategies; assess and manage AI risks, including system failures and bias.</x:v>
       </x:c>
       <x:c r="G258" s="32" t="str"/>
       <x:c r="H258" s="32" t="str">
@@ -10692,11 +10712,17 @@
       <x:c r="J258" s="32" t="str">
         <x:v>Extraído do documento</x:v>
       </x:c>
-      <x:c r="K258" s="33"/>
-      <x:c r="L258" s="33"/>
-      <x:c r="M258" s="33"/>
+      <x:c r="K258" s="33" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="L258" s="33" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="M258" s="33" t="n">
+        <x:v>40</x:v>
+      </x:c>
       <x:c r="N258" s="32" t="str">
-        <x:v>Coursera: https://www.coursera.org/account/accomplishments/specialization/FWGA4AWODSM4</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/specialization/FWGA4AWODSM4; página do curso: https://www.coursera.org/specializations/ai-foundations-business-professionals; duração exibida: 4 semanas com 10 por semana para concluir</x:v>
       </x:c>
     </x:row>
     <x:row r="259">
@@ -11390,7 +11416,7 @@
         <x:v>AI in Healthcare Capstone</x:v>
       </x:c>
       <x:c r="F276" s="32" t="str">
-        <x:v>A u g 2 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o A I i n H e a l t h c a r e C a p s t o n e a n o n l i n e c o u r s e a u t h o r i z e d b y S t a n f o r d U n i v e r s i t y a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d L a u r e n c e B a k e r , M a t t h e w L u n g r e n , N i g a m S h a h , S e r e n a Y e u n g a n d T i n a H e r n a n d e z - B o u s s a r d V e r i f y a t : h t t p s : / / c o u r s e r a . o r g / </x:v>
+        <x:v>Applied capstone integrating artificial intelligence concepts for healthcare problem-solving and evaluation.</x:v>
       </x:c>
       <x:c r="G276" s="32" t="str"/>
       <x:c r="H276" s="32" t="str">
@@ -11454,7 +11480,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="N277" s="32" t="str">
-        <x:v>Coursera: https://www.coursera.org/account/accomplishments/specialization/7GM7A9EIJ9W4; estimativa derivada do tempo exibido: 1 meses com 10 por semana para concluir</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/specialization/7GM7A9EIJ9W4; duração exibida: 1 meses com 10 por semana para concluir</x:v>
       </x:c>
     </x:row>
     <x:row r="278">
@@ -11496,7 +11522,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="N278" s="32" t="str">
-        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/FZV2SBU6I8NI; estimativa derivada do tempo exibido: 5 horas (aproximadamente)</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/FZV2SBU6I8NI; duração exibida: 5 horas (aproximadamente)</x:v>
       </x:c>
     </x:row>
     <x:row r="279">
@@ -11622,7 +11648,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="N281" s="32" t="str">
-        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/WFZW6W7MXCAN; estimativa derivada do tempo exibido: 11 horas (aproximadamente)</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/WFZW6W7MXCAN; duração exibida: 11 horas (aproximadamente)</x:v>
       </x:c>
     </x:row>
     <x:row r="282">
@@ -11706,7 +11732,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="N283" s="32" t="str">
-        <x:v>Coursera: https://www.coursera.org/account/accomplishments/specialization/E8700K9GB2WD; estimativa derivada do tempo exibido: 1 meses com 10 por semana para concluir</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/specialization/E8700K9GB2WD; duração exibida: 1 meses com 10 por semana para concluir</x:v>
       </x:c>
     </x:row>
     <x:row r="284">
@@ -11832,7 +11858,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="N286" s="32" t="str">
-        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/OYTO0JAKNOFA; estimativa derivada do tempo exibido: 10 horas (aproximadamente)</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/verify/OYTO0JAKNOFA; duração exibida: 10 horas (aproximadamente)</x:v>
       </x:c>
     </x:row>
     <x:row r="287">
@@ -12556,7 +12582,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="N305" s="32" t="str">
-        <x:v>Coursera: https://www.coursera.org/account/accomplishments/specialization/IXQRUXCLXP3K; estimativa derivada do tempo exibido: 1 meses com 10 por semana para concluir</x:v>
+        <x:v>Coursera: https://www.coursera.org/account/accomplishments/specialization/IXQRUXCLXP3K; duração exibida: 1 meses com 10 por semana para concluir</x:v>
       </x:c>
     </x:row>
     <x:row r="306">
@@ -13250,7 +13276,7 @@
         <x:v>Essentials of Global Health</x:v>
       </x:c>
       <x:c r="F325" s="32" t="str">
-        <x:v>A u g 5 , 2 0 2 6 P e d r o L a m o u n i e r S a m p a i o E s s e n t i a l s o f G l o b a l H e a l t h a n o n l i n e c o u r s e a u t h o r i z e d b y Y a l e U n i v e r s i t y a n d o f f e r e d t h r o u g h C o u r s e r a h a s s u c c e s s f u l l y c o m p l e t e d R i c h a r d S k o l n i k F o r m e r L e c t u r e r , D e p a r t m e n t o f H e a l t h P o l i c y a n d M a n a g e m e n t , Y a l e S c h o o l o f P u b l i c H e a l t h a n d L e c t u r e r i n t h e </x:v>
+        <x:v>Global health determinants, health systems, disease burden, and strategies to improve population health.</x:v>
       </x:c>
       <x:c r="G325" s="32" t="str"/>
       <x:c r="H325" s="32" t="str">
@@ -13317,7 +13343,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb129e16c7bb24d8c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R103faf6a78d1499c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15456,7 +15482,7 @@
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="24" t="str">
-        <x:v>Duke-Coursera_Telehealth_Neurological Exam Course_Certificate_UCSTLLOAX0QZ.pdf</x:v>
+        <x:v>DUNS Resolved Inquiry # 10536566 (Case # 10601194) - Update for LAMOUNI.pdf</x:v>
       </x:c>
       <x:c r="B78" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -15471,7 +15497,7 @@
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="24" t="str">
-        <x:v>Duke-Coursera_Telehealth_Neurology_Certificate_UCSTLLOAX0QZ.pdf</x:v>
+        <x:v>E-mail confirmation sent by Alpha.pdf</x:v>
       </x:c>
       <x:c r="B79" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -15486,7 +15512,7 @@
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="24" t="str">
-        <x:v>DUNS Resolved Inquiry # 10536566 (Case # 10601194) - Update for LAMOUNI.pdf</x:v>
+        <x:v>E-mail from Alison.pdf</x:v>
       </x:c>
       <x:c r="B80" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -15501,10 +15527,10 @@
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="24" t="str">
-        <x:v>E-mail confirmation sent by Alpha.pdf</x:v>
+        <x:v>e1acc2cd-ba6a-4a63-8230-37366add71b1_eb96ae20cd844243b17a7d4ffb8e6c57_LLPC_Badge.png</x:v>
       </x:c>
       <x:c r="B81" s="24" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>PDF/imagem sem texto extraível</x:v>
       </x:c>
       <x:c r="C81" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
@@ -15516,7 +15542,7 @@
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="24" t="str">
-        <x:v>E-mail from Alison.pdf</x:v>
+        <x:v>EADV_00042657_certificate.pdf</x:v>
       </x:c>
       <x:c r="B82" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -15531,10 +15557,10 @@
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="24" t="str">
-        <x:v>e1acc2cd-ba6a-4a63-8230-37366add71b1_eb96ae20cd844243b17a7d4ffb8e6c57_LLPC_Badge.png</x:v>
+        <x:v>EGS003_Pedro Lamounier Sampaio_Participant_WPP__20260704-204242.pdf</x:v>
       </x:c>
       <x:c r="B83" s="24" t="str">
-        <x:v>PDF/imagem sem texto extraível</x:v>
+        <x:v>Carga horária não localizada</x:v>
       </x:c>
       <x:c r="C83" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
@@ -15546,7 +15572,7 @@
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="24" t="str">
-        <x:v>EADV_00042657_certificate.pdf</x:v>
+        <x:v>Ementa Curso Auditoria SES.pdf</x:v>
       </x:c>
       <x:c r="B84" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -15561,7 +15587,7 @@
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="24" t="str">
-        <x:v>EGS003_Pedro Lamounier Sampaio_Participant_WPP__20260704-204242.pdf</x:v>
+        <x:v>Ementa Curso POP-T-SVS-012.pdf</x:v>
       </x:c>
       <x:c r="B85" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -15576,7 +15602,7 @@
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="24" t="str">
-        <x:v>Ementa Curso Auditoria SES.pdf</x:v>
+        <x:v>Ementa Inspeção SVSS.pdf</x:v>
       </x:c>
       <x:c r="B86" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -15591,7 +15617,7 @@
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="24" t="str">
-        <x:v>Ementa Curso POP-T-SVS-012.pdf</x:v>
+        <x:v>EPICourses_OSHAin Healthcare and BPT_Certificate.pdf</x:v>
       </x:c>
       <x:c r="B87" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -15606,7 +15632,7 @@
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="24" t="str">
-        <x:v>Ementa Inspeção SVSS.pdf</x:v>
+        <x:v>fd91e062-545f-0a1b-40b2-14937c01b355_file.pdf</x:v>
       </x:c>
       <x:c r="B88" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -15621,7 +15647,7 @@
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="24" t="str">
-        <x:v>EPICourses_OSHAin Healthcare and BPT_Certificate.pdf</x:v>
+        <x:v>FDCE-UFMG_Certificado_Extensão_Tributação Previdenciária_2020.10.pdf</x:v>
       </x:c>
       <x:c r="B89" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -15636,7 +15662,7 @@
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="24" t="str">
-        <x:v>fd91e062-545f-0a1b-40b2-14937c01b355_file.pdf</x:v>
+        <x:v>form-q-svs-005-v-00-programa-de-auditoria-interna.pdf</x:v>
       </x:c>
       <x:c r="B90" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -15651,7 +15677,7 @@
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="24" t="str">
-        <x:v>FDCE-UFMG_Certificado_Extensão_Tributação Previdenciária_2020.10.pdf</x:v>
+        <x:v>form-q-svs-006-v-00-relatorio-de-auditoria-interna.pdf</x:v>
       </x:c>
       <x:c r="B91" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -15666,10 +15692,10 @@
     </x:row>
     <x:row r="92">
       <x:c r="A92" s="24" t="str">
-        <x:v>form-q-svs-005-v-00-programa-de-auditoria-interna.pdf</x:v>
+        <x:v>GHLC_HC WF Productivity and Quality_Certificate.pdf</x:v>
       </x:c>
       <x:c r="B92" s="24" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>PDF/imagem sem texto extraível</x:v>
       </x:c>
       <x:c r="C92" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
@@ -15681,10 +15707,10 @@
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="24" t="str">
-        <x:v>form-q-svs-006-v-00-relatorio-de-auditoria-interna.pdf</x:v>
+        <x:v>GHTC_Infrastructure and Good Governance_Certificate.pdf</x:v>
       </x:c>
       <x:c r="B93" s="24" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>PDF/imagem sem texto extraível</x:v>
       </x:c>
       <x:c r="C93" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
@@ -15696,10 +15722,10 @@
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="24" t="str">
-        <x:v>GHLC_HC WF Productivity and Quality_Certificate.pdf</x:v>
+        <x:v>GIACC_ Common types of corruption in project construction Certificate.pdf</x:v>
       </x:c>
       <x:c r="B94" s="24" t="str">
-        <x:v>PDF/imagem sem texto extraível</x:v>
+        <x:v>Carga horária não localizada</x:v>
       </x:c>
       <x:c r="C94" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
@@ -15711,10 +15737,10 @@
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="24" t="str">
-        <x:v>GHTC_Infrastructure and Good Governance_Certificate.pdf</x:v>
+        <x:v>GIACC_Benefits and Requirements of ISO 37301_Certificate.pdf</x:v>
       </x:c>
       <x:c r="B95" s="24" t="str">
-        <x:v>PDF/imagem sem texto extraível</x:v>
+        <x:v>Carga horária não localizada</x:v>
       </x:c>
       <x:c r="C95" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
@@ -15726,7 +15752,7 @@
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="24" t="str">
-        <x:v>GIACC_ Common types of corruption in project construction Certificate.pdf</x:v>
+        <x:v>GIACC_Construction and Procurement Contracts_Certificate.pdf</x:v>
       </x:c>
       <x:c r="B96" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -15741,7 +15767,7 @@
     </x:row>
     <x:row r="97">
       <x:c r="A97" s="24" t="str">
-        <x:v>GIACC_Benefits and Requirements of ISO 37301_Certificate.pdf</x:v>
+        <x:v>GIACC_Construction Corruption Prevention Certificate.pdf</x:v>
       </x:c>
       <x:c r="B97" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -15756,7 +15782,7 @@
     </x:row>
     <x:row r="98">
       <x:c r="A98" s="24" t="str">
-        <x:v>GIACC_Construction and Procurement Contracts_Certificate.pdf</x:v>
+        <x:v>GIACC_Corruption in Procurement Certificate.pdf</x:v>
       </x:c>
       <x:c r="B98" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -15771,7 +15797,7 @@
     </x:row>
     <x:row r="99">
       <x:c r="A99" s="24" t="str">
-        <x:v>GIACC_Construction Corruption Prevention Certificate.pdf</x:v>
+        <x:v>GIACC_Corruption Investigation in Procurement_Certificate.pdf</x:v>
       </x:c>
       <x:c r="B99" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -15786,7 +15812,7 @@
     </x:row>
     <x:row r="100">
       <x:c r="A100" s="24" t="str">
-        <x:v>GIACC_Corruption in Procurement Certificate.pdf</x:v>
+        <x:v>GIACC_Mod11_Corruption Dilemmas_Certificate.pdf</x:v>
       </x:c>
       <x:c r="B100" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -15801,7 +15827,7 @@
     </x:row>
     <x:row r="101">
       <x:c r="A101" s="24" t="str">
-        <x:v>GIACC_Corruption Investigation in Procurement_Certificate.pdf</x:v>
+        <x:v>GIACC_Module 3_Certificate.pdf</x:v>
       </x:c>
       <x:c r="B101" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -15816,7 +15842,7 @@
     </x:row>
     <x:row r="102">
       <x:c r="A102" s="24" t="str">
-        <x:v>GIACC_Mod11_Corruption Dilemmas_Certificate.pdf</x:v>
+        <x:v>GICR-1 Certificate of Completion - WHO Academy.pdf</x:v>
       </x:c>
       <x:c r="B102" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -15831,7 +15857,7 @@
     </x:row>
     <x:row r="103">
       <x:c r="A103" s="24" t="str">
-        <x:v>GIACC_Module 3_Certificate.pdf</x:v>
+        <x:v>GICR-O Certificate of Completion - WHO Academy.pdf</x:v>
       </x:c>
       <x:c r="B103" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -15846,10 +15872,10 @@
     </x:row>
     <x:row r="104">
       <x:c r="A104" s="24" t="str">
-        <x:v>GICR-1 Certificate of Completion - WHO Academy.pdf</x:v>
+        <x:v>Global Health Governance Certificate.pdf</x:v>
       </x:c>
       <x:c r="B104" s="24" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>PDF/imagem sem texto extraível</x:v>
       </x:c>
       <x:c r="C104" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
@@ -15861,7 +15887,7 @@
     </x:row>
     <x:row r="105">
       <x:c r="A105" s="24" t="str">
-        <x:v>GICR-O Certificate of Completion - WHO Academy.pdf</x:v>
+        <x:v>Global Infrastructure Anti-Corruption Centre Module 2 Certificate.pdf</x:v>
       </x:c>
       <x:c r="B105" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -15876,10 +15902,10 @@
     </x:row>
     <x:row r="106">
       <x:c r="A106" s="24" t="str">
-        <x:v>Global Health Governance Certificate.pdf</x:v>
+        <x:v>Global Infrastructure Anti-Corruption Centre.pdf</x:v>
       </x:c>
       <x:c r="B106" s="24" t="str">
-        <x:v>PDF/imagem sem texto extraível</x:v>
+        <x:v>Carga horária não localizada</x:v>
       </x:c>
       <x:c r="C106" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
@@ -15891,10 +15917,10 @@
     </x:row>
     <x:row r="107">
       <x:c r="A107" s="24" t="str">
-        <x:v>Global Infrastructure Anti-Corruption Centre Module 2 Certificate.pdf</x:v>
+        <x:v>Glossary_Modern_Project_Management_Microsoft365.zip</x:v>
       </x:c>
       <x:c r="B107" s="24" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>PDF/imagem sem texto extraível</x:v>
       </x:c>
       <x:c r="C107" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
@@ -15906,7 +15932,7 @@
     </x:row>
     <x:row r="108">
       <x:c r="A108" s="24" t="str">
-        <x:v>Global Infrastructure Anti-Corruption Centre.pdf</x:v>
+        <x:v>HIPAA_Training_Certificate.pdf</x:v>
       </x:c>
       <x:c r="B108" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -15921,10 +15947,10 @@
     </x:row>
     <x:row r="109">
       <x:c r="A109" s="24" t="str">
-        <x:v>Glossary_Modern_Project_Management_Microsoft365.zip</x:v>
+        <x:v>HomeTown Health Certificate.pdf</x:v>
       </x:c>
       <x:c r="B109" s="24" t="str">
-        <x:v>PDF/imagem sem texto extraível</x:v>
+        <x:v>Carga horária não localizada</x:v>
       </x:c>
       <x:c r="C109" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
@@ -15936,7 +15962,7 @@
     </x:row>
     <x:row r="110">
       <x:c r="A110" s="24" t="str">
-        <x:v>HIPAA_Training_Certificate.pdf</x:v>
+        <x:v>HomeTown Health_Care Coordination and Continuity.pdf</x:v>
       </x:c>
       <x:c r="B110" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -15951,10 +15977,10 @@
     </x:row>
     <x:row r="111">
       <x:c r="A111" s="24" t="str">
-        <x:v>HomeTown Health Certificate.pdf</x:v>
+        <x:v>HSC_Curso sobre avaliação biológica ISO 10993_certificado-3533631.pdf</x:v>
       </x:c>
       <x:c r="B111" s="24" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>PDF/imagem sem texto extraível</x:v>
       </x:c>
       <x:c r="C111" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
@@ -15966,10 +15992,10 @@
     </x:row>
     <x:row r="112">
       <x:c r="A112" s="24" t="str">
-        <x:v>HomeTown Health_Care Coordination and Continuity.pdf</x:v>
+        <x:v>HSC_Curso sobre Avaliação Clínica ISO 10993_certificado-3533419.pdf</x:v>
       </x:c>
       <x:c r="B112" s="24" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>PDF/imagem sem texto extraível</x:v>
       </x:c>
       <x:c r="C112" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
@@ -15981,7 +16007,7 @@
     </x:row>
     <x:row r="113">
       <x:c r="A113" s="24" t="str">
-        <x:v>HSC_Curso sobre avaliação biológica ISO 10993_certificado-3533631.pdf</x:v>
+        <x:v>HSC_Curso sobre MDSAP AU_certificado-3533417.pdf</x:v>
       </x:c>
       <x:c r="B113" s="24" t="str">
         <x:v>PDF/imagem sem texto extraível</x:v>
@@ -15996,7 +16022,7 @@
     </x:row>
     <x:row r="114">
       <x:c r="A114" s="24" t="str">
-        <x:v>HSC_Curso sobre Avaliação Clínica ISO 10993_certificado-3533419.pdf</x:v>
+        <x:v>HSC_ISO 10994 Gestão de Risco_certificado-3536529.pdf</x:v>
       </x:c>
       <x:c r="B114" s="24" t="str">
         <x:v>PDF/imagem sem texto extraível</x:v>
@@ -16011,7 +16037,7 @@
     </x:row>
     <x:row r="115">
       <x:c r="A115" s="24" t="str">
-        <x:v>HSC_Curso sobre MDSAP AU_certificado-3533417.pdf</x:v>
+        <x:v>HSC_Registro no FDA_certificado-3533688.pdf</x:v>
       </x:c>
       <x:c r="B115" s="24" t="str">
         <x:v>PDF/imagem sem texto extraível</x:v>
@@ -16026,10 +16052,10 @@
     </x:row>
     <x:row r="116">
       <x:c r="A116" s="24" t="str">
-        <x:v>HSC_ISO 10994 Gestão de Risco_certificado-3536529.pdf</x:v>
+        <x:v>HTH_Systems Thinking and Design Certificate.pdf</x:v>
       </x:c>
       <x:c r="B116" s="24" t="str">
-        <x:v>PDF/imagem sem texto extraível</x:v>
+        <x:v>Carga horária não localizada</x:v>
       </x:c>
       <x:c r="C116" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
@@ -16041,7 +16067,7 @@
     </x:row>
     <x:row r="117">
       <x:c r="A117" s="24" t="str">
-        <x:v>HSC_Registro no FDA_certificado-3533688.pdf</x:v>
+        <x:v>IBSEC_ISO 27001 Essentials_Certificate.pdf</x:v>
       </x:c>
       <x:c r="B117" s="24" t="str">
         <x:v>PDF/imagem sem texto extraível</x:v>
@@ -16056,10 +16082,10 @@
     </x:row>
     <x:row r="118">
       <x:c r="A118" s="24" t="str">
-        <x:v>HTH_Systems Thinking and Design Certificate.pdf</x:v>
+        <x:v>IBSEC_ISO 27001 Fundamentos_ProfCertificate.pdf</x:v>
       </x:c>
       <x:c r="B118" s="24" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>PDF/imagem sem texto extraível</x:v>
       </x:c>
       <x:c r="C118" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
@@ -16071,7 +16097,7 @@
     </x:row>
     <x:row r="119">
       <x:c r="A119" s="24" t="str">
-        <x:v>IBSEC_ISO 27001 Essentials_Certificate.pdf</x:v>
+        <x:v>IBSEC_Perícia Digital, Investigação e Custódia Segurança Digital_Essentials_ProfCertificate.pdf</x:v>
       </x:c>
       <x:c r="B119" s="24" t="str">
         <x:v>PDF/imagem sem texto extraível</x:v>
@@ -16086,10 +16112,10 @@
     </x:row>
     <x:row r="120">
       <x:c r="A120" s="24" t="str">
-        <x:v>IBSEC_ISO 27001 Fundamentos_ProfCertificate.pdf</x:v>
+        <x:v>IIBA_6S Green Belt Certificate.pdf</x:v>
       </x:c>
       <x:c r="B120" s="24" t="str">
-        <x:v>PDF/imagem sem texto extraível</x:v>
+        <x:v>Carga horária não localizada</x:v>
       </x:c>
       <x:c r="C120" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
@@ -16101,7 +16127,7 @@
     </x:row>
     <x:row r="121">
       <x:c r="A121" s="24" t="str">
-        <x:v>IBSEC_Perícia Digital, Investigação e Custódia Segurança Digital_Essentials_ProfCertificate.pdf</x:v>
+        <x:v>Injetáveis Curso_certificate_1779855229036 (1).pdf</x:v>
       </x:c>
       <x:c r="B121" s="24" t="str">
         <x:v>PDF/imagem sem texto extraível</x:v>
@@ -16116,10 +16142,10 @@
     </x:row>
     <x:row r="122">
       <x:c r="A122" s="24" t="str">
-        <x:v>IIBA_6S Green Belt Certificate.pdf</x:v>
+        <x:v>Injetáveis Curso_certificate_1779855229036.pdf</x:v>
       </x:c>
       <x:c r="B122" s="24" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>PDF/imagem sem texto extraível</x:v>
       </x:c>
       <x:c r="C122" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
@@ -16131,10 +16157,10 @@
     </x:row>
     <x:row r="123">
       <x:c r="A123" s="24" t="str">
-        <x:v>Injetáveis Curso_certificate_1779855229036 (1).pdf</x:v>
+        <x:v>International Institute of Business Analysis (IIBA®).pdf</x:v>
       </x:c>
       <x:c r="B123" s="24" t="str">
-        <x:v>PDF/imagem sem texto extraível</x:v>
+        <x:v>Carga horária não localizada</x:v>
       </x:c>
       <x:c r="C123" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
@@ -16146,7 +16172,7 @@
     </x:row>
     <x:row r="124">
       <x:c r="A124" s="24" t="str">
-        <x:v>Injetáveis Curso_certificate_1779855229036.pdf</x:v>
+        <x:v>IPE-Creighton - Certicate-ish.docx</x:v>
       </x:c>
       <x:c r="B124" s="24" t="str">
         <x:v>PDF/imagem sem texto extraível</x:v>
@@ -16161,7 +16187,7 @@
     </x:row>
     <x:row r="125">
       <x:c r="A125" s="24" t="str">
-        <x:v>International Institute of Business Analysis (IIBA®).pdf</x:v>
+        <x:v>ISO 9001 and 27001 Essentials Certificate_Great Learning.pdf</x:v>
       </x:c>
       <x:c r="B125" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16169,14 +16195,16 @@
       <x:c r="C125" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
       </x:c>
-      <x:c r="D125" s="24" t="str"/>
+      <x:c r="D125" s="24" t="str">
+        <x:v>https://www.mygreatlearning.com/certificate/PSXVKTXD</x:v>
+      </x:c>
       <x:c r="E125" s="24" t="str">
         <x:v>Pendente</x:v>
       </x:c>
     </x:row>
     <x:row r="126">
       <x:c r="A126" s="24" t="str">
-        <x:v>IPE-Creighton - Certicate-ish.docx</x:v>
+        <x:v>ISO9001_Badge_SkillFront96337181584206.png</x:v>
       </x:c>
       <x:c r="B126" s="24" t="str">
         <x:v>PDF/imagem sem texto extraível</x:v>
@@ -16191,24 +16219,22 @@
     </x:row>
     <x:row r="127">
       <x:c r="A127" s="24" t="str">
-        <x:v>ISO 9001 and 27001 Essentials Certificate_Great Learning.pdf</x:v>
+        <x:v>IU_Primary Plagiarism Certificate.pdf</x:v>
       </x:c>
       <x:c r="B127" s="24" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>PDF/imagem sem texto extraível</x:v>
       </x:c>
       <x:c r="C127" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
       </x:c>
-      <x:c r="D127" s="24" t="str">
-        <x:v>https://www.mygreatlearning.com/certificate/PSXVKTXD</x:v>
-      </x:c>
+      <x:c r="D127" s="24" t="str"/>
       <x:c r="E127" s="24" t="str">
         <x:v>Pendente</x:v>
       </x:c>
     </x:row>
     <x:row r="128">
       <x:c r="A128" s="24" t="str">
-        <x:v>ISO9001_Badge_SkillFront96337181584206.png</x:v>
+        <x:v>IU_Primary Plagiarism Certificate_signed.pdf</x:v>
       </x:c>
       <x:c r="B128" s="24" t="str">
         <x:v>PDF/imagem sem texto extraível</x:v>
@@ -16223,10 +16249,10 @@
     </x:row>
     <x:row r="129">
       <x:c r="A129" s="24" t="str">
-        <x:v>IU_Primary Plagiarism Certificate.pdf</x:v>
+        <x:v>LinkedIn Learning_Building Blocks in AI Certificate.pdf</x:v>
       </x:c>
       <x:c r="B129" s="24" t="str">
-        <x:v>PDF/imagem sem texto extraível</x:v>
+        <x:v>Carga horária não localizada</x:v>
       </x:c>
       <x:c r="C129" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
@@ -16238,10 +16264,10 @@
     </x:row>
     <x:row r="130">
       <x:c r="A130" s="24" t="str">
-        <x:v>IU_Primary Plagiarism Certificate_signed.pdf</x:v>
+        <x:v>LinkedIn_AI para Profissionais da Justiça_Certificado.pdf</x:v>
       </x:c>
       <x:c r="B130" s="24" t="str">
-        <x:v>PDF/imagem sem texto extraível</x:v>
+        <x:v>Carga horária não localizada</x:v>
       </x:c>
       <x:c r="C130" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
@@ -16253,7 +16279,7 @@
     </x:row>
     <x:row r="131">
       <x:c r="A131" s="24" t="str">
-        <x:v>JHU-Coursera_Biostatistics in PH_4XIVGLM9A4VF.pdf</x:v>
+        <x:v>LinkedIn_AI Products Introduction_Certificate.pdf</x:v>
       </x:c>
       <x:c r="B131" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16268,7 +16294,7 @@
     </x:row>
     <x:row r="132">
       <x:c r="A132" s="24" t="str">
-        <x:v>LinkedIn Learning_Building Blocks in AI Certificate.pdf</x:v>
+        <x:v>LinkedIn_Top Performers Reinvention_Completion Certificate.pdf</x:v>
       </x:c>
       <x:c r="B132" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16283,7 +16309,7 @@
     </x:row>
     <x:row r="133">
       <x:c r="A133" s="24" t="str">
-        <x:v>LinkedIn_AI para Profissionais da Justiça_Certificado.pdf</x:v>
+        <x:v>LOC Certificate for 'Breaking the Routine- Modernizing Mealtime Insulin Manageme.pdf</x:v>
       </x:c>
       <x:c r="B133" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16298,10 +16324,10 @@
     </x:row>
     <x:row r="134">
       <x:c r="A134" s="24" t="str">
-        <x:v>LinkedIn_AI Products Introduction_Certificate.pdf</x:v>
+        <x:v>MedScape_Updates on infections_LOC Certificate.pdf</x:v>
       </x:c>
       <x:c r="B134" s="24" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>PDF/imagem sem texto extraível</x:v>
       </x:c>
       <x:c r="C134" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
@@ -16313,7 +16339,7 @@
     </x:row>
     <x:row r="135">
       <x:c r="A135" s="24" t="str">
-        <x:v>LinkedIn_Top Performers Reinvention_Completion Certificate.pdf</x:v>
+        <x:v>My Support Cases.pdf</x:v>
       </x:c>
       <x:c r="B135" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16321,14 +16347,16 @@
       <x:c r="C135" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
       </x:c>
-      <x:c r="D135" s="24" t="str"/>
+      <x:c r="D135" s="24" t="str">
+        <x:v>https://www.coursera.org/my-purchases/transactions?utm_medium=email&amp;utm_source=other&amp;utm_campaign=…</x:v>
+      </x:c>
       <x:c r="E135" s="24" t="str">
         <x:v>Pendente</x:v>
       </x:c>
     </x:row>
     <x:row r="136">
       <x:c r="A136" s="24" t="str">
-        <x:v>LOC Certificate for 'Breaking the Routine- Modernizing Mealtime Insulin Manageme.pdf</x:v>
+        <x:v>My Support Casespt2.pdf</x:v>
       </x:c>
       <x:c r="B136" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16336,17 +16364,19 @@
       <x:c r="C136" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
       </x:c>
-      <x:c r="D136" s="24" t="str"/>
+      <x:c r="D136" s="24" t="str">
+        <x:v>http://play.google.com/store/apps/details? | https://about.coursera.org/ | https://about.coursera.org/afﬁliates | https://about.coursera.org/careers | https://about.coursera.org/how-coursera-works/ | https://about.coursera.org/leadership | https://blog.coursera.org/ | https://building.coursera.org/developer-program/ | https://investor.coursera.com/ | https://itunes.apple.com/app/apple- | https://learner.coursera.help/hc | https://learner.coursera.help/hc/articles/360050668591- | https://medium.com/coursera-engineering | https://www.coursera.community/ | https://www.coursera.community/#beta-tester | https://www.coursera.community/#gtc | https://www.coursera.org/about/contact | https://www.coursera.org/about/partners | https://www.coursera.org/about/press | https://www.coursera.org/about/privacy | https://www.coursera.org/about/terms | https://www.coursera.org/articles | https://www.coursera.org/browse | https://www.coursera.org/business | https://www.coursera.org/campus | https://www.coursera.org/degrees | https://www.coursera.org/directory | https://www.coursera.org/government | https://www.coursera.org/professional- | https://www.coursera.org/teaching-center</x:v>
+      </x:c>
       <x:c r="E136" s="24" t="str">
         <x:v>Pendente</x:v>
       </x:c>
     </x:row>
     <x:row r="137">
       <x:c r="A137" s="24" t="str">
-        <x:v>MedScape_Updates on infections_LOC Certificate.pdf</x:v>
+        <x:v>NASB-LinkedIn_Certificate_PME_Budgets.pdf</x:v>
       </x:c>
       <x:c r="B137" s="24" t="str">
-        <x:v>PDF/imagem sem texto extraível</x:v>
+        <x:v>Carga horária não localizada</x:v>
       </x:c>
       <x:c r="C137" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
@@ -16358,7 +16388,7 @@
     </x:row>
     <x:row r="138">
       <x:c r="A138" s="24" t="str">
-        <x:v>My Support Cases.pdf</x:v>
+        <x:v>NASBA-LikedIn_PMF_Communication_Certificate.pdf</x:v>
       </x:c>
       <x:c r="B138" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16366,16 +16396,14 @@
       <x:c r="C138" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
       </x:c>
-      <x:c r="D138" s="24" t="str">
-        <x:v>https://www.coursera.org/my-purchases/transactions?utm_medium=email&amp;utm_source=other&amp;utm_campaign=…</x:v>
-      </x:c>
+      <x:c r="D138" s="24" t="str"/>
       <x:c r="E138" s="24" t="str">
         <x:v>Pendente</x:v>
       </x:c>
     </x:row>
     <x:row r="139">
       <x:c r="A139" s="24" t="str">
-        <x:v>My Support Casespt2.pdf</x:v>
+        <x:v>NASBA-LinkedIn Certificate - Six Sigma Black Belt.pdf</x:v>
       </x:c>
       <x:c r="B139" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16383,16 +16411,14 @@
       <x:c r="C139" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
       </x:c>
-      <x:c r="D139" s="24" t="str">
-        <x:v>http://play.google.com/store/apps/details? | https://about.coursera.org/ | https://about.coursera.org/afﬁliates | https://about.coursera.org/careers | https://about.coursera.org/how-coursera-works/ | https://about.coursera.org/leadership | https://blog.coursera.org/ | https://building.coursera.org/developer-program/ | https://investor.coursera.com/ | https://itunes.apple.com/app/apple- | https://learner.coursera.help/hc | https://learner.coursera.help/hc/articles/360050668591- | https://medium.com/coursera-engineering | https://www.coursera.community/ | https://www.coursera.community/#beta-tester | https://www.coursera.community/#gtc | https://www.coursera.org/about/contact | https://www.coursera.org/about/partners | https://www.coursera.org/about/press | https://www.coursera.org/about/privacy | https://www.coursera.org/about/terms | https://www.coursera.org/articles | https://www.coursera.org/browse | https://www.coursera.org/business | https://www.coursera.org/campus | https://www.coursera.org/degrees | https://www.coursera.org/directory | https://www.coursera.org/government | https://www.coursera.org/professional- | https://www.coursera.org/teaching-center</x:v>
-      </x:c>
+      <x:c r="D139" s="24" t="str"/>
       <x:c r="E139" s="24" t="str">
         <x:v>Pendente</x:v>
       </x:c>
     </x:row>
     <x:row r="140">
       <x:c r="A140" s="24" t="str">
-        <x:v>NASB-LinkedIn_Certificate_PME_Budgets.pdf</x:v>
+        <x:v>NASBA-LinkedIn Certificate_PMF_Teams.pdf</x:v>
       </x:c>
       <x:c r="B140" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16407,7 +16433,7 @@
     </x:row>
     <x:row r="141">
       <x:c r="A141" s="24" t="str">
-        <x:v>NASBA-LikedIn_PMF_Communication_Certificate.pdf</x:v>
+        <x:v>NASBA-LinkedIn Certificate_Project Management Foundations.pdf</x:v>
       </x:c>
       <x:c r="B141" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16422,7 +16448,7 @@
     </x:row>
     <x:row r="142">
       <x:c r="A142" s="24" t="str">
-        <x:v>NASBA-LinkedIn Certificate - Six Sigma Black Belt.pdf</x:v>
+        <x:v>NASBA-LinkedIn Learning - PM Risk Certificate.pdf</x:v>
       </x:c>
       <x:c r="B142" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16437,7 +16463,7 @@
     </x:row>
     <x:row r="143">
       <x:c r="A143" s="24" t="str">
-        <x:v>NASBA-LinkedIn Certificate_PMF_Teams.pdf</x:v>
+        <x:v>NASBA-LinkedIn_Certificate_PM Foundations_Ethics.pdf</x:v>
       </x:c>
       <x:c r="B143" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16452,7 +16478,7 @@
     </x:row>
     <x:row r="144">
       <x:c r="A144" s="24" t="str">
-        <x:v>NASBA-LinkedIn Certificate_Project Management Foundations.pdf</x:v>
+        <x:v>NASBA-LinkedIn_MicrosoftMPM_Certificaye.pdf</x:v>
       </x:c>
       <x:c r="B144" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16467,7 +16493,7 @@
     </x:row>
     <x:row r="145">
       <x:c r="A145" s="24" t="str">
-        <x:v>NASBA-LinkedIn Learning - PM Risk Certificate.pdf</x:v>
+        <x:v>NASBA-LinkedIn_PM Foundations Requirements.pdf</x:v>
       </x:c>
       <x:c r="B145" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16482,7 +16508,7 @@
     </x:row>
     <x:row r="146">
       <x:c r="A146" s="24" t="str">
-        <x:v>NASBA-LinkedIn_Certificate_PM Foundations_Ethics.pdf</x:v>
+        <x:v>NASBA-LinkedIn_PME_Schedules.pdf</x:v>
       </x:c>
       <x:c r="B146" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16497,7 +16523,7 @@
     </x:row>
     <x:row r="147">
       <x:c r="A147" s="24" t="str">
-        <x:v>NASBA-LinkedIn_MicrosoftMPM_Certificaye.pdf</x:v>
+        <x:v>NASBA-LinkedIn_PMF_Risks Certificate_.pdf</x:v>
       </x:c>
       <x:c r="B147" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16512,7 +16538,7 @@
     </x:row>
     <x:row r="148">
       <x:c r="A148" s="24" t="str">
-        <x:v>NASBA-LinkedIn_PM Foundations Requirements.pdf</x:v>
+        <x:v>NASBA-LinkedIn_PMF_Stakeholders_Certificate.pdf</x:v>
       </x:c>
       <x:c r="B148" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16527,7 +16553,7 @@
     </x:row>
     <x:row r="149">
       <x:c r="A149" s="24" t="str">
-        <x:v>NASBA-LinkedIn_PME_Schedules.pdf</x:v>
+        <x:v>NASBA_Certificate_Healthcare Projects.pdf</x:v>
       </x:c>
       <x:c r="B149" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16542,7 +16568,7 @@
     </x:row>
     <x:row r="150">
       <x:c r="A150" s="24" t="str">
-        <x:v>NASBA-LinkedIn_PMF_Risks Certificate_.pdf</x:v>
+        <x:v>New opioid treatments_cmeucert_20260731_134129.pdf</x:v>
       </x:c>
       <x:c r="B150" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16557,7 +16583,7 @@
     </x:row>
     <x:row r="151">
       <x:c r="A151" s="24" t="str">
-        <x:v>NASBA-LinkedIn_PMF_Stakeholders_Certificate.pdf</x:v>
+        <x:v>NIDA GCP Certificate.pdf</x:v>
       </x:c>
       <x:c r="B151" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16572,10 +16598,10 @@
     </x:row>
     <x:row r="152">
       <x:c r="A152" s="24" t="str">
-        <x:v>NASBA_Certificate_Healthcare Projects.pdf</x:v>
+        <x:v>Pedro Lamounier Sampaio - CV 2.pdf</x:v>
       </x:c>
       <x:c r="B152" s="24" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>PDF/imagem sem texto extraível</x:v>
       </x:c>
       <x:c r="C152" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
@@ -16587,7 +16613,7 @@
     </x:row>
     <x:row r="153">
       <x:c r="A153" s="24" t="str">
-        <x:v>New opioid treatments_cmeucert_20260731_134129.pdf</x:v>
+        <x:v>Pedro Lamounier Sampaio - PDF Certificate (ISO 19011 Lead Auditor).pdf</x:v>
       </x:c>
       <x:c r="B153" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16602,10 +16628,10 @@
     </x:row>
     <x:row r="154">
       <x:c r="A154" s="24" t="str">
-        <x:v>NIDA GCP Certificate.pdf</x:v>
+        <x:v>Pedro Lamounier Sampaio _ LinkedIn_Duolingo LVL128.pdf</x:v>
       </x:c>
       <x:c r="B154" s="24" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>PDF/imagem sem texto extraível</x:v>
       </x:c>
       <x:c r="C154" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
@@ -16617,10 +16643,10 @@
     </x:row>
     <x:row r="155">
       <x:c r="A155" s="24" t="str">
-        <x:v>Pedro Lamounier Sampaio - CV 2.pdf</x:v>
+        <x:v>Pedro Lamounier Sampaio ACLS (Advanced Cardiac Life Support) Online Course Completion Certificate 2026.pdf</x:v>
       </x:c>
       <x:c r="B155" s="24" t="str">
-        <x:v>PDF/imagem sem texto extraível</x:v>
+        <x:v>Carga horária não localizada</x:v>
       </x:c>
       <x:c r="C155" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
@@ -16632,7 +16658,7 @@
     </x:row>
     <x:row r="156">
       <x:c r="A156" s="24" t="str">
-        <x:v>Pedro Lamounier Sampaio - PDF Certificate (ISO 19011 Lead Auditor).pdf</x:v>
+        <x:v>Pedro Lamounier Sampaio ACLS Course Completion Certificate.pdf</x:v>
       </x:c>
       <x:c r="B156" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16647,10 +16673,10 @@
     </x:row>
     <x:row r="157">
       <x:c r="A157" s="24" t="str">
-        <x:v>Pedro Lamounier Sampaio _ LinkedIn_Duolingo LVL128.pdf</x:v>
+        <x:v>Pedro Lamounier Sampaio BLS (Basic Life Support) Online Course Completion Certificate 2026.pdf</x:v>
       </x:c>
       <x:c r="B157" s="24" t="str">
-        <x:v>PDF/imagem sem texto extraível</x:v>
+        <x:v>Carga horária não localizada</x:v>
       </x:c>
       <x:c r="C157" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
@@ -16662,7 +16688,7 @@
     </x:row>
     <x:row r="158">
       <x:c r="A158" s="24" t="str">
-        <x:v>Pedro Lamounier Sampaio ACLS (Advanced Cardiac Life Support) Online Course Completion Certificate 2026.pdf</x:v>
+        <x:v>Pedro Lamounier Sampaio- PDF Certificate (Advanced Cardiac Life Support (ACLS)).pdf</x:v>
       </x:c>
       <x:c r="B158" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16677,10 +16703,10 @@
     </x:row>
     <x:row r="159">
       <x:c r="A159" s="24" t="str">
-        <x:v>Pedro Lamounier Sampaio ACLS Course Completion Certificate.pdf</x:v>
+        <x:v>PEDRO_LAMOUNIER_SAMPAIO_Cybersecurity_Awareness_-_Production.pdf</x:v>
       </x:c>
       <x:c r="B159" s="24" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>PDF/imagem sem texto extraível</x:v>
       </x:c>
       <x:c r="C159" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
@@ -16692,10 +16718,10 @@
     </x:row>
     <x:row r="160">
       <x:c r="A160" s="24" t="str">
-        <x:v>Pedro Lamounier Sampaio BLS (Basic Life Support) Online Course Completion Certificate 2026.pdf</x:v>
+        <x:v>PEDRO_LAMOUNIER_SAMPAIO_Project_Management_Essentials_-_Production.pdf</x:v>
       </x:c>
       <x:c r="B160" s="24" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>PDF/imagem sem texto extraível</x:v>
       </x:c>
       <x:c r="C160" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
@@ -16707,7 +16733,7 @@
     </x:row>
     <x:row r="161">
       <x:c r="A161" s="24" t="str">
-        <x:v>Pedro Lamounier Sampaio- PDF Certificate (Advanced Cardiac Life Support (ACLS)).pdf</x:v>
+        <x:v>Personalidade INTP (Lógico) _ 16Personalities.pdf</x:v>
       </x:c>
       <x:c r="B161" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16722,7 +16748,7 @@
     </x:row>
     <x:row r="162">
       <x:c r="A162" s="24" t="str">
-        <x:v>PEDRO_LAMOUNIER_SAMPAIO_Cybersecurity_Awareness_-_Production.pdf</x:v>
+        <x:v>PET_ESOL Entry 3 Certificate.pdf</x:v>
       </x:c>
       <x:c r="B162" s="24" t="str">
         <x:v>PDF/imagem sem texto extraível</x:v>
@@ -16737,10 +16763,10 @@
     </x:row>
     <x:row r="163">
       <x:c r="A163" s="24" t="str">
-        <x:v>PEDRO_LAMOUNIER_SAMPAIO_Project_Management_Essentials_-_Production.pdf</x:v>
+        <x:v>PHC Course - WHO Academy.pdf</x:v>
       </x:c>
       <x:c r="B163" s="24" t="str">
-        <x:v>PDF/imagem sem texto extraível</x:v>
+        <x:v>Carga horária não localizada</x:v>
       </x:c>
       <x:c r="C163" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
@@ -16752,7 +16778,7 @@
     </x:row>
     <x:row r="164">
       <x:c r="A164" s="24" t="str">
-        <x:v>Personalidade INTP (Lógico) _ 16Personalities.pdf</x:v>
+        <x:v>pjrtraining _ ISO 9001-2015 Clause-by-Clau... (CBC9000) _ Final Exam.pdf</x:v>
       </x:c>
       <x:c r="B164" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16760,17 +16786,19 @@
       <x:c r="C164" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
       </x:c>
-      <x:c r="D164" s="24" t="str"/>
+      <x:c r="D164" s="24" t="str">
+        <x:v>https://pjrtraining.talentlms.com/dashboard | https://pjrtraining.talentlms.com/unit/viewtestsurvey/id:1746,mode:test</x:v>
+      </x:c>
       <x:c r="E164" s="24" t="str">
         <x:v>Pendente</x:v>
       </x:c>
     </x:row>
     <x:row r="165">
       <x:c r="A165" s="24" t="str">
-        <x:v>PET_ESOL Entry 3 Certificate.pdf</x:v>
+        <x:v>PMI-LinkedIn Certificate - Six Sigma Black Belt.pdf</x:v>
       </x:c>
       <x:c r="B165" s="24" t="str">
-        <x:v>PDF/imagem sem texto extraível</x:v>
+        <x:v>Carga horária não localizada</x:v>
       </x:c>
       <x:c r="C165" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
@@ -16782,7 +16810,7 @@
     </x:row>
     <x:row r="166">
       <x:c r="A166" s="24" t="str">
-        <x:v>PHC Course - WHO Academy.pdf</x:v>
+        <x:v>PMI-LinkedIn Certificate_Problem Solving for Leadership.pdf</x:v>
       </x:c>
       <x:c r="B166" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16797,7 +16825,7 @@
     </x:row>
     <x:row r="167">
       <x:c r="A167" s="24" t="str">
-        <x:v>pjrtraining _ ISO 9001-2015 Clause-by-Clau... (CBC9000) _ Final Exam.pdf</x:v>
+        <x:v>PMI-LinkedIn Certificate_Project Management Foundations.pdf</x:v>
       </x:c>
       <x:c r="B167" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16805,16 +16833,14 @@
       <x:c r="C167" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
       </x:c>
-      <x:c r="D167" s="24" t="str">
-        <x:v>https://pjrtraining.talentlms.com/dashboard | https://pjrtraining.talentlms.com/unit/viewtestsurvey/id:1746,mode:test</x:v>
-      </x:c>
+      <x:c r="D167" s="24" t="str"/>
       <x:c r="E167" s="24" t="str">
         <x:v>Pendente</x:v>
       </x:c>
     </x:row>
     <x:row r="168">
       <x:c r="A168" s="24" t="str">
-        <x:v>PMI-LinkedIn Certificate - Six Sigma Black Belt.pdf</x:v>
+        <x:v>PMI-LinkedIn Learning Certificate_Healthcare Projects.pdf</x:v>
       </x:c>
       <x:c r="B168" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16829,7 +16855,7 @@
     </x:row>
     <x:row r="169">
       <x:c r="A169" s="24" t="str">
-        <x:v>PMI-LinkedIn Certificate_Problem Solving for Leadership.pdf</x:v>
+        <x:v>PMI-LinkedIn_Certificate_PM Foundations Requirements.pdf</x:v>
       </x:c>
       <x:c r="B169" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16844,7 +16870,7 @@
     </x:row>
     <x:row r="170">
       <x:c r="A170" s="24" t="str">
-        <x:v>PMI-LinkedIn Certificate_Project Management Foundations.pdf</x:v>
+        <x:v>PMI-LinkedIn_Certificate_PM Foundations_Ethics.pdf</x:v>
       </x:c>
       <x:c r="B170" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16859,7 +16885,7 @@
     </x:row>
     <x:row r="171">
       <x:c r="A171" s="24" t="str">
-        <x:v>PMI-LinkedIn Learning Certificate_Healthcare Projects.pdf</x:v>
+        <x:v>PMI-LinkedIn_Certificate_PME_Budgets.pdf</x:v>
       </x:c>
       <x:c r="B171" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16874,7 +16900,7 @@
     </x:row>
     <x:row r="172">
       <x:c r="A172" s="24" t="str">
-        <x:v>PMI-LinkedIn_Certificate_PM Foundations Requirements.pdf</x:v>
+        <x:v>PMI-LinkedIn_Certificate_PME_Schedules.pdf</x:v>
       </x:c>
       <x:c r="B172" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16889,7 +16915,7 @@
     </x:row>
     <x:row r="173">
       <x:c r="A173" s="24" t="str">
-        <x:v>PMI-LinkedIn_Certificate_PM Foundations_Ethics.pdf</x:v>
+        <x:v>PMI-LinkedIn_Certificate_PMF_Teams.pdf</x:v>
       </x:c>
       <x:c r="B173" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16904,7 +16930,7 @@
     </x:row>
     <x:row r="174">
       <x:c r="A174" s="24" t="str">
-        <x:v>PMI-LinkedIn_Certificate_PME_Budgets.pdf</x:v>
+        <x:v>PMI-LinkedIn_Leveraging AI_GRC_Certificate.pdf</x:v>
       </x:c>
       <x:c r="B174" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16919,7 +16945,7 @@
     </x:row>
     <x:row r="175">
       <x:c r="A175" s="24" t="str">
-        <x:v>PMI-LinkedIn_Certificate_PME_Schedules.pdf</x:v>
+        <x:v>PMI-LinkedIn_MicrosoftMPM_Certificate.pdf</x:v>
       </x:c>
       <x:c r="B175" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16934,7 +16960,7 @@
     </x:row>
     <x:row r="176">
       <x:c r="A176" s="24" t="str">
-        <x:v>PMI-LinkedIn_Certificate_PMF_Teams.pdf</x:v>
+        <x:v>PMI-LinkedIn_PMF_Communication_Certificate.pdf</x:v>
       </x:c>
       <x:c r="B176" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16949,7 +16975,7 @@
     </x:row>
     <x:row r="177">
       <x:c r="A177" s="24" t="str">
-        <x:v>PMI-LinkedIn_Leveraging AI_GRC_Certificate.pdf</x:v>
+        <x:v>PMI-LinkedIn_PMF_Risks_Certificate.pdf</x:v>
       </x:c>
       <x:c r="B177" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16964,7 +16990,7 @@
     </x:row>
     <x:row r="178">
       <x:c r="A178" s="24" t="str">
-        <x:v>PMI-LinkedIn_MicrosoftMPM_Certificate.pdf</x:v>
+        <x:v>PMI-LinkedIn_PMF_Stakeholders_Certificate.pdf</x:v>
       </x:c>
       <x:c r="B178" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16979,7 +17005,7 @@
     </x:row>
     <x:row r="179">
       <x:c r="A179" s="24" t="str">
-        <x:v>PMI-LinkedIn_PMF_Communication_Certificate.pdf</x:v>
+        <x:v>PMI_LinkedIn_Certificate_AI_Projects.pdf</x:v>
       </x:c>
       <x:c r="B179" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -16994,7 +17020,7 @@
     </x:row>
     <x:row r="180">
       <x:c r="A180" s="24" t="str">
-        <x:v>PMI-LinkedIn_PMF_Risks_Certificate.pdf</x:v>
+        <x:v>PMP ExamPrep1_Project Management Institute (PMI)®.pdf</x:v>
       </x:c>
       <x:c r="B180" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -17009,7 +17035,7 @@
     </x:row>
     <x:row r="181">
       <x:c r="A181" s="24" t="str">
-        <x:v>PMI-LinkedIn_PMF_Stakeholders_Certificate.pdf</x:v>
+        <x:v>Podcast APS_CME answers certificate-2026-7-12_1735.pdf</x:v>
       </x:c>
       <x:c r="B181" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -17017,14 +17043,16 @@
       <x:c r="C181" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
       </x:c>
-      <x:c r="D181" s="24" t="str"/>
+      <x:c r="D181" s="24" t="str">
+        <x:v>https://answersincme.com/DDT</x:v>
+      </x:c>
       <x:c r="E181" s="24" t="str">
         <x:v>Pendente</x:v>
       </x:c>
     </x:row>
     <x:row r="182">
       <x:c r="A182" s="24" t="str">
-        <x:v>PMI_LinkedIn_Certificate_AI_Projects.pdf</x:v>
+        <x:v>Processo Civil no pós-pandemia - Certificado ESAOAB.pdf</x:v>
       </x:c>
       <x:c r="B182" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -17039,7 +17067,7 @@
     </x:row>
     <x:row r="183">
       <x:c r="A183" s="24" t="str">
-        <x:v>PMP ExamPrep1_Project Management Institute (PMI)®.pdf</x:v>
+        <x:v>Project Management Institute (PMI)_6S Green Belt.pdf</x:v>
       </x:c>
       <x:c r="B183" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -17054,7 +17082,7 @@
     </x:row>
     <x:row r="184">
       <x:c r="A184" s="24" t="str">
-        <x:v>Podcast APS_CME answers certificate-2026-7-12_1735.pdf</x:v>
+        <x:v>Project Management Institute (PMI)®.pdf</x:v>
       </x:c>
       <x:c r="B184" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -17062,16 +17090,14 @@
       <x:c r="C184" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
       </x:c>
-      <x:c r="D184" s="24" t="str">
-        <x:v>https://answersincme.com/DDT</x:v>
-      </x:c>
+      <x:c r="D184" s="24" t="str"/>
       <x:c r="E184" s="24" t="str">
         <x:v>Pendente</x:v>
       </x:c>
     </x:row>
     <x:row r="185">
       <x:c r="A185" s="24" t="str">
-        <x:v>Processo Civil no pós-pandemia - Certificado ESAOAB.pdf</x:v>
+        <x:v>Public Health Law Academy_Certificate.pdf</x:v>
       </x:c>
       <x:c r="B185" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -17086,10 +17112,10 @@
     </x:row>
     <x:row r="186">
       <x:c r="A186" s="24" t="str">
-        <x:v>Project Management Institute (PMI)_6S Green Belt.pdf</x:v>
+        <x:v>Python.pdf</x:v>
       </x:c>
       <x:c r="B186" s="24" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>PDF/imagem sem texto extraível</x:v>
       </x:c>
       <x:c r="C186" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
@@ -17101,7 +17127,7 @@
     </x:row>
     <x:row r="187">
       <x:c r="A187" s="24" t="str">
-        <x:v>Project Management Institute (PMI)®.pdf</x:v>
+        <x:v>QMS_ISO 19011-2026_Fundamentos_Certificado 0014912.pdf</x:v>
       </x:c>
       <x:c r="B187" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -17116,7 +17142,7 @@
     </x:row>
     <x:row r="188">
       <x:c r="A188" s="24" t="str">
-        <x:v>Public Health Law Academy_Certificate.pdf</x:v>
+        <x:v>Relatório_Extensao_CEPROC.pdf</x:v>
       </x:c>
       <x:c r="B188" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -17131,10 +17157,10 @@
     </x:row>
     <x:row r="189">
       <x:c r="A189" s="24" t="str">
-        <x:v>Python.pdf</x:v>
+        <x:v>revivr-CPR_certificate_2026.08.22.pdf</x:v>
       </x:c>
       <x:c r="B189" s="24" t="str">
-        <x:v>PDF/imagem sem texto extraível</x:v>
+        <x:v>Carga horária não localizada</x:v>
       </x:c>
       <x:c r="C189" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
@@ -17146,7 +17172,7 @@
     </x:row>
     <x:row r="190">
       <x:c r="A190" s="24" t="str">
-        <x:v>QMS_ISO 19011-2026_Fundamentos_Certificado 0014912.pdf</x:v>
+        <x:v>SkillFront-ISO 9001_Associate_Certificate_SFE0232f5d549bbc-96337181584206.pdf</x:v>
       </x:c>
       <x:c r="B190" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -17161,7 +17187,7 @@
     </x:row>
     <x:row r="191">
       <x:c r="A191" s="24" t="str">
-        <x:v>Relatório_Extensao_CEPROC.pdf</x:v>
+        <x:v>SkillFront_ISO 27001 ISMS Associate SFE0166da11827fd-47327192991292_Certificate.pdf</x:v>
       </x:c>
       <x:c r="B191" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -17176,7 +17202,7 @@
     </x:row>
     <x:row r="192">
       <x:c r="A192" s="24" t="str">
-        <x:v>revivr-CPR_certificate_2026.08.22.pdf</x:v>
+        <x:v>texto 2.txt</x:v>
       </x:c>
       <x:c r="B192" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -17191,7 +17217,7 @@
     </x:row>
     <x:row r="193">
       <x:c r="A193" s="24" t="str">
-        <x:v>Said-Oxford-Coursera_Specialization AI for Business_Certificate_FWGA4AWODSM4.pdf</x:v>
+        <x:v>texto 3.txt</x:v>
       </x:c>
       <x:c r="B193" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -17199,14 +17225,16 @@
       <x:c r="C193" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
       </x:c>
-      <x:c r="D193" s="24" t="str"/>
+      <x:c r="D193" s="24" t="str">
+        <x:v>https://produto.mercadolivre.com.br/MLB-3554868073-creme-despigmentante-alfa-arbutin-7-40g-_JM", | https://shopee.com.br/search?keyword=Alfa+Arbutin+Axilas", | https://shopee.com.br/search?keyword=Alfa+Arbutin+Formulab", | https://shopee.com.br/search?keyword=Alfa+Arbutin+Locao", | https://shopee.com.br/search?keyword=Alpha+Arbutin", | https://shopee.com.br/search?keyword=Creme%20Gel%20para%20Peeling%20com%20%C3%81cido%20Retin%C3%B3ico%20e%20Hidroquinona", | https://shopee.com.br/search?keyword=Hidroquinona", | https://www.amazon.com.br/alpha-arbutin/s?k=alpha+arbutin", | https://www.amazon.com.br/s?k=Gel+Facial+Alfa+Arbutin", | https://www.belezasaude.com.br/creme-alfa-arbutin-10-vitamina-c-estabilizada-10-40g", | https://www.drogariaminasbrasil.com.br/hidroquinona-5-acid-retinoico-0-025-dexametasona-0-05-creme-30g.html", | https://www.drogariaminasbrasil.com.br/search?q=hidroquinona", | https://www.drogariasaopaulo.com.br/search?w=Melan-Off", | https://www.drogariasaopaulo.com.br/search?w=suavicid", | https://www.drogasil.com.br/search?w=Blancy", | https://www.drogasil.com.br/search?w=Classis%20TX", | https://www.drogasil.com.br/search?w=vitacid%20plus", | https://www.epocacosmeticos.com.br/search?q=Eucerin+Anti+Pigment", | https://www.farmaciabelladona.com.br/search?q=alfa+arbutin", | https://www.farmaciabelladona.com.br/search?q=hidroquinona", | https://www.farmaciabotanica.com.br/search?q=alfa+arbutin", | https://www.farmaciaeficacia.com.br/search?q=alfa+arbutin", | https://www.farmaciaeficacia.com.br/search?q=hidroquinona", | https://www.farmasesi.com.br/produto/5424-hidroquinona--ems-400mg-4-creme-30g", | https://www.farmasite.com.br/hidroquinona-4-alfa-bisabolol-1-creme-30g", | https://www.farmasite.com.br/search?q=hidroquinona", | https://www.manipulart.com.br/search?q=hidroquinona" | https://www.manipulart.com.br/search?q=hidroquinona", | https://www.mercadolivre.com.br/p/MLB39792525", | https://www.mercadolivre.com.br/search?keyword=Arbutin+Creme", | https://www.mercadolivre.com.br/search?keyword=Raavi%20Alfa%20Arbutin", | https://www.naturalforma.com.br/search?q=alfa+arbutin", | https://www.naturalforma.com.br/search?q=hidroquinona", | https://www.panvel.com/search?q=hormoskin", | https://www.rituaria.com.br/produtos/formula-uniformizadora",</x:v>
+      </x:c>
       <x:c r="E193" s="24" t="str">
         <x:v>Pendente</x:v>
       </x:c>
     </x:row>
     <x:row r="194">
       <x:c r="A194" s="24" t="str">
-        <x:v>SkillFront-ISO 9001_Associate_Certificate_SFE0232f5d549bbc-96337181584206.pdf</x:v>
+        <x:v>texto.txt</x:v>
       </x:c>
       <x:c r="B194" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -17214,14 +17242,16 @@
       <x:c r="C194" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
       </x:c>
-      <x:c r="D194" s="24" t="str"/>
+      <x:c r="D194" s="24" t="str">
+        <x:v>https://cursa.app/pt/downapp</x:v>
+      </x:c>
       <x:c r="E194" s="24" t="str">
         <x:v>Pendente</x:v>
       </x:c>
     </x:row>
     <x:row r="195">
       <x:c r="A195" s="24" t="str">
-        <x:v>SkillFront_ISO 27001 ISMS Associate SFE0166da11827fd-47327192991292_Certificate.pdf</x:v>
+        <x:v>TRREE (2023)_Certificate of completion for module 1_Intro to Research.pdf</x:v>
       </x:c>
       <x:c r="B195" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -17229,14 +17259,16 @@
       <x:c r="C195" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
       </x:c>
-      <x:c r="D195" s="24" t="str"/>
+      <x:c r="D195" s="24" t="str">
+        <x:v>http://www.cihr-irsc.gc.ca/e/2891.html</x:v>
+      </x:c>
       <x:c r="E195" s="24" t="str">
         <x:v>Pendente</x:v>
       </x:c>
     </x:row>
     <x:row r="196">
       <x:c r="A196" s="24" t="str">
-        <x:v>texto 2.txt</x:v>
+        <x:v>TRREE (2023)_Certificate of completion for module 2_Ethics Evaluation in Research.pdf</x:v>
       </x:c>
       <x:c r="B196" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -17244,14 +17276,16 @@
       <x:c r="C196" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
       </x:c>
-      <x:c r="D196" s="24" t="str"/>
+      <x:c r="D196" s="24" t="str">
+        <x:v>http://www.cihr-irsc.gc.ca/e/2891.html</x:v>
+      </x:c>
       <x:c r="E196" s="24" t="str">
         <x:v>Pendente</x:v>
       </x:c>
     </x:row>
     <x:row r="197">
       <x:c r="A197" s="24" t="str">
-        <x:v>texto 3.txt</x:v>
+        <x:v>TRREE (2023)_Certificate of completion for module 3_Informed Consent_Certificate.pdf</x:v>
       </x:c>
       <x:c r="B197" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -17260,7 +17294,7 @@
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
       </x:c>
       <x:c r="D197" s="24" t="str">
-        <x:v>https://produto.mercadolivre.com.br/MLB-3554868073-creme-despigmentante-alfa-arbutin-7-40g-_JM", | https://shopee.com.br/search?keyword=Alfa+Arbutin+Axilas", | https://shopee.com.br/search?keyword=Alfa+Arbutin+Formulab", | https://shopee.com.br/search?keyword=Alfa+Arbutin+Locao", | https://shopee.com.br/search?keyword=Alpha+Arbutin", | https://shopee.com.br/search?keyword=Creme%20Gel%20para%20Peeling%20com%20%C3%81cido%20Retin%C3%B3ico%20e%20Hidroquinona", | https://shopee.com.br/search?keyword=Hidroquinona", | https://www.amazon.com.br/alpha-arbutin/s?k=alpha+arbutin", | https://www.amazon.com.br/s?k=Gel+Facial+Alfa+Arbutin", | https://www.belezasaude.com.br/creme-alfa-arbutin-10-vitamina-c-estabilizada-10-40g", | https://www.drogariaminasbrasil.com.br/hidroquinona-5-acid-retinoico-0-025-dexametasona-0-05-creme-30g.html", | https://www.drogariaminasbrasil.com.br/search?q=hidroquinona", | https://www.drogariasaopaulo.com.br/search?w=Melan-Off", | https://www.drogariasaopaulo.com.br/search?w=suavicid", | https://www.drogasil.com.br/search?w=Blancy", | https://www.drogasil.com.br/search?w=Classis%20TX", | https://www.drogasil.com.br/search?w=vitacid%20plus", | https://www.epocacosmeticos.com.br/search?q=Eucerin+Anti+Pigment", | https://www.farmaciabelladona.com.br/search?q=alfa+arbutin", | https://www.farmaciabelladona.com.br/search?q=hidroquinona", | https://www.farmaciabotanica.com.br/search?q=alfa+arbutin", | https://www.farmaciaeficacia.com.br/search?q=alfa+arbutin", | https://www.farmaciaeficacia.com.br/search?q=hidroquinona", | https://www.farmasesi.com.br/produto/5424-hidroquinona--ems-400mg-4-creme-30g", | https://www.farmasite.com.br/hidroquinona-4-alfa-bisabolol-1-creme-30g", | https://www.farmasite.com.br/search?q=hidroquinona", | https://www.manipulart.com.br/search?q=hidroquinona" | https://www.manipulart.com.br/search?q=hidroquinona", | https://www.mercadolivre.com.br/p/MLB39792525", | https://www.mercadolivre.com.br/search?keyword=Arbutin+Creme", | https://www.mercadolivre.com.br/search?keyword=Raavi%20Alfa%20Arbutin", | https://www.naturalforma.com.br/search?q=alfa+arbutin", | https://www.naturalforma.com.br/search?q=hidroquinona", | https://www.panvel.com/search?q=hormoskin", | https://www.rituaria.com.br/produtos/formula-uniformizadora",</x:v>
+        <x:v>http://www.cihr-irsc.gc.ca/e/2891.html</x:v>
       </x:c>
       <x:c r="E197" s="24" t="str">
         <x:v>Pendente</x:v>
@@ -17268,7 +17302,7 @@
     </x:row>
     <x:row r="198">
       <x:c r="A198" s="24" t="str">
-        <x:v>texto.txt</x:v>
+        <x:v>TRREE_Module 4_R3_GCP_Certificate.pdf</x:v>
       </x:c>
       <x:c r="B198" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -17277,7 +17311,7 @@
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
       </x:c>
       <x:c r="D198" s="24" t="str">
-        <x:v>https://cursa.app/pt/downapp</x:v>
+        <x:v>http://www.cihr-irsc.gc.ca/e/2891.html</x:v>
       </x:c>
       <x:c r="E198" s="24" t="str">
         <x:v>Pendente</x:v>
@@ -17285,7 +17319,7 @@
     </x:row>
     <x:row r="199">
       <x:c r="A199" s="24" t="str">
-        <x:v>TRREE (2023)_Certificate of completion for module 1_Intro to Research.pdf</x:v>
+        <x:v>TRREE_Module 4R2_GCP_Certificate.pdf</x:v>
       </x:c>
       <x:c r="B199" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -17302,7 +17336,7 @@
     </x:row>
     <x:row r="200">
       <x:c r="A200" s="24" t="str">
-        <x:v>TRREE (2023)_Certificate of completion for module 2_Ethics Evaluation in Research.pdf</x:v>
+        <x:v>TRREE_Module 5.1 HIV Vaccine TrialsTraining certificate.pdf</x:v>
       </x:c>
       <x:c r="B200" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -17319,7 +17353,7 @@
     </x:row>
     <x:row r="201">
       <x:c r="A201" s="24" t="str">
-        <x:v>TRREE (2023)_Certificate of completion for module 3_Informed Consent_Certificate.pdf</x:v>
+        <x:v>TRREE_Module 5.2_Adolescent participants in HIV Trials_Training certificate - Module 5.2.pdf</x:v>
       </x:c>
       <x:c r="B201" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -17336,7 +17370,7 @@
     </x:row>
     <x:row r="202">
       <x:c r="A202" s="24" t="str">
-        <x:v>TRREE_Module 4_R3_GCP_Certificate.pdf</x:v>
+        <x:v>TRREE_Module 5.3_Ethics in PH Research_Training Certificate.pdf</x:v>
       </x:c>
       <x:c r="B202" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -17353,7 +17387,7 @@
     </x:row>
     <x:row r="203">
       <x:c r="A203" s="24" t="str">
-        <x:v>TRREE_Module 4R2_GCP_Certificate.pdf</x:v>
+        <x:v>TRREE_Reg. Frameworks_Suisse-2025_Certificate.pdf</x:v>
       </x:c>
       <x:c r="B203" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -17370,24 +17404,22 @@
     </x:row>
     <x:row r="204">
       <x:c r="A204" s="24" t="str">
-        <x:v>TRREE_Module 5.1 HIV Vaccine TrialsTraining certificate.pdf</x:v>
+        <x:v>UFMA_DRC na APS_Certificafdo de Curso.pdf</x:v>
       </x:c>
       <x:c r="B204" s="24" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>PDF/imagem sem texto extraível</x:v>
       </x:c>
       <x:c r="C204" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
       </x:c>
-      <x:c r="D204" s="24" t="str">
-        <x:v>http://www.cihr-irsc.gc.ca/e/2891.html</x:v>
-      </x:c>
+      <x:c r="D204" s="24" t="str"/>
       <x:c r="E204" s="24" t="str">
         <x:v>Pendente</x:v>
       </x:c>
     </x:row>
     <x:row r="205">
       <x:c r="A205" s="24" t="str">
-        <x:v>TRREE_Module 5.2_Adolescent participants in HIV Trials_Training certificate - Module 5.2.pdf</x:v>
+        <x:v>UFMG-UNA-SUS_M1_Atributos da APS_certificado_1f198775-dbe8-6290-b71e-85b8bf09b5ac.pdf</x:v>
       </x:c>
       <x:c r="B205" s="24" t="str">
         <x:v>Carga horária não localizada</x:v>
@@ -17395,50 +17427,44 @@
       <x:c r="C205" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
       </x:c>
-      <x:c r="D205" s="24" t="str">
-        <x:v>http://www.cihr-irsc.gc.ca/e/2891.html</x:v>
-      </x:c>
+      <x:c r="D205" s="24" t="str"/>
       <x:c r="E205" s="24" t="str">
         <x:v>Pendente</x:v>
       </x:c>
     </x:row>
     <x:row r="206">
       <x:c r="A206" s="24" t="str">
-        <x:v>TRREE_Module 5.3_Ethics in PH Research_Training Certificate.pdf</x:v>
+        <x:v>UNA-SUS-UFMA_Aperfeiçoamento em DRC_Certificado.pdf</x:v>
       </x:c>
       <x:c r="B206" s="24" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>PDF/imagem sem texto extraível</x:v>
       </x:c>
       <x:c r="C206" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
       </x:c>
-      <x:c r="D206" s="24" t="str">
-        <x:v>http://www.cihr-irsc.gc.ca/e/2891.html</x:v>
-      </x:c>
+      <x:c r="D206" s="24" t="str"/>
       <x:c r="E206" s="24" t="str">
         <x:v>Pendente</x:v>
       </x:c>
     </x:row>
     <x:row r="207">
       <x:c r="A207" s="24" t="str">
-        <x:v>TRREE_Reg. Frameworks_Suisse-2025_Certificate.pdf</x:v>
+        <x:v>UNA-SUS-UFMA_Atendimento Interdisciplinar DRC_M5_Certificado.pdf</x:v>
       </x:c>
       <x:c r="B207" s="24" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>PDF/imagem sem texto extraível</x:v>
       </x:c>
       <x:c r="C207" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
       </x:c>
-      <x:c r="D207" s="24" t="str">
-        <x:v>http://www.cihr-irsc.gc.ca/e/2891.html</x:v>
-      </x:c>
+      <x:c r="D207" s="24" t="str"/>
       <x:c r="E207" s="24" t="str">
         <x:v>Pendente</x:v>
       </x:c>
     </x:row>
     <x:row r="208">
       <x:c r="A208" s="24" t="str">
-        <x:v>UFMA_DRC na APS_Certificafdo de Curso.pdf</x:v>
+        <x:v>UNA-SUS-UFMA_Diálise Peritoneal_M4_Certificado.pdf</x:v>
       </x:c>
       <x:c r="B208" s="24" t="str">
         <x:v>PDF/imagem sem texto extraível</x:v>
@@ -17453,10 +17479,10 @@
     </x:row>
     <x:row r="209">
       <x:c r="A209" s="24" t="str">
-        <x:v>UFMG-UNA-SUS_M1_Atributos da APS_certificado_1f198775-dbe8-6290-b71e-85b8bf09b5ac.pdf</x:v>
+        <x:v>UNA-SUS-UFMA_IA na Saúde_Extensão_Certificado.pdf</x:v>
       </x:c>
       <x:c r="B209" s="24" t="str">
-        <x:v>Carga horária não localizada</x:v>
+        <x:v>PDF/imagem sem texto extraível</x:v>
       </x:c>
       <x:c r="C209" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
@@ -17468,7 +17494,7 @@
     </x:row>
     <x:row r="210">
       <x:c r="A210" s="24" t="str">
-        <x:v>UNA-SUS-UFMA_Aperfeiçoamento em DRC_Certificado.pdf</x:v>
+        <x:v>UNA-SUS-UFMA_Introdução à DRC_M1_Certificado.pdf</x:v>
       </x:c>
       <x:c r="B210" s="24" t="str">
         <x:v>PDF/imagem sem texto extraível</x:v>
@@ -17483,7 +17509,7 @@
     </x:row>
     <x:row r="211">
       <x:c r="A211" s="24" t="str">
-        <x:v>UNA-SUS-UFMA_Atendimento Interdisciplinar DRC_M5_Certificado.pdf</x:v>
+        <x:v>UNA-SUS-UFMA_Manejo clínico da DRC_M3_Certificado.pdf</x:v>
       </x:c>
       <x:c r="B211" s="24" t="str">
         <x:v>PDF/imagem sem texto extraível</x:v>
@@ -17498,7 +17524,7 @@
     </x:row>
     <x:row r="212">
       <x:c r="A212" s="24" t="str">
-        <x:v>UNA-SUS-UFMA_Diálise Peritoneal_M4_Certificado.pdf</x:v>
+        <x:v>UNA-SUS-UFMA_Registros e Qualidade na Saúde Digital_Certificado de Conclusao_.pdf</x:v>
       </x:c>
       <x:c r="B212" s="24" t="str">
         <x:v>PDF/imagem sem texto extraível</x:v>
@@ -17513,7 +17539,7 @@
     </x:row>
     <x:row r="213">
       <x:c r="A213" s="24" t="str">
-        <x:v>UNA-SUS-UFMA_IA na Saúde_Extensão_Certificado.pdf</x:v>
+        <x:v>UNA-SUS-UFMA_Saude Digital e SUS_Certificado Extensão.pdf</x:v>
       </x:c>
       <x:c r="B213" s="24" t="str">
         <x:v>PDF/imagem sem texto extraível</x:v>
@@ -17528,7 +17554,7 @@
     </x:row>
     <x:row r="214">
       <x:c r="A214" s="24" t="str">
-        <x:v>UNA-SUS-UFMA_Introdução à DRC_M1_Certificado.pdf</x:v>
+        <x:v>UNA-SUS-UFMA_Saúde Digital Inclusiva_Certificado.pdf</x:v>
       </x:c>
       <x:c r="B214" s="24" t="str">
         <x:v>PDF/imagem sem texto extraível</x:v>
@@ -17543,7 +17569,7 @@
     </x:row>
     <x:row r="215">
       <x:c r="A215" s="24" t="str">
-        <x:v>UNA-SUS-UFMA_Manejo clínico da DRC_M3_Certificado.pdf</x:v>
+        <x:v>UNA-SUS-UFMA_Saúde Digital Noções fundamentais_Certificado.pdf</x:v>
       </x:c>
       <x:c r="B215" s="24" t="str">
         <x:v>PDF/imagem sem texto extraível</x:v>
@@ -17558,7 +17584,7 @@
     </x:row>
     <x:row r="216">
       <x:c r="A216" s="24" t="str">
-        <x:v>UNA-SUS-UFMA_Registros e Qualidade na Saúde Digital_Certificado de Conclusao_.pdf</x:v>
+        <x:v>UNA-SUS-UFMA_Transf Digital_Extensao_Certificado.pdf</x:v>
       </x:c>
       <x:c r="B216" s="24" t="str">
         <x:v>PDF/imagem sem texto extraível</x:v>
@@ -17573,7 +17599,7 @@
     </x:row>
     <x:row r="217">
       <x:c r="A217" s="24" t="str">
-        <x:v>UNA-SUS-UFMA_Saude Digital e SUS_Certificado Extensão.pdf</x:v>
+        <x:v>UNA-SUS_Certificado_Introducao Saúde Digital.pdf</x:v>
       </x:c>
       <x:c r="B217" s="24" t="str">
         <x:v>PDF/imagem sem texto extraível</x:v>
@@ -17588,7 +17614,7 @@
     </x:row>
     <x:row r="218">
       <x:c r="A218" s="24" t="str">
-        <x:v>UNA-SUS-UFMA_Saúde Digital Inclusiva_Certificado.pdf</x:v>
+        <x:v>UNA-SUS_UFMA_Cultura da Saúde Digital_Certificado de Extensão_.pdf</x:v>
       </x:c>
       <x:c r="B218" s="24" t="str">
         <x:v>PDF/imagem sem texto extraível</x:v>
@@ -17603,7 +17629,7 @@
     </x:row>
     <x:row r="219">
       <x:c r="A219" s="24" t="str">
-        <x:v>UNA-SUS-UFMA_Saúde Digital Noções fundamentais_Certificado.pdf</x:v>
+        <x:v>UNA-SUS_UFMA_Etica e Responsabilidade_Saude Digital_Certificado Extensão.pdf</x:v>
       </x:c>
       <x:c r="B219" s="24" t="str">
         <x:v>PDF/imagem sem texto extraível</x:v>
@@ -17618,7 +17644,7 @@
     </x:row>
     <x:row r="220">
       <x:c r="A220" s="24" t="str">
-        <x:v>UNA-SUS-UFMA_Transf Digital_Extensao_Certificado.pdf</x:v>
+        <x:v>UNA-SUS_UFMA_Programa_Aperfeicoamento_Saude Digital_Certificado.pdf</x:v>
       </x:c>
       <x:c r="B220" s="24" t="str">
         <x:v>PDF/imagem sem texto extraível</x:v>
@@ -17633,10 +17659,10 @@
     </x:row>
     <x:row r="221">
       <x:c r="A221" s="24" t="str">
-        <x:v>UNA-SUS_Certificado_Introducao Saúde Digital.pdf</x:v>
+        <x:v>VMEdu_SFC_PedroLamounierSampaio-1182483.pdf</x:v>
       </x:c>
       <x:c r="B221" s="24" t="str">
-        <x:v>PDF/imagem sem texto extraível</x:v>
+        <x:v>Carga horária não localizada</x:v>
       </x:c>
       <x:c r="C221" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
@@ -17648,76 +17674,16 @@
     </x:row>
     <x:row r="222">
       <x:c r="A222" s="24" t="str">
-        <x:v>UNA-SUS_UFMA_Cultura da Saúde Digital_Certificado de Extensão_.pdf</x:v>
+        <x:v>Your D-U-N-S Number is enclosed_.pdf</x:v>
       </x:c>
       <x:c r="B222" s="24" t="str">
-        <x:v>PDF/imagem sem texto extraível</x:v>
+        <x:v>Carga horária não localizada</x:v>
       </x:c>
       <x:c r="C222" s="24" t="str">
         <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
       </x:c>
       <x:c r="D222" s="24" t="str"/>
       <x:c r="E222" s="24" t="str">
-        <x:v>Pendente</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="223">
-      <x:c r="A223" s="24" t="str">
-        <x:v>UNA-SUS_UFMA_Etica e Responsabilidade_Saude Digital_Certificado Extensão.pdf</x:v>
-      </x:c>
-      <x:c r="B223" s="24" t="str">
-        <x:v>PDF/imagem sem texto extraível</x:v>
-      </x:c>
-      <x:c r="C223" s="24" t="str">
-        <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
-      </x:c>
-      <x:c r="D223" s="24" t="str"/>
-      <x:c r="E223" s="24" t="str">
-        <x:v>Pendente</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="224">
-      <x:c r="A224" s="24" t="str">
-        <x:v>UNA-SUS_UFMA_Programa_Aperfeicoamento_Saude Digital_Certificado.pdf</x:v>
-      </x:c>
-      <x:c r="B224" s="24" t="str">
-        <x:v>PDF/imagem sem texto extraível</x:v>
-      </x:c>
-      <x:c r="C224" s="24" t="str">
-        <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
-      </x:c>
-      <x:c r="D224" s="24" t="str"/>
-      <x:c r="E224" s="24" t="str">
-        <x:v>Pendente</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="225">
-      <x:c r="A225" s="24" t="str">
-        <x:v>VMEdu_SFC_PedroLamounierSampaio-1182483.pdf</x:v>
-      </x:c>
-      <x:c r="B225" s="24" t="str">
-        <x:v>Carga horária não localizada</x:v>
-      </x:c>
-      <x:c r="C225" s="24" t="str">
-        <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
-      </x:c>
-      <x:c r="D225" s="24" t="str"/>
-      <x:c r="E225" s="24" t="str">
-        <x:v>Pendente</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="226">
-      <x:c r="A226" s="24" t="str">
-        <x:v>Your D-U-N-S Number is enclosed_.pdf</x:v>
-      </x:c>
-      <x:c r="B226" s="24" t="str">
-        <x:v>Carga horária não localizada</x:v>
-      </x:c>
-      <x:c r="C226" s="24" t="str">
-        <x:v>Conferir visualmente e, no Coursera, abrir o link de verificação do certificado</x:v>
-      </x:c>
-      <x:c r="D226" s="24" t="str"/>
-      <x:c r="E226" s="24" t="str">
         <x:v>Pendente</x:v>
       </x:c>
     </x:row>
